--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="characterization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="building blocks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +34,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +49,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -87,6 +98,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -904,4 +923,560 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>params</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>flop_count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>NAND_eq_gates</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MUX_levels</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>NAND_levels</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>data-&gt;D TT (ps)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>data-&gt;D FF (ps)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>data-&gt;D SS (ps)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>fmax TT (MHz)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fmax FF (MHz)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>fmax SS (MHz)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>P1=W, P2=D</t>
+        </is>
+      </c>
+      <c r="I2">
+        <f>B2*C2 + C2 + 2</f>
+        <v/>
+      </c>
+      <c r="J2">
+        <f>B2*C2*4 + 10</f>
+        <v/>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="6">
+        <f>K2*characterization!$D$13 + L2*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N2" s="6">
+        <f>K2*characterization!$G$13 + L2*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O2" s="6">
+        <f>K2*characterization!$J$13 + L2*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P2" s="6">
+        <f>ROUND(1000000/(M2 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q2" s="6">
+        <f>ROUND(1000000/(N2 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R2" s="6">
+        <f>ROUND(1000000/(O2 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>data-&gt;D path is the bypass MUX2 (1 level). Flops = W*D storage + D valid + 2 control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync (REG=0)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>P1=W, P2=D</t>
+        </is>
+      </c>
+      <c r="I3">
+        <f>B3*C3 + 3*CEILING(LOG(C3,2),1) + 1</f>
+        <v/>
+      </c>
+      <c r="J3">
+        <f>B3*C3*6 + CEILING(LOG(C3,2),1)*8 + 20</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>CEILING(LOG(C3,2),1)</f>
+        <v/>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="6">
+        <f>K3*characterization!$D$13 + L3*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N3" s="6">
+        <f>K3*characterization!$G$13 + L3*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O3" s="6">
+        <f>K3*characterization!$J$13 + L3*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P3" s="6">
+        <f>ROUND(1000000/(M3 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q3" s="6">
+        <f>ROUND(1000000/(N3 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R3" s="6">
+        <f>ROUND(1000000/(O3 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync (REG=1)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>P1=W, P2=D</t>
+        </is>
+      </c>
+      <c r="I4">
+        <f>B4*C4 + 3*CEILING(LOG(C4,2),1) + B4 + 1</f>
+        <v/>
+      </c>
+      <c r="J4">
+        <f>B4*C4*6 + CEILING(LOG(C4,2),1)*8 + 20</f>
+        <v/>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="6">
+        <f>K4*characterization!$D$13 + L4*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N4" s="6">
+        <f>K4*characterization!$G$13 + L4*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O4" s="6">
+        <f>K4*characterization!$J$13 + L4*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P4" s="6">
+        <f>ROUND(1000000/(M4 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q4" s="6">
+        <f>ROUND(1000000/(N4 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R4" s="6">
+        <f>ROUND(1000000/(O4 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>REGISTERED=1 adds an output flop bank (W flops); the read mux is hidden behind it so data-&gt;D shrinks to ~1 NAND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>arbiter_round_robin</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P1=N</t>
+        </is>
+      </c>
+      <c r="I5">
+        <f>B5 + 2</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>B5*8</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>CEILING(LOG(B5,2),1)</f>
+        <v/>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="6">
+        <f>K5*characterization!$D$13 + L5*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N5" s="6">
+        <f>K5*characterization!$G$13 + L5*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O5" s="6">
+        <f>K5*characterization!$J$13 + L5*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P5" s="6">
+        <f>ROUND(1000000/(M5 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q5" s="6">
+        <f>ROUND(1000000/(N5 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R5" s="6">
+        <f>ROUND(1000000/(O5 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Priority encoder is log2(N) MUX levels. Flops = N (last-grant tracker) + 2 (state).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>axi4_master_rd</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AR, P6=SKID_R</t>
+        </is>
+      </c>
+      <c r="I6">
+        <f>F6*(B6+D6+E6+29) + G6*(D6+C6+E6+3)</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>4*(F6*(B6+D6+E6+29) + G6*(D6+C6+E6+3))</f>
+        <v/>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="6">
+        <f>K6*characterization!$D$13 + L6*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N6" s="6">
+        <f>K6*characterization!$G$13 + L6*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O6" s="6">
+        <f>K6*characterization!$J$13 + L6*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P6" s="6">
+        <f>ROUND(1000000/(M6 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="6">
+        <f>ROUND(1000000/(N6 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R6" s="6">
+        <f>ROUND(1000000/(O6 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Two skid buffers in series (AR + R). data-&gt;D path is the skid bypass MUX. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>axi4_master_wr</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AW, P6=SKID_W</t>
+        </is>
+      </c>
+      <c r="I7">
+        <f>F7*(B7+D7+E7+29) + G7*(C7+C7/8+E7+1) + 2*(D7+E7+2)</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>4*(F7*(B7+D7+E7+29) + G7*(C7+C7/8+E7+1) + 2*(D7+E7+2))</f>
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="6">
+        <f>K7*characterization!$D$13 + L7*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="N7" s="6">
+        <f>K7*characterization!$G$13 + L7*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="O7" s="6">
+        <f>K7*characterization!$J$13 + L7*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="P7" s="6">
+        <f>ROUND(1000000/(M7 + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="6">
+        <f>ROUND(1000000/(N7 + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="R7" s="6">
+        <f>ROUND(1000000/(O7 + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Three skid buffers (AW + W + B); SKID_B fixed at 2 in this row. data-&gt;D path is the skid bypass MUX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Cell coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Yellow = editable param</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Grey = derived formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>data-&gt;D = critical combinational delay on the path that loads the downstream flop. Compare against (period - Tflop) to size for a freq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Estimates are first-order: structural flop/gate counts + characterization per-level delays. Treat them as design-time SWAGs, not post-synth truth.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="characterization" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="building blocks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stream" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1479,4 +1480,557 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FUB</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>input signal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>building block crossed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>local NAND depth</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>local NAND count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>terminator (flop / output / BB port)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>local delay TT (ps)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>local delay FF (ps)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>local delay SS (ps)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>s_valid</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>r_drain_ip (flop D)</t>
+        </is>
+      </c>
+      <c r="G2" s="6">
+        <f>D2*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H2" s="6">
+        <f>D2*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I2" s="6">
+        <f>D2*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>s_valid AND s_ready -&gt; w_drain_fifo -&gt; flop D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>s_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.wr_data</t>
+        </is>
+      </c>
+      <c r="G3" s="6">
+        <f>D3*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H3" s="6">
+        <f>D3*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I3" s="6">
+        <f>D3*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>direct wire to FIFO write port; cost inside BB row</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>m_ready (path 1)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>s_ready (output port)</t>
+        </is>
+      </c>
+      <c r="G4" s="6">
+        <f>D4*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H4" s="6">
+        <f>D4*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I4" s="6">
+        <f>D4*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m_ready AND m_valid -&gt; w_draining_now -&gt; OR w_room_available -&gt; s_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>m_ready (path 2)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_ready</t>
+        </is>
+      </c>
+      <c r="G5" s="6">
+        <f>D5*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H5" s="6">
+        <f>D5*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I5" s="6">
+        <f>D5*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>direct wire to FIFO read port</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>r_drain_ip (Q)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.wr_valid</t>
+        </is>
+      </c>
+      <c r="G6" s="6">
+        <f>D6*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H6" s="6">
+        <f>D6*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I6" s="6">
+        <f>D6*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>skid_wr_valid = r_drain_ip; pure wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>r_drain_ip (Q)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dbg_r_pending (output)</t>
+        </is>
+      </c>
+      <c r="G7" s="6">
+        <f>D7*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H7" s="6">
+        <f>D7*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I7" s="6">
+        <f>D7*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dbg_r_pending = r_drain_ip; pure wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_valid</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>m_valid (output)</t>
+        </is>
+      </c>
+      <c r="G8" s="6">
+        <f>D8*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H8" s="6">
+        <f>D8*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I8" s="6">
+        <f>D8*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>wire from FIFO rd_valid; m_valid = u_skid_buffer.rd_valid</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_data</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>m_data[DW-1:0] (output)</t>
+        </is>
+      </c>
+      <c r="G9" s="6">
+        <f>D9*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H9" s="6">
+        <f>D9*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I9" s="6">
+        <f>D9*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>wire from FIFO rd_data</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.count</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>s_ready (output port)</t>
+        </is>
+      </c>
+      <c r="G10" s="6">
+        <f>D10*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H10" s="6">
+        <f>D10*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I10" s="6">
+        <f>D10*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>skid_count + write_stalled (3b adder) -&gt; magnitude cmp &lt; SKID_DEPTH -&gt; OR -&gt; s_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.count</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>occupancy[2:0] (output)</t>
+        </is>
+      </c>
+      <c r="G11" s="6">
+        <f>D11*characterization!$D$11</f>
+        <v/>
+      </c>
+      <c r="H11" s="6">
+        <f>D11*characterization!$G$11</f>
+        <v/>
+      </c>
+      <c r="I11" s="6">
+        <f>D11*characterization!$J$11</f>
+        <v/>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>occupancy = skid_count; direct wire</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>One row per (input signal, end-point) pair. End-point is one of: a flop's D pin, an output port, or a building-block port (whose internal cost is captured on the 'building blocks' sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>'local NAND depth' = combinational gate-equivalents on the path *within this FUB*. Walked by hand from the RTL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>'local delay' = depth * per_NAND[corner] (from characterization sheet). Underestimates wide-bus buffering - same caveat as 'building blocks' SWAG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>When a signal enters a BB, the row's depth/count is for the wires only; the BB row in the 'building blocks' sheet adds the internal cost.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A16:J16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -98,14 +98,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -738,137 +738,159 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Max CARRY levels</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Per-level gate delay (ps)  - freq-independent</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Max MULT levels  (PROXY for mixed-bag logic)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>per NAND delay (ps)</t>
+          <t>Max GRAY_CTR levels</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7.25</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>7.25</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7.25</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5.93</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5.93</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5.93</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11.47</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.47</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.47</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>per XOR delay (ps)</t>
+          <t>Max QUEUE levels</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>26.77</v>
+        <v>171</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>26.77</v>
+        <v>113</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>26.77</v>
+        <v>84</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16.01</v>
+        <v>49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>16.01</v>
+        <v>32</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16.01</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>39.69</v>
+        <v>36</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>39.69</v>
+        <v>24</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>39.69</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>per MUX delay (ps)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>16.29</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>24.97</v>
-      </c>
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Per-level gate delay (ps)  - freq-independent</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -880,42 +902,402 @@
       <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>per NAND delay (ps)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>11.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
-        </is>
+          <t>per XOR delay (ps)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>39.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
-        </is>
+          <t>per MUX delay (ps)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>24.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
-        </is>
+          <t>per CARRY delay (ps)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>45.22</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>INV chain omitted: ABC's strash collapses inverter pairs, so the chain depth is not preserved through optimization and the two-point probe is degenerate (delta_D = 0). Use NAND or MUX as the buffer-cost proxy.</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>per MULT delay (ps)  (PROXY)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>37.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>per GRAY_CTR delay (ps)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>58.44</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>per QUEUE delay (ps)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>54.23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Reference single-point delays (ps) - degenerate slope, no per-level number</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>INV flop-to-flop delay (ps)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>22.33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CLK_DIV flop-to-flop delay (ps)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>31.29</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>** When the critical path is a mixed bag of cells (typical for datapath / FSM next-state / arbitration logic), use the MULT per-level number. It bakes in AND / XOR / full-adder / carry mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>INV: ABC's strash collapses inverter pairs across the chain, so lev doesn't change between probe sizes - per-level slope is degenerate. Single-point delay is reported in the reference table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CLK_DIV: critical path is intra-stage (counter + pickoff), so NUM_STAGES doesn't move lev. Single-point delay is reported in the reference table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Raw probe data is in work/timing_char_data.csv. Reproducer is work/timing_char_sweep.py.</t>
         </is>
@@ -1054,7 +1436,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>gaxi_skid_buffer</t>
         </is>
@@ -1084,27 +1466,27 @@
       <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="7">
         <f>K2*characterization!$D$13 + L2*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="7">
         <f>K2*characterization!$G$13 + L2*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="7">
         <f>K2*characterization!$J$13 + L2*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="7">
         <f>ROUND(1000000/(M2 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="7">
         <f>ROUND(1000000/(N2 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="7">
         <f>ROUND(1000000/(O2 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1115,7 +1497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync (REG=0)</t>
         </is>
@@ -1146,27 +1528,27 @@
       <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="7">
         <f>K3*characterization!$D$13 + L3*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="7">
         <f>K3*characterization!$G$13 + L3*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="7">
         <f>K3*characterization!$J$13 + L3*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="7">
         <f>ROUND(1000000/(M3 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="7">
         <f>ROUND(1000000/(N3 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R3" s="6">
+      <c r="R3" s="7">
         <f>ROUND(1000000/(O3 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1177,7 +1559,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync (REG=1)</t>
         </is>
@@ -1207,27 +1589,27 @@
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="7">
         <f>K4*characterization!$D$13 + L4*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="7">
         <f>K4*characterization!$G$13 + L4*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="7">
         <f>K4*characterization!$J$13 + L4*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="7">
         <f>ROUND(1000000/(M4 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="7">
         <f>ROUND(1000000/(N4 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="7">
         <f>ROUND(1000000/(O4 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1238,7 +1620,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>arbiter_round_robin</t>
         </is>
@@ -1266,27 +1648,27 @@
       <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="7">
         <f>K5*characterization!$D$13 + L5*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="7">
         <f>K5*characterization!$G$13 + L5*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="7">
         <f>K5*characterization!$J$13 + L5*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="7">
         <f>ROUND(1000000/(M5 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="7">
         <f>ROUND(1000000/(N5 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="7">
         <f>ROUND(1000000/(O5 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1297,7 +1679,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>axi4_master_rd</t>
         </is>
@@ -1339,27 +1721,27 @@
       <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="7">
         <f>K6*characterization!$D$13 + L6*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="7">
         <f>K6*characterization!$G$13 + L6*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="7">
         <f>K6*characterization!$J$13 + L6*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="7">
         <f>ROUND(1000000/(M6 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="7">
         <f>ROUND(1000000/(N6 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="7">
         <f>ROUND(1000000/(O6 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1370,7 +1752,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>axi4_master_wr</t>
         </is>
@@ -1412,27 +1794,27 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="7">
         <f>K7*characterization!$D$13 + L7*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="7">
         <f>K7*characterization!$G$13 + L7*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="7">
         <f>K7*characterization!$J$13 + L7*characterization!$J$11</f>
         <v/>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="7">
         <f>ROUND(1000000/(M7 + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="7">
         <f>ROUND(1000000/(N7 + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="R7" s="6">
+      <c r="R7" s="7">
         <f>ROUND(1000000/(O7 + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -1443,14 +1825,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Cell coding</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Yellow = editable param</t>
         </is>
@@ -1578,15 +1960,15 @@
           <t>r_drain_ip (flop D)</t>
         </is>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="7">
         <f>D2*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="7">
         <f>D2*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="7">
         <f>D2*characterization!$J$11</f>
         <v/>
       </c>
@@ -1623,15 +2005,15 @@
           <t>u_skid_buffer.wr_data</t>
         </is>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="7">
         <f>D3*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <f>D3*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="7">
         <f>D3*characterization!$J$11</f>
         <v/>
       </c>
@@ -1664,15 +2046,15 @@
           <t>s_ready (output port)</t>
         </is>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="7">
         <f>D4*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <f>D4*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="7">
         <f>D4*characterization!$J$11</f>
         <v/>
       </c>
@@ -1709,15 +2091,15 @@
           <t>u_skid_buffer.rd_ready</t>
         </is>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="7">
         <f>D5*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <f>D5*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="7">
         <f>D5*characterization!$J$11</f>
         <v/>
       </c>
@@ -1750,15 +2132,15 @@
           <t>u_skid_buffer.wr_valid</t>
         </is>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <f>D6*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <f>D6*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <f>D6*characterization!$J$11</f>
         <v/>
       </c>
@@ -1791,15 +2173,15 @@
           <t>dbg_r_pending (output)</t>
         </is>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <f>D7*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="7">
         <f>D7*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <f>D7*characterization!$J$11</f>
         <v/>
       </c>
@@ -1836,15 +2218,15 @@
           <t>m_valid (output)</t>
         </is>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <f>D8*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <f>D8*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <f>D8*characterization!$J$11</f>
         <v/>
       </c>
@@ -1881,15 +2263,15 @@
           <t>m_data[DW-1:0] (output)</t>
         </is>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <f>D9*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="7">
         <f>D9*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="7">
         <f>D9*characterization!$J$11</f>
         <v/>
       </c>
@@ -1926,15 +2308,15 @@
           <t>s_ready (output port)</t>
         </is>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <f>D10*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="7">
         <f>D10*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="7">
         <f>D10*characterization!$J$11</f>
         <v/>
       </c>
@@ -1971,15 +2353,15 @@
           <t>occupancy[2:0] (output)</t>
         </is>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <f>D11*characterization!$D$11</f>
         <v/>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="7">
         <f>D11*characterization!$G$11</f>
         <v/>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="7">
         <f>D11*characterization!$J$11</f>
         <v/>
       </c>
@@ -1990,7 +2372,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Methodology</t>
         </is>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1248,56 +1248,227 @@
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Wire delay per mm by metal layer (buffered route, ps/mm) - cross-partition route estimate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
-        </is>
+          <t>M2/M3 (local / intermediate)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>156</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
-        </is>
+          <t>M4/M5 (semi-global)</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>84.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
-        </is>
+          <t>M6/M7 (global)</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>** When the critical path is a mixed bag of cells (typical for datapath / FSM next-state / arbitration logic), use the MULT per-level number. It bakes in AND / XOR / full-adder / carry mix.</t>
-        </is>
+          <t>M8/M9 (thick)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>28.6</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>INV: ABC's strash collapses inverter pairs across the chain, so lev doesn't change between probe sizes - per-level slope is degenerate. Single-point delay is reported in the reference table.</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CLK_DIV: critical path is intra-stage (counter + pickoff), so NUM_STAGES doesn't move lev. Single-point delay is reported in the reference table.</t>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>** When the critical path is a mixed bag of cells (typical for datapath / FSM next-state / arbitration logic), use the MULT per-level number. It bakes in AND / XOR / full-adder / carry mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>INV: ABC's strash collapses inverter pairs across the chain, so lev doesn't change between probe sizes - per-level slope is degenerate. Single-point delay is reported in the reference table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CLK_DIV: critical path is intra-stage (counter + pickoff), so NUM_STAGES doesn't move lev. Single-point delay is reported in the reference table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Wire delays are 7nm industry rule-of-thumb for buffered routes; the ASAP7 NLDM ships no wire_load table so ABC measured gate delay only. For partition-to-partition output budgeting, look up the destination metal layer and multiply by route length (mm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Raw probe data is in work/timing_char_data.csv. Reproducer is work/timing_char_sweep.py.</t>
         </is>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,13 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -103,10 +113,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1485,28 +1498,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1562,12 +1580,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>MUX_levels</t>
+          <t>in MUX lv</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>NAND_levels</t>
+          <t>in NAND lv</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1587,159 +1605,146 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>out MUX lv</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>out NAND lv</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>flop-&gt;out TT (ps)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>flop-&gt;out FF (ps)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>flop-&gt;out SS (ps)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>fmax TT (MHz)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>fmax FF (MHz)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>fmax SS (MHz)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>P1=W, P2=D</t>
-        </is>
-      </c>
-      <c r="I2">
-        <f>B2*C2 + C2 + 2</f>
-        <v/>
-      </c>
-      <c r="J2">
-        <f>B2*C2*4 + 10</f>
-        <v/>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="7">
-        <f>K2*characterization!$D$13 + L2*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N2" s="7">
-        <f>K2*characterization!$G$13 + L2*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O2" s="7">
-        <f>K2*characterization!$J$13 + L2*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P2" s="7">
-        <f>ROUND(1000000/(M2 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q2" s="7">
-        <f>ROUND(1000000/(N2 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R2" s="7">
-        <f>ROUND(1000000/(O2 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>data-&gt;D path is the bypass MUX2 (1 level). Flops = W*D storage + D valid + 2 control.</t>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>SRAMs</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync (REG=0)</t>
+          <t>SRAM (raw macro)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2</v>
+        <v>512</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>P1=W, P2=D</t>
         </is>
       </c>
-      <c r="I3">
-        <f>B3*C3 + 3*CEILING(LOG(C3,2),1) + 1</f>
-        <v/>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
       <c r="J3">
-        <f>B3*C3*6 + CEILING(LOG(C3,2),1)*8 + 20</f>
-        <v/>
-      </c>
-      <c r="K3">
-        <f>CEILING(LOG(C3,2),1)</f>
-        <v/>
+        <f>4*B3 + 8*CEILING(LOG(C3,2),1)</f>
+        <v/>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="7">
-        <f>K3*characterization!$D$13 + L3*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N3" s="7">
-        <f>K3*characterization!$G$13 + L3*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O3" s="7">
-        <f>K3*characterization!$J$13 + L3*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P3" s="7">
-        <f>ROUND(1000000/(M3 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q3" s="7">
-        <f>ROUND(1000000/(N3 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R3" s="7">
-        <f>ROUND(1000000/(O3 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state.</t>
+        <v>1</v>
+      </c>
+      <c r="M3" s="8">
+        <f>K3*characterization!$D$17 + L3*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N3" s="8">
+        <f>K3*characterization!$G$17 + L3*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O3" s="8">
+        <f>K3*characterization!$J$17 + L3*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8">
+        <f>P3*characterization!$D$17 + Q3*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S3" s="8">
+        <f>P3*characterization!$G$17 + Q3*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T3" s="8">
+        <f>P3*characterization!$J$17 + Q3*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U3" s="8">
+        <f>ROUND(1000000/(MAX(M3,R3) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V3" s="8">
+        <f>ROUND(1000000/(MAX(N3,S3) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W3" s="8">
+        <f>ROUND(1000000/(MAX(O3,T3) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>SRAM macro (single-port, synchronous read). Storage = W*D bits goes to the macro, not flop count. Read latency = 1 cycle (data appears next clock). Replace this row's per-bit delay with vendor SRAM datasheet for accurate timing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync (REG=1)</t>
+          <t>gaxi_fifo_sync (REG=1, SRAM-backed)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2</v>
+        <v>512</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1747,11 +1752,11 @@
         </is>
       </c>
       <c r="I4">
-        <f>B4*C4 + 3*CEILING(LOG(C4,2),1) + B4 + 1</f>
+        <f>3*CEILING(LOG(C4,2),1) + 1</f>
         <v/>
       </c>
       <c r="J4">
-        <f>B4*C4*6 + CEILING(LOG(C4,2),1)*8 + 20</f>
+        <f>B4*4 + CEILING(LOG(C4,2),1)*8 + 20</f>
         <v/>
       </c>
       <c r="K4" t="n">
@@ -1760,130 +1765,84 @@
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="7">
-        <f>K4*characterization!$D$13 + L4*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N4" s="7">
-        <f>K4*characterization!$G$13 + L4*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O4" s="7">
-        <f>K4*characterization!$J$13 + L4*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P4" s="7">
-        <f>ROUND(1000000/(M4 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q4" s="7">
-        <f>ROUND(1000000/(N4 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R4" s="7">
-        <f>ROUND(1000000/(O4 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>REGISTERED=1 adds an output flop bank (W flops); the read mux is hidden behind it so data-&gt;D shrinks to ~1 NAND.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>arbiter_round_robin</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>P1=N</t>
-        </is>
-      </c>
-      <c r="I5">
-        <f>B5 + 2</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>B5*8</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>CEILING(LOG(B5,2),1)</f>
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="7">
-        <f>K5*characterization!$D$13 + L5*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N5" s="7">
-        <f>K5*characterization!$G$13 + L5*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O5" s="7">
-        <f>K5*characterization!$J$13 + L5*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P5" s="7">
-        <f>ROUND(1000000/(M5 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q5" s="7">
-        <f>ROUND(1000000/(N5 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R5" s="7">
-        <f>ROUND(1000000/(O5 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Priority encoder is log2(N) MUX levels. Flops = N (last-grant tracker) + 2 (state).</t>
+      <c r="M4" s="8">
+        <f>K4*characterization!$D$17 + L4*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N4" s="8">
+        <f>K4*characterization!$G$17 + L4*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O4" s="8">
+        <f>K4*characterization!$J$17 + L4*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="8">
+        <f>P4*characterization!$D$17 + Q4*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S4" s="8">
+        <f>P4*characterization!$G$17 + Q4*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T4" s="8">
+        <f>P4*characterization!$J$17 + Q4*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U4" s="8">
+        <f>ROUND(1000000/(MAX(M4,R4) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V4" s="8">
+        <f>ROUND(1000000/(MAX(N4,S4) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W4" s="8">
+        <f>ROUND(1000000/(MAX(O4,T4) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>REGISTERED=1 + MEM_STYLE=BRAM: storage is in an SRAM/BRAM macro, not flops. Used only by SRAM controller units in STREAM/RAPIDS. Storage bits = W*D. fmax is limited by the SRAM macro clock-to-Q, not by std-cell timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Building Blocks</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>axi4_master_rd</t>
+          <t>gaxi_skid_buffer</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AR, P6=SKID_R</t>
+          <t>P1=W, P2=D</t>
         </is>
       </c>
       <c r="I6">
-        <f>F6*(B6+D6+E6+29) + G6*(D6+C6+E6+3)</f>
+        <f>B6*C6 + C6 + 2</f>
         <v/>
       </c>
       <c r="J6">
-        <f>4*(F6*(B6+D6+E6+29) + G6*(D6+C6+E6+3))</f>
+        <f>B6*C6*4 + 10</f>
         <v/>
       </c>
       <c r="K6" t="n">
@@ -1892,145 +1851,497 @@
       <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="7">
-        <f>K6*characterization!$D$13 + L6*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N6" s="7">
-        <f>K6*characterization!$G$13 + L6*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O6" s="7">
-        <f>K6*characterization!$J$13 + L6*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P6" s="7">
-        <f>ROUND(1000000/(M6 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="7">
-        <f>ROUND(1000000/(N6 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R6" s="7">
-        <f>ROUND(1000000/(O6 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Two skid buffers in series (AR + R). data-&gt;D path is the skid bypass MUX. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
+      <c r="M6" s="8">
+        <f>K6*characterization!$D$17 + L6*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N6" s="8">
+        <f>K6*characterization!$G$17 + L6*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O6" s="8">
+        <f>K6*characterization!$J$17 + L6*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <f>P6*characterization!$D$17 + Q6*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S6" s="8">
+        <f>P6*characterization!$G$17 + Q6*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T6" s="8">
+        <f>P6*characterization!$J$17 + Q6*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U6" s="8">
+        <f>ROUND(1000000/(MAX(M6,R6) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V6" s="8">
+        <f>ROUND(1000000/(MAX(N6,S6) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W6" s="8">
+        <f>ROUND(1000000/(MAX(O6,T6) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Skid buffer outputs come straight from the head flop Q - no output muxing. Input side has the bypass MUX2. Flops = W*D storage + D valid + 2 control.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>axi4_master_wr</t>
+          <t>gaxi_fifo_sync (REG=0)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P1=W, P2=D</t>
+        </is>
+      </c>
+      <c r="I7">
+        <f>B7*C7 + 3*CEILING(LOG(C7,2),1) + 1</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>B7*C7*6 + CEILING(LOG(C7,2),1)*8 + 20</f>
+        <v/>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AW, P6=SKID_W</t>
-        </is>
-      </c>
-      <c r="I7">
-        <f>F7*(B7+D7+E7+29) + G7*(C7+C7/8+E7+1) + 2*(D7+E7+2)</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>4*(F7*(B7+D7+E7+29) + G7*(C7+C7/8+E7+1) + 2*(D7+E7+2))</f>
-        <v/>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" s="7">
-        <f>K7*characterization!$D$13 + L7*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="N7" s="7">
-        <f>K7*characterization!$G$13 + L7*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="O7" s="7">
-        <f>K7*characterization!$J$13 + L7*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="P7" s="7">
-        <f>ROUND(1000000/(M7 + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="7">
-        <f>ROUND(1000000/(N7 + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="R7" s="7">
-        <f>ROUND(1000000/(O7 + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Three skid buffers (AW + W + B); SKID_B fixed at 2 in this row. data-&gt;D path is the skid bypass MUX.</t>
+      <c r="M7" s="8">
+        <f>K7*characterization!$D$17 + L7*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N7" s="8">
+        <f>K7*characterization!$G$17 + L7*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O7" s="8">
+        <f>K7*characterization!$J$17 + L7*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>CEILING(LOG(C7,2),1)</f>
+        <v/>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <f>P7*characterization!$D$17 + Q7*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S7" s="8">
+        <f>P7*characterization!$G$17 + Q7*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T7" s="8">
+        <f>P7*characterization!$J$17 + Q7*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U7" s="8">
+        <f>ROUND(1000000/(MAX(M7,R7) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V7" s="8">
+        <f>ROUND(1000000/(MAX(N7,S7) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W7" s="8">
+        <f>ROUND(1000000/(MAX(O7,T7) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Output critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state. Default FIFO in STREAM/RAPIDS (non-SRAM-backed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>arbiter_round_robin</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>P1=N</t>
+        </is>
+      </c>
+      <c r="I8">
+        <f>B8 + 2</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>B8*8</f>
+        <v/>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8">
+        <f>K8*characterization!$D$17 + L8*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N8" s="8">
+        <f>K8*characterization!$G$17 + L8*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O8" s="8">
+        <f>K8*characterization!$J$17 + L8*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P8">
+        <f>CEILING(LOG(B8,2),1)</f>
+        <v/>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="8">
+        <f>P8*characterization!$D$17 + Q8*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S8" s="8">
+        <f>P8*characterization!$G$17 + Q8*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T8" s="8">
+        <f>P8*characterization!$J$17 + Q8*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U8" s="8">
+        <f>ROUND(1000000/(MAX(M8,R8) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V8" s="8">
+        <f>ROUND(1000000/(MAX(N8,S8) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W8" s="8">
+        <f>ROUND(1000000/(MAX(O8,T8) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Priority encoder is log2(N) MUX levels on the OUTPUT side (req -&gt; encode -&gt; gnt). Flops = N (last-grant tracker) + 2.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Cell coding</t>
+          <t>axi4_master_rd</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AR, P6=SKID_R</t>
+        </is>
+      </c>
+      <c r="I9">
+        <f>F9*(B9+D9+E9+29) + G9*(D9+C9+E9+3)</f>
+        <v/>
+      </c>
+      <c r="J9">
+        <f>4*(F9*(B9+D9+E9+29) + G9*(D9+C9+E9+3))</f>
+        <v/>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="8">
+        <f>K9*characterization!$D$17 + L9*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N9" s="8">
+        <f>K9*characterization!$G$17 + L9*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O9" s="8">
+        <f>K9*characterization!$J$17 + L9*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="8">
+        <f>P9*characterization!$D$17 + Q9*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S9" s="8">
+        <f>P9*characterization!$G$17 + Q9*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T9" s="8">
+        <f>P9*characterization!$J$17 + Q9*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U9" s="8">
+        <f>ROUND(1000000/(MAX(M9,R9) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V9" s="8">
+        <f>ROUND(1000000/(MAX(N9,S9) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W9" s="8">
+        <f>ROUND(1000000/(MAX(O9,T9) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Two skid buffers in series (AR + R). Input bypass MUX2 + output select MUX2. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Yellow = editable param</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Grey = derived formula</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>axi4_master_wr</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AW, P6=SKID_W</t>
+        </is>
+      </c>
+      <c r="I10">
+        <f>F10*(B10+D10+E10+29) + G10*(C10+C10/8+E10+1) + 2*(D10+E10+2)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>4*(F10*(B10+D10+E10+29) + G10*(C10+C10/8+E10+1) + 2*(D10+E10+2))</f>
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8">
+        <f>K10*characterization!$D$17 + L10*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N10" s="8">
+        <f>K10*characterization!$G$17 + L10*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O10" s="8">
+        <f>K10*characterization!$J$17 + L10*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="8">
+        <f>P10*characterization!$D$17 + Q10*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S10" s="8">
+        <f>P10*characterization!$G$17 + Q10*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T10" s="8">
+        <f>P10*characterization!$J$17 + Q10*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U10" s="8">
+        <f>ROUND(1000000/(MAX(M10,R10) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V10" s="8">
+        <f>ROUND(1000000/(MAX(N10,S10) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W10" s="8">
+        <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Three skid buffers (AW + W + B); SKID_B fixed at 2 in this row. Input bypass + output select MUXes; both are 1 level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>SRAM storage size reference</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>data-&gt;D = critical combinational delay on the path that loads the downstream flop. Compare against (period - Tflop) to size for a freq.</t>
+          <t xml:space="preserve">SRAM raw macro: storage bits = W * D = </t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>B3*C3</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>bits =</t>
+        </is>
+      </c>
+      <c r="F13">
+        <f>B3*C3/8/1024</f>
+        <v/>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t xml:space="preserve">FIFO REG=1 SRAM-backed: storage bits = W * D = </t>
+        </is>
+      </c>
+      <c r="D14">
+        <f>B4*C4</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>bits =</t>
+        </is>
+      </c>
+      <c r="F14">
+        <f>B4*C4/8/1024</f>
+        <v/>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Cell coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Yellow = editable param</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Grey = derived formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>data-&gt;D = critical combinational delay on the path that loads the downstream flop. Compare against (period - Tflop) to size for a freq.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Estimates are first-order: structural flop/gate counts + characterization per-level delays. Treat them as design-time SWAGs, not post-synth truth.</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>REG=1 SRAM-backed FIFO is only used by SRAM controller units in STREAM/RAPIDS (sram_controller_unit, src/snk_sram_controller_unit_beats). Everywhere else uses REG=0 - that's why the Building Blocks section lists only the REG=0 variant.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A5:X5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2041,19 +2352,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="80" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2064,88 +2376,59 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>input signal</t>
+          <t>port</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>dir</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>building block crossed</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>local NAND depth</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>local NAND count</t>
+          <t>MUX lv</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>terminator (flop / output / BB port)</t>
+          <t>NAND lv</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>source/sink flop or BB port</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>local delay TT (ps)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>local delay FF (ps)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>local delay SS (ps)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>places it goes (consumer / producer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>stream_latency_bridge</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>s_valid</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>r_drain_ip (flop D)</t>
-        </is>
-      </c>
-      <c r="G2" s="7">
-        <f>D2*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H2" s="7">
-        <f>D2*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I2" s="7">
-        <f>D2*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>s_valid AND s_ready -&gt; w_drain_fifo -&gt; flop D</t>
         </is>
       </c>
     </row>
@@ -2157,40 +2440,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>s_data[DW-1:0]</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>s_valid</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>u_skid_buffer.wr_data</t>
-        </is>
-      </c>
-      <c r="G3" s="7">
-        <f>D3*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H3" s="7">
-        <f>D3*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I3" s="7">
-        <f>D3*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>direct wire to FIFO write port; cost inside BB row</t>
+        <v>1</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>r_drain_ip flop D</t>
+        </is>
+      </c>
+      <c r="H3" s="8">
+        <f>E3*characterization!$D$17 + F3*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I3" s="8">
+        <f>E3*characterization!$G$17 + F3*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J3" s="8">
+        <f>E3*characterization!$J$17 + F3*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo.rd_valid in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -2202,36 +2486,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>m_ready (path 1)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" s="5" t="n">
-        <v>2</v>
+          <t>s_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>s_ready (output port)</t>
-        </is>
-      </c>
-      <c r="G4" s="7">
-        <f>D4*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
-        <f>D4*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I4" s="7">
-        <f>D4*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m_ready AND m_valid -&gt; w_draining_now -&gt; OR w_room_available -&gt; s_ready</t>
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.wr_data</t>
+        </is>
+      </c>
+      <c r="H4" s="8">
+        <f>E4*characterization!$D$17 + F4*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I4" s="8">
+        <f>E4*characterization!$G$17 + F4*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>E4*characterization!$J$17 + F4*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo.rd_data</t>
         </is>
       </c>
     </row>
@@ -2243,40 +2536,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>m_ready (path 2)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>s_ready</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>u_skid_buffer.rd_ready</t>
-        </is>
-      </c>
-      <c r="G5" s="7">
-        <f>D5*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H5" s="7">
-        <f>D5*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I5" s="7">
-        <f>D5*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>direct wire to FIFO read port</t>
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>comb of skid count + drain</t>
+        </is>
+      </c>
+      <c r="H5" s="8">
+        <f>E5*characterization!$D$17 + F5*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I5" s="8">
+        <f>E5*characterization!$G$17 + F5*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J5" s="8">
+        <f>E5*characterization!$J$17 + F5*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>to u_channel_fifo.rd_ready</t>
         </is>
       </c>
     </row>
@@ -2288,36 +2582,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>r_drain_ip (Q)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
+          <t>m_valid</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>u_skid_buffer.wr_valid</t>
-        </is>
-      </c>
-      <c r="G6" s="7">
-        <f>D6*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H6" s="7">
-        <f>D6*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I6" s="7">
-        <f>D6*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>skid_wr_valid = r_drain_ip; pure wire</t>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_valid</t>
+        </is>
+      </c>
+      <c r="H6" s="8">
+        <f>E6*characterization!$D$17 + F6*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I6" s="8">
+        <f>E6*characterization!$G$17 + F6*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>E6*characterization!$J$17 + F6*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>to axi_write_engine.sram_rd_valid</t>
         </is>
       </c>
     </row>
@@ -2329,36 +2632,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>r_drain_ip (Q)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
+          <t>m_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>dbg_r_pending (output)</t>
-        </is>
-      </c>
-      <c r="G7" s="7">
-        <f>D7*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>D7*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>D7*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dbg_r_pending = r_drain_ip; pure wire</t>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_data</t>
+        </is>
+      </c>
+      <c r="H7" s="8">
+        <f>E7*characterization!$D$17 + F7*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I7" s="8">
+        <f>E7*characterization!$G$17 + F7*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>E7*characterization!$J$17 + F7*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>to axi_write_engine.sram_rd_data</t>
         </is>
       </c>
     </row>
@@ -2370,40 +2682,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_valid</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+          <t>m_ready</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>m_valid (output)</t>
-        </is>
-      </c>
-      <c r="G8" s="7">
-        <f>D8*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>D8*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>D8*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>wire from FIFO rd_valid; m_valid = u_skid_buffer.rd_valid</t>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_ready</t>
+        </is>
+      </c>
+      <c r="H8" s="8">
+        <f>E8*characterization!$D$17 + F8*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I8" s="8">
+        <f>E8*characterization!$G$17 + F8*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J8" s="8">
+        <f>E8*characterization!$J$17 + F8*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>from axi_write_engine.sram_rd_ready</t>
         </is>
       </c>
     </row>
@@ -2415,174 +2732,3854 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_data</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+          <t>occupancy[2:0]</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>m_data[DW-1:0] (output)</t>
-        </is>
-      </c>
-      <c r="G9" s="7">
-        <f>D9*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H9" s="7">
-        <f>D9*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>D9*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>wire from FIFO rd_data</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>stream_latency_bridge</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>u_skid_buffer.count</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>s_ready (output port)</t>
-        </is>
-      </c>
-      <c r="G10" s="7">
-        <f>D10*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
-        <f>D10*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>D10*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>skid_count + write_stalled (3b adder) -&gt; magnitude cmp &lt; SKID_DEPTH -&gt; OR -&gt; s_ready</t>
+      <c r="H9" s="8">
+        <f>E9*characterization!$D$17 + F9*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I9" s="8">
+        <f>E9*characterization!$G$17 + F9*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J9" s="8">
+        <f>E9*characterization!$J$17 + F9*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>to scheduler (drain-IP backpressure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stream_latency_bridge</t>
+          <t>stream_alloc_ctrl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>u_skid_buffer.count</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>0</v>
-      </c>
+          <t>wr_valid</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>occupancy[2:0] (output)</t>
-        </is>
-      </c>
-      <c r="G11" s="7">
-        <f>D11*characterization!$D$11</f>
-        <v/>
-      </c>
-      <c r="H11" s="7">
-        <f>D11*characterization!$G$11</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>D11*characterization!$J$11</f>
-        <v/>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>occupancy = skid_count; direct wire</t>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>r_wr_ptr flop D (+wr_size)</t>
+        </is>
+      </c>
+      <c r="H11" s="8">
+        <f>E11*characterization!$D$17 + F11*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I11" s="8">
+        <f>E11*characterization!$G$17 + F11*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J11" s="8">
+        <f>E11*characterization!$J$17 + F11*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (allocate request)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>wr_size[7:0]</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>r_wr_ptr adder input</t>
+        </is>
+      </c>
+      <c r="H12" s="8">
+        <f>E12*characterization!$D$17 + F12*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I12" s="8">
+        <f>E12*characterization!$G$17 + F12*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J12" s="8">
+        <f>E12*characterization!$J$17 + F12*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Methodology</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rd_valid</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>r_rd_ptr flop D</t>
+        </is>
+      </c>
+      <c r="H13" s="8">
+        <f>E13*characterization!$D$17 + F13*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I13" s="8">
+        <f>E13*characterization!$G$17 + F13*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J13" s="8">
+        <f>E13*characterization!$J$17 + F13*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit (release event)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>One row per (input signal, end-point) pair. End-point is one of: a flop's D pin, an output port, or a building-block port (whose internal cost is captured on the 'building blocks' sheet).</t>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>space_free[AW:0]</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>r_space_free (registered)</t>
+        </is>
+      </c>
+      <c r="H14" s="8">
+        <f>E14*characterization!$D$17 + F14*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I14" s="8">
+        <f>E14*characterization!$G$17 + F14*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J14" s="8">
+        <f>E14*characterization!$J$17 + F14*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (sram_alloc_space_free)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>'local NAND depth' = combinational gate-equivalents on the path *within this FUB*. Walked by hand from the RTL.</t>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>wr_full</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>comb of r_space_free</t>
+        </is>
+      </c>
+      <c r="H15" s="8">
+        <f>E15*characterization!$D$17 + F15*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I15" s="8">
+        <f>E15*characterization!$G$17 + F15*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J15" s="8">
+        <f>E15*characterization!$J$17 + F15*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (back-pressure)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>'local delay' = depth * per_NAND[corner] (from characterization sheet). Underestimates wide-bus buffering - same caveat as 'building blocks' SWAG.</t>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>wr_almost_full</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>comb of r_space_free</t>
+        </is>
+      </c>
+      <c r="H16" s="8">
+        <f>E16*characterization!$D$17 + F16*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I16" s="8">
+        <f>E16*characterization!$G$17 + F16*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J16" s="8">
+        <f>E16*characterization!$J$17 + F16*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (threshold)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>When a signal enters a BB, the row's depth/count is for the wires only; the BB row in the 'building blocks' sheet adds the internal cost.</t>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rd_empty</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>comb of r_space_free</t>
+        </is>
+      </c>
+      <c r="H17" s="8">
+        <f>E17*characterization!$D$17 + F17*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I17" s="8">
+        <f>E17*characterization!$G$17 + F17*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J17" s="8">
+        <f>E17*characterization!$J$17 + F17*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>unused (debug)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>wr_valid</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>r_wr_ptr flop D</t>
+        </is>
+      </c>
+      <c r="H19" s="8">
+        <f>E19*characterization!$D$17 + F19*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I19" s="8">
+        <f>E19*characterization!$G$17 + F19*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J19" s="8">
+        <f>E19*characterization!$J$17 + F19*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo handshake in sram_controller_unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rd_valid</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>r_rd_ptr flop D (+rd_size)</t>
+        </is>
+      </c>
+      <c r="H20" s="8">
+        <f>E20*characterization!$D$17 + F20*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I20" s="8">
+        <f>E20*characterization!$G$17 + F20*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J20" s="8">
+        <f>E20*characterization!$J$17 + F20*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>from axi_write_engine (drain reservation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rd_size[7:0]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>r_rd_ptr adder input</t>
+        </is>
+      </c>
+      <c r="H21" s="8">
+        <f>E21*characterization!$D$17 + F21*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>E21*characterization!$G$17 + F21*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J21" s="8">
+        <f>E21*characterization!$J$17 + F21*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>data_available[AW:0]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>r_data_available (registered)</t>
+        </is>
+      </c>
+      <c r="H22" s="8">
+        <f>E22*characterization!$D$17 + F22*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I22" s="8">
+        <f>E22*characterization!$G$17 + F22*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J22" s="8">
+        <f>E22*characterization!$J$17 + F22*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rd_empty</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>comb of r_data_available</t>
+        </is>
+      </c>
+      <c r="H23" s="8">
+        <f>E23*characterization!$D$17 + F23*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I23" s="8">
+        <f>E23*characterization!$G$17 + F23*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J23" s="8">
+        <f>E23*characterization!$J$17 + F23*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>to axi_write_engine (no data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wr_full</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>comb of r_data_available</t>
+        </is>
+      </c>
+      <c r="H24" s="8">
+        <f>E24*characterization!$D$17 + F24*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I24" s="8">
+        <f>E24*characterization!$G$17 + F24*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J24" s="8">
+        <f>E24*characterization!$J$17 + F24*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit (back-pressure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>axi_rd_alloc_req</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>alloc_ctrl.wr_valid</t>
+        </is>
+      </c>
+      <c r="H26" s="8">
+        <f>E26*characterization!$D$17 + F26*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I26" s="8">
+        <f>E26*characterization!$G$17 + F26*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J26" s="8">
+        <f>E26*characterization!$J$17 + F26*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (reserve burst space)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>axi_rd_alloc_size[7:0]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>alloc_ctrl.wr_size</t>
+        </is>
+      </c>
+      <c r="H27" s="8">
+        <f>E27*characterization!$D$17 + F27*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I27" s="8">
+        <f>E27*characterization!$G$17 + F27*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J27" s="8">
+        <f>E27*characterization!$J$17 + F27*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>axi_rd_alloc_space_free[AW:0]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>alloc_ctrl.space_free</t>
+        </is>
+      </c>
+      <c r="H28" s="8">
+        <f>E28*characterization!$D$17 + F28*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I28" s="8">
+        <f>E28*characterization!$G$17 + F28*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J28" s="8">
+        <f>E28*characterization!$J$17 + F28*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>axi_rd_sram_valid</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>u_channel_fifo.wr_valid</t>
+        </is>
+      </c>
+      <c r="H29" s="8">
+        <f>E29*characterization!$D$17 + F29*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I29" s="8">
+        <f>E29*characterization!$G$17 + F29*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J29" s="8">
+        <f>E29*characterization!$J$17 + F29*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (write data into SRAM FIFO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>axi_rd_sram_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>u_channel_fifo.wr_data</t>
+        </is>
+      </c>
+      <c r="H30" s="8">
+        <f>E30*characterization!$D$17 + F30*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I30" s="8">
+        <f>E30*characterization!$G$17 + F30*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J30" s="8">
+        <f>E30*characterization!$J$17 + F30*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>axi_rd_sram_ready</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>u_channel_fifo.wr_ready</t>
+        </is>
+      </c>
+      <c r="H31" s="8">
+        <f>E31*characterization!$D$17 + F31*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I31" s="8">
+        <f>E31*characterization!$G$17 + F31*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J31" s="8">
+        <f>E31*characterization!$J$17 + F31*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_valid</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>u_latency_bridge.m_valid</t>
+        </is>
+      </c>
+      <c r="H32" s="8">
+        <f>E32*characterization!$D$17 + F32*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I32" s="8">
+        <f>E32*characterization!$G$17 + F32*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J32" s="8">
+        <f>E32*characterization!$J$17 + F32*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>u_latency_bridge.m_data</t>
+        </is>
+      </c>
+      <c r="H33" s="8">
+        <f>E33*characterization!$D$17 + F33*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>E33*characterization!$G$17 + F33*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J33" s="8">
+        <f>E33*characterization!$J$17 + F33*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_ready</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>u_latency_bridge.m_ready</t>
+        </is>
+      </c>
+      <c r="H34" s="8">
+        <f>E34*characterization!$D$17 + F34*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I34" s="8">
+        <f>E34*characterization!$G$17 + F34*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J34" s="8">
+        <f>E34*characterization!$J$17 + F34*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wr_drain_req</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>drain_ctrl.rd_valid</t>
+        </is>
+      </c>
+      <c r="H35" s="8">
+        <f>E35*characterization!$D$17 + F35*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I35" s="8">
+        <f>E35*characterization!$G$17 + F35*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J35" s="8">
+        <f>E35*characterization!$J$17 + F35*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ch_alloc_req[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>per-ch sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="H37" s="8">
+        <f>E37*characterization!$D$17 + F37*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I37" s="8">
+        <f>E37*characterization!$G$17 + F37*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J37" s="8">
+        <f>E37*characterization!$J$17 + F37*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (N-channel fan-out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ch_alloc_space_free[N-1:0][AW:0]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>per-ch alloc.space_free</t>
+        </is>
+      </c>
+      <c r="H38" s="8">
+        <f>E38*characterization!$D$17 + F38*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I38" s="8">
+        <f>E38*characterization!$G$17 + F38*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J38" s="8">
+        <f>E38*characterization!$J$17 + F38*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ch_rd_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>per-ch SRAM FIFO wr</t>
+        </is>
+      </c>
+      <c r="H39" s="8">
+        <f>E39*characterization!$D$17 + F39*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I39" s="8">
+        <f>E39*characterization!$G$17 + F39*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J39" s="8">
+        <f>E39*characterization!$J$17 + F39*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ch_wr_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>per-ch SRAM FIFO read</t>
+        </is>
+      </c>
+      <c r="H40" s="8">
+        <f>E40*characterization!$D$17 + F40*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I40" s="8">
+        <f>E40*characterization!$G$17 + F40*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J40" s="8">
+        <f>E40*characterization!$J$17 + F40*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ch_wr_data[N-1:0][DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>per-ch fifo rd_data</t>
+        </is>
+      </c>
+      <c r="H41" s="8">
+        <f>E41*characterization!$D$17 + F41*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I41" s="8">
+        <f>E41*characterization!$G$17 + F41*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J41" s="8">
+        <f>E41*characterization!$J$17 + F41*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>channel_idle[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>edge-detect flops</t>
+        </is>
+      </c>
+      <c r="H43" s="8">
+        <f>E43*characterization!$D$17 + F43*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I43" s="8">
+        <f>E43*characterization!$G$17 + F43*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J43" s="8">
+        <f>E43*characterization!$J$17 + F43*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>from scheduler (per-ch idle state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cfg_enable</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>control flop</t>
+        </is>
+      </c>
+      <c r="H44" s="8">
+        <f>E44*characterization!$D$17 + F44*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I44" s="8">
+        <f>E44*characterization!$G$17 + F44*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J44" s="8">
+        <f>E44*characterization!$J$17 + F44*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>from APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>cfg_clear</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>FIFO reset path</t>
+        </is>
+      </c>
+      <c r="H45" s="8">
+        <f>E45*characterization!$D$17 + F45*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I45" s="8">
+        <f>E45*characterization!$G$17 + F45*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J45" s="8">
+        <f>E45*characterization!$J$17 + F45*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>from APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>perf_fifo_rd</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>u_perf_fifo.rd_valid</t>
+        </is>
+      </c>
+      <c r="H46" s="8">
+        <f>E46*characterization!$D$17 + F46*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I46" s="8">
+        <f>E46*characterization!$G$17 + F46*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J46" s="8">
+        <f>E46*characterization!$J$17 + F46*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>from APB CSR pop strobe</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>perf_fifo_data_low[31:0]</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>u_perf_fifo.rd_data[31:0]</t>
+        </is>
+      </c>
+      <c r="H47" s="8">
+        <f>E47*characterization!$D$17 + F47*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I47" s="8">
+        <f>E47*characterization!$G$17 + F47*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J47" s="8">
+        <f>E47*characterization!$J$17 + F47*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>to APB CSR (host read)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>perf_fifo_data_high[31:0]</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>u_perf_fifo.rd_data[63:32]</t>
+        </is>
+      </c>
+      <c r="H48" s="8">
+        <f>E48*characterization!$D$17 + F48*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I48" s="8">
+        <f>E48*characterization!$G$17 + F48*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J48" s="8">
+        <f>E48*characterization!$J$17 + F48*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>to APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>perf_fifo_empty</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>u_perf_fifo empty flag</t>
+        </is>
+      </c>
+      <c r="H49" s="8">
+        <f>E49*characterization!$D$17 + F49*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I49" s="8">
+        <f>E49*characterization!$G$17 + F49*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J49" s="8">
+        <f>E49*characterization!$J$17 + F49*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>to APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>perf_fifo_count[15:0]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>u_perf_fifo.count</t>
+        </is>
+      </c>
+      <c r="H50" s="8">
+        <f>E50*characterization!$D$17 + F50*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I50" s="8">
+        <f>E50*characterization!$G$17 + F50*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J50" s="8">
+        <f>E50*characterization!$J$17 + F50*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>to APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>apb_cmd_valid</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>r_apb_cmd_valid</t>
+        </is>
+      </c>
+      <c r="H52" s="8">
+        <f>E52*characterization!$D$17 + F52*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I52" s="8">
+        <f>E52*characterization!$G$17 + F52*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J52" s="8">
+        <f>E52*characterization!$J$17 + F52*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>from APB master</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>apb_cmd_addr[ADDR_WIDTH-1:0]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>address decoder</t>
+        </is>
+      </c>
+      <c r="H53" s="8">
+        <f>E53*characterization!$D$17 + F53*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I53" s="8">
+        <f>E53*characterization!$G$17 + F53*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J53" s="8">
+        <f>E53*characterization!$J$17 + F53*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>from APB master</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>apb_cmd_wdata[DATA_WIDTH-1:0]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>per-ch desc address mux</t>
+        </is>
+      </c>
+      <c r="H54" s="8">
+        <f>E54*characterization!$D$17 + F54*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I54" s="8">
+        <f>E54*characterization!$G$17 + F54*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J54" s="8">
+        <f>E54*characterization!$J$17 + F54*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>from APB master (descriptor pointer write)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>apb_cmd_ready</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>comb (FIFO ready AND)</t>
+        </is>
+      </c>
+      <c r="H55" s="8">
+        <f>E55*characterization!$D$17 + F55*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I55" s="8">
+        <f>E55*characterization!$G$17 + F55*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J55" s="8">
+        <f>E55*characterization!$J$17 + F55*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>to APB master</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>apb_rsp_valid</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>rsp pipeline flop</t>
+        </is>
+      </c>
+      <c r="H56" s="8">
+        <f>E56*characterization!$D$17 + F56*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I56" s="8">
+        <f>E56*characterization!$G$17 + F56*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J56" s="8">
+        <f>E56*characterization!$J$17 + F56*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>to APB master</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>desc_apb_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>per-ch valid demux</t>
+        </is>
+      </c>
+      <c r="H57" s="8">
+        <f>E57*characterization!$D$17 + F57*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I57" s="8">
+        <f>E57*characterization!$G$17 + F57*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J57" s="8">
+        <f>E57*characterization!$J$17 + F57*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>to descriptor_engine[N] (kick-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>desc_apb_addr[N-1:0][DA-1:0]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>per-ch addr flops</t>
+        </is>
+      </c>
+      <c r="H58" s="8">
+        <f>E58*characterization!$D$17 + F58*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I58" s="8">
+        <f>E58*characterization!$G$17 + F58*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J58" s="8">
+        <f>E58*characterization!$J$17 + F58*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>to descriptor_engine[N] (initial descriptor pointer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>desc_apb_ready[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>per-ch desc_engine ack</t>
+        </is>
+      </c>
+      <c r="H59" s="8">
+        <f>E59*characterization!$D$17 + F59*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I59" s="8">
+        <f>E59*characterization!$G$17 + F59*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J59" s="8">
+        <f>E59*characterization!$J$17 + F59*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>from descriptor_engine[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>desc_apb_valid</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>r_state IDLE -&gt; FETCH</t>
+        </is>
+      </c>
+      <c r="H61" s="8">
+        <f>E61*characterization!$D$17 + F61*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I61" s="8">
+        <f>E61*characterization!$G$17 + F61*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J61" s="8">
+        <f>E61*characterization!$J$17 + F61*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>from apbtodescr (kick-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>desc_apb_addr[DA-1:0]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>r_desc_addr flop</t>
+        </is>
+      </c>
+      <c r="H62" s="8">
+        <f>E62*characterization!$D$17 + F62*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I62" s="8">
+        <f>E62*characterization!$G$17 + F62*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J62" s="8">
+        <f>E62*characterization!$J$17 + F62*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>from apbtodescr</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>desc_axi_ar_*</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>AR skid head Q</t>
+        </is>
+      </c>
+      <c r="H63" s="8">
+        <f>E63*characterization!$D$17 + F63*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I63" s="8">
+        <f>E63*characterization!$G$17 + F63*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J63" s="8">
+        <f>E63*characterization!$J$17 + F63*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>to scheduler_group desc_axi master</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>desc_axi_r_*</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>R skid input</t>
+        </is>
+      </c>
+      <c r="H64" s="8">
+        <f>E64*characterization!$D$17 + F64*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I64" s="8">
+        <f>E64*characterization!$G$17 + F64*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J64" s="8">
+        <f>E64*characterization!$J$17 + F64*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>from scheduler_group desc_axi master</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>descriptor_valid</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>i_descriptor_fifo.rd_valid</t>
+        </is>
+      </c>
+      <c r="H65" s="8">
+        <f>E65*characterization!$D$17 + F65*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I65" s="8">
+        <f>E65*characterization!$G$17 + F65*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J65" s="8">
+        <f>E65*characterization!$J$17 + F65*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>to scheduler (descriptor dispatch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>descriptor_data[256-1:0]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>i_descriptor_fifo.rd_data</t>
+        </is>
+      </c>
+      <c r="H66" s="8">
+        <f>E66*characterization!$D$17 + F66*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I66" s="8">
+        <f>E66*characterization!$G$17 + F66*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J66" s="8">
+        <f>E66*characterization!$J$17 + F66*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>to scheduler</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>descriptor_ready</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>i_descriptor_fifo.rd_ready</t>
+        </is>
+      </c>
+      <c r="H67" s="8">
+        <f>E67*characterization!$D$17 + F67*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I67" s="8">
+        <f>E67*characterization!$G$17 + F67*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J67" s="8">
+        <f>E67*characterization!$J$17 + F67*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>from scheduler</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>descriptor_valid</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>r_state IDLE -&gt; RUN</t>
+        </is>
+      </c>
+      <c r="H69" s="8">
+        <f>E69*characterization!$D$17 + F69*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I69" s="8">
+        <f>E69*characterization!$G$17 + F69*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J69" s="8">
+        <f>E69*characterization!$J$17 + F69*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>from descriptor_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>descriptor_data[256-1:0]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>r_descriptor latch</t>
+        </is>
+      </c>
+      <c r="H70" s="8">
+        <f>E70*characterization!$D$17 + F70*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I70" s="8">
+        <f>E70*characterization!$G$17 + F70*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J70" s="8">
+        <f>E70*characterization!$J$17 + F70*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>from descriptor_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>axi_rd_req_valid</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>r_axi_rd_req state</t>
+        </is>
+      </c>
+      <c r="H71" s="8">
+        <f>E71*characterization!$D$17 + F71*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I71" s="8">
+        <f>E71*characterization!$G$17 + F71*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J71" s="8">
+        <f>E71*characterization!$J$17 + F71*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (per-channel request)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>axi_rd_req_addr[63:0]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>r_src_addr+offset</t>
+        </is>
+      </c>
+      <c r="H72" s="8">
+        <f>E72*characterization!$D$17 + F72*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I72" s="8">
+        <f>E72*characterization!$G$17 + F72*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J72" s="8">
+        <f>E72*characterization!$J$17 + F72*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>axi_wr_req_valid</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>r_axi_wr_req state</t>
+        </is>
+      </c>
+      <c r="H73" s="8">
+        <f>E73*characterization!$D$17 + F73*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I73" s="8">
+        <f>E73*characterization!$G$17 + F73*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J73" s="8">
+        <f>E73*characterization!$J$17 + F73*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>axi_wr_req_addr[63:0]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>r_dst_addr+offset</t>
+        </is>
+      </c>
+      <c r="H74" s="8">
+        <f>E74*characterization!$D$17 + F74*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I74" s="8">
+        <f>E74*characterization!$G$17 + F74*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J74" s="8">
+        <f>E74*characterization!$J$17 + F74*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ch_idle</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>r_state == IDLE</t>
+        </is>
+      </c>
+      <c r="H75" s="8">
+        <f>E75*characterization!$D$17 + F75*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I75" s="8">
+        <f>E75*characterization!$G$17 + F75*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J75" s="8">
+        <f>E75*characterization!$J$17 + F75*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>to perf_profiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ch_done_strobe</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>r_state -&gt; DONE pulse</t>
+        </is>
+      </c>
+      <c r="H76" s="8">
+        <f>E76*characterization!$D$17 + F76*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I76" s="8">
+        <f>E76*characterization!$G$17 + F76*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J76" s="8">
+        <f>E76*characterization!$J$17 + F76*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>to monbus_reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>monbus_pkt</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>event-encode comb</t>
+        </is>
+      </c>
+      <c r="H77" s="8">
+        <f>E77*characterization!$D$17 + F77*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I77" s="8">
+        <f>E77*characterization!$G$17 + F77*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J77" s="8">
+        <f>E77*characterization!$J$17 + F77*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>to monbus group / reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>sched_req_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>u_arbiter (CLIENTS=N)</t>
+        </is>
+      </c>
+      <c r="H79" s="8">
+        <f>E79*characterization!$D$17 + F79*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I79" s="8">
+        <f>E79*characterization!$G$17 + F79*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J79" s="8">
+        <f>E79*characterization!$J$17 + F79*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>from scheduler[N] (per-channel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sched_req_addr[N-1:0][63:0]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>u_arbiter granted addr mux</t>
+        </is>
+      </c>
+      <c r="H80" s="8">
+        <f>E80*characterization!$D$17 + F80*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I80" s="8">
+        <f>E80*characterization!$G$17 + F80*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J80" s="8">
+        <f>E80*characterization!$J$17 + F80*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>m_axi_ar_*</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid (AR side)</t>
+        </is>
+      </c>
+      <c r="H81" s="8">
+        <f>E81*characterization!$D$17 + F81*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I81" s="8">
+        <f>E81*characterization!$G$17 + F81*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J81" s="8">
+        <f>E81*characterization!$J$17 + F81*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>to AXI4 master read system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>m_axi_r_*</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid (R side)</t>
+        </is>
+      </c>
+      <c r="H82" s="8">
+        <f>E82*characterization!$D$17 + F82*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I82" s="8">
+        <f>E82*characterization!$G$17 + F82*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J82" s="8">
+        <f>E82*characterization!$J$17 + F82*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>from AXI4 master read system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>sram_alloc_req[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>per-ch alloc req gen</t>
+        </is>
+      </c>
+      <c r="H83" s="8">
+        <f>E83*characterization!$D$17 + F83*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I83" s="8">
+        <f>E83*characterization!$G$17 + F83*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J83" s="8">
+        <f>E83*characterization!$J$17 + F83*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N] (reserve burst space)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>sram_alloc_space_free[N-1:0][AW:0]</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>per-ch space cmp</t>
+        </is>
+      </c>
+      <c r="H84" s="8">
+        <f>E84*characterization!$D$17 + F84*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I84" s="8">
+        <f>E84*characterization!$G$17 + F84*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J84" s="8">
+        <f>E84*characterization!$J$17 + F84*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>sram_wr_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>post-arbiter demux</t>
+        </is>
+      </c>
+      <c r="H85" s="8">
+        <f>E85*characterization!$D$17 + F85*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I85" s="8">
+        <f>E85*characterization!$G$17 + F85*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J85" s="8">
+        <f>E85*characterization!$J$17 + F85*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N].wr</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>sram_wr_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>R-skid data wire</t>
+        </is>
+      </c>
+      <c r="H86" s="8">
+        <f>E86*characterization!$D$17 + F86*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I86" s="8">
+        <f>E86*characterization!$G$17 + F86*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J86" s="8">
+        <f>E86*characterization!$J$17 + F86*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N].wr (channel-id muxed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>sched_req_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>arbiter granted</t>
+        </is>
+      </c>
+      <c r="H88" s="8">
+        <f>E88*characterization!$D$17 + F88*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I88" s="8">
+        <f>E88*characterization!$G$17 + F88*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J88" s="8">
+        <f>E88*characterization!$J$17 + F88*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>sched_req_addr[N-1:0][63:0]</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>arbiter granted addr</t>
+        </is>
+      </c>
+      <c r="H89" s="8">
+        <f>E89*characterization!$D$17 + F89*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I89" s="8">
+        <f>E89*characterization!$G$17 + F89*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J89" s="8">
+        <f>E89*characterization!$J$17 + F89*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>sram_rd_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>drain ready cmp</t>
+        </is>
+      </c>
+      <c r="H90" s="8">
+        <f>E90*characterization!$D$17 + F90*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I90" s="8">
+        <f>E90*characterization!$G$17 + F90*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J90" s="8">
+        <f>E90*characterization!$J$17 + F90*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N] (data ready)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>sram_rd_data[N-1:0][DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>per-ch read mux</t>
+        </is>
+      </c>
+      <c r="H91" s="8">
+        <f>E91*characterization!$D$17 + F91*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I91" s="8">
+        <f>E91*characterization!$G$17 + F91*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J91" s="8">
+        <f>E91*characterization!$J$17 + F91*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sram_drain_req[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>drain reservation gen</t>
+        </is>
+      </c>
+      <c r="H92" s="8">
+        <f>E92*characterization!$D$17 + F92*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I92" s="8">
+        <f>E92*characterization!$G$17 + F92*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J92" s="8">
+        <f>E92*characterization!$J$17 + F92*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>m_axi_aw_*</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid (AW side)</t>
+        </is>
+      </c>
+      <c r="H93" s="8">
+        <f>E93*characterization!$D$17 + F93*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I93" s="8">
+        <f>E93*characterization!$G$17 + F93*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J93" s="8">
+        <f>E93*characterization!$J$17 + F93*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>to AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>m_axi_w_*</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid (W side)</t>
+        </is>
+      </c>
+      <c r="H94" s="8">
+        <f>E94*characterization!$D$17 + F94*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I94" s="8">
+        <f>E94*characterization!$G$17 + F94*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J94" s="8">
+        <f>E94*characterization!$J$17 + F94*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>to AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>m_axi_b_*</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid (B side)</t>
+        </is>
+      </c>
+      <c r="H95" s="8">
+        <f>E95*characterization!$D$17 + F95*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I95" s="8">
+        <f>E95*characterization!$G$17 + F95*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J95" s="8">
+        <f>E95*characterization!$J$17 + F95*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>from AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>u_b_phase_txn_fifo wr</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>b-phase txn capture</t>
+        </is>
+      </c>
+      <c r="H96" s="8">
+        <f>E96*characterization!$D$17 + F96*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I96" s="8">
+        <f>E96*characterization!$G$17 + F96*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J96" s="8">
+        <f>E96*characterization!$J$17 + F96*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>B-phase awaiting response</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>u_w_phase_txn_fifo wr</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>w-phase txn capture</t>
+        </is>
+      </c>
+      <c r="H97" s="8">
+        <f>E97*characterization!$D$17 + F97*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I97" s="8">
+        <f>E97*characterization!$G$17 + F97*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J97" s="8">
+        <f>E97*characterization!$J$17 + F97*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>W-phase awaiting last-beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>One row per port (or significant internal handshake) per FUB. Hand-walked from the RTL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MUX lv / NAND lv = combinational gate-equivalents on the path within this FUB only - between the port and its nearest flop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>When a port enters/exits a building block (gaxi_fifo_sync, gaxi_skid_buffer), the BB internal cost is captured on the 'building blocks' sheet - no double-counting here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>'places it goes' lists the concrete consumer/producer in the wider STREAM hierarchy (stream_core / scheduler_group / APB CSR / system AXI bus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AXI bus signals (m_axi_ar_*, m_axi_r_*, m_axi_aw_*, m_axi_w_*, m_axi_b_*) are summarized as channel groups for brevity; each is a set of skid buffer outputs whose detailed cost is in the building blocks 'gaxi_skid_buffer' / 'axi4_master_rd/wr' rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A16:J16"/>
+  <mergeCells count="16">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A100:K100"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A87:K87"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A104:K104"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="A103:K103"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -64,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,13 +113,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1498,7 +1498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1524,7 +1524,9 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="60" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
+    <col width="60" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1645,99 +1647,55 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>delay_in TT (ps)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>delay_out TT (ps)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>CONFIG -&gt; target period (ps):</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>30% default delay_in (ps):</t>
+        </is>
+      </c>
+      <c r="D2" s="7">
+        <f>B2*0.3</f>
+        <v/>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  delay_in defaults to 0.3*period (external). Overwrite a cell with =Y_prev to chain from the previous block's delay_out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>SRAMs</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>SRAM (raw macro)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>512</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>P1=W, P2=D</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <f>4*B3 + 8*CEILING(LOG(C3,2),1)</f>
-        <v/>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8">
-        <f>K3*characterization!$D$17 + L3*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="N3" s="8">
-        <f>K3*characterization!$G$17 + L3*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="O3" s="8">
-        <f>K3*characterization!$J$17 + L3*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="8">
-        <f>P3*characterization!$D$17 + Q3*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="S3" s="8">
-        <f>P3*characterization!$G$17 + Q3*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="T3" s="8">
-        <f>P3*characterization!$J$17 + Q3*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="U3" s="8">
-        <f>ROUND(1000000/(MAX(M3,R3) + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="V3" s="8">
-        <f>ROUND(1000000/(MAX(N3,S3) + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="W3" s="8">
-        <f>ROUND(1000000/(MAX(O3,T3) + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>SRAM macro (single-port, synchronous read). Storage = W*D bits goes to the macro, not flop count. Read latency = 1 cycle (data appears next clock). Replace this row's per-bit delay with vendor SRAM datasheet for accurate timing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync (REG=1, SRAM-backed)</t>
+          <t>SRAM (raw macro)</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -1751,12 +1709,11 @@
           <t>P1=W, P2=D</t>
         </is>
       </c>
-      <c r="I4">
-        <f>3*CEILING(LOG(C4,2),1) + 1</f>
-        <v/>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
       <c r="J4">
-        <f>B4*4 + CEILING(LOG(C4,2),1)*8 + 20</f>
+        <f>4*B4 + 8*CEILING(LOG(C4,2),1)</f>
         <v/>
       </c>
       <c r="K4" t="n">
@@ -1765,15 +1722,15 @@
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7">
         <f>K4*characterization!$D$17 + L4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="7">
         <f>K4*characterization!$G$17 + L4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="7">
         <f>K4*characterization!$J$17 + L4*characterization!$J$15</f>
         <v/>
       </c>
@@ -1783,126 +1740,142 @@
       <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="7">
         <f>P4*characterization!$D$17 + Q4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S4" s="8">
+      <c r="S4" s="7">
         <f>P4*characterization!$G$17 + Q4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T4" s="8">
+      <c r="T4" s="7">
         <f>P4*characterization!$J$17 + Q4*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U4" s="8">
+      <c r="U4" s="7">
         <f>ROUND(1000000/(MAX(M4,R4) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V4" s="8">
+      <c r="V4" s="7">
         <f>ROUND(1000000/(MAX(N4,S4) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W4" s="8">
+      <c r="W4" s="7">
         <f>ROUND(1000000/(MAX(O4,T4) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y4" s="7">
+        <f>X4 + M4 + R4</f>
+        <v/>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>SRAM macro (single-port, synchronous read). Storage = W*D bits goes to the macro, not flop count. Read latency = 1 cycle (data appears next clock). Replace this row's per-bit delay with vendor SRAM datasheet for accurate timing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync (REG=1, SRAM-backed)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>512</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>512</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>P1=W, P2=D</t>
+        </is>
+      </c>
+      <c r="I5">
+        <f>3*CEILING(LOG(C5,2),1) + 1</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>B5*4 + CEILING(LOG(C5,2),1)*8 + 20</f>
+        <v/>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="7">
+        <f>K5*characterization!$D$17 + L5*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N5" s="7">
+        <f>K5*characterization!$G$17 + L5*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O5" s="7">
+        <f>K5*characterization!$J$17 + L5*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="7">
+        <f>P5*characterization!$D$17 + Q5*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S5" s="7">
+        <f>P5*characterization!$G$17 + Q5*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T5" s="7">
+        <f>P5*characterization!$J$17 + Q5*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U5" s="7">
+        <f>ROUND(1000000/(MAX(M5,R5) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V5" s="7">
+        <f>ROUND(1000000/(MAX(N5,S5) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W5" s="7">
+        <f>ROUND(1000000/(MAX(O5,T5) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X5" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y5" s="7">
+        <f>X5 + M5 + R5</f>
+        <v/>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>REGISTERED=1 + MEM_STYLE=BRAM: storage is in an SRAM/BRAM macro, not flops. Used only by SRAM controller units in STREAM/RAPIDS. Storage bits = W*D. fmax is limited by the SRAM macro clock-to-Q, not by std-cell timing.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Building Blocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>P1=W, P2=D</t>
-        </is>
-      </c>
-      <c r="I6">
-        <f>B6*C6 + C6 + 2</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>B6*C6*4 + 10</f>
-        <v/>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" s="8">
-        <f>K6*characterization!$D$17 + L6*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="N6" s="8">
-        <f>K6*characterization!$G$17 + L6*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="O6" s="8">
-        <f>K6*characterization!$J$17 + L6*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="8">
-        <f>P6*characterization!$D$17 + Q6*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="S6" s="8">
-        <f>P6*characterization!$G$17 + Q6*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="T6" s="8">
-        <f>P6*characterization!$J$17 + Q6*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="U6" s="8">
-        <f>ROUND(1000000/(MAX(M6,R6) + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="V6" s="8">
-        <f>ROUND(1000000/(MAX(N6,S6) + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="W6" s="8">
-        <f>ROUND(1000000/(MAX(O6,T6) + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Skid buffer outputs come straight from the head flop Q - no output muxing. Input side has the bypass MUX2. Flops = W*D storage + D valid + 2 control.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync (REG=0)</t>
+          <t>gaxi_skid_buffer</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -1917,240 +1890,252 @@
         </is>
       </c>
       <c r="I7">
-        <f>B7*C7 + 3*CEILING(LOG(C7,2),1) + 1</f>
+        <f>B7*C7 + C7 + 2</f>
         <v/>
       </c>
       <c r="J7">
-        <f>B7*C7*6 + CEILING(LOG(C7,2),1)*8 + 20</f>
+        <f>B7*C7*4 + 10</f>
         <v/>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="7">
         <f>K7*characterization!$D$17 + L7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="7">
         <f>K7*characterization!$G$17 + L7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="7">
         <f>K7*characterization!$J$17 + L7*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="P7">
-        <f>CEILING(LOG(C7,2),1)</f>
-        <v/>
+      <c r="P7" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="7">
         <f>P7*characterization!$D$17 + Q7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S7" s="8">
+      <c r="S7" s="7">
         <f>P7*characterization!$G$17 + Q7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="7">
         <f>P7*characterization!$J$17 + Q7*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U7" s="8">
+      <c r="U7" s="7">
         <f>ROUND(1000000/(MAX(M7,R7) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V7" s="8">
+      <c r="V7" s="7">
         <f>ROUND(1000000/(MAX(N7,S7) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W7" s="8">
+      <c r="W7" s="7">
         <f>ROUND(1000000/(MAX(O7,T7) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Output critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state. Default FIFO in STREAM/RAPIDS (non-SRAM-backed).</t>
+      <c r="X7" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y7" s="7">
+        <f>X7 + M7 + R7</f>
+        <v/>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Skid buffer outputs come straight from the head flop Q - no output muxing. Input side has the bypass MUX2. Flops = W*D storage + D valid + 2 control.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>arbiter_round_robin</t>
+          <t>gaxi_fifo_sync (REG=0)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P1=N</t>
+          <t>P1=W, P2=D</t>
         </is>
       </c>
       <c r="I8">
-        <f>B8 + 2</f>
+        <f>B8*C8 + 3*CEILING(LOG(C8,2),1) + 1</f>
         <v/>
       </c>
       <c r="J8">
-        <f>B8*8</f>
+        <f>B8*C8*6 + CEILING(LOG(C8,2),1)*8 + 20</f>
         <v/>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="8">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7">
         <f>K8*characterization!$D$17 + L8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <f>K8*characterization!$G$17 + L8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <f>K8*characterization!$J$17 + L8*characterization!$J$15</f>
         <v/>
       </c>
       <c r="P8">
-        <f>CEILING(LOG(B8,2),1)</f>
+        <f>CEILING(LOG(C8,2),1)</f>
         <v/>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="7">
         <f>P8*characterization!$D$17 + Q8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S8" s="8">
+      <c r="S8" s="7">
         <f>P8*characterization!$G$17 + Q8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T8" s="8">
+      <c r="T8" s="7">
         <f>P8*characterization!$J$17 + Q8*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U8" s="8">
+      <c r="U8" s="7">
         <f>ROUND(1000000/(MAX(M8,R8) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V8" s="8">
+      <c r="V8" s="7">
         <f>ROUND(1000000/(MAX(N8,S8) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W8" s="8">
+      <c r="W8" s="7">
         <f>ROUND(1000000/(MAX(O8,T8) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Priority encoder is log2(N) MUX levels on the OUTPUT side (req -&gt; encode -&gt; gnt). Flops = N (last-grant tracker) + 2.</t>
+      <c r="X8" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y8" s="7">
+        <f>X8 + M8 + R8</f>
+        <v/>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Output critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state. Default FIFO in STREAM/RAPIDS (non-SRAM-backed).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>axi4_master_rd</t>
+          <t>arbiter_round_robin</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AR, P6=SKID_R</t>
+          <t>P1=N</t>
         </is>
       </c>
       <c r="I9">
-        <f>F9*(B9+D9+E9+29) + G9*(D9+C9+E9+3)</f>
+        <f>B9 + 2</f>
         <v/>
       </c>
       <c r="J9">
-        <f>4*(F9*(B9+D9+E9+29) + G9*(D9+C9+E9+3))</f>
+        <f>B9*8</f>
         <v/>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="7">
         <f>K9*characterization!$D$17 + L9*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="7">
         <f>K9*characterization!$G$17 + L9*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="7">
         <f>K9*characterization!$J$17 + L9*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="P9" t="n">
-        <v>1</v>
+      <c r="P9">
+        <f>CEILING(LOG(B9,2),1)</f>
+        <v/>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="7">
         <f>P9*characterization!$D$17 + Q9*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S9" s="8">
+      <c r="S9" s="7">
         <f>P9*characterization!$G$17 + Q9*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T9" s="8">
+      <c r="T9" s="7">
         <f>P9*characterization!$J$17 + Q9*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U9" s="8">
+      <c r="U9" s="7">
         <f>ROUND(1000000/(MAX(M9,R9) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="7">
         <f>ROUND(1000000/(MAX(N9,S9) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W9" s="8">
+      <c r="W9" s="7">
         <f>ROUND(1000000/(MAX(O9,T9) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Two skid buffers in series (AR + R). Input bypass MUX2 + output select MUX2. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
+      <c r="X9" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y9" s="7">
+        <f>X9 + M9 + R9</f>
+        <v/>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Priority encoder is log2(N) MUX levels on the OUTPUT side (req -&gt; encode -&gt; gnt). Flops = N (last-grant tracker) + 2.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>axi4_master_wr</t>
+          <t>axi4_master_rd</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -2173,107 +2158,189 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AR, P6=SKID_R</t>
+        </is>
+      </c>
+      <c r="I10">
+        <f>F10*(B10+D10+E10+29) + G10*(D10+C10+E10+3)</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>4*(F10*(B10+D10+E10+29) + G10*(D10+C10+E10+3))</f>
+        <v/>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="7">
+        <f>K10*characterization!$D$17 + L10*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N10" s="7">
+        <f>K10*characterization!$G$17 + L10*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O10" s="7">
+        <f>K10*characterization!$J$17 + L10*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="7">
+        <f>P10*characterization!$D$17 + Q10*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S10" s="7">
+        <f>P10*characterization!$G$17 + Q10*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T10" s="7">
+        <f>P10*characterization!$J$17 + Q10*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U10" s="7">
+        <f>ROUND(1000000/(MAX(M10,R10) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V10" s="7">
+        <f>ROUND(1000000/(MAX(N10,S10) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W10" s="7">
+        <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X10" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y10" s="7">
+        <f>X10 + M10 + R10</f>
+        <v/>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Two skid buffers in series (AR + R). Input bypass MUX2 + output select MUX2. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>axi4_master_wr</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>P1=AW, P2=DW, P3=IW, P4=UW, P5=SKID_AW, P6=SKID_W</t>
         </is>
       </c>
-      <c r="I10">
-        <f>F10*(B10+D10+E10+29) + G10*(C10+C10/8+E10+1) + 2*(D10+E10+2)</f>
-        <v/>
-      </c>
-      <c r="J10">
-        <f>4*(F10*(B10+D10+E10+29) + G10*(C10+C10/8+E10+1) + 2*(D10+E10+2))</f>
-        <v/>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="8">
-        <f>K10*characterization!$D$17 + L10*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="N10" s="8">
-        <f>K10*characterization!$G$17 + L10*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="O10" s="8">
-        <f>K10*characterization!$J$17 + L10*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" s="8">
-        <f>P10*characterization!$D$17 + Q10*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="S10" s="8">
-        <f>P10*characterization!$G$17 + Q10*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="T10" s="8">
-        <f>P10*characterization!$J$17 + Q10*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="U10" s="8">
-        <f>ROUND(1000000/(MAX(M10,R10) + characterization!$D$3), 0)</f>
-        <v/>
-      </c>
-      <c r="V10" s="8">
-        <f>ROUND(1000000/(MAX(N10,S10) + characterization!$G$3), 0)</f>
-        <v/>
-      </c>
-      <c r="W10" s="8">
-        <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
-        <v/>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="I11">
+        <f>F11*(B11+D11+E11+29) + G11*(C11+C11/8+E11+1) + 2*(D11+E11+2)</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>4*(F11*(B11+D11+E11+29) + G11*(C11+C11/8+E11+1) + 2*(D11+E11+2))</f>
+        <v/>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="7">
+        <f>K11*characterization!$D$17 + L11*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="N11" s="7">
+        <f>K11*characterization!$G$17 + L11*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="O11" s="7">
+        <f>K11*characterization!$J$17 + L11*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="7">
+        <f>P11*characterization!$D$17 + Q11*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="S11" s="7">
+        <f>P11*characterization!$G$17 + Q11*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="T11" s="7">
+        <f>P11*characterization!$J$17 + Q11*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="U11" s="7">
+        <f>ROUND(1000000/(MAX(M11,R11) + characterization!$D$3), 0)</f>
+        <v/>
+      </c>
+      <c r="V11" s="7">
+        <f>ROUND(1000000/(MAX(N11,S11) + characterization!$G$3), 0)</f>
+        <v/>
+      </c>
+      <c r="W11" s="7">
+        <f>ROUND(1000000/(MAX(O11,T11) + characterization!$J$3), 0)</f>
+        <v/>
+      </c>
+      <c r="X11" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="Y11" s="7">
+        <f>X11 + M11 + R11</f>
+        <v/>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Three skid buffers (AW + W + B); SKID_B fixed at 2 in this row. Input bypass + output select MUXes; both are 1 level.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>SRAM storage size reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SRAM raw macro: storage bits = W * D = </t>
-        </is>
-      </c>
-      <c r="D13">
-        <f>B3*C3</f>
-        <v/>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bits =</t>
-        </is>
-      </c>
-      <c r="F13">
-        <f>B3*C3/8/1024</f>
-        <v/>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KB</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIFO REG=1 SRAM-backed: storage bits = W * D = </t>
+          <t xml:space="preserve">SRAM raw macro: storage bits = W * D = </t>
         </is>
       </c>
       <c r="D14">
@@ -2295,52 +2362,77 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIFO REG=1 SRAM-backed: storage bits = W * D = </t>
+        </is>
+      </c>
+      <c r="D15">
+        <f>B5*C5</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>bits =</t>
+        </is>
+      </c>
+      <c r="F15">
+        <f>B5*C5/8/1024</f>
+        <v/>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Cell coding</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Yellow = editable param</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Grey = derived formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>data-&gt;D = critical combinational delay on the path that loads the downstream flop. Compare against (period - Tflop) to size for a freq.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Estimates are first-order: structural flop/gate counts + characterization per-level delays. Treat them as design-time SWAGs, not post-synth truth.</t>
+          <t>data-&gt;D = critical combinational delay on the path that loads the downstream flop. Compare against (period - Tflop) to size for a freq.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Estimates are first-order: structural flop/gate counts + characterization per-level delays. Treat them as design-time SWAGs, not post-synth truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>REG=1 SRAM-backed FIFO is only used by SRAM controller units in STREAM/RAPIDS (sram_controller_unit, src/snk_sram_controller_unit_beats). Everywhere else uses REG=0 - that's why the Building Blocks section lists only the REG=0 variant.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="A5:X5"/>
+    <mergeCell ref="A3:Z3"/>
+    <mergeCell ref="A6:Z6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2352,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:M105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2457,9 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2421,60 +2515,48 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>delay_in TT (ps)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>delay_out TT (ps)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>places it goes (consumer / producer)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>CONFIG -&gt; target period (ps):</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>30% default delay_in (ps):</t>
+        </is>
+      </c>
+      <c r="D2" s="7">
+        <f>B2*0.3</f>
+        <v/>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  delay_in defaults to 0.3*period; chain by setting delay_in = =L_prev_row from the previous block's delay_out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>stream_latency_bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>stream_latency_bridge</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>s_valid</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>r_drain_ip flop D</t>
-        </is>
-      </c>
-      <c r="H3" s="8">
-        <f>E3*characterization!$D$17 + F3*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I3" s="8">
-        <f>E3*characterization!$G$17 + F3*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J3" s="8">
-        <f>E3*characterization!$J$17 + F3*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>from u_channel_fifo.rd_valid in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2568,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>s_data[DW-1:0]</t>
+          <t>s_valid</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2494,37 +2576,41 @@
           <t>in</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>u_skid_buffer.wr_data</t>
-        </is>
-      </c>
-      <c r="H4" s="8">
+          <t>r_drain_ip flop D</t>
+        </is>
+      </c>
+      <c r="H4" s="7">
         <f>E4*characterization!$D$17 + F4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <f>E4*characterization!$G$17 + F4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <f>E4*characterization!$J$17 + F4*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>from u_channel_fifo.rd_data</t>
+      <c r="K4" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L4" s="7">
+        <f>K4 + H4</f>
+        <v/>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo.rd_valid in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -2536,41 +2622,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>s_ready</t>
+          <t>s_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>comb of skid count + drain</t>
-        </is>
-      </c>
-      <c r="H5" s="8">
+          <t>u_skid_buffer.wr_data</t>
+        </is>
+      </c>
+      <c r="H5" s="7">
         <f>E5*characterization!$D$17 + F5*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <f>E5*characterization!$G$17 + F5*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <f>E5*characterization!$J$17 + F5*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>to u_channel_fifo.rd_ready</t>
+      <c r="K5" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L5" s="7">
+        <f>K5 + H5</f>
+        <v/>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo.rd_data</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2680,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>m_valid</t>
+          <t>s_ready</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2590,37 +2688,41 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_valid</t>
-        </is>
-      </c>
-      <c r="H6" s="8">
+          <t>comb of skid count + drain</t>
+        </is>
+      </c>
+      <c r="H6" s="7">
         <f>E6*characterization!$D$17 + F6*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>E6*characterization!$G$17 + F6*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>E6*characterization!$J$17 + F6*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>to axi_write_engine.sram_rd_valid</t>
+      <c r="K6" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L6" s="7">
+        <f>K6 + H6</f>
+        <v/>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>to u_channel_fifo.rd_ready</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2734,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>m_data[DW-1:0]</t>
+          <t>m_valid</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2653,24 +2755,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_data</t>
-        </is>
-      </c>
-      <c r="H7" s="8">
+          <t>u_skid_buffer.rd_valid</t>
+        </is>
+      </c>
+      <c r="H7" s="7">
         <f>E7*characterization!$D$17 + F7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <f>E7*characterization!$G$17 + F7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="7">
         <f>E7*characterization!$J$17 + F7*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>to axi_write_engine.sram_rd_data</t>
+      <c r="K7" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L7" s="7">
+        <f>K7 + H7</f>
+        <v/>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>to axi_write_engine.sram_rd_valid</t>
         </is>
       </c>
     </row>
@@ -2682,12 +2792,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>m_ready</t>
+          <t>m_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2703,24 +2813,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_ready</t>
-        </is>
-      </c>
-      <c r="H8" s="8">
+          <t>u_skid_buffer.rd_data</t>
+        </is>
+      </c>
+      <c r="H8" s="7">
         <f>E8*characterization!$D$17 + F8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <f>E8*characterization!$G$17 + F8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <f>E8*characterization!$J$17 + F8*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>from axi_write_engine.sram_rd_ready</t>
+      <c r="K8" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>K8 + H8</f>
+        <v/>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>to axi_write_engine.sram_rd_data</t>
         </is>
       </c>
     </row>
@@ -2732,98 +2850,118 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>m_ready</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.rd_ready</t>
+        </is>
+      </c>
+      <c r="H9" s="7">
+        <f>E9*characterization!$D$17 + F9*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I9" s="7">
+        <f>E9*characterization!$G$17 + F9*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J9" s="7">
+        <f>E9*characterization!$J$17 + F9*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K9" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L9" s="7">
+        <f>K9 + H9</f>
+        <v/>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>from axi_write_engine.sram_rd_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>occupancy[2:0]</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>u_skid_buffer.count</t>
         </is>
       </c>
-      <c r="H9" s="8">
-        <f>E9*characterization!$D$17 + F9*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I9" s="8">
-        <f>E9*characterization!$G$17 + F9*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J9" s="8">
-        <f>E9*characterization!$J$17 + F9*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="H10" s="7">
+        <f>E10*characterization!$D$17 + F10*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I10" s="7">
+        <f>E10*characterization!$G$17 + F10*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J10" s="7">
+        <f>E10*characterization!$J$17 + F10*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K10" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L10" s="7">
+        <f>K10 + H10</f>
+        <v/>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>to scheduler (drain-IP backpressure)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>stream_alloc_ctrl</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>stream_alloc_ctrl</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wr_valid</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>r_wr_ptr flop D (+wr_size)</t>
-        </is>
-      </c>
-      <c r="H11" s="8">
-        <f>E11*characterization!$D$17 + F11*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I11" s="8">
-        <f>E11*characterization!$G$17 + F11*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J11" s="8">
-        <f>E11*characterization!$J$17 + F11*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>from axi_read_engine (allocate request)</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2973,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wr_size[7:0]</t>
+          <t>wr_valid</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2852,24 +2990,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>r_wr_ptr adder input</t>
-        </is>
-      </c>
-      <c r="H12" s="8">
+          <t>r_wr_ptr flop D (+wr_size)</t>
+        </is>
+      </c>
+      <c r="H12" s="7">
         <f>E12*characterization!$D$17 + F12*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <f>E12*characterization!$G$17 + F12*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="7">
         <f>E12*characterization!$J$17 + F12*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>from axi_read_engine</t>
+      <c r="K12" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L12" s="7">
+        <f>K12 + H12</f>
+        <v/>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (allocate request)</t>
         </is>
       </c>
     </row>
@@ -2881,7 +3027,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rd_valid</t>
+          <t>wr_size[7:0]</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2898,24 +3044,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>r_rd_ptr flop D</t>
-        </is>
-      </c>
-      <c r="H13" s="8">
+          <t>r_wr_ptr adder input</t>
+        </is>
+      </c>
+      <c r="H13" s="7">
         <f>E13*characterization!$D$17 + F13*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <f>E13*characterization!$G$17 + F13*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="7">
         <f>E13*characterization!$J$17 + F13*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>from sram_controller_unit (release event)</t>
+      <c r="K13" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L13" s="7">
+        <f>K13 + H13</f>
+        <v/>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -2927,12 +3081,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>space_free[AW:0]</t>
+          <t>rd_valid</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2940,28 +3094,36 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>r_space_free (registered)</t>
-        </is>
-      </c>
-      <c r="H14" s="8">
+          <t>r_rd_ptr flop D</t>
+        </is>
+      </c>
+      <c r="H14" s="7">
         <f>E14*characterization!$D$17 + F14*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <f>E14*characterization!$G$17 + F14*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="7">
         <f>E14*characterization!$J$17 + F14*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>to axi_read_engine (sram_alloc_space_free)</t>
+      <c r="K14" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L14" s="7">
+        <f>K14 + H14</f>
+        <v/>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit (release event)</t>
         </is>
       </c>
     </row>
@@ -2973,7 +3135,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wr_full</t>
+          <t>space_free[AW:0]</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2986,28 +3148,36 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>comb of r_space_free</t>
-        </is>
-      </c>
-      <c r="H15" s="8">
+          <t>r_space_free (registered)</t>
+        </is>
+      </c>
+      <c r="H15" s="7">
         <f>E15*characterization!$D$17 + F15*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <f>E15*characterization!$G$17 + F15*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <f>E15*characterization!$J$17 + F15*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>to axi_read_engine (back-pressure)</t>
+      <c r="K15" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L15" s="7">
+        <f>K15 + H15</f>
+        <v/>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (sram_alloc_space_free)</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3189,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wr_almost_full</t>
+          <t>wr_full</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3039,21 +3209,29 @@
           <t>comb of r_space_free</t>
         </is>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <f>E16*characterization!$D$17 + F16*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <f>E16*characterization!$G$17 + F16*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="7">
         <f>E16*characterization!$J$17 + F16*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>to axi_read_engine (threshold)</t>
+      <c r="K16" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L16" s="7">
+        <f>K16 + H16</f>
+        <v/>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (back-pressure)</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3243,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rd_empty</t>
+          <t>wr_almost_full</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3085,74 +3263,90 @@
           <t>comb of r_space_free</t>
         </is>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <f>E17*characterization!$D$17 + F17*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <f>E17*characterization!$G$17 + F17*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="7">
         <f>E17*characterization!$J$17 + F17*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L17" s="7">
+        <f>K17 + H17</f>
+        <v/>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (threshold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rd_empty</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>comb of r_space_free</t>
+        </is>
+      </c>
+      <c r="H18" s="7">
+        <f>E18*characterization!$D$17 + F18*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I18" s="7">
+        <f>E18*characterization!$G$17 + F18*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J18" s="7">
+        <f>E18*characterization!$J$17 + F18*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K18" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L18" s="7">
+        <f>K18 + H18</f>
+        <v/>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>unused (debug)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>stream_drain_ctrl</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>stream_drain_ctrl</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>wr_valid</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>r_wr_ptr flop D</t>
-        </is>
-      </c>
-      <c r="H19" s="8">
-        <f>E19*characterization!$D$17 + F19*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I19" s="8">
-        <f>E19*characterization!$G$17 + F19*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J19" s="8">
-        <f>E19*characterization!$J$17 + F19*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>from u_channel_fifo handshake in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3358,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rd_valid</t>
+          <t>wr_valid</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3181,24 +3375,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>r_rd_ptr flop D (+rd_size)</t>
-        </is>
-      </c>
-      <c r="H20" s="8">
+          <t>r_wr_ptr flop D</t>
+        </is>
+      </c>
+      <c r="H20" s="7">
         <f>E20*characterization!$D$17 + F20*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <f>E20*characterization!$G$17 + F20*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="7">
         <f>E20*characterization!$J$17 + F20*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>from axi_write_engine (drain reservation)</t>
+      <c r="K20" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L20" s="7">
+        <f>K20 + H20</f>
+        <v/>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>from u_channel_fifo handshake in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3412,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rd_size[7:0]</t>
+          <t>rd_valid</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3227,24 +3429,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>r_rd_ptr adder input</t>
-        </is>
-      </c>
-      <c r="H21" s="8">
+          <t>r_rd_ptr flop D (+rd_size)</t>
+        </is>
+      </c>
+      <c r="H21" s="7">
         <f>E21*characterization!$D$17 + F21*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="7">
         <f>E21*characterization!$G$17 + F21*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="7">
         <f>E21*characterization!$J$17 + F21*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>from axi_write_engine</t>
+      <c r="K21" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L21" s="7">
+        <f>K21 + H21</f>
+        <v/>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>from axi_write_engine (drain reservation)</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3466,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>data_available[AW:0]</t>
+          <t>rd_size[7:0]</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3269,28 +3479,36 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>r_data_available (registered)</t>
-        </is>
-      </c>
-      <c r="H22" s="8">
+          <t>r_rd_ptr adder input</t>
+        </is>
+      </c>
+      <c r="H22" s="7">
         <f>E22*characterization!$D$17 + F22*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <f>E22*characterization!$G$17 + F22*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="7">
         <f>E22*characterization!$J$17 + F22*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
+      <c r="K22" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L22" s="7">
+        <f>K22 + H22</f>
+        <v/>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3520,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rd_empty</t>
+          <t>data_available[AW:0]</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3315,28 +3533,36 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>comb of r_data_available</t>
-        </is>
-      </c>
-      <c r="H23" s="8">
+          <t>r_data_available (registered)</t>
+        </is>
+      </c>
+      <c r="H23" s="7">
         <f>E23*characterization!$D$17 + F23*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="7">
         <f>E23*characterization!$G$17 + F23*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="7">
         <f>E23*characterization!$J$17 + F23*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>to axi_write_engine (no data)</t>
+      <c r="K23" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L23" s="7">
+        <f>K23 + H23</f>
+        <v/>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3574,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wr_full</t>
+          <t>rd_empty</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3368,74 +3594,90 @@
           <t>comb of r_data_available</t>
         </is>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <f>E24*characterization!$D$17 + F24*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="7">
         <f>E24*characterization!$G$17 + F24*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="7">
         <f>E24*characterization!$J$17 + F24*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L24" s="7">
+        <f>K24 + H24</f>
+        <v/>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>to axi_write_engine (no data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wr_full</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>comb of r_data_available</t>
+        </is>
+      </c>
+      <c r="H25" s="7">
+        <f>E25*characterization!$D$17 + F25*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I25" s="7">
+        <f>E25*characterization!$G$17 + F25*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J25" s="7">
+        <f>E25*characterization!$J$17 + F25*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K25" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L25" s="7">
+        <f>K25 + H25</f>
+        <v/>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>to sram_controller_unit (back-pressure)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>sram_controller_unit</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sram_controller_unit</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>axi_rd_alloc_req</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>alloc_ctrl.wr_valid</t>
-        </is>
-      </c>
-      <c r="H26" s="8">
-        <f>E26*characterization!$D$17 + F26*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I26" s="8">
-        <f>E26*characterization!$G$17 + F26*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J26" s="8">
-        <f>E26*characterization!$J$17 + F26*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>from axi_read_engine (reserve burst space)</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3689,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>axi_rd_alloc_size[7:0]</t>
+          <t>axi_rd_alloc_req</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3460,28 +3702,36 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>alloc_ctrl.wr_size</t>
-        </is>
-      </c>
-      <c r="H27" s="8">
+          <t>alloc_ctrl.wr_valid</t>
+        </is>
+      </c>
+      <c r="H27" s="7">
         <f>E27*characterization!$D$17 + F27*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="7">
         <f>E27*characterization!$G$17 + F27*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="7">
         <f>E27*characterization!$J$17 + F27*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>from axi_read_engine</t>
+      <c r="K27" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L27" s="7">
+        <f>K27 + H27</f>
+        <v/>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (reserve burst space)</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3743,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>axi_rd_alloc_space_free[AW:0]</t>
+          <t>axi_rd_alloc_size[7:0]</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3510,24 +3760,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>alloc_ctrl.space_free</t>
-        </is>
-      </c>
-      <c r="H28" s="8">
+          <t>alloc_ctrl.wr_size</t>
+        </is>
+      </c>
+      <c r="H28" s="7">
         <f>E28*characterization!$D$17 + F28*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="7">
         <f>E28*characterization!$G$17 + F28*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="7">
         <f>E28*characterization!$J$17 + F28*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>to axi_read_engine</t>
+      <c r="K28" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L28" s="7">
+        <f>K28 + H28</f>
+        <v/>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3539,19 +3797,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>axi_rd_sram_valid</t>
+          <t>axi_rd_alloc_space_free[AW:0]</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" s="5" t="n">
         <v>0</v>
       </c>
@@ -3560,24 +3814,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_valid</t>
-        </is>
-      </c>
-      <c r="H29" s="8">
+          <t>alloc_ctrl.space_free</t>
+        </is>
+      </c>
+      <c r="H29" s="7">
         <f>E29*characterization!$D$17 + F29*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="7">
         <f>E29*characterization!$G$17 + F29*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="7">
         <f>E29*characterization!$J$17 + F29*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>from axi_read_engine (write data into SRAM FIFO)</t>
+      <c r="K29" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L29" s="7">
+        <f>K29 + H29</f>
+        <v/>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3851,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>axi_rd_sram_data[DW-1:0]</t>
+          <t>axi_rd_sram_valid</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3610,24 +3872,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_data</t>
-        </is>
-      </c>
-      <c r="H30" s="8">
+          <t>u_channel_fifo.wr_valid</t>
+        </is>
+      </c>
+      <c r="H30" s="7">
         <f>E30*characterization!$D$17 + F30*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="7">
         <f>E30*characterization!$G$17 + F30*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="7">
         <f>E30*characterization!$J$17 + F30*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>from axi_read_engine</t>
+      <c r="K30" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L30" s="7">
+        <f>K30 + H30</f>
+        <v/>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (write data into SRAM FIFO)</t>
         </is>
       </c>
     </row>
@@ -3639,12 +3909,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>axi_rd_sram_ready</t>
+          <t>axi_rd_sram_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3660,24 +3930,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_ready</t>
-        </is>
-      </c>
-      <c r="H31" s="8">
+          <t>u_channel_fifo.wr_data</t>
+        </is>
+      </c>
+      <c r="H31" s="7">
         <f>E31*characterization!$D$17 + F31*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="7">
         <f>E31*characterization!$G$17 + F31*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="7">
         <f>E31*characterization!$J$17 + F31*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>to axi_read_engine</t>
+      <c r="K31" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L31" s="7">
+        <f>K31 + H31</f>
+        <v/>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3967,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>axi_wr_sram_valid</t>
+          <t>axi_rd_sram_ready</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3710,24 +3988,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>u_latency_bridge.m_valid</t>
-        </is>
-      </c>
-      <c r="H32" s="8">
+          <t>u_channel_fifo.wr_ready</t>
+        </is>
+      </c>
+      <c r="H32" s="7">
         <f>E32*characterization!$D$17 + F32*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="7">
         <f>E32*characterization!$G$17 + F32*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="7">
         <f>E32*characterization!$J$17 + F32*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
+      <c r="K32" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L32" s="7">
+        <f>K32 + H32</f>
+        <v/>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3739,7 +4025,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>axi_wr_sram_data[DW-1:0]</t>
+          <t>axi_wr_sram_valid</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3760,22 +4046,30 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>u_latency_bridge.m_data</t>
-        </is>
-      </c>
-      <c r="H33" s="8">
+          <t>u_latency_bridge.m_valid</t>
+        </is>
+      </c>
+      <c r="H33" s="7">
         <f>E33*characterization!$D$17 + F33*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="7">
         <f>E33*characterization!$G$17 + F33*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="7">
         <f>E33*characterization!$J$17 + F33*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L33" s="7">
+        <f>K33 + H33</f>
+        <v/>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -3789,15 +4083,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>axi_wr_sram_ready</t>
+          <t>axi_wr_sram_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
@@ -3806,24 +4104,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>u_latency_bridge.m_ready</t>
-        </is>
-      </c>
-      <c r="H34" s="8">
+          <t>u_latency_bridge.m_data</t>
+        </is>
+      </c>
+      <c r="H34" s="7">
         <f>E34*characterization!$D$17 + F34*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I34" s="8">
+      <c r="I34" s="7">
         <f>E34*characterization!$G$17 + F34*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="7">
         <f>E34*characterization!$J$17 + F34*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>from axi_write_engine</t>
+      <c r="K34" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L34" s="7">
+        <f>K34 + H34</f>
+        <v/>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -3835,7 +4141,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wr_drain_req</t>
+          <t>axi_wr_sram_ready</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3848,81 +4154,97 @@
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>u_latency_bridge.m_ready</t>
+        </is>
+      </c>
+      <c r="H35" s="7">
+        <f>E35*characterization!$D$17 + F35*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I35" s="7">
+        <f>E35*characterization!$G$17 + F35*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J35" s="7">
+        <f>E35*characterization!$J$17 + F35*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K35" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L35" s="7">
+        <f>K35 + H35</f>
+        <v/>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wr_drain_req</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>drain_ctrl.rd_valid</t>
         </is>
       </c>
-      <c r="H35" s="8">
-        <f>E35*characterization!$D$17 + F35*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I35" s="8">
-        <f>E35*characterization!$G$17 + F35*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J35" s="8">
-        <f>E35*characterization!$J$17 + F35*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K35" t="inlineStr">
+      <c r="H36" s="7">
+        <f>E36*characterization!$D$17 + F36*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I36" s="7">
+        <f>E36*characterization!$G$17 + F36*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J36" s="7">
+        <f>E36*characterization!$J$17 + F36*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K36" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L36" s="7">
+        <f>K36 + H36</f>
+        <v/>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>from axi_write_engine</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>sram_controller</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sram_controller</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ch_alloc_req[N-1:0]</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>per-ch sram_controller_unit</t>
-        </is>
-      </c>
-      <c r="H37" s="8">
-        <f>E37*characterization!$D$17 + F37*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I37" s="8">
-        <f>E37*characterization!$G$17 + F37*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J37" s="8">
-        <f>E37*characterization!$J$17 + F37*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>from axi_read_engine (N-channel fan-out)</t>
         </is>
       </c>
     </row>
@@ -3934,12 +4256,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ch_alloc_space_free[N-1:0][AW:0]</t>
+          <t>ch_alloc_req[N-1:0]</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3947,28 +4269,36 @@
         <v>1</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>per-ch alloc.space_free</t>
-        </is>
-      </c>
-      <c r="H38" s="8">
+          <t>per-ch sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="H38" s="7">
         <f>E38*characterization!$D$17 + F38*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I38" s="8">
+      <c r="I38" s="7">
         <f>E38*characterization!$G$17 + F38*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="7">
         <f>E38*characterization!$J$17 + F38*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>to axi_read_engine</t>
+      <c r="K38" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L38" s="7">
+        <f>K38 + H38</f>
+        <v/>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>from axi_read_engine (N-channel fan-out)</t>
         </is>
       </c>
     </row>
@@ -3980,12 +4310,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ch_rd_valid[N-1:0]</t>
+          <t>ch_alloc_space_free[N-1:0][AW:0]</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3993,28 +4323,36 @@
         <v>1</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>per-ch SRAM FIFO wr</t>
-        </is>
-      </c>
-      <c r="H39" s="8">
+          <t>per-ch alloc.space_free</t>
+        </is>
+      </c>
+      <c r="H39" s="7">
         <f>E39*characterization!$D$17 + F39*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I39" s="8">
+      <c r="I39" s="7">
         <f>E39*characterization!$G$17 + F39*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="7">
         <f>E39*characterization!$J$17 + F39*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>from axi_read_engine</t>
+      <c r="K39" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L39" s="7">
+        <f>K39 + H39</f>
+        <v/>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4364,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ch_wr_valid[N-1:0]</t>
+          <t>ch_rd_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -4039,28 +4377,36 @@
         <v>1</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>per-ch SRAM FIFO read</t>
-        </is>
-      </c>
-      <c r="H40" s="8">
+          <t>per-ch SRAM FIFO wr</t>
+        </is>
+      </c>
+      <c r="H40" s="7">
         <f>E40*characterization!$D$17 + F40*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I40" s="8">
+      <c r="I40" s="7">
         <f>E40*characterization!$G$17 + F40*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="7">
         <f>E40*characterization!$J$17 + F40*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
+      <c r="K40" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L40" s="7">
+        <f>K40 + H40</f>
+        <v/>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4418,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ch_wr_data[N-1:0][DW-1:0]</t>
+          <t>ch_wr_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4089,77 +4435,93 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>per-ch SRAM FIFO read</t>
+        </is>
+      </c>
+      <c r="H41" s="7">
+        <f>E41*characterization!$D$17 + F41*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I41" s="7">
+        <f>E41*characterization!$G$17 + F41*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J41" s="7">
+        <f>E41*characterization!$J$17 + F41*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K41" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L41" s="7">
+        <f>K41 + H41</f>
+        <v/>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ch_wr_data[N-1:0][DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>per-ch fifo rd_data</t>
         </is>
       </c>
-      <c r="H41" s="8">
-        <f>E41*characterization!$D$17 + F41*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I41" s="8">
-        <f>E41*characterization!$G$17 + F41*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J41" s="8">
-        <f>E41*characterization!$J$17 + F41*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K41" t="inlineStr">
+      <c r="H42" s="7">
+        <f>E42*characterization!$D$17 + F42*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I42" s="7">
+        <f>E42*characterization!$G$17 + F42*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J42" s="7">
+        <f>E42*characterization!$J$17 + F42*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K42" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L42" s="7">
+        <f>K42 + H42</f>
+        <v/>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>perf_profiler</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>perf_profiler</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>channel_idle[N-1:0]</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>edge-detect flops</t>
-        </is>
-      </c>
-      <c r="H43" s="8">
-        <f>E43*characterization!$D$17 + F43*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I43" s="8">
-        <f>E43*characterization!$G$17 + F43*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J43" s="8">
-        <f>E43*characterization!$J$17 + F43*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>from scheduler (per-ch idle state)</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4533,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cfg_enable</t>
+          <t>channel_idle[N-1:0]</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4181,31 +4543,39 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>control flop</t>
-        </is>
-      </c>
-      <c r="H44" s="8">
+          <t>edge-detect flops</t>
+        </is>
+      </c>
+      <c r="H44" s="7">
         <f>E44*characterization!$D$17 + F44*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I44" s="8">
+      <c r="I44" s="7">
         <f>E44*characterization!$G$17 + F44*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J44" s="8">
+      <c r="J44" s="7">
         <f>E44*characterization!$J$17 + F44*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>from APB CSR</t>
+      <c r="K44" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L44" s="7">
+        <f>K44 + H44</f>
+        <v/>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>from scheduler (per-ch idle state)</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4587,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cfg_clear</t>
+          <t>cfg_enable</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4234,22 +4604,30 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>FIFO reset path</t>
-        </is>
-      </c>
-      <c r="H45" s="8">
+          <t>control flop</t>
+        </is>
+      </c>
+      <c r="H45" s="7">
         <f>E45*characterization!$D$17 + F45*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I45" s="8">
+      <c r="I45" s="7">
         <f>E45*characterization!$G$17 + F45*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="7">
         <f>E45*characterization!$J$17 + F45*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L45" s="7">
+        <f>K45 + H45</f>
+        <v/>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>from APB CSR</t>
         </is>
@@ -4263,7 +4641,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>perf_fifo_rd</t>
+          <t>cfg_clear</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4271,37 +4649,41 @@
           <t>in</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_valid</t>
-        </is>
-      </c>
-      <c r="H46" s="8">
+          <t>FIFO reset path</t>
+        </is>
+      </c>
+      <c r="H46" s="7">
         <f>E46*characterization!$D$17 + F46*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I46" s="8">
+      <c r="I46" s="7">
         <f>E46*characterization!$G$17 + F46*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J46" s="8">
+      <c r="J46" s="7">
         <f>E46*characterization!$J$17 + F46*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>from APB CSR pop strobe</t>
+      <c r="K46" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L46" s="7">
+        <f>K46 + H46</f>
+        <v/>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>from APB CSR</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4695,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>perf_fifo_data_low[31:0]</t>
+          <t>perf_fifo_rd</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4334,24 +4716,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_data[31:0]</t>
-        </is>
-      </c>
-      <c r="H47" s="8">
+          <t>u_perf_fifo.rd_valid</t>
+        </is>
+      </c>
+      <c r="H47" s="7">
         <f>E47*characterization!$D$17 + F47*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I47" s="8">
+      <c r="I47" s="7">
         <f>E47*characterization!$G$17 + F47*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="7">
         <f>E47*characterization!$J$17 + F47*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>to APB CSR (host read)</t>
+      <c r="K47" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L47" s="7">
+        <f>K47 + H47</f>
+        <v/>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>from APB CSR pop strobe</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4753,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>perf_fifo_data_high[31:0]</t>
+          <t>perf_fifo_data_low[31:0]</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4384,24 +4774,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_data[63:32]</t>
-        </is>
-      </c>
-      <c r="H48" s="8">
+          <t>u_perf_fifo.rd_data[31:0]</t>
+        </is>
+      </c>
+      <c r="H48" s="7">
         <f>E48*characterization!$D$17 + F48*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I48" s="8">
+      <c r="I48" s="7">
         <f>E48*characterization!$G$17 + F48*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J48" s="8">
+      <c r="J48" s="7">
         <f>E48*characterization!$J$17 + F48*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>to APB CSR</t>
+      <c r="K48" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L48" s="7">
+        <f>K48 + H48</f>
+        <v/>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>to APB CSR (host read)</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4811,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>perf_fifo_empty</t>
+          <t>perf_fifo_data_high[31:0]</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4434,22 +4832,30 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>u_perf_fifo empty flag</t>
-        </is>
-      </c>
-      <c r="H49" s="8">
+          <t>u_perf_fifo.rd_data[63:32]</t>
+        </is>
+      </c>
+      <c r="H49" s="7">
         <f>E49*characterization!$D$17 + F49*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I49" s="8">
+      <c r="I49" s="7">
         <f>E49*characterization!$G$17 + F49*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="7">
         <f>E49*characterization!$J$17 + F49*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L49" s="7">
+        <f>K49 + H49</f>
+        <v/>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>to APB CSR</t>
         </is>
@@ -4463,98 +4869,118 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>perf_fifo_empty</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>u_perf_fifo empty flag</t>
+        </is>
+      </c>
+      <c r="H50" s="7">
+        <f>E50*characterization!$D$17 + F50*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I50" s="7">
+        <f>E50*characterization!$G$17 + F50*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J50" s="7">
+        <f>E50*characterization!$J$17 + F50*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K50" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L50" s="7">
+        <f>K50 + H50</f>
+        <v/>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>to APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>perf_fifo_count[15:0]</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t>u_perf_fifo.count</t>
         </is>
       </c>
-      <c r="H50" s="8">
-        <f>E50*characterization!$D$17 + F50*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I50" s="8">
-        <f>E50*characterization!$G$17 + F50*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J50" s="8">
-        <f>E50*characterization!$J$17 + F50*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="H51" s="7">
+        <f>E51*characterization!$D$17 + F51*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I51" s="7">
+        <f>E51*characterization!$G$17 + F51*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J51" s="7">
+        <f>E51*characterization!$J$17 + F51*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K51" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L51" s="7">
+        <f>K51 + H51</f>
+        <v/>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>to APB CSR</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>apbtodescr</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>apbtodescr</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>apb_cmd_valid</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>r_apb_cmd_valid</t>
-        </is>
-      </c>
-      <c r="H52" s="8">
-        <f>E52*characterization!$D$17 + F52*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I52" s="8">
-        <f>E52*characterization!$G$17 + F52*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J52" s="8">
-        <f>E52*characterization!$J$17 + F52*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>from APB master</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4992,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>apb_cmd_addr[ADDR_WIDTH-1:0]</t>
+          <t>apb_cmd_valid</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4583,22 +5009,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>address decoder</t>
-        </is>
-      </c>
-      <c r="H53" s="8">
+          <t>r_apb_cmd_valid</t>
+        </is>
+      </c>
+      <c r="H53" s="7">
         <f>E53*characterization!$D$17 + F53*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I53" s="8">
+      <c r="I53" s="7">
         <f>E53*characterization!$G$17 + F53*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J53" s="8">
+      <c r="J53" s="7">
         <f>E53*characterization!$J$17 + F53*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L53" s="7">
+        <f>K53 + H53</f>
+        <v/>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>from APB master</t>
         </is>
@@ -4612,7 +5046,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>apb_cmd_wdata[DATA_WIDTH-1:0]</t>
+          <t>apb_cmd_addr[ADDR_WIDTH-1:0]</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4622,31 +5056,39 @@
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>per-ch desc address mux</t>
-        </is>
-      </c>
-      <c r="H54" s="8">
+          <t>address decoder</t>
+        </is>
+      </c>
+      <c r="H54" s="7">
         <f>E54*characterization!$D$17 + F54*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I54" s="8">
+      <c r="I54" s="7">
         <f>E54*characterization!$G$17 + F54*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J54" s="8">
+      <c r="J54" s="7">
         <f>E54*characterization!$J$17 + F54*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>from APB master (descriptor pointer write)</t>
+      <c r="K54" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L54" s="7">
+        <f>K54 + H54</f>
+        <v/>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>from APB master</t>
         </is>
       </c>
     </row>
@@ -4658,41 +5100,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>apb_cmd_ready</t>
+          <t>apb_cmd_wdata[DATA_WIDTH-1:0]</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>comb (FIFO ready AND)</t>
-        </is>
-      </c>
-      <c r="H55" s="8">
+          <t>per-ch desc address mux</t>
+        </is>
+      </c>
+      <c r="H55" s="7">
         <f>E55*characterization!$D$17 + F55*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="7">
         <f>E55*characterization!$G$17 + F55*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="7">
         <f>E55*characterization!$J$17 + F55*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>to APB master</t>
+      <c r="K55" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L55" s="7">
+        <f>K55 + H55</f>
+        <v/>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>from APB master (descriptor pointer write)</t>
         </is>
       </c>
     </row>
@@ -4704,7 +5154,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>apb_rsp_valid</t>
+          <t>apb_cmd_ready</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4721,22 +5171,30 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>rsp pipeline flop</t>
-        </is>
-      </c>
-      <c r="H56" s="8">
+          <t>comb (FIFO ready AND)</t>
+        </is>
+      </c>
+      <c r="H56" s="7">
         <f>E56*characterization!$D$17 + F56*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I56" s="8">
+      <c r="I56" s="7">
         <f>E56*characterization!$G$17 + F56*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="7">
         <f>E56*characterization!$J$17 + F56*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L56" s="7">
+        <f>K56 + H56</f>
+        <v/>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>to APB master</t>
         </is>
@@ -4750,7 +5208,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>desc_apb_valid[N-1:0]</t>
+          <t>apb_rsp_valid</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4760,31 +5218,39 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>per-ch valid demux</t>
-        </is>
-      </c>
-      <c r="H57" s="8">
+          <t>rsp pipeline flop</t>
+        </is>
+      </c>
+      <c r="H57" s="7">
         <f>E57*characterization!$D$17 + F57*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I57" s="8">
+      <c r="I57" s="7">
         <f>E57*characterization!$G$17 + F57*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J57" s="8">
+      <c r="J57" s="7">
         <f>E57*characterization!$J$17 + F57*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>to descriptor_engine[N] (kick-off)</t>
+      <c r="K57" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L57" s="7">
+        <f>K57 + H57</f>
+        <v/>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>to APB master</t>
         </is>
       </c>
     </row>
@@ -4796,7 +5262,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>desc_apb_addr[N-1:0][DA-1:0]</t>
+          <t>desc_apb_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4806,31 +5272,39 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>per-ch addr flops</t>
-        </is>
-      </c>
-      <c r="H58" s="8">
+          <t>per-ch valid demux</t>
+        </is>
+      </c>
+      <c r="H58" s="7">
         <f>E58*characterization!$D$17 + F58*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I58" s="8">
+      <c r="I58" s="7">
         <f>E58*characterization!$G$17 + F58*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="7">
         <f>E58*characterization!$J$17 + F58*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>to descriptor_engine[N] (initial descriptor pointer)</t>
+      <c r="K58" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L58" s="7">
+        <f>K58 + H58</f>
+        <v/>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>to descriptor_engine[N] (kick-off)</t>
         </is>
       </c>
     </row>
@@ -4842,94 +5316,110 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>desc_apb_ready[N-1:0]</t>
+          <t>desc_apb_addr[N-1:0][DA-1:0]</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>per-ch addr flops</t>
+        </is>
+      </c>
+      <c r="H59" s="7">
+        <f>E59*characterization!$D$17 + F59*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I59" s="7">
+        <f>E59*characterization!$G$17 + F59*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J59" s="7">
+        <f>E59*characterization!$J$17 + F59*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K59" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L59" s="7">
+        <f>K59 + H59</f>
+        <v/>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>to descriptor_engine[N] (initial descriptor pointer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>desc_apb_ready[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>per-ch desc_engine ack</t>
         </is>
       </c>
-      <c r="H59" s="8">
-        <f>E59*characterization!$D$17 + F59*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I59" s="8">
-        <f>E59*characterization!$G$17 + F59*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J59" s="8">
-        <f>E59*characterization!$J$17 + F59*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="H60" s="7">
+        <f>E60*characterization!$D$17 + F60*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I60" s="7">
+        <f>E60*characterization!$G$17 + F60*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J60" s="7">
+        <f>E60*characterization!$J$17 + F60*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K60" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L60" s="7">
+        <f>K60 + H60</f>
+        <v/>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>from descriptor_engine[N]</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>descriptor_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>descriptor_engine</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>desc_apb_valid</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>r_state IDLE -&gt; FETCH</t>
-        </is>
-      </c>
-      <c r="H61" s="8">
-        <f>E61*characterization!$D$17 + F61*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I61" s="8">
-        <f>E61*characterization!$G$17 + F61*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J61" s="8">
-        <f>E61*characterization!$J$17 + F61*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>from apbtodescr (kick-off)</t>
         </is>
       </c>
     </row>
@@ -4941,7 +5431,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>desc_apb_addr[DA-1:0]</t>
+          <t>desc_apb_valid</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4954,28 +5444,36 @@
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>r_desc_addr flop</t>
-        </is>
-      </c>
-      <c r="H62" s="8">
+          <t>r_state IDLE -&gt; FETCH</t>
+        </is>
+      </c>
+      <c r="H62" s="7">
         <f>E62*characterization!$D$17 + F62*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I62" s="8">
+      <c r="I62" s="7">
         <f>E62*characterization!$G$17 + F62*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J62" s="8">
+      <c r="J62" s="7">
         <f>E62*characterization!$J$17 + F62*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>from apbtodescr</t>
+      <c r="K62" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L62" s="7">
+        <f>K62 + H62</f>
+        <v/>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>from apbtodescr (kick-off)</t>
         </is>
       </c>
     </row>
@@ -4987,19 +5485,15 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>desc_axi_ar_*</t>
+          <t>desc_apb_addr[DA-1:0]</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
@@ -5008,24 +5502,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>AR skid head Q</t>
-        </is>
-      </c>
-      <c r="H63" s="8">
+          <t>r_desc_addr flop</t>
+        </is>
+      </c>
+      <c r="H63" s="7">
         <f>E63*characterization!$D$17 + F63*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I63" s="8">
+      <c r="I63" s="7">
         <f>E63*characterization!$G$17 + F63*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J63" s="8">
+      <c r="J63" s="7">
         <f>E63*characterization!$J$17 + F63*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>to scheduler_group desc_axi master</t>
+      <c r="K63" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L63" s="7">
+        <f>K63 + H63</f>
+        <v/>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>from apbtodescr</t>
         </is>
       </c>
     </row>
@@ -5037,12 +5539,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>desc_axi_r_*</t>
+          <t>desc_axi_ar_*</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5058,24 +5560,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>R skid input</t>
-        </is>
-      </c>
-      <c r="H64" s="8">
+          <t>AR skid head Q</t>
+        </is>
+      </c>
+      <c r="H64" s="7">
         <f>E64*characterization!$D$17 + F64*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I64" s="8">
+      <c r="I64" s="7">
         <f>E64*characterization!$G$17 + F64*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J64" s="8">
+      <c r="J64" s="7">
         <f>E64*characterization!$J$17 + F64*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>from scheduler_group desc_axi master</t>
+      <c r="K64" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L64" s="7">
+        <f>K64 + H64</f>
+        <v/>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>to scheduler_group desc_axi master</t>
         </is>
       </c>
     </row>
@@ -5087,17 +5597,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>descriptor_valid</t>
+          <t>desc_axi_r_*</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync</t>
+          <t>gaxi_skid_buffer</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -5108,24 +5618,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>i_descriptor_fifo.rd_valid</t>
-        </is>
-      </c>
-      <c r="H65" s="8">
+          <t>R skid input</t>
+        </is>
+      </c>
+      <c r="H65" s="7">
         <f>E65*characterization!$D$17 + F65*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I65" s="8">
+      <c r="I65" s="7">
         <f>E65*characterization!$G$17 + F65*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J65" s="8">
+      <c r="J65" s="7">
         <f>E65*characterization!$J$17 + F65*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>to scheduler (descriptor dispatch)</t>
+      <c r="K65" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L65" s="7">
+        <f>K65 + H65</f>
+        <v/>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>from scheduler_group desc_axi master</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5655,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>descriptor_data[256-1:0]</t>
+          <t>descriptor_valid</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5158,24 +5676,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>i_descriptor_fifo.rd_data</t>
-        </is>
-      </c>
-      <c r="H66" s="8">
+          <t>i_descriptor_fifo.rd_valid</t>
+        </is>
+      </c>
+      <c r="H66" s="7">
         <f>E66*characterization!$D$17 + F66*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I66" s="8">
+      <c r="I66" s="7">
         <f>E66*characterization!$G$17 + F66*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J66" s="8">
+      <c r="J66" s="7">
         <f>E66*characterization!$J$17 + F66*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>to scheduler</t>
+      <c r="K66" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L66" s="7">
+        <f>K66 + H66</f>
+        <v/>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>to scheduler (descriptor dispatch)</t>
         </is>
       </c>
     </row>
@@ -5187,98 +5713,118 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>descriptor_data[256-1:0]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>i_descriptor_fifo.rd_data</t>
+        </is>
+      </c>
+      <c r="H67" s="7">
+        <f>E67*characterization!$D$17 + F67*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I67" s="7">
+        <f>E67*characterization!$G$17 + F67*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J67" s="7">
+        <f>E67*characterization!$J$17 + F67*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K67" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L67" s="7">
+        <f>K67 + H67</f>
+        <v/>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>to scheduler</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>descriptor_ready</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>i_descriptor_fifo.rd_ready</t>
         </is>
       </c>
-      <c r="H67" s="8">
-        <f>E67*characterization!$D$17 + F67*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I67" s="8">
-        <f>E67*characterization!$G$17 + F67*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J67" s="8">
-        <f>E67*characterization!$J$17 + F67*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K67" t="inlineStr">
+      <c r="H68" s="7">
+        <f>E68*characterization!$D$17 + F68*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I68" s="7">
+        <f>E68*characterization!$G$17 + F68*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J68" s="7">
+        <f>E68*characterization!$J$17 + F68*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K68" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L68" s="7">
+        <f>K68 + H68</f>
+        <v/>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>from scheduler</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>scheduler</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>scheduler</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>descriptor_valid</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>r_state IDLE -&gt; RUN</t>
-        </is>
-      </c>
-      <c r="H69" s="8">
-        <f>E69*characterization!$D$17 + F69*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I69" s="8">
-        <f>E69*characterization!$G$17 + F69*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J69" s="8">
-        <f>E69*characterization!$J$17 + F69*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>from descriptor_engine</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5836,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>descriptor_data[256-1:0]</t>
+          <t>descriptor_valid</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5303,26 +5849,34 @@
         <v>0</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>r_descriptor latch</t>
-        </is>
-      </c>
-      <c r="H70" s="8">
+          <t>r_state IDLE -&gt; RUN</t>
+        </is>
+      </c>
+      <c r="H70" s="7">
         <f>E70*characterization!$D$17 + F70*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="7">
         <f>E70*characterization!$G$17 + F70*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J70" s="8">
+      <c r="J70" s="7">
         <f>E70*characterization!$J$17 + F70*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L70" s="7">
+        <f>K70 + H70</f>
+        <v/>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>from descriptor_engine</t>
         </is>
@@ -5336,12 +5890,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>axi_rd_req_valid</t>
+          <t>descriptor_data[256-1:0]</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5349,28 +5903,36 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>r_axi_rd_req state</t>
-        </is>
-      </c>
-      <c r="H71" s="8">
+          <t>r_descriptor latch</t>
+        </is>
+      </c>
+      <c r="H71" s="7">
         <f>E71*characterization!$D$17 + F71*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I71" s="8">
+      <c r="I71" s="7">
         <f>E71*characterization!$G$17 + F71*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="7">
         <f>E71*characterization!$J$17 + F71*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>to axi_read_engine (per-channel request)</t>
+      <c r="K71" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L71" s="7">
+        <f>K71 + H71</f>
+        <v/>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>from descriptor_engine</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5944,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>axi_rd_req_addr[63:0]</t>
+          <t>axi_rd_req_valid</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5395,28 +5957,36 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>r_src_addr+offset</t>
-        </is>
-      </c>
-      <c r="H72" s="8">
+          <t>r_axi_rd_req state</t>
+        </is>
+      </c>
+      <c r="H72" s="7">
         <f>E72*characterization!$D$17 + F72*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="7">
         <f>E72*characterization!$G$17 + F72*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J72" s="8">
+      <c r="J72" s="7">
         <f>E72*characterization!$J$17 + F72*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>to axi_read_engine</t>
+      <c r="K72" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L72" s="7">
+        <f>K72 + H72</f>
+        <v/>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>to axi_read_engine (per-channel request)</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5998,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>axi_wr_req_valid</t>
+          <t>axi_rd_req_addr[63:0]</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5441,28 +6011,36 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>r_axi_wr_req state</t>
-        </is>
-      </c>
-      <c r="H73" s="8">
+          <t>r_src_addr+offset</t>
+        </is>
+      </c>
+      <c r="H73" s="7">
         <f>E73*characterization!$D$17 + F73*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="7">
         <f>E73*characterization!$G$17 + F73*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="7">
         <f>E73*characterization!$J$17 + F73*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
+      <c r="K73" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L73" s="7">
+        <f>K73 + H73</f>
+        <v/>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -5474,7 +6052,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>axi_wr_req_addr[63:0]</t>
+          <t>axi_wr_req_valid</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5487,26 +6065,34 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>r_dst_addr+offset</t>
-        </is>
-      </c>
-      <c r="H74" s="8">
+          <t>r_axi_wr_req state</t>
+        </is>
+      </c>
+      <c r="H74" s="7">
         <f>E74*characterization!$D$17 + F74*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="7">
         <f>E74*characterization!$G$17 + F74*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J74" s="8">
+      <c r="J74" s="7">
         <f>E74*characterization!$J$17 + F74*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L74" s="7">
+        <f>K74 + H74</f>
+        <v/>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -5520,7 +6106,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ch_idle</t>
+          <t>axi_wr_req_addr[63:0]</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5533,28 +6119,36 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>r_state == IDLE</t>
-        </is>
-      </c>
-      <c r="H75" s="8">
+          <t>r_dst_addr+offset</t>
+        </is>
+      </c>
+      <c r="H75" s="7">
         <f>E75*characterization!$D$17 + F75*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="7">
         <f>E75*characterization!$G$17 + F75*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J75" s="8">
+      <c r="J75" s="7">
         <f>E75*characterization!$J$17 + F75*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>to perf_profiler</t>
+      <c r="K75" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L75" s="7">
+        <f>K75 + H75</f>
+        <v/>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -5566,7 +6160,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ch_done_strobe</t>
+          <t>ch_idle</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5583,24 +6177,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>r_state -&gt; DONE pulse</t>
-        </is>
-      </c>
-      <c r="H76" s="8">
+          <t>r_state == IDLE</t>
+        </is>
+      </c>
+      <c r="H76" s="7">
         <f>E76*characterization!$D$17 + F76*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I76" s="8">
+      <c r="I76" s="7">
         <f>E76*characterization!$G$17 + F76*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J76" s="8">
+      <c r="J76" s="7">
         <f>E76*characterization!$J$17 + F76*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>to monbus_reporter</t>
+      <c r="K76" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L76" s="7">
+        <f>K76 + H76</f>
+        <v/>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>to perf_profiler</t>
         </is>
       </c>
     </row>
@@ -5612,7 +6214,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>monbus_pkt</t>
+          <t>ch_done_strobe</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5629,77 +6231,93 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>r_state -&gt; DONE pulse</t>
+        </is>
+      </c>
+      <c r="H77" s="7">
+        <f>E77*characterization!$D$17 + F77*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I77" s="7">
+        <f>E77*characterization!$G$17 + F77*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J77" s="7">
+        <f>E77*characterization!$J$17 + F77*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K77" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L77" s="7">
+        <f>K77 + H77</f>
+        <v/>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>to monbus_reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>monbus_pkt</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>event-encode comb</t>
         </is>
       </c>
-      <c r="H77" s="8">
-        <f>E77*characterization!$D$17 + F77*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I77" s="8">
-        <f>E77*characterization!$G$17 + F77*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J77" s="8">
-        <f>E77*characterization!$J$17 + F77*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K77" t="inlineStr">
+      <c r="H78" s="7">
+        <f>E78*characterization!$D$17 + F78*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I78" s="7">
+        <f>E78*characterization!$G$17 + F78*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J78" s="7">
+        <f>E78*characterization!$J$17 + F78*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K78" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L78" s="7">
+        <f>K78 + H78</f>
+        <v/>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>to monbus group / reporter</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>axi_read_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>axi_read_engine</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>sched_req_valid[N-1:0]</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>u_arbiter (CLIENTS=N)</t>
-        </is>
-      </c>
-      <c r="H79" s="8">
-        <f>E79*characterization!$D$17 + F79*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I79" s="8">
-        <f>E79*characterization!$G$17 + F79*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J79" s="8">
-        <f>E79*characterization!$J$17 + F79*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>from scheduler[N] (per-channel)</t>
         </is>
       </c>
     </row>
@@ -5711,7 +6329,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sched_req_addr[N-1:0][63:0]</t>
+          <t>sched_req_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5724,28 +6342,36 @@
         <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>u_arbiter granted addr mux</t>
-        </is>
-      </c>
-      <c r="H80" s="8">
+          <t>u_arbiter (CLIENTS=N)</t>
+        </is>
+      </c>
+      <c r="H80" s="7">
         <f>E80*characterization!$D$17 + F80*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="7">
         <f>E80*characterization!$G$17 + F80*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J80" s="8">
+      <c r="J80" s="7">
         <f>E80*characterization!$J$17 + F80*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>from scheduler[N]</t>
+      <c r="K80" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L80" s="7">
+        <f>K80 + H80</f>
+        <v/>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>from scheduler[N] (per-channel)</t>
         </is>
       </c>
     </row>
@@ -5757,45 +6383,49 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>m_axi_ar_*</t>
+          <t>sched_req_addr[N-1:0][63:0]</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>u_rd_axi_skid (AR side)</t>
-        </is>
-      </c>
-      <c r="H81" s="8">
+          <t>u_arbiter granted addr mux</t>
+        </is>
+      </c>
+      <c r="H81" s="7">
         <f>E81*characterization!$D$17 + F81*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I81" s="8">
+      <c r="I81" s="7">
         <f>E81*characterization!$G$17 + F81*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J81" s="8">
+      <c r="J81" s="7">
         <f>E81*characterization!$J$17 + F81*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>to AXI4 master read system bus</t>
+      <c r="K81" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L81" s="7">
+        <f>K81 + H81</f>
+        <v/>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
         </is>
       </c>
     </row>
@@ -5807,12 +6437,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>m_axi_r_*</t>
+          <t>m_axi_ar_*</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5828,24 +6458,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>u_rd_axi_skid (R side)</t>
-        </is>
-      </c>
-      <c r="H82" s="8">
+          <t>u_rd_axi_skid (AR side)</t>
+        </is>
+      </c>
+      <c r="H82" s="7">
         <f>E82*characterization!$D$17 + F82*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I82" s="8">
+      <c r="I82" s="7">
         <f>E82*characterization!$G$17 + F82*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J82" s="8">
+      <c r="J82" s="7">
         <f>E82*characterization!$J$17 + F82*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>from AXI4 master read system bus</t>
+      <c r="K82" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L82" s="7">
+        <f>K82 + H82</f>
+        <v/>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>to AXI4 master read system bus</t>
         </is>
       </c>
     </row>
@@ -5857,41 +6495,53 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>sram_alloc_req[N-1:0]</t>
+          <t>m_axi_r_*</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>per-ch alloc req gen</t>
-        </is>
-      </c>
-      <c r="H83" s="8">
+          <t>u_rd_axi_skid (R side)</t>
+        </is>
+      </c>
+      <c r="H83" s="7">
         <f>E83*characterization!$D$17 + F83*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I83" s="8">
+      <c r="I83" s="7">
         <f>E83*characterization!$G$17 + F83*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="7">
         <f>E83*characterization!$J$17 + F83*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>to sram_controller_unit[N] (reserve burst space)</t>
+      <c r="K83" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L83" s="7">
+        <f>K83 + H83</f>
+        <v/>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>from AXI4 master read system bus</t>
         </is>
       </c>
     </row>
@@ -5903,41 +6553,49 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>sram_alloc_space_free[N-1:0][AW:0]</t>
+          <t>sram_alloc_req[N-1:0]</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>per-ch space cmp</t>
-        </is>
-      </c>
-      <c r="H84" s="8">
+          <t>per-ch alloc req gen</t>
+        </is>
+      </c>
+      <c r="H84" s="7">
         <f>E84*characterization!$D$17 + F84*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I84" s="8">
+      <c r="I84" s="7">
         <f>E84*characterization!$G$17 + F84*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J84" s="8">
+      <c r="J84" s="7">
         <f>E84*characterization!$J$17 + F84*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>from sram_controller_unit[N]</t>
+      <c r="K84" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L84" s="7">
+        <f>K84 + H84</f>
+        <v/>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N] (reserve burst space)</t>
         </is>
       </c>
     </row>
@@ -5949,12 +6607,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>sram_wr_valid[N-1:0]</t>
+          <t>sram_alloc_space_free[N-1:0][AW:0]</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -5966,24 +6624,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>post-arbiter demux</t>
-        </is>
-      </c>
-      <c r="H85" s="8">
+          <t>per-ch space cmp</t>
+        </is>
+      </c>
+      <c r="H85" s="7">
         <f>E85*characterization!$D$17 + F85*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="7">
         <f>E85*characterization!$G$17 + F85*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J85" s="8">
+      <c r="J85" s="7">
         <f>E85*characterization!$J$17 + F85*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>to sram_controller_unit[N].wr</t>
+      <c r="K85" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L85" s="7">
+        <f>K85 + H85</f>
+        <v/>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6661,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>sram_wr_data[DW-1:0]</t>
+          <t>sram_wr_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6005,84 +6671,100 @@
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>post-arbiter demux</t>
+        </is>
+      </c>
+      <c r="H86" s="7">
+        <f>E86*characterization!$D$17 + F86*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I86" s="7">
+        <f>E86*characterization!$G$17 + F86*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J86" s="7">
+        <f>E86*characterization!$J$17 + F86*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K86" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L86" s="7">
+        <f>K86 + H86</f>
+        <v/>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N].wr</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>sram_wr_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>R-skid data wire</t>
         </is>
       </c>
-      <c r="H86" s="8">
-        <f>E86*characterization!$D$17 + F86*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I86" s="8">
-        <f>E86*characterization!$G$17 + F86*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J86" s="8">
-        <f>E86*characterization!$J$17 + F86*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K86" t="inlineStr">
+      <c r="H87" s="7">
+        <f>E87*characterization!$D$17 + F87*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I87" s="7">
+        <f>E87*characterization!$G$17 + F87*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J87" s="7">
+        <f>E87*characterization!$J$17 + F87*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K87" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L87" s="7">
+        <f>K87 + H87</f>
+        <v/>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>to sram_controller_unit[N].wr (channel-id muxed)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>axi_write_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>axi_write_engine</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>sched_req_valid[N-1:0]</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>arbiter granted</t>
-        </is>
-      </c>
-      <c r="H88" s="8">
-        <f>E88*characterization!$D$17 + F88*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I88" s="8">
-        <f>E88*characterization!$G$17 + F88*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J88" s="8">
-        <f>E88*characterization!$J$17 + F88*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>from scheduler[N]</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6776,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>sched_req_addr[N-1:0][63:0]</t>
+          <t>sched_req_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6107,26 +6789,34 @@
         <v>1</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>arbiter granted addr</t>
-        </is>
-      </c>
-      <c r="H89" s="8">
+          <t>arbiter granted</t>
+        </is>
+      </c>
+      <c r="H89" s="7">
         <f>E89*characterization!$D$17 + F89*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I89" s="8">
+      <c r="I89" s="7">
         <f>E89*characterization!$G$17 + F89*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J89" s="8">
+      <c r="J89" s="7">
         <f>E89*characterization!$J$17 + F89*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K89" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L89" s="7">
+        <f>K89 + H89</f>
+        <v/>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>from scheduler[N]</t>
         </is>
@@ -6140,7 +6830,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>sram_rd_valid[N-1:0]</t>
+          <t>sched_req_addr[N-1:0][63:0]</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -6153,28 +6843,36 @@
         <v>1</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>drain ready cmp</t>
-        </is>
-      </c>
-      <c r="H90" s="8">
+          <t>arbiter granted addr</t>
+        </is>
+      </c>
+      <c r="H90" s="7">
         <f>E90*characterization!$D$17 + F90*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I90" s="8">
+      <c r="I90" s="7">
         <f>E90*characterization!$G$17 + F90*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J90" s="8">
+      <c r="J90" s="7">
         <f>E90*characterization!$J$17 + F90*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>from sram_controller_unit[N] (data ready)</t>
+      <c r="K90" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L90" s="7">
+        <f>K90 + H90</f>
+        <v/>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6884,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>sram_rd_data[N-1:0][DW-1:0]</t>
+          <t>sram_rd_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6199,28 +6897,36 @@
         <v>1</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>per-ch read mux</t>
-        </is>
-      </c>
-      <c r="H91" s="8">
+          <t>drain ready cmp</t>
+        </is>
+      </c>
+      <c r="H91" s="7">
         <f>E91*characterization!$D$17 + F91*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I91" s="8">
+      <c r="I91" s="7">
         <f>E91*characterization!$G$17 + F91*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J91" s="8">
+      <c r="J91" s="7">
         <f>E91*characterization!$J$17 + F91*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>from sram_controller_unit[N]</t>
+      <c r="K91" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L91" s="7">
+        <f>K91 + H91</f>
+        <v/>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N] (data ready)</t>
         </is>
       </c>
     </row>
@@ -6232,41 +6938,49 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>sram_drain_req[N-1:0]</t>
+          <t>sram_rd_data[N-1:0][DW-1:0]</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>drain reservation gen</t>
-        </is>
-      </c>
-      <c r="H92" s="8">
+          <t>per-ch read mux</t>
+        </is>
+      </c>
+      <c r="H92" s="7">
         <f>E92*characterization!$D$17 + F92*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="7">
         <f>E92*characterization!$G$17 + F92*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J92" s="8">
+      <c r="J92" s="7">
         <f>E92*characterization!$J$17 + F92*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>to sram_controller_unit[N]</t>
+      <c r="K92" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L92" s="7">
+        <f>K92 + H92</f>
+        <v/>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6992,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>m_axi_aw_*</t>
+          <t>sram_drain_req[N-1:0]</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6286,37 +7000,41 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (AW side)</t>
-        </is>
-      </c>
-      <c r="H93" s="8">
+          <t>drain reservation gen</t>
+        </is>
+      </c>
+      <c r="H93" s="7">
         <f>E93*characterization!$D$17 + F93*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I93" s="8">
+      <c r="I93" s="7">
         <f>E93*characterization!$G$17 + F93*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J93" s="8">
+      <c r="J93" s="7">
         <f>E93*characterization!$J$17 + F93*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>to AXI4 master write system bus</t>
+      <c r="K93" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L93" s="7">
+        <f>K93 + H93</f>
+        <v/>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N]</t>
         </is>
       </c>
     </row>
@@ -6328,7 +7046,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>m_axi_w_*</t>
+          <t>m_axi_aw_*</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6349,22 +7067,30 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (W side)</t>
-        </is>
-      </c>
-      <c r="H94" s="8">
+          <t>u_wr_axi_skid (AW side)</t>
+        </is>
+      </c>
+      <c r="H94" s="7">
         <f>E94*characterization!$D$17 + F94*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I94" s="8">
+      <c r="I94" s="7">
         <f>E94*characterization!$G$17 + F94*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J94" s="8">
+      <c r="J94" s="7">
         <f>E94*characterization!$J$17 + F94*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L94" s="7">
+        <f>K94 + H94</f>
+        <v/>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>to AXI4 master write system bus</t>
         </is>
@@ -6378,12 +7104,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>m_axi_b_*</t>
+          <t>m_axi_w_*</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6399,24 +7125,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (B side)</t>
-        </is>
-      </c>
-      <c r="H95" s="8">
+          <t>u_wr_axi_skid (W side)</t>
+        </is>
+      </c>
+      <c r="H95" s="7">
         <f>E95*characterization!$D$17 + F95*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I95" s="8">
+      <c r="I95" s="7">
         <f>E95*characterization!$G$17 + F95*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J95" s="8">
+      <c r="J95" s="7">
         <f>E95*characterization!$J$17 + F95*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>from AXI4 master write system bus</t>
+      <c r="K95" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L95" s="7">
+        <f>K95 + H95</f>
+        <v/>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>to AXI4 master write system bus</t>
         </is>
       </c>
     </row>
@@ -6428,17 +7162,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>u_b_phase_txn_fifo wr</t>
+          <t>m_axi_b_*</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>gaxi_fifo_sync</t>
+          <t>gaxi_skid_buffer</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -6449,24 +7183,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>b-phase txn capture</t>
-        </is>
-      </c>
-      <c r="H96" s="8">
+          <t>u_wr_axi_skid (B side)</t>
+        </is>
+      </c>
+      <c r="H96" s="7">
         <f>E96*characterization!$D$17 + F96*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="I96" s="8">
+      <c r="I96" s="7">
         <f>E96*characterization!$G$17 + F96*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="J96" s="8">
+      <c r="J96" s="7">
         <f>E96*characterization!$J$17 + F96*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>B-phase awaiting response</t>
+      <c r="K96" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L96" s="7">
+        <f>K96 + H96</f>
+        <v/>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>from AXI4 master write system bus</t>
         </is>
       </c>
     </row>
@@ -6478,108 +7220,174 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>u_b_phase_txn_fifo wr</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>b-phase txn capture</t>
+        </is>
+      </c>
+      <c r="H97" s="7">
+        <f>E97*characterization!$D$17 + F97*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I97" s="7">
+        <f>E97*characterization!$G$17 + F97*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J97" s="7">
+        <f>E97*characterization!$J$17 + F97*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K97" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L97" s="7">
+        <f>K97 + H97</f>
+        <v/>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>B-phase awaiting response</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>u_w_phase_txn_fifo wr</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>internal</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="E98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>w-phase txn capture</t>
         </is>
       </c>
-      <c r="H97" s="8">
-        <f>E97*characterization!$D$17 + F97*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I97" s="8">
-        <f>E97*characterization!$G$17 + F97*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J97" s="8">
-        <f>E97*characterization!$J$17 + F97*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K97" t="inlineStr">
+      <c r="H98" s="7">
+        <f>E98*characterization!$D$17 + F98*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I98" s="7">
+        <f>E98*characterization!$G$17 + F98*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J98" s="7">
+        <f>E98*characterization!$J$17 + F98*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K98" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L98" s="7">
+        <f>K98 + H98</f>
+        <v/>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>W-phase awaiting last-beat</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>Methodology</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>One row per port (or significant internal handshake) per FUB. Hand-walked from the RTL.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MUX lv / NAND lv = combinational gate-equivalents on the path within this FUB only - between the port and its nearest flop.</t>
+          <t>One row per port (or significant internal handshake) per FUB. Hand-walked from the RTL.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>When a port enters/exits a building block (gaxi_fifo_sync, gaxi_skid_buffer), the BB internal cost is captured on the 'building blocks' sheet - no double-counting here.</t>
+          <t>MUX lv / NAND lv = combinational gate-equivalents on the path within this FUB only - between the port and its nearest flop.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>'places it goes' lists the concrete consumer/producer in the wider STREAM hierarchy (stream_core / scheduler_group / APB CSR / system AXI bus).</t>
+          <t>When a port enters/exits a building block (gaxi_fifo_sync, gaxi_skid_buffer), the BB internal cost is captured on the 'building blocks' sheet - no double-counting here.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>'places it goes' lists the concrete consumer/producer in the wider STREAM hierarchy (stream_core / scheduler_group / APB CSR / system AXI bus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>AXI bus signals (m_axi_ar_*, m_axi_r_*, m_axi_aw_*, m_axi_w_*, m_axi_b_*) are summarized as channel groups for brevity; each is a set of skid buffer outputs whose detailed cost is in the building blocks 'gaxi_skid_buffer' / 'axi4_master_rd/wr' rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A100:K100"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="A101:K101"/>
-    <mergeCell ref="A68:K68"/>
-    <mergeCell ref="A87:K87"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A104:K104"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="A103:M103"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A79:M79"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A105:M105"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A101:M101"/>
+    <mergeCell ref="A69:M69"/>
+    <mergeCell ref="A104:M104"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A52:M52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -29,7 +29,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <b val="1"/>
@@ -40,17 +40,12 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -107,19 +102,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2444,7 +2439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2585,7 +2580,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>r_drain_ip flop D</t>
+          <t>r_drain_ip (D)</t>
         </is>
       </c>
       <c r="H4" s="7">
@@ -2680,24 +2675,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>s_ready</t>
+          <t>r_drain_ip</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>comb of skid count + drain</t>
+          <t>u_skid_buffer.wr_valid (D)</t>
         </is>
       </c>
       <c r="H6" s="7">
@@ -2722,7 +2717,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>to u_channel_fifo.rd_ready</t>
+          <t>internal: only local flop; gates the skid push</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2729,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>m_valid</t>
+          <t>s_ready</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2742,20 +2737,16 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_valid</t>
+          <t>comb of u_skid_buffer.count + r_drain_ip</t>
         </is>
       </c>
       <c r="H7" s="7">
@@ -2780,7 +2771,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>to axi_write_engine.sram_rd_valid</t>
+          <t>to u_channel_fifo.rd_ready</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2783,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>m_data[DW-1:0]</t>
+          <t>m_valid</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2813,7 +2804,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_data</t>
+          <t>u_skid_buffer.rd_valid (Q)</t>
         </is>
       </c>
       <c r="H8" s="7">
@@ -2838,7 +2829,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>to axi_write_engine.sram_rd_data</t>
+          <t>to sram_controller_unit.axi_wr_sram_valid -&gt; axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2841,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>m_ready</t>
+          <t>m_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2871,7 +2862,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>u_skid_buffer.rd_ready</t>
+          <t>u_skid_buffer.rd_data (Q)</t>
         </is>
       </c>
       <c r="H9" s="7">
@@ -2896,7 +2887,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>from axi_write_engine.sram_rd_ready</t>
+          <t>to sram_controller_unit.axi_wr_sram_data -&gt; axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>occupancy[2:0]</t>
+          <t>m_ready</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2929,7 +2920,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>u_skid_buffer.count</t>
+          <t>u_skid_buffer.rd_ready</t>
         </is>
       </c>
       <c r="H10" s="7">
@@ -2954,31 +2945,82 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>from axi_write_engine via sram_controller_unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>stream_latency_bridge</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>occupancy[2:0]</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>u_skid_buffer.count (Q)</t>
+        </is>
+      </c>
+      <c r="H11" s="7">
+        <f>E11*characterization!$D$17 + F11*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>E11*characterization!$G$17 + F11*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J11" s="7">
+        <f>E11*characterization!$J$17 + F11*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K11" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L11" s="7">
+        <f>K11 + H11</f>
+        <v/>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>to scheduler (drain-IP backpressure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>stream_alloc_ctrl</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stream_alloc_ctrl</t>
+          <t>stream_latency_bridge</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wr_valid</t>
+          <t>dbg_r_pending</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2986,11 +3028,11 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>r_wr_ptr flop D (+wr_size)</t>
+          <t>r_drain_ip (Q)</t>
         </is>
       </c>
       <c r="H12" s="7">
@@ -3015,61 +3057,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>from axi_read_engine (allocate request)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+          <t>debug observability</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>stream_alloc_ctrl</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>wr_size[7:0]</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>r_wr_ptr adder input</t>
-        </is>
-      </c>
-      <c r="H13" s="7">
-        <f>E13*characterization!$D$17 + F13*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I13" s="7">
-        <f>E13*characterization!$G$17 + F13*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>E13*characterization!$J$17 + F13*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K13" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L13" s="7">
-        <f>K13 + H13</f>
-        <v/>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rd_valid</t>
+          <t>wr_valid</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3098,7 +3093,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>r_rd_ptr flop D</t>
+          <t>r_wr_ptr (D)</t>
         </is>
       </c>
       <c r="H14" s="7">
@@ -3123,7 +3118,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>from sram_controller_unit (release event)</t>
+          <t>from axi_read_engine (allocate request)</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3130,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>space_free[AW:0]</t>
+          <t>wr_size[7:0]</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3148,11 +3143,11 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>r_space_free (registered)</t>
+          <t>r_wr_ptr adder input</t>
         </is>
       </c>
       <c r="H15" s="7">
@@ -3177,7 +3172,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>to axi_read_engine (sram_alloc_space_free)</t>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3184,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wr_full</t>
+          <t>rd_valid</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -3206,7 +3201,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>comb of r_space_free</t>
+          <t>r_rd_ptr (D)</t>
         </is>
       </c>
       <c r="H16" s="7">
@@ -3231,7 +3226,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>to axi_read_engine (back-pressure)</t>
+          <t>from sram_controller_unit (release event)</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3238,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wr_almost_full</t>
+          <t>r_wr_ptr</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3260,7 +3255,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>comb of r_space_free</t>
+          <t>r_space_free (D)</t>
         </is>
       </c>
       <c r="H17" s="7">
@@ -3285,7 +3280,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>to axi_read_engine (threshold)</t>
+          <t>internal: wr_ptr - rd_ptr = space_free</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3292,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rd_empty</t>
+          <t>r_rd_ptr</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -3314,7 +3309,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>comb of r_space_free</t>
+          <t>r_space_free (D)</t>
         </is>
       </c>
       <c r="H18" s="7">
@@ -3339,31 +3334,78 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>unused (debug)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>stream_drain_ctrl</t>
+          <t>internal: subtractor into space_free</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>stream_alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>r_space_free</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>r_wr_full (D)</t>
+        </is>
+      </c>
+      <c r="H19" s="7">
+        <f>E19*characterization!$D$17 + F19*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I19" s="7">
+        <f>E19*characterization!$G$17 + F19*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J19" s="7">
+        <f>E19*characterization!$J$17 + F19*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K19" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L19" s="7">
+        <f>K19 + H19</f>
+        <v/>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>internal: cmp against DEPTH for full/almost_full flops</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>stream_drain_ctrl</t>
+          <t>stream_alloc_ctrl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wr_valid</t>
+          <t>space_free[AW:0]</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3371,11 +3413,11 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>r_wr_ptr flop D</t>
+          <t>r_space_free (Q)</t>
         </is>
       </c>
       <c r="H20" s="7">
@@ -3400,24 +3442,24 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>from u_channel_fifo handshake in sram_controller_unit</t>
+          <t>to axi_read_engine (sram_alloc_space_free)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>stream_drain_ctrl</t>
+          <t>stream_alloc_ctrl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rd_valid</t>
+          <t>wr_full</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3425,11 +3467,11 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>r_rd_ptr flop D (+rd_size)</t>
+          <t>r_wr_full (Q)</t>
         </is>
       </c>
       <c r="H21" s="7">
@@ -3454,24 +3496,24 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>from axi_write_engine (drain reservation)</t>
+          <t>to axi_read_engine (back-pressure)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>stream_drain_ctrl</t>
+          <t>stream_alloc_ctrl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rd_size[7:0]</t>
+          <t>wr_almost_full</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3479,11 +3521,11 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>r_rd_ptr adder input</t>
+          <t>r_wr_almost_full (Q)</t>
         </is>
       </c>
       <c r="H22" s="7">
@@ -3508,61 +3550,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>from axi_write_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+          <t>to axi_read_engine (threshold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>stream_drain_ctrl</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>data_available[AW:0]</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>r_data_available (registered)</t>
-        </is>
-      </c>
-      <c r="H23" s="7">
-        <f>E23*characterization!$D$17 + F23*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I23" s="7">
-        <f>E23*characterization!$G$17 + F23*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J23" s="7">
-        <f>E23*characterization!$J$17 + F23*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K23" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L23" s="7">
-        <f>K23 + H23</f>
-        <v/>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3569,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rd_empty</t>
+          <t>wr_valid</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -3591,7 +3586,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>comb of r_data_available</t>
+          <t>r_wr_ptr (D)</t>
         </is>
       </c>
       <c r="H24" s="7">
@@ -3616,7 +3611,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>to axi_write_engine (no data)</t>
+          <t>from u_channel_fifo handshake in sram_controller_unit</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3623,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wr_full</t>
+          <t>rd_valid</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -3645,7 +3640,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>comb of r_data_available</t>
+          <t>r_rd_ptr (D)</t>
         </is>
       </c>
       <c r="H25" s="7">
@@ -3670,31 +3665,78 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>to sram_controller_unit (back-pressure)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>sram_controller_unit</t>
+          <t>from axi_write_engine (drain reservation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>stream_drain_ctrl</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>rd_size[7:0]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>r_rd_ptr adder input</t>
+        </is>
+      </c>
+      <c r="H26" s="7">
+        <f>E26*characterization!$D$17 + F26*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I26" s="7">
+        <f>E26*characterization!$G$17 + F26*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J26" s="7">
+        <f>E26*characterization!$J$17 + F26*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K26" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L26" s="7">
+        <f>K26 + H26</f>
+        <v/>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>axi_rd_alloc_req</t>
+          <t>r_wr_ptr</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3706,7 +3748,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>alloc_ctrl.wr_valid</t>
+          <t>r_data_available (D)</t>
         </is>
       </c>
       <c r="H27" s="7">
@@ -3731,24 +3773,24 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>from axi_read_engine (reserve burst space)</t>
+          <t>internal: wr_ptr - rd_ptr = data_available</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>axi_rd_alloc_size[7:0]</t>
+          <t>r_rd_ptr</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3756,11 +3798,11 @@
         <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>alloc_ctrl.wr_size</t>
+          <t>r_data_available (D)</t>
         </is>
       </c>
       <c r="H28" s="7">
@@ -3785,24 +3827,24 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>from axi_read_engine</t>
+          <t>internal: subtractor into data_available</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>axi_rd_alloc_space_free[AW:0]</t>
+          <t>r_data_available</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -3810,11 +3852,11 @@
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alloc_ctrl.space_free</t>
+          <t>r_rd_empty (D)</t>
         </is>
       </c>
       <c r="H29" s="7">
@@ -3839,31 +3881,27 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>to axi_read_engine</t>
+          <t>internal: cmp 0 / cmp DEPTH for empty / full flops</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>axi_rd_sram_valid</t>
+          <t>data_available[AW:0]</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" s="5" t="n">
         <v>0</v>
       </c>
@@ -3872,7 +3910,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_valid</t>
+          <t>r_data_available (Q)</t>
         </is>
       </c>
       <c r="H30" s="7">
@@ -3897,31 +3935,27 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>from axi_read_engine (write data into SRAM FIFO)</t>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>axi_rd_sram_data[DW-1:0]</t>
+          <t>rd_empty</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
         <v>0</v>
       </c>
@@ -3930,7 +3964,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_data</t>
+          <t>r_rd_empty (Q)</t>
         </is>
       </c>
       <c r="H31" s="7">
@@ -3955,19 +3989,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>from axi_read_engine</t>
+          <t>to axi_write_engine (no data)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sram_controller_unit</t>
+          <t>stream_drain_ctrl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>axi_rd_sram_ready</t>
+          <t>wr_full</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3975,11 +4009,7 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
         <v>0</v>
       </c>
@@ -3988,7 +4018,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>u_channel_fifo.wr_ready</t>
+          <t>r_wr_full (Q)</t>
         </is>
       </c>
       <c r="H32" s="7">
@@ -4013,65 +4043,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>to axi_read_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+          <t>to sram_controller_unit (back-pressure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>sram_controller_unit</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>axi_wr_sram_valid</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>u_latency_bridge.m_valid</t>
-        </is>
-      </c>
-      <c r="H33" s="7">
-        <f>E33*characterization!$D$17 + F33*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I33" s="7">
-        <f>E33*characterization!$G$17 + F33*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J33" s="7">
-        <f>E33*characterization!$J$17 + F33*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K33" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L33" s="7">
-        <f>K33 + H33</f>
-        <v/>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
@@ -4083,28 +4062,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>axi_wr_sram_data[DW-1:0]</t>
+          <t>axi_rd_alloc_req</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>u_latency_bridge.m_data</t>
+          <t>u_alloc_ctrl.wr_valid</t>
         </is>
       </c>
       <c r="H34" s="7">
@@ -4129,7 +4104,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>to axi_write_engine</t>
+          <t>from axi_read_engine (reserve burst space)</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4116,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>axi_wr_sram_ready</t>
+          <t>axi_rd_alloc_size[7:0]</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4158,7 +4133,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>u_latency_bridge.m_ready</t>
+          <t>u_alloc_ctrl.wr_size</t>
         </is>
       </c>
       <c r="H35" s="7">
@@ -4183,7 +4158,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>from axi_write_engine</t>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4170,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wr_drain_req</t>
+          <t>r_axi_wr_sram_valid</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4208,11 +4183,11 @@
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>drain_ctrl.rd_valid</t>
+          <t>axi_wr_sram_valid (Q)</t>
         </is>
       </c>
       <c r="H36" s="7">
@@ -4237,26 +4212,73 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>from axi_write_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>sram_controller</t>
+          <t>registers latency_bridge.m_valid before driving the boundary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>axi_rd_alloc_space_free[AW:0]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>u_alloc_ctrl.space_free (Q)</t>
+        </is>
+      </c>
+      <c r="H37" s="7">
+        <f>E37*characterization!$D$17 + F37*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I37" s="7">
+        <f>E37*characterization!$G$17 + F37*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J37" s="7">
+        <f>E37*characterization!$J$17 + F37*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K37" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L37" s="7">
+        <f>K37 + H37</f>
+        <v/>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sram_controller</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ch_alloc_req[N-1:0]</t>
+          <t>axi_rd_sram_valid</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4264,16 +4286,20 @@
           <t>in</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>per-ch sram_controller_unit</t>
+          <t>u_channel_fifo.wr_valid</t>
         </is>
       </c>
       <c r="H38" s="7">
@@ -4298,36 +4324,40 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>from axi_read_engine (N-channel fan-out)</t>
+          <t>from axi_read_engine (write data into SRAM FIFO)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sram_controller</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ch_alloc_space_free[N-1:0][AW:0]</t>
+          <t>axi_rd_sram_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>per-ch alloc.space_free</t>
+          <t>u_channel_fifo.wr_data</t>
         </is>
       </c>
       <c r="H39" s="7">
@@ -4352,36 +4382,40 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>to axi_read_engine</t>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sram_controller</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ch_rd_valid[N-1:0]</t>
+          <t>axi_rd_sram_ready</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>per-ch SRAM FIFO wr</t>
+          <t>u_channel_fifo.wr_ready (Q)</t>
         </is>
       </c>
       <c r="H40" s="7">
@@ -4406,19 +4440,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>from axi_read_engine</t>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sram_controller</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ch_wr_valid[N-1:0]</t>
+          <t>axi_wr_sram_valid</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4428,14 +4462,14 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>per-ch SRAM FIFO read</t>
+          <t>r_axi_wr_sram_valid (Q)</t>
         </is>
       </c>
       <c r="H41" s="7">
@@ -4467,12 +4501,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sram_controller</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ch_wr_data[N-1:0][DW-1:0]</t>
+          <t>axi_wr_sram_data[DW-1:0]</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4480,16 +4514,20 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>per-ch fifo rd_data</t>
+          <t>u_latency_bridge.m_data (Q)</t>
         </is>
       </c>
       <c r="H42" s="7">
@@ -4518,22 +4556,69 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>perf_profiler</t>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_ready</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>u_latency_bridge.m_ready</t>
+        </is>
+      </c>
+      <c r="H43" s="7">
+        <f>E43*characterization!$D$17 + F43*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I43" s="7">
+        <f>E43*characterization!$G$17 + F43*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J43" s="7">
+        <f>E43*characterization!$J$17 + F43*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K43" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L43" s="7">
+        <f>K43 + H43</f>
+        <v/>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>from axi_write_engine</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller_unit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>channel_idle[N-1:0]</t>
+          <t>wr_drain_req</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4543,14 +4628,14 @@
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>edge-detect flops</t>
+          <t>u_drain_ctrl.rd_valid</t>
         </is>
       </c>
       <c r="H44" s="7">
@@ -4575,73 +4660,26 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>from scheduler (per-ch idle state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>perf_profiler</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>cfg_enable</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>control flop</t>
-        </is>
-      </c>
-      <c r="H45" s="7">
-        <f>E45*characterization!$D$17 + F45*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I45" s="7">
-        <f>E45*characterization!$G$17 + F45*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J45" s="7">
-        <f>E45*characterization!$J$17 + F45*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K45" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L45" s="7">
-        <f>K45 + H45</f>
-        <v/>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>from APB CSR</t>
+          <t>from axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>sram_controller</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cfg_clear</t>
+          <t>ch_alloc_req[N-1:0]</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4651,14 +4689,14 @@
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>FIFO reset path</t>
+          <t>u_unit[ch].axi_rd_alloc_req (D)</t>
         </is>
       </c>
       <c r="H46" s="7">
@@ -4683,40 +4721,36 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>from APB CSR</t>
+          <t>from axi_read_engine (N-channel fan-out)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>perf_fifo_rd</t>
+          <t>ch_alloc_space_free[N-1:0][AW:0]</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_valid</t>
+          <t>u_unit[ch].axi_rd_alloc_space_free</t>
         </is>
       </c>
       <c r="H47" s="7">
@@ -4741,40 +4775,36 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>from APB CSR pop strobe</t>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>perf_fifo_data_low[31:0]</t>
+          <t>ch_rd_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_data[31:0]</t>
+          <t>u_unit[ch].axi_rd_sram_valid (D)</t>
         </is>
       </c>
       <c r="H48" s="7">
@@ -4799,19 +4829,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>to APB CSR (host read)</t>
+          <t>from axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>perf_fifo_data_high[31:0]</t>
+          <t>ch_wr_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4819,20 +4849,16 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>u_perf_fifo.rd_data[63:32]</t>
+          <t>u_unit[ch].axi_wr_sram_valid (Q)</t>
         </is>
       </c>
       <c r="H49" s="7">
@@ -4857,19 +4883,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>to APB CSR</t>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>perf_profiler</t>
+          <t>sram_controller</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>perf_fifo_empty</t>
+          <t>ch_wr_data[N-1:0][DW-1:0]</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4877,20 +4903,16 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>u_perf_fifo empty flag</t>
+          <t>u_unit[ch].axi_wr_sram_data (Q)</t>
         </is>
       </c>
       <c r="H50" s="7">
@@ -4915,84 +4937,80 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>to APB CSR</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>perf_profiler</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>perf_fifo_count[15:0]</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>u_perf_fifo.count</t>
-        </is>
-      </c>
-      <c r="H51" s="7">
-        <f>E51*characterization!$D$17 + F51*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I51" s="7">
-        <f>E51*characterization!$G$17 + F51*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J51" s="7">
-        <f>E51*characterization!$J$17 + F51*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K51" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L51" s="7">
-        <f>K51 + H51</f>
-        <v/>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>to APB CSR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>apbtodescr</t>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>channel_idle[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>r_channel_idle_prev (D)</t>
+        </is>
+      </c>
+      <c r="H52" s="7">
+        <f>E52*characterization!$D$17 + F52*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I52" s="7">
+        <f>E52*characterization!$G$17 + F52*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J52" s="7">
+        <f>E52*characterization!$J$17 + F52*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K52" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L52" s="7">
+        <f>K52 + H52</f>
+        <v/>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>from scheduler (per-ch idle state)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>apb_cmd_valid</t>
+          <t>cfg_enable</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -5009,7 +5027,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>r_apb_cmd_valid</t>
+          <t>r_enable (D)</t>
         </is>
       </c>
       <c r="H53" s="7">
@@ -5034,19 +5052,19 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>from APB master</t>
+          <t>from APB CSR</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>apb_cmd_addr[ADDR_WIDTH-1:0]</t>
+          <t>cfg_clear</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5063,7 +5081,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>address decoder</t>
+          <t>FIFO async-clear path</t>
         </is>
       </c>
       <c r="H54" s="7">
@@ -5088,36 +5106,36 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>from APB master</t>
+          <t>from APB CSR</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>apb_cmd_wdata[DATA_WIDTH-1:0]</t>
+          <t>r_timestamp[63:0]</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>per-ch desc address mux</t>
+          <t>r_event_payload (D)</t>
         </is>
       </c>
       <c r="H55" s="7">
@@ -5142,24 +5160,24 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>from APB master (descriptor pointer write)</t>
+          <t>free-running counter; +1 every cycle when enabled</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>apb_cmd_ready</t>
+          <t>r_channel_idle_prev</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -5171,7 +5189,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>comb (FIFO ready AND)</t>
+          <t>r_event_pending (D)</t>
         </is>
       </c>
       <c r="H56" s="7">
@@ -5196,24 +5214,24 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>to APB master</t>
+          <t>XOR with channel_idle = edge detect</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>apb_rsp_valid</t>
+          <t>r_event_pending</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5225,7 +5243,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>rsp pipeline flop</t>
+          <t>u_perf_fifo.wr_valid (D)</t>
         </is>
       </c>
       <c r="H57" s="7">
@@ -5250,36 +5268,36 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>to APB master</t>
+          <t>1 cycle pulse when edge detected</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>desc_apb_valid[N-1:0]</t>
+          <t>r_event_type</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>per-ch valid demux</t>
+          <t>u_perf_fifo.wr_data[high] (D)</t>
         </is>
       </c>
       <c r="H58" s="7">
@@ -5304,27 +5322,31 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>to descriptor_engine[N] (kick-off)</t>
+          <t>rise / fall event code</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>desc_apb_addr[N-1:0][DA-1:0]</t>
+          <t>perf_fifo_rd</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
       </c>
@@ -5333,7 +5355,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>per-ch addr flops</t>
+          <t>u_perf_fifo.rd_valid</t>
         </is>
       </c>
       <c r="H59" s="7">
@@ -5358,36 +5380,40 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>to descriptor_engine[N] (initial descriptor pointer)</t>
+          <t>from APB CSR pop strobe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>apbtodescr</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>desc_apb_ready[N-1:0]</t>
+          <t>perf_fifo_data_low[31:0]</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>per-ch desc_engine ack</t>
+          <t>u_perf_fifo.rd_data[31:0] (Q)</t>
         </is>
       </c>
       <c r="H60" s="7">
@@ -5412,43 +5438,98 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>from descriptor_engine[N]</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>descriptor_engine</t>
+          <t>to APB CSR (host read)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>perf_profiler</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>perf_fifo_data_high[31:0]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>u_perf_fifo.rd_data[63:32] (Q)</t>
+        </is>
+      </c>
+      <c r="H61" s="7">
+        <f>E61*characterization!$D$17 + F61*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I61" s="7">
+        <f>E61*characterization!$G$17 + F61*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J61" s="7">
+        <f>E61*characterization!$J$17 + F61*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K61" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L61" s="7">
+        <f>K61 + H61</f>
+        <v/>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>to APB CSR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>desc_apb_valid</t>
+          <t>perf_fifo_empty</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>r_state IDLE -&gt; FETCH</t>
+          <t>u_perf_fifo.empty (Q)</t>
         </is>
       </c>
       <c r="H62" s="7">
@@ -5473,27 +5554,31 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>from apbtodescr (kick-off)</t>
+          <t>to APB CSR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>perf_profiler</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>desc_apb_addr[DA-1:0]</t>
+          <t>perf_fifo_count[15:0]</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
@@ -5502,7 +5587,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>r_desc_addr flop</t>
+          <t>u_perf_fifo.count (Q)</t>
         </is>
       </c>
       <c r="H63" s="7">
@@ -5527,77 +5612,26 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>from apbtodescr</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>descriptor_engine</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>desc_axi_ar_*</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>AR skid head Q</t>
-        </is>
-      </c>
-      <c r="H64" s="7">
-        <f>E64*characterization!$D$17 + F64*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I64" s="7">
-        <f>E64*characterization!$G$17 + F64*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J64" s="7">
-        <f>E64*characterization!$J$17 + F64*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K64" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L64" s="7">
-        <f>K64 + H64</f>
-        <v/>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>to scheduler_group desc_axi master</t>
+          <t>to APB CSR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>desc_axi_r_*</t>
+          <t>apb_cmd_valid</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5605,20 +5639,16 @@
           <t>in</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>R skid input</t>
+          <t>r_apb_cmd_valid (D)</t>
         </is>
       </c>
       <c r="H65" s="7">
@@ -5643,40 +5673,36 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>from scheduler_group desc_axi master</t>
+          <t>from APB master</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>descriptor_valid</t>
+          <t>apb_cmd_addr[ADDR_WIDTH-1:0]</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>i_descriptor_fifo.rd_valid</t>
+          <t>r_state addr-decode (D)</t>
         </is>
       </c>
       <c r="H66" s="7">
@@ -5701,40 +5727,36 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>to scheduler (descriptor dispatch)</t>
+          <t>from APB master</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>descriptor_data[256-1:0]</t>
+          <t>apb_cmd_wdata[DATA_WIDTH-1:0]</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>i_descriptor_fifo.rd_data</t>
+          <t>r_ch_addr[ch] (D)</t>
         </is>
       </c>
       <c r="H67" s="7">
@@ -5759,40 +5781,36 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>to scheduler</t>
+          <t>from APB master (descriptor pointer write)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>descriptor_engine</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>descriptor_ready</t>
+          <t>r_state</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>i_descriptor_fifo.rd_ready</t>
+          <t>r_apb_rsp_valid (D)</t>
         </is>
       </c>
       <c r="H68" s="7">
@@ -5817,31 +5835,78 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>from scheduler</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>scheduler</t>
+          <t>1-state FSM: ACCEPT -&gt; RSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>apbtodescr</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>r_ch_addr[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>desc_apb_addr (Q)</t>
+        </is>
+      </c>
+      <c r="H69" s="7">
+        <f>E69*characterization!$D$17 + F69*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I69" s="7">
+        <f>E69*characterization!$G$17 + F69*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J69" s="7">
+        <f>E69*characterization!$J$17 + F69*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K69" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L69" s="7">
+        <f>K69 + H69</f>
+        <v/>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>per-channel registered descriptor pointer</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>descriptor_valid</t>
+          <t>r_ch_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5853,7 +5918,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>r_state IDLE -&gt; RUN</t>
+          <t>desc_apb_valid (Q)</t>
         </is>
       </c>
       <c r="H70" s="7">
@@ -5878,24 +5943,24 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>from descriptor_engine</t>
+          <t>per-channel kickoff valid; clears on desc_engine ack</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>descriptor_data[256-1:0]</t>
+          <t>apb_cmd_ready</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5903,11 +5968,11 @@
         <v>0</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>r_descriptor latch</t>
+          <t>comb (FIFO ready AND)</t>
         </is>
       </c>
       <c r="H71" s="7">
@@ -5932,19 +5997,19 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>from descriptor_engine</t>
+          <t>to APB master</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>axi_rd_req_valid</t>
+          <t>apb_rsp_valid</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5957,11 +6022,11 @@
         <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>r_axi_rd_req state</t>
+          <t>r_apb_rsp_valid (Q)</t>
         </is>
       </c>
       <c r="H72" s="7">
@@ -5986,19 +6051,19 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>to axi_read_engine (per-channel request)</t>
+          <t>to APB master</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>axi_rd_req_addr[63:0]</t>
+          <t>desc_apb_valid[N-1:0]</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6015,7 +6080,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>r_src_addr+offset</t>
+          <t>r_ch_valid (Q)</t>
         </is>
       </c>
       <c r="H73" s="7">
@@ -6040,19 +6105,19 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>to axi_read_engine</t>
+          <t>to descriptor_engine[N] (kick-off)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>axi_wr_req_valid</t>
+          <t>desc_apb_addr[N-1:0][DA-1:0]</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6065,11 +6130,11 @@
         <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>r_axi_wr_req state</t>
+          <t>r_ch_addr (Q)</t>
         </is>
       </c>
       <c r="H74" s="7">
@@ -6094,36 +6159,36 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>to axi_write_engine</t>
+          <t>to descriptor_engine[N] (initial descriptor pointer)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>apbtodescr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>axi_wr_req_addr[63:0]</t>
+          <t>desc_apb_ready[N-1:0]</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>r_dst_addr+offset</t>
+          <t>clears r_ch_valid[ch]</t>
         </is>
       </c>
       <c r="H75" s="7">
@@ -6148,78 +6213,31 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>to axi_write_engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>scheduler</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ch_idle</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>r_state == IDLE</t>
-        </is>
-      </c>
-      <c r="H76" s="7">
-        <f>E76*characterization!$D$17 + F76*characterization!$D$15</f>
-        <v/>
-      </c>
-      <c r="I76" s="7">
-        <f>E76*characterization!$G$17 + F76*characterization!$G$15</f>
-        <v/>
-      </c>
-      <c r="J76" s="7">
-        <f>E76*characterization!$J$17 + F76*characterization!$J$15</f>
-        <v/>
-      </c>
-      <c r="K76" s="5">
-        <f>$D$2</f>
-        <v/>
-      </c>
-      <c r="L76" s="7">
-        <f>K76 + H76</f>
-        <v/>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>to perf_profiler</t>
+          <t>from descriptor_engine[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ch_done_strobe</t>
+          <t>desc_apb_valid</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6231,7 +6249,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>r_state -&gt; DONE pulse</t>
+          <t>r_state (D)</t>
         </is>
       </c>
       <c r="H77" s="7">
@@ -6256,24 +6274,24 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>to monbus_reporter</t>
+          <t>from apbtodescr (kick-off)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>scheduler</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>monbus_pkt</t>
+          <t>desc_apb_addr[DA-1:0]</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6281,11 +6299,11 @@
         <v>0</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>event-encode comb</t>
+          <t>r_desc_addr (D)</t>
         </is>
       </c>
       <c r="H78" s="7">
@@ -6310,43 +6328,90 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>to monbus group / reporter</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
-        <is>
-          <t>axi_read_engine</t>
+          <t>from apbtodescr</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>descriptor_engine</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>r_state</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>AR skid wr_valid (D)</t>
+        </is>
+      </c>
+      <c r="H79" s="7">
+        <f>E79*characterization!$D$17 + F79*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I79" s="7">
+        <f>E79*characterization!$G$17 + F79*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J79" s="7">
+        <f>E79*characterization!$J$17 + F79*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K79" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L79" s="7">
+        <f>K79 + H79</f>
+        <v/>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>FSM IDLE -&gt; FETCH -&gt; WAIT_RDATA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sched_req_valid[N-1:0]</t>
+          <t>r_desc_addr</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>u_arbiter (CLIENTS=N)</t>
+          <t>AR skid wr_data (D)</t>
         </is>
       </c>
       <c r="H80" s="7">
@@ -6371,36 +6436,36 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>from scheduler[N] (per-channel)</t>
+          <t>drives ARADDR into the AR skid buffer</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>sched_req_addr[N-1:0][63:0]</t>
+          <t>r_descriptor[256:0]</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>u_arbiter granted addr mux</t>
+          <t>i_descriptor_fifo.wr_data (D)</t>
         </is>
       </c>
       <c r="H81" s="7">
@@ -6425,40 +6490,36 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>from scheduler[N]</t>
+          <t>captured descriptor data from R-channel</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>m_axi_ar_*</t>
+          <t>r_chain_valid</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>u_rd_axi_skid (AR side)</t>
+          <t>r_desc_addr (D, next pointer)</t>
         </is>
       </c>
       <c r="H82" s="7">
@@ -6483,24 +6544,24 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>to AXI4 master read system bus</t>
+          <t>decodes next_descriptor_ptr -&gt; re-arm FSM</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>m_axi_r_*</t>
+          <t>desc_axi_ar_*</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>out</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6516,7 +6577,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>u_rd_axi_skid (R side)</t>
+          <t>AR skid head Q</t>
         </is>
       </c>
       <c r="H83" s="7">
@@ -6541,36 +6602,40 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>from AXI4 master read system bus</t>
+          <t>to scheduler_group desc_axi master</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>sram_alloc_req[N-1:0]</t>
+          <t>desc_axi_r_*</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>per-ch alloc req gen</t>
+          <t>R skid input</t>
         </is>
       </c>
       <c r="H84" s="7">
@@ -6595,36 +6660,40 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>to sram_controller_unit[N] (reserve burst space)</t>
+          <t>from scheduler_group desc_axi master</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>sram_alloc_space_free[N-1:0][AW:0]</t>
+          <t>descriptor_valid</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>per-ch space cmp</t>
+          <t>i_descriptor_fifo.rd_valid (Q)</t>
         </is>
       </c>
       <c r="H85" s="7">
@@ -6649,19 +6718,19 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>from sram_controller_unit[N]</t>
+          <t>to scheduler (descriptor dispatch)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>sram_wr_valid[N-1:0]</t>
+          <t>descriptor_data[256-1:0]</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6669,16 +6738,20 @@
           <t>out</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>post-arbiter demux</t>
+          <t>i_descriptor_fifo.rd_data (Q)</t>
         </is>
       </c>
       <c r="H86" s="7">
@@ -6703,27 +6776,31 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>to sram_controller_unit[N].wr</t>
+          <t>to scheduler</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>axi_read_engine</t>
+          <t>descriptor_engine</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>sram_wr_data[DW-1:0]</t>
+          <t>descriptor_ready</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
@@ -6732,7 +6809,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>R-skid data wire</t>
+          <t>i_descriptor_fifo.rd_ready</t>
         </is>
       </c>
       <c r="H87" s="7">
@@ -6757,26 +6834,26 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>to sram_controller_unit[N].wr (channel-id muxed)</t>
+          <t>from scheduler</t>
         </is>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>sched_req_valid[N-1:0]</t>
+          <t>descriptor_valid</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6786,14 +6863,14 @@
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>arbiter granted</t>
+          <t>r_state (D)</t>
         </is>
       </c>
       <c r="H89" s="7">
@@ -6818,19 +6895,19 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>from scheduler[N]</t>
+          <t>from descriptor_engine</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>sched_req_addr[N-1:0][63:0]</t>
+          <t>descriptor_data[256-1:0]</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -6840,14 +6917,14 @@
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>arbiter granted addr</t>
+          <t>r_descriptor (D)</t>
         </is>
       </c>
       <c r="H90" s="7">
@@ -6872,36 +6949,36 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>from scheduler[N]</t>
+          <t>from descriptor_engine: latch on accept</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>sram_rd_valid[N-1:0]</t>
+          <t>r_descriptor</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>drain ready cmp</t>
+          <t>r_src_addr, r_dst_addr, r_length (D)</t>
         </is>
       </c>
       <c r="H91" s="7">
@@ -6926,36 +7003,36 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>from sram_controller_unit[N] (data ready)</t>
+          <t>field unpack: SRC[63:0], DST[127:64], LEN[159:128]</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>sram_rd_data[N-1:0][DW-1:0]</t>
+          <t>r_state</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>per-ch read mux</t>
+          <t>r_axi_rd_req / r_axi_wr_req (D)</t>
         </is>
       </c>
       <c r="H92" s="7">
@@ -6980,24 +7057,24 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>from sram_controller_unit[N]</t>
+          <t>FSM IDLE -&gt; ISSUE_RD -&gt; ISSUE_WR -&gt; WAIT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sram_drain_req[N-1:0]</t>
+          <t>r_src_addr</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>local</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7009,7 +7086,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>drain reservation gen</t>
+          <t>r_axi_rd_req addr-incr (D)</t>
         </is>
       </c>
       <c r="H93" s="7">
@@ -7034,40 +7111,36 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>to sram_controller_unit[N]</t>
+          <t>src_addr + (beats_issued * DW/8)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>m_axi_aw_*</t>
+          <t>r_beats_remaining</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (AW side)</t>
+          <t>r_state DONE transition (D)</t>
         </is>
       </c>
       <c r="H94" s="7">
@@ -7092,40 +7165,36 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>to AXI4 master write system bus</t>
+          <t>decrement on each request; 0 -&gt; COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>m_axi_w_*</t>
+          <t>r_rd_outstanding</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>out</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (W side)</t>
+          <t>r_axi_rd_req throttle (D)</t>
         </is>
       </c>
       <c r="H95" s="7">
@@ -7150,31 +7219,27 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>to AXI4 master write system bus</t>
+          <t>request flow-control counter</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>m_axi_b_*</t>
+          <t>axi_rd_req_valid</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>gaxi_skid_buffer</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" s="5" t="n">
         <v>0</v>
       </c>
@@ -7183,7 +7248,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>u_wr_axi_skid (B side)</t>
+          <t>r_axi_rd_req (Q)</t>
         </is>
       </c>
       <c r="H96" s="7">
@@ -7208,31 +7273,27 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>from AXI4 master write system bus</t>
+          <t>to axi_read_engine (per-channel request)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>u_b_phase_txn_fifo wr</t>
+          <t>axi_rd_req_addr[63:0]</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" s="5" t="n">
         <v>0</v>
       </c>
@@ -7241,7 +7302,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>b-phase txn capture</t>
+          <t>r_src_addr + offset (Q)</t>
         </is>
       </c>
       <c r="H97" s="7">
@@ -7266,31 +7327,27 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>B-phase awaiting response</t>
+          <t>to axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>axi_write_engine</t>
+          <t>scheduler</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>u_w_phase_txn_fifo wr</t>
+          <t>axi_wr_req_valid</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>internal</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>gaxi_fifo_sync</t>
-        </is>
-      </c>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" s="5" t="n">
         <v>0</v>
       </c>
@@ -7299,7 +7356,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>w-phase txn capture</t>
+          <t>r_axi_wr_req (Q)</t>
         </is>
       </c>
       <c r="H98" s="7">
@@ -7324,70 +7381,2110 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>W-phase awaiting last-beat</t>
+          <t>to axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>axi_wr_req_addr[63:0]</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>r_dst_addr + offset (Q)</t>
+        </is>
+      </c>
+      <c r="H99" s="7">
+        <f>E99*characterization!$D$17 + F99*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I99" s="7">
+        <f>E99*characterization!$G$17 + F99*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J99" s="7">
+        <f>E99*characterization!$J$17 + F99*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K99" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L99" s="7">
+        <f>K99 + H99</f>
+        <v/>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>to axi_write_engine</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="inlineStr">
-        <is>
-          <t>Methodology</t>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ch_idle</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>comb of r_state == IDLE</t>
+        </is>
+      </c>
+      <c r="H100" s="7">
+        <f>E100*characterization!$D$17 + F100*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I100" s="7">
+        <f>E100*characterization!$G$17 + F100*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J100" s="7">
+        <f>E100*characterization!$J$17 + F100*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K100" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L100" s="7">
+        <f>K100 + H100</f>
+        <v/>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>to perf_profiler</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>One row per port (or significant internal handshake) per FUB. Hand-walked from the RTL.</t>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ch_done_strobe</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>r_state DONE-pulse (Q)</t>
+        </is>
+      </c>
+      <c r="H101" s="7">
+        <f>E101*characterization!$D$17 + F101*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I101" s="7">
+        <f>E101*characterization!$G$17 + F101*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J101" s="7">
+        <f>E101*characterization!$J$17 + F101*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K101" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L101" s="7">
+        <f>K101 + H101</f>
+        <v/>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>to monbus_reporter</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MUX lv / NAND lv = combinational gate-equivalents on the path within this FUB only - between the port and its nearest flop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>When a port enters/exits a building block (gaxi_fifo_sync, gaxi_skid_buffer), the BB internal cost is captured on the 'building blocks' sheet - no double-counting here.</t>
+          <t>scheduler</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>monbus_pkt</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>r_monbus_pkt event-encode (Q)</t>
+        </is>
+      </c>
+      <c r="H102" s="7">
+        <f>E102*characterization!$D$17 + F102*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I102" s="7">
+        <f>E102*characterization!$G$17 + F102*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J102" s="7">
+        <f>E102*characterization!$J$17 + F102*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K102" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L102" s="7">
+        <f>K102 + H102</f>
+        <v/>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>to monbus group / reporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>'places it goes' lists the concrete consumer/producer in the wider STREAM hierarchy (stream_core / scheduler_group / APB CSR / system AXI bus).</t>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sched_req_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>u_arbiter (CLIENTS=N)</t>
+        </is>
+      </c>
+      <c r="H104" s="7">
+        <f>E104*characterization!$D$17 + F104*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I104" s="7">
+        <f>E104*characterization!$G$17 + F104*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J104" s="7">
+        <f>E104*characterization!$J$17 + F104*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K104" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L104" s="7">
+        <f>K104 + H104</f>
+        <v/>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>from scheduler[N] (per-channel)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>sched_req_addr[N-1:0][63:0]</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>u_arbiter granted addr mux</t>
+        </is>
+      </c>
+      <c r="H105" s="7">
+        <f>E105*characterization!$D$17 + F105*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I105" s="7">
+        <f>E105*characterization!$G$17 + F105*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J105" s="7">
+        <f>E105*characterization!$J$17 + F105*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K105" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L105" s="7">
+        <f>K105 + H105</f>
+        <v/>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>r_arb_winner[clog2(N)-1:0]</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>r_active_ch (D)</t>
+        </is>
+      </c>
+      <c r="H106" s="7">
+        <f>E106*characterization!$D$17 + F106*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I106" s="7">
+        <f>E106*characterization!$G$17 + F106*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J106" s="7">
+        <f>E106*characterization!$J$17 + F106*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K106" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L106" s="7">
+        <f>K106 + H106</f>
+        <v/>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>round-robin output latch</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>r_active_ch</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>r_axi_ar_addr / r_axi_ar_len (D)</t>
+        </is>
+      </c>
+      <c r="H107" s="7">
+        <f>E107*characterization!$D$17 + F107*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I107" s="7">
+        <f>E107*characterization!$G$17 + F107*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J107" s="7">
+        <f>E107*characterization!$J$17 + F107*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K107" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L107" s="7">
+        <f>K107 + H107</f>
+        <v/>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>channel context for AR launch + R capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>r_axi_ar_addr</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid.wr_data (D)</t>
+        </is>
+      </c>
+      <c r="H108" s="7">
+        <f>E108*characterization!$D$17 + F108*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I108" s="7">
+        <f>E108*characterization!$G$17 + F108*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J108" s="7">
+        <f>E108*characterization!$J$17 + F108*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K108" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L108" s="7">
+        <f>K108 + H108</f>
+        <v/>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>pipelined ARADDR before skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>r_axi_ar_valid</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid.wr_valid (D)</t>
+        </is>
+      </c>
+      <c r="H109" s="7">
+        <f>E109*characterization!$D$17 + F109*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I109" s="7">
+        <f>E109*characterization!$G$17 + F109*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J109" s="7">
+        <f>E109*characterization!$J$17 + F109*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K109" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L109" s="7">
+        <f>K109 + H109</f>
+        <v/>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>registered request to skid</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>r_outstanding[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>r_axi_ar_valid throttle</t>
+        </is>
+      </c>
+      <c r="H110" s="7">
+        <f>E110*characterization!$D$17 + F110*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I110" s="7">
+        <f>E110*characterization!$G$17 + F110*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J110" s="7">
+        <f>E110*characterization!$J$17 + F110*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K110" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L110" s="7">
+        <f>K110 + H110</f>
+        <v/>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>per-channel in-flight counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>r_burst_id_ctr</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>r_axi_ar_addr id field (D)</t>
+        </is>
+      </c>
+      <c r="H111" s="7">
+        <f>E111*characterization!$D$17 + F111*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I111" s="7">
+        <f>E111*characterization!$G$17 + F111*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J111" s="7">
+        <f>E111*characterization!$J$17 + F111*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K111" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L111" s="7">
+        <f>K111 + H111</f>
+        <v/>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>monotonic AXI ID generator</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>m_axi_ar_*</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid AR head (Q)</t>
+        </is>
+      </c>
+      <c r="H112" s="7">
+        <f>E112*characterization!$D$17 + F112*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I112" s="7">
+        <f>E112*characterization!$G$17 + F112*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J112" s="7">
+        <f>E112*characterization!$J$17 + F112*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K112" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L112" s="7">
+        <f>K112 + H112</f>
+        <v/>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>to AXI4 master read system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>m_axi_r_*</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid R input</t>
+        </is>
+      </c>
+      <c r="H113" s="7">
+        <f>E113*characterization!$D$17 + F113*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I113" s="7">
+        <f>E113*characterization!$G$17 + F113*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J113" s="7">
+        <f>E113*characterization!$J$17 + F113*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K113" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L113" s="7">
+        <f>K113 + H113</f>
+        <v/>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>from AXI4 master read system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sram_alloc_req[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>r_axi_ar_valid demux (Q)</t>
+        </is>
+      </c>
+      <c r="H114" s="7">
+        <f>E114*characterization!$D$17 + F114*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I114" s="7">
+        <f>E114*characterization!$G$17 + F114*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J114" s="7">
+        <f>E114*characterization!$J$17 + F114*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K114" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L114" s="7">
+        <f>K114 + H114</f>
+        <v/>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N] (reserve burst space)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>sram_alloc_space_free[N-1:0][AW:0]</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>back-pressure cmp</t>
+        </is>
+      </c>
+      <c r="H115" s="7">
+        <f>E115*characterization!$D$17 + F115*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I115" s="7">
+        <f>E115*characterization!$G$17 + F115*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J115" s="7">
+        <f>E115*characterization!$J$17 + F115*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K115" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L115" s="7">
+        <f>K115 + H115</f>
+        <v/>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>sram_wr_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>r_active_ch demux of R-skid valid (Q)</t>
+        </is>
+      </c>
+      <c r="H116" s="7">
+        <f>E116*characterization!$D$17 + F116*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I116" s="7">
+        <f>E116*characterization!$G$17 + F116*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J116" s="7">
+        <f>E116*characterization!$J$17 + F116*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K116" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L116" s="7">
+        <f>K116 + H116</f>
+        <v/>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N].wr</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sram_wr_data[DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>u_rd_axi_skid.rd_data (Q)</t>
+        </is>
+      </c>
+      <c r="H117" s="7">
+        <f>E117*characterization!$D$17 + F117*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I117" s="7">
+        <f>E117*characterization!$G$17 + F117*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J117" s="7">
+        <f>E117*characterization!$J$17 + F117*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K117" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L117" s="7">
+        <f>K117 + H117</f>
+        <v/>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N].wr (channel-id muxed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>sched_req_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>arbiter (D)</t>
+        </is>
+      </c>
+      <c r="H119" s="7">
+        <f>E119*characterization!$D$17 + F119*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I119" s="7">
+        <f>E119*characterization!$G$17 + F119*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J119" s="7">
+        <f>E119*characterization!$J$17 + F119*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K119" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L119" s="7">
+        <f>K119 + H119</f>
+        <v/>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>sched_req_addr[N-1:0][63:0]</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>arbiter addr mux (D)</t>
+        </is>
+      </c>
+      <c r="H120" s="7">
+        <f>E120*characterization!$D$17 + F120*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I120" s="7">
+        <f>E120*characterization!$G$17 + F120*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J120" s="7">
+        <f>E120*characterization!$J$17 + F120*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K120" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L120" s="7">
+        <f>K120 + H120</f>
+        <v/>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>from scheduler[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sram_rd_valid[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>r_w_phase_active (D)</t>
+        </is>
+      </c>
+      <c r="H121" s="7">
+        <f>E121*characterization!$D$17 + F121*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I121" s="7">
+        <f>E121*characterization!$G$17 + F121*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J121" s="7">
+        <f>E121*characterization!$J$17 + F121*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K121" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L121" s="7">
+        <f>K121 + H121</f>
+        <v/>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N] (data ready)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sram_rd_data[N-1:0][DW-1:0]</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>r_axi_w_data (D)</t>
+        </is>
+      </c>
+      <c r="H122" s="7">
+        <f>E122*characterization!$D$17 + F122*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I122" s="7">
+        <f>E122*characterization!$G$17 + F122*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J122" s="7">
+        <f>E122*characterization!$J$17 + F122*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K122" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L122" s="7">
+        <f>K122 + H122</f>
+        <v/>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>from sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>r_arb_winner</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>r_active_ch (D)</t>
+        </is>
+      </c>
+      <c r="H123" s="7">
+        <f>E123*characterization!$D$17 + F123*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I123" s="7">
+        <f>E123*characterization!$G$17 + F123*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J123" s="7">
+        <f>E123*characterization!$J$17 + F123*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K123" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L123" s="7">
+        <f>K123 + H123</f>
+        <v/>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>round-robin output latch</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>r_active_ch</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>r_axi_aw_addr / r_axi_w_data (D)</t>
+        </is>
+      </c>
+      <c r="H124" s="7">
+        <f>E124*characterization!$D$17 + F124*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I124" s="7">
+        <f>E124*characterization!$G$17 + F124*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J124" s="7">
+        <f>E124*characterization!$J$17 + F124*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K124" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L124" s="7">
+        <f>K124 + H124</f>
+        <v/>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>channel context for AW launch + W stream</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>r_axi_aw_addr</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid AW.wr_data (D)</t>
+        </is>
+      </c>
+      <c r="H125" s="7">
+        <f>E125*characterization!$D$17 + F125*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I125" s="7">
+        <f>E125*characterization!$G$17 + F125*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J125" s="7">
+        <f>E125*characterization!$J$17 + F125*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K125" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L125" s="7">
+        <f>K125 + H125</f>
+        <v/>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>pipelined AWADDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>r_axi_aw_valid</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid AW.wr_valid (D)</t>
+        </is>
+      </c>
+      <c r="H126" s="7">
+        <f>E126*characterization!$D$17 + F126*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I126" s="7">
+        <f>E126*characterization!$G$17 + F126*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J126" s="7">
+        <f>E126*characterization!$J$17 + F126*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K126" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L126" s="7">
+        <f>K126 + H126</f>
+        <v/>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>registered AW request</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>r_axi_w_data</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid W.wr_data (D)</t>
+        </is>
+      </c>
+      <c r="H127" s="7">
+        <f>E127*characterization!$D$17 + F127*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I127" s="7">
+        <f>E127*characterization!$G$17 + F127*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J127" s="7">
+        <f>E127*characterization!$J$17 + F127*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K127" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L127" s="7">
+        <f>K127 + H127</f>
+        <v/>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>W-beat data pipeline reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>r_axi_w_last</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid W.wr_data WLAST bit (D)</t>
+        </is>
+      </c>
+      <c r="H128" s="7">
+        <f>E128*characterization!$D$17 + F128*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I128" s="7">
+        <f>E128*characterization!$G$17 + F128*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J128" s="7">
+        <f>E128*characterization!$J$17 + F128*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K128" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L128" s="7">
+        <f>K128 + H128</f>
+        <v/>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>burst termination flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>r_w_phase_active</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>r_drain_req (D)</t>
+        </is>
+      </c>
+      <c r="H129" s="7">
+        <f>E129*characterization!$D$17 + F129*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I129" s="7">
+        <f>E129*characterization!$G$17 + F129*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J129" s="7">
+        <f>E129*characterization!$J$17 + F129*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K129" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L129" s="7">
+        <f>K129 + H129</f>
+        <v/>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>tracks burst in-flight; gates drain request</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>r_b_phase_active</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>u_b_phase_txn_fifo wr enable (D)</t>
+        </is>
+      </c>
+      <c r="H130" s="7">
+        <f>E130*characterization!$D$17 + F130*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I130" s="7">
+        <f>E130*characterization!$G$17 + F130*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J130" s="7">
+        <f>E130*characterization!$J$17 + F130*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K130" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L130" s="7">
+        <f>K130 + H130</f>
+        <v/>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>BRESP-await counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>r_drain_req</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>sram_drain_req (Q)</t>
+        </is>
+      </c>
+      <c r="H131" s="7">
+        <f>E131*characterization!$D$17 + F131*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I131" s="7">
+        <f>E131*characterization!$G$17 + F131*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J131" s="7">
+        <f>E131*characterization!$J$17 + F131*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K131" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L131" s="7">
+        <f>K131 + H131</f>
+        <v/>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>sram_drain_req[N-1:0]</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>r_drain_req demux (Q)</t>
+        </is>
+      </c>
+      <c r="H132" s="7">
+        <f>E132*characterization!$D$17 + F132*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I132" s="7">
+        <f>E132*characterization!$G$17 + F132*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J132" s="7">
+        <f>E132*characterization!$J$17 + F132*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K132" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L132" s="7">
+        <f>K132 + H132</f>
+        <v/>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>to sram_controller_unit[N]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>m_axi_aw_*</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid AW head (Q)</t>
+        </is>
+      </c>
+      <c r="H133" s="7">
+        <f>E133*characterization!$D$17 + F133*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I133" s="7">
+        <f>E133*characterization!$G$17 + F133*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J133" s="7">
+        <f>E133*characterization!$J$17 + F133*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K133" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L133" s="7">
+        <f>K133 + H133</f>
+        <v/>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>to AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>m_axi_w_*</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid W head (Q)</t>
+        </is>
+      </c>
+      <c r="H134" s="7">
+        <f>E134*characterization!$D$17 + F134*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I134" s="7">
+        <f>E134*characterization!$G$17 + F134*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J134" s="7">
+        <f>E134*characterization!$J$17 + F134*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K134" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L134" s="7">
+        <f>K134 + H134</f>
+        <v/>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>to AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>m_axi_b_*</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>gaxi_skid_buffer</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>u_wr_axi_skid B input</t>
+        </is>
+      </c>
+      <c r="H135" s="7">
+        <f>E135*characterization!$D$17 + F135*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I135" s="7">
+        <f>E135*characterization!$G$17 + F135*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J135" s="7">
+        <f>E135*characterization!$J$17 + F135*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K135" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L135" s="7">
+        <f>K135 + H135</f>
+        <v/>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>from AXI4 master write system bus</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>u_b_phase_txn_fifo wr</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>b-phase txn capture</t>
+        </is>
+      </c>
+      <c r="H136" s="7">
+        <f>E136*characterization!$D$17 + F136*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I136" s="7">
+        <f>E136*characterization!$G$17 + F136*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J136" s="7">
+        <f>E136*characterization!$J$17 + F136*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K136" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L136" s="7">
+        <f>K136 + H136</f>
+        <v/>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>B-phase awaiting response</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>axi_write_engine</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>u_w_phase_txn_fifo wr</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>gaxi_fifo_sync</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>w-phase txn capture</t>
+        </is>
+      </c>
+      <c r="H137" s="7">
+        <f>E137*characterization!$D$17 + F137*characterization!$D$15</f>
+        <v/>
+      </c>
+      <c r="I137" s="7">
+        <f>E137*characterization!$G$17 + F137*characterization!$G$15</f>
+        <v/>
+      </c>
+      <c r="J137" s="7">
+        <f>E137*characterization!$J$17 + F137*characterization!$J$15</f>
+        <v/>
+      </c>
+      <c r="K137" s="5">
+        <f>$D$2</f>
+        <v/>
+      </c>
+      <c r="L137" s="7">
+        <f>K137 + H137</f>
+        <v/>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>W-phase awaiting last-beat</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>One row per port (or significant internal handshake) per FUB. Hand-walked from the RTL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>MUX lv / NAND lv = combinational gate-equivalents on the path within this FUB only - between the port and its nearest flop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>When a port enters/exits a building block (gaxi_fifo_sync, gaxi_skid_buffer), the BB internal cost is captured on the 'building blocks' sheet - no double-counting here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>'places it goes' lists the concrete consumer/producer in the wider STREAM hierarchy (stream_core / scheduler_group / APB CSR / system AXI bus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>AXI bus signals (m_axi_ar_*, m_axi_r_*, m_axi_aw_*, m_axi_w_*, m_axi_b_*) are summarized as channel groups for brevity; each is a set of skid buffer outputs whose detailed cost is in the building blocks 'gaxi_skid_buffer' / 'axi4_master_rd/wr' rows.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="A76:M76"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="A142:M142"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A23:M23"/>
     <mergeCell ref="A103:M103"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A79:M79"/>
-    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A118:M118"/>
+    <mergeCell ref="A141:M141"/>
+    <mergeCell ref="A144:M144"/>
     <mergeCell ref="A88:M88"/>
-    <mergeCell ref="A105:M105"/>
+    <mergeCell ref="A143:M143"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A26:M26"/>
-    <mergeCell ref="A101:M101"/>
-    <mergeCell ref="A69:M69"/>
-    <mergeCell ref="A104:M104"/>
-    <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="A140:M140"/>
+    <mergeCell ref="A64:M64"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A51:M51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -107,10 +107,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1258,7 +1258,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Clocks defined</t>
+          <t>Design clock  -  single configurable target</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1274,435 +1274,306 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>clk_500MHz  (500 MHz)</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>2000</v>
+          <t>Target clock frequency (MHz):</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Target clock period (ps):</t>
+        </is>
+      </c>
+      <c r="D28" s="6">
+        <f>1000000/B28</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>clk_750MHz  (750 MHz)</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>1333.3</v>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>clk_1000MHz  (1000 MHz)</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1000</v>
-      </c>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>STA boundary timing budget defaults  -  input 60% / output 40% of design period</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Input delay (60% of design period, ps):</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>D28*0.6</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>STA boundary timing budget defaults  -  input 60% / output 40% of period</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Output delay (40% of design period, ps):</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <f>D28*0.4</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Input delay  (60% of period, ps)</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>600</v>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Output delay (40% of period, ps)</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>533.3</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>533.3</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>533.3</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>400</v>
-      </c>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Wire delay per mm by metal layer (buffered route, ps/mm) - cross-partition route estimate</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>M2/M3 (local / intermediate)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Wire delay per mm by metal layer (buffered route, ps/mm) - cross-partition route estimate</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>M4/M5 (semi-global)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>M2/M3 (local / intermediate)</t>
+          <t>M6/M7 (global)</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>156</v>
+        <v>52</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>156</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>M4/M5 (semi-global)</t>
+          <t>M8/M9 (thick)</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>52</v>
+        <v>17.6</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>52</v>
+        <v>17.6</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>52</v>
+        <v>17.6</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>84.5</v>
+        <v>28.6</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>84.5</v>
+        <v>28.6</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>84.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>M6/M7 (global)</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D39" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>52</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>52</v>
-      </c>
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>M8/M9 (thick)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D40" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>28.6</v>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Probe corner_freq columns are independent measurements (see Per-level table above).</t>
+          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tflop = Tcq + Tsu derived from NAND chain two-point probe (LEVELS={3,6}).</t>
+          <t>** When the critical path is a mixed bag of cells (typical for datapath / FSM next-state / arbitration logic), use the MULT per-level number. It bakes in AND / XOR / full-adder / carry mix.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>max_levels = floor((period_ps - Tflop) / per_level_delay).</t>
+          <t>INV: ABC's strash collapses inverter pairs across the chain, so lev doesn't change between probe sizes - per-level slope is degenerate. Single-point delay is reported in the reference table.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>** When the critical path is a mixed bag of cells (typical for datapath / FSM next-state / arbitration logic), use the MULT per-level number. It bakes in AND / XOR / full-adder / carry mix.</t>
+          <t>CLK_DIV: critical path is intra-stage (counter + pickoff), so NUM_STAGES doesn't move lev. Single-point delay is reported in the reference table.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>INV: ABC's strash collapses inverter pairs across the chain, so lev doesn't change between probe sizes - per-level slope is degenerate. Single-point delay is reported in the reference table.</t>
+          <t>Wire delays are 7nm industry rule-of-thumb for buffered routes; the ASAP7 NLDM ships no wire_load table so ABC measured gate delay only. For partition-to-partition output budgeting, look up the destination metal layer and multiply by route length (mm).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
-        <is>
-          <t>CLK_DIV: critical path is intra-stage (counter + pickoff), so NUM_STAGES doesn't move lev. Single-point delay is reported in the reference table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Wire delays are 7nm industry rule-of-thumb for buffered routes; the ASAP7 NLDM ships no wire_load table so ABC measured gate delay only. For partition-to-partition output budgeting, look up the destination metal layer and multiply by route length (mm).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
         <is>
           <t>Raw probe data is in work/timing_char_data.csv. Reproducer is work/timing_char_sweep.py.</t>
         </is>
@@ -1915,7 +1786,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>CONFIG -&gt; target period (ps):</t>
         </is>
@@ -1923,21 +1794,21 @@
       <c r="B2" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>input delay 60% (ps):</t>
         </is>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <f>B2*0.6</f>
         <v/>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>output delay 40% (ps):</t>
         </is>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <f>B2*0.4</f>
         <v/>
       </c>
@@ -1955,7 +1826,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>SRAM (raw macro)</t>
         </is>
@@ -1984,15 +1855,15 @@
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <f>K4*characterization!$D$17 + L4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="6">
         <f>K4*characterization!$G$17 + L4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="6">
         <f>K4*characterization!$J$17 + L4*characterization!$J$15</f>
         <v/>
       </c>
@@ -2002,27 +1873,27 @@
       <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <f>P4*characterization!$D$17 + Q4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="6">
         <f>P4*characterization!$G$17 + Q4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T4" s="7">
+      <c r="T4" s="6">
         <f>P4*characterization!$J$17 + Q4*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="6">
         <f>ROUND(1000000/(MAX(M4,R4) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V4" s="7">
+      <c r="V4" s="6">
         <f>ROUND(1000000/(MAX(N4,S4) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W4" s="7">
+      <c r="W4" s="6">
         <f>ROUND(1000000/(MAX(O4,T4) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2030,27 +1901,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="6">
         <f>X4 + M4 + R4</f>
         <v/>
       </c>
-      <c r="Z4" s="7">
+      <c r="Z4" s="6">
         <f>X4 + N4 + S4</f>
         <v/>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="6">
         <f>X4 + O4 + T4</f>
         <v/>
       </c>
-      <c r="AC4" s="7">
+      <c r="AC4" s="6">
         <f>$B$2 - Y4 - $F$2</f>
         <v/>
       </c>
-      <c r="AD4" s="7">
+      <c r="AD4" s="6">
         <f>$B$2 - Z4 - $F$2</f>
         <v/>
       </c>
-      <c r="AE4" s="7">
+      <c r="AE4" s="6">
         <f>$B$2 - AA4 - $F$2</f>
         <v/>
       </c>
@@ -2061,7 +1932,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync (REG=1, SRAM-backed)</t>
         </is>
@@ -2091,15 +1962,15 @@
       <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <f>K5*characterization!$D$17 + L5*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="6">
         <f>K5*characterization!$G$17 + L5*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="6">
         <f>K5*characterization!$J$17 + L5*characterization!$J$15</f>
         <v/>
       </c>
@@ -2109,27 +1980,27 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="6">
         <f>P5*characterization!$D$17 + Q5*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S5" s="7">
+      <c r="S5" s="6">
         <f>P5*characterization!$G$17 + Q5*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T5" s="7">
+      <c r="T5" s="6">
         <f>P5*characterization!$J$17 + Q5*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U5" s="7">
+      <c r="U5" s="6">
         <f>ROUND(1000000/(MAX(M5,R5) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V5" s="7">
+      <c r="V5" s="6">
         <f>ROUND(1000000/(MAX(N5,S5) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W5" s="7">
+      <c r="W5" s="6">
         <f>ROUND(1000000/(MAX(O5,T5) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2137,27 +2008,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y5" s="7">
+      <c r="Y5" s="6">
         <f>X5 + M5 + R5</f>
         <v/>
       </c>
-      <c r="Z5" s="7">
+      <c r="Z5" s="6">
         <f>X5 + N5 + S5</f>
         <v/>
       </c>
-      <c r="AA5" s="7">
+      <c r="AA5" s="6">
         <f>X5 + O5 + T5</f>
         <v/>
       </c>
-      <c r="AC5" s="7">
+      <c r="AC5" s="6">
         <f>$B$2 - Y5 - $F$2</f>
         <v/>
       </c>
-      <c r="AD5" s="7">
+      <c r="AD5" s="6">
         <f>$B$2 - Z5 - $F$2</f>
         <v/>
       </c>
-      <c r="AE5" s="7">
+      <c r="AE5" s="6">
         <f>$B$2 - AA5 - $F$2</f>
         <v/>
       </c>
@@ -2175,7 +2046,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>gaxi_skid_buffer</t>
         </is>
@@ -2205,15 +2076,15 @@
       <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <f>K7*characterization!$D$17 + L7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="6">
         <f>K7*characterization!$G$17 + L7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="6">
         <f>K7*characterization!$J$17 + L7*characterization!$J$15</f>
         <v/>
       </c>
@@ -2223,27 +2094,27 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <f>P7*characterization!$D$17 + Q7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="6">
         <f>P7*characterization!$G$17 + Q7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T7" s="7">
+      <c r="T7" s="6">
         <f>P7*characterization!$J$17 + Q7*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U7" s="7">
+      <c r="U7" s="6">
         <f>ROUND(1000000/(MAX(M7,R7) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V7" s="7">
+      <c r="V7" s="6">
         <f>ROUND(1000000/(MAX(N7,S7) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W7" s="7">
+      <c r="W7" s="6">
         <f>ROUND(1000000/(MAX(O7,T7) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2251,27 +2122,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="6">
         <f>X7 + M7 + R7</f>
         <v/>
       </c>
-      <c r="Z7" s="7">
+      <c r="Z7" s="6">
         <f>X7 + N7 + S7</f>
         <v/>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="6">
         <f>X7 + O7 + T7</f>
         <v/>
       </c>
-      <c r="AC7" s="7">
+      <c r="AC7" s="6">
         <f>$B$2 - Y7 - $F$2</f>
         <v/>
       </c>
-      <c r="AD7" s="7">
+      <c r="AD7" s="6">
         <f>$B$2 - Z7 - $F$2</f>
         <v/>
       </c>
-      <c r="AE7" s="7">
+      <c r="AE7" s="6">
         <f>$B$2 - AA7 - $F$2</f>
         <v/>
       </c>
@@ -2282,7 +2153,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>gaxi_fifo_sync (REG=0)</t>
         </is>
@@ -2312,15 +2183,15 @@
       <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <f>K8*characterization!$D$17 + L8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="6">
         <f>K8*characterization!$G$17 + L8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="6">
         <f>K8*characterization!$J$17 + L8*characterization!$J$15</f>
         <v/>
       </c>
@@ -2331,27 +2202,27 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <f>P8*characterization!$D$17 + Q8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="6">
         <f>P8*characterization!$G$17 + Q8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T8" s="7">
+      <c r="T8" s="6">
         <f>P8*characterization!$J$17 + Q8*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U8" s="7">
+      <c r="U8" s="6">
         <f>ROUND(1000000/(MAX(M8,R8) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V8" s="7">
+      <c r="V8" s="6">
         <f>ROUND(1000000/(MAX(N8,S8) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W8" s="7">
+      <c r="W8" s="6">
         <f>ROUND(1000000/(MAX(O8,T8) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2359,27 +2230,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="6">
         <f>X8 + M8 + R8</f>
         <v/>
       </c>
-      <c r="Z8" s="7">
+      <c r="Z8" s="6">
         <f>X8 + N8 + S8</f>
         <v/>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="6">
         <f>X8 + O8 + T8</f>
         <v/>
       </c>
-      <c r="AC8" s="7">
+      <c r="AC8" s="6">
         <f>$B$2 - Y8 - $F$2</f>
         <v/>
       </c>
-      <c r="AD8" s="7">
+      <c r="AD8" s="6">
         <f>$B$2 - Z8 - $F$2</f>
         <v/>
       </c>
-      <c r="AE8" s="7">
+      <c r="AE8" s="6">
         <f>$B$2 - AA8 - $F$2</f>
         <v/>
       </c>
@@ -2390,7 +2261,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>arbiter_round_robin</t>
         </is>
@@ -2417,15 +2288,15 @@
       <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <f>K9*characterization!$D$17 + L9*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="6">
         <f>K9*characterization!$G$17 + L9*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="6">
         <f>K9*characterization!$J$17 + L9*characterization!$J$15</f>
         <v/>
       </c>
@@ -2436,27 +2307,27 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="6">
         <f>P9*characterization!$D$17 + Q9*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S9" s="7">
+      <c r="S9" s="6">
         <f>P9*characterization!$G$17 + Q9*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T9" s="7">
+      <c r="T9" s="6">
         <f>P9*characterization!$J$17 + Q9*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U9" s="7">
+      <c r="U9" s="6">
         <f>ROUND(1000000/(MAX(M9,R9) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V9" s="7">
+      <c r="V9" s="6">
         <f>ROUND(1000000/(MAX(N9,S9) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W9" s="7">
+      <c r="W9" s="6">
         <f>ROUND(1000000/(MAX(O9,T9) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2464,27 +2335,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="6">
         <f>X9 + M9 + R9</f>
         <v/>
       </c>
-      <c r="Z9" s="7">
+      <c r="Z9" s="6">
         <f>X9 + N9 + S9</f>
         <v/>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="6">
         <f>X9 + O9 + T9</f>
         <v/>
       </c>
-      <c r="AC9" s="7">
+      <c r="AC9" s="6">
         <f>$B$2 - Y9 - $F$2</f>
         <v/>
       </c>
-      <c r="AD9" s="7">
+      <c r="AD9" s="6">
         <f>$B$2 - Z9 - $F$2</f>
         <v/>
       </c>
-      <c r="AE9" s="7">
+      <c r="AE9" s="6">
         <f>$B$2 - AA9 - $F$2</f>
         <v/>
       </c>
@@ -2495,7 +2366,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>axi4_master_rd</t>
         </is>
@@ -2537,15 +2408,15 @@
       <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <f>K10*characterization!$D$17 + L10*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="6">
         <f>K10*characterization!$G$17 + L10*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="6">
         <f>K10*characterization!$J$17 + L10*characterization!$J$15</f>
         <v/>
       </c>
@@ -2555,27 +2426,27 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <f>P10*characterization!$D$17 + Q10*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S10" s="7">
+      <c r="S10" s="6">
         <f>P10*characterization!$G$17 + Q10*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T10" s="7">
+      <c r="T10" s="6">
         <f>P10*characterization!$J$17 + Q10*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U10" s="7">
+      <c r="U10" s="6">
         <f>ROUND(1000000/(MAX(M10,R10) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V10" s="7">
+      <c r="V10" s="6">
         <f>ROUND(1000000/(MAX(N10,S10) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W10" s="7">
+      <c r="W10" s="6">
         <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2583,27 +2454,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y10" s="7">
+      <c r="Y10" s="6">
         <f>X10 + M10 + R10</f>
         <v/>
       </c>
-      <c r="Z10" s="7">
+      <c r="Z10" s="6">
         <f>X10 + N10 + S10</f>
         <v/>
       </c>
-      <c r="AA10" s="7">
+      <c r="AA10" s="6">
         <f>X10 + O10 + T10</f>
         <v/>
       </c>
-      <c r="AC10" s="7">
+      <c r="AC10" s="6">
         <f>$B$2 - Y10 - $F$2</f>
         <v/>
       </c>
-      <c r="AD10" s="7">
+      <c r="AD10" s="6">
         <f>$B$2 - Z10 - $F$2</f>
         <v/>
       </c>
-      <c r="AE10" s="7">
+      <c r="AE10" s="6">
         <f>$B$2 - AA10 - $F$2</f>
         <v/>
       </c>
@@ -2614,7 +2485,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>axi4_master_wr</t>
         </is>
@@ -2656,15 +2527,15 @@
       <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <f>K11*characterization!$D$17 + L11*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="6">
         <f>K11*characterization!$G$17 + L11*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <f>K11*characterization!$J$17 + L11*characterization!$J$15</f>
         <v/>
       </c>
@@ -2674,27 +2545,27 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <f>P11*characterization!$D$17 + Q11*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="6">
         <f>P11*characterization!$G$17 + Q11*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="T11" s="7">
+      <c r="T11" s="6">
         <f>P11*characterization!$J$17 + Q11*characterization!$J$15</f>
         <v/>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="6">
         <f>ROUND(1000000/(MAX(M11,R11) + characterization!$D$3), 0)</f>
         <v/>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="6">
         <f>ROUND(1000000/(MAX(N11,S11) + characterization!$G$3), 0)</f>
         <v/>
       </c>
-      <c r="W11" s="7">
+      <c r="W11" s="6">
         <f>ROUND(1000000/(MAX(O11,T11) + characterization!$J$3), 0)</f>
         <v/>
       </c>
@@ -2702,27 +2573,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="Y11" s="7">
+      <c r="Y11" s="6">
         <f>X11 + M11 + R11</f>
         <v/>
       </c>
-      <c r="Z11" s="7">
+      <c r="Z11" s="6">
         <f>X11 + N11 + S11</f>
         <v/>
       </c>
-      <c r="AA11" s="7">
+      <c r="AA11" s="6">
         <f>X11 + O11 + T11</f>
         <v/>
       </c>
-      <c r="AC11" s="7">
+      <c r="AC11" s="6">
         <f>$B$2 - Y11 - $F$2</f>
         <v/>
       </c>
-      <c r="AD11" s="7">
+      <c r="AD11" s="6">
         <f>$B$2 - Z11 - $F$2</f>
         <v/>
       </c>
-      <c r="AE11" s="7">
+      <c r="AE11" s="6">
         <f>$B$2 - AA11 - $F$2</f>
         <v/>
       </c>
@@ -2733,7 +2604,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>SRAM storage size reference</t>
         </is>
@@ -2790,7 +2661,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Cell coding</t>
         </is>
@@ -2970,7 +2841,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>CONFIG -&gt; target period (ps):</t>
         </is>
@@ -2978,21 +2849,21 @@
       <c r="B2" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>input 60% (ps):</t>
         </is>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <f>B2*0.6</f>
         <v/>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>output 40% (ps):</t>
         </is>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <f>B2*0.4</f>
         <v/>
       </c>
@@ -3042,15 +2913,15 @@
           <t>r_drain_ip (D)</t>
         </is>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <f>F4*characterization!$D$17 + G4*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <f>F4*characterization!$G$17 + G4*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <f>F4*characterization!$J$17 + G4*characterization!$J$15</f>
         <v/>
       </c>
@@ -3058,27 +2929,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <f>L4 + I4</f>
         <v/>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="6">
         <f>L4 + J4</f>
         <v/>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="6">
         <f>L4 + K4</f>
         <v/>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="6">
         <f>$B$2 - M4 - $F$2</f>
         <v/>
       </c>
-      <c r="R4" s="7">
+      <c r="R4" s="6">
         <f>$B$2 - N4 - $F$2</f>
         <v/>
       </c>
-      <c r="S4" s="7">
+      <c r="S4" s="6">
         <f>$B$2 - O4 - $F$2</f>
         <v/>
       </c>
@@ -3125,15 +2996,15 @@
           <t>u_skid_buffer.wr_data</t>
         </is>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="6">
         <f>F5*characterization!$D$17 + G5*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <f>F5*characterization!$G$17 + G5*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <f>F5*characterization!$J$17 + G5*characterization!$J$15</f>
         <v/>
       </c>
@@ -3141,27 +3012,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <f>L5 + I5</f>
         <v/>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="6">
         <f>L5 + J5</f>
         <v/>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="6">
         <f>L5 + K5</f>
         <v/>
       </c>
-      <c r="Q5" s="7">
+      <c r="Q5" s="6">
         <f>$B$2 - M5 - $F$2</f>
         <v/>
       </c>
-      <c r="R5" s="7">
+      <c r="R5" s="6">
         <f>$B$2 - N5 - $F$2</f>
         <v/>
       </c>
-      <c r="S5" s="7">
+      <c r="S5" s="6">
         <f>$B$2 - O5 - $F$2</f>
         <v/>
       </c>
@@ -3204,15 +3075,15 @@
           <t>u_skid_buffer.wr_valid (D)</t>
         </is>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="6">
         <f>F6*characterization!$D$17 + G6*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <f>F6*characterization!$G$17 + G6*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <f>F6*characterization!$J$17 + G6*characterization!$J$15</f>
         <v/>
       </c>
@@ -3220,27 +3091,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <f>L6 + I6</f>
         <v/>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="6">
         <f>L6 + J6</f>
         <v/>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="6">
         <f>L6 + K6</f>
         <v/>
       </c>
-      <c r="Q6" s="7">
+      <c r="Q6" s="6">
         <f>$B$2 - M6 - $F$2</f>
         <v/>
       </c>
-      <c r="R6" s="7">
+      <c r="R6" s="6">
         <f>$B$2 - N6 - $F$2</f>
         <v/>
       </c>
-      <c r="S6" s="7">
+      <c r="S6" s="6">
         <f>$B$2 - O6 - $F$2</f>
         <v/>
       </c>
@@ -3283,15 +3154,15 @@
           <t>comb of u_skid_buffer.count + r_drain_ip</t>
         </is>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="6">
         <f>F7*characterization!$D$17 + G7*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <f>F7*characterization!$G$17 + G7*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <f>F7*characterization!$J$17 + G7*characterization!$J$15</f>
         <v/>
       </c>
@@ -3299,27 +3170,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="6">
         <f>L7 + I7</f>
         <v/>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="6">
         <f>L7 + J7</f>
         <v/>
       </c>
-      <c r="O7" s="7">
+      <c r="O7" s="6">
         <f>L7 + K7</f>
         <v/>
       </c>
-      <c r="Q7" s="7">
+      <c r="Q7" s="6">
         <f>$B$2 - M7 - $F$2</f>
         <v/>
       </c>
-      <c r="R7" s="7">
+      <c r="R7" s="6">
         <f>$B$2 - N7 - $F$2</f>
         <v/>
       </c>
-      <c r="S7" s="7">
+      <c r="S7" s="6">
         <f>$B$2 - O7 - $F$2</f>
         <v/>
       </c>
@@ -3366,15 +3237,15 @@
           <t>u_skid_buffer.rd_valid (Q)</t>
         </is>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="6">
         <f>F8*characterization!$D$17 + G8*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <f>F8*characterization!$G$17 + G8*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <f>F8*characterization!$J$17 + G8*characterization!$J$15</f>
         <v/>
       </c>
@@ -3382,27 +3253,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <f>L8 + I8</f>
         <v/>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="6">
         <f>L8 + J8</f>
         <v/>
       </c>
-      <c r="O8" s="7">
+      <c r="O8" s="6">
         <f>L8 + K8</f>
         <v/>
       </c>
-      <c r="Q8" s="7">
+      <c r="Q8" s="6">
         <f>$B$2 - M8 - $F$2</f>
         <v/>
       </c>
-      <c r="R8" s="7">
+      <c r="R8" s="6">
         <f>$B$2 - N8 - $F$2</f>
         <v/>
       </c>
-      <c r="S8" s="7">
+      <c r="S8" s="6">
         <f>$B$2 - O8 - $F$2</f>
         <v/>
       </c>
@@ -3449,15 +3320,15 @@
           <t>u_skid_buffer.rd_data (Q)</t>
         </is>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="6">
         <f>F9*characterization!$D$17 + G9*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <f>F9*characterization!$G$17 + G9*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <f>F9*characterization!$J$17 + G9*characterization!$J$15</f>
         <v/>
       </c>
@@ -3465,27 +3336,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <f>L9 + I9</f>
         <v/>
       </c>
-      <c r="N9" s="7">
+      <c r="N9" s="6">
         <f>L9 + J9</f>
         <v/>
       </c>
-      <c r="O9" s="7">
+      <c r="O9" s="6">
         <f>L9 + K9</f>
         <v/>
       </c>
-      <c r="Q9" s="7">
+      <c r="Q9" s="6">
         <f>$B$2 - M9 - $F$2</f>
         <v/>
       </c>
-      <c r="R9" s="7">
+      <c r="R9" s="6">
         <f>$B$2 - N9 - $F$2</f>
         <v/>
       </c>
-      <c r="S9" s="7">
+      <c r="S9" s="6">
         <f>$B$2 - O9 - $F$2</f>
         <v/>
       </c>
@@ -3532,15 +3403,15 @@
           <t>u_skid_buffer.rd_ready</t>
         </is>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="6">
         <f>F10*characterization!$D$17 + G10*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <f>F10*characterization!$G$17 + G10*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <f>F10*characterization!$J$17 + G10*characterization!$J$15</f>
         <v/>
       </c>
@@ -3548,27 +3419,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <f>L10 + I10</f>
         <v/>
       </c>
-      <c r="N10" s="7">
+      <c r="N10" s="6">
         <f>L10 + J10</f>
         <v/>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="6">
         <f>L10 + K10</f>
         <v/>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="6">
         <f>$B$2 - M10 - $F$2</f>
         <v/>
       </c>
-      <c r="R10" s="7">
+      <c r="R10" s="6">
         <f>$B$2 - N10 - $F$2</f>
         <v/>
       </c>
-      <c r="S10" s="7">
+      <c r="S10" s="6">
         <f>$B$2 - O10 - $F$2</f>
         <v/>
       </c>
@@ -3615,15 +3486,15 @@
           <t>u_skid_buffer.count (Q)</t>
         </is>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="6">
         <f>F11*characterization!$D$17 + G11*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <f>F11*characterization!$G$17 + G11*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <f>F11*characterization!$J$17 + G11*characterization!$J$15</f>
         <v/>
       </c>
@@ -3631,27 +3502,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M11" s="7">
+      <c r="M11" s="6">
         <f>L11 + I11</f>
         <v/>
       </c>
-      <c r="N11" s="7">
+      <c r="N11" s="6">
         <f>L11 + J11</f>
         <v/>
       </c>
-      <c r="O11" s="7">
+      <c r="O11" s="6">
         <f>L11 + K11</f>
         <v/>
       </c>
-      <c r="Q11" s="7">
+      <c r="Q11" s="6">
         <f>$B$2 - M11 - $F$2</f>
         <v/>
       </c>
-      <c r="R11" s="7">
+      <c r="R11" s="6">
         <f>$B$2 - N11 - $F$2</f>
         <v/>
       </c>
-      <c r="S11" s="7">
+      <c r="S11" s="6">
         <f>$B$2 - O11 - $F$2</f>
         <v/>
       </c>
@@ -3694,15 +3565,15 @@
           <t>r_drain_ip (Q)</t>
         </is>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <f>F12*characterization!$D$17 + G12*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <f>F12*characterization!$G$17 + G12*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <f>F12*characterization!$J$17 + G12*characterization!$J$15</f>
         <v/>
       </c>
@@ -3710,27 +3581,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="6">
         <f>L12 + I12</f>
         <v/>
       </c>
-      <c r="N12" s="7">
+      <c r="N12" s="6">
         <f>L12 + J12</f>
         <v/>
       </c>
-      <c r="O12" s="7">
+      <c r="O12" s="6">
         <f>L12 + K12</f>
         <v/>
       </c>
-      <c r="Q12" s="7">
+      <c r="Q12" s="6">
         <f>$B$2 - M12 - $F$2</f>
         <v/>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="6">
         <f>$B$2 - N12 - $F$2</f>
         <v/>
       </c>
-      <c r="S12" s="7">
+      <c r="S12" s="6">
         <f>$B$2 - O12 - $F$2</f>
         <v/>
       </c>
@@ -3780,15 +3651,15 @@
           <t>r_wr_ptr (D)</t>
         </is>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="6">
         <f>F14*characterization!$D$17 + G14*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="6">
         <f>F14*characterization!$G$17 + G14*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <f>F14*characterization!$J$17 + G14*characterization!$J$15</f>
         <v/>
       </c>
@@ -3796,27 +3667,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M14" s="7">
+      <c r="M14" s="6">
         <f>L14 + I14</f>
         <v/>
       </c>
-      <c r="N14" s="7">
+      <c r="N14" s="6">
         <f>L14 + J14</f>
         <v/>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="6">
         <f>L14 + K14</f>
         <v/>
       </c>
-      <c r="Q14" s="7">
+      <c r="Q14" s="6">
         <f>$B$2 - M14 - $F$2</f>
         <v/>
       </c>
-      <c r="R14" s="7">
+      <c r="R14" s="6">
         <f>$B$2 - N14 - $F$2</f>
         <v/>
       </c>
-      <c r="S14" s="7">
+      <c r="S14" s="6">
         <f>$B$2 - O14 - $F$2</f>
         <v/>
       </c>
@@ -3859,15 +3730,15 @@
           <t>r_wr_ptr adder input</t>
         </is>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="6">
         <f>F15*characterization!$D$17 + G15*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="6">
         <f>F15*characterization!$G$17 + G15*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="6">
         <f>F15*characterization!$J$17 + G15*characterization!$J$15</f>
         <v/>
       </c>
@@ -3875,27 +3746,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="6">
         <f>L15 + I15</f>
         <v/>
       </c>
-      <c r="N15" s="7">
+      <c r="N15" s="6">
         <f>L15 + J15</f>
         <v/>
       </c>
-      <c r="O15" s="7">
+      <c r="O15" s="6">
         <f>L15 + K15</f>
         <v/>
       </c>
-      <c r="Q15" s="7">
+      <c r="Q15" s="6">
         <f>$B$2 - M15 - $F$2</f>
         <v/>
       </c>
-      <c r="R15" s="7">
+      <c r="R15" s="6">
         <f>$B$2 - N15 - $F$2</f>
         <v/>
       </c>
-      <c r="S15" s="7">
+      <c r="S15" s="6">
         <f>$B$2 - O15 - $F$2</f>
         <v/>
       </c>
@@ -3938,15 +3809,15 @@
           <t>r_rd_ptr (D)</t>
         </is>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="6">
         <f>F16*characterization!$D$17 + G16*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="6">
         <f>F16*characterization!$G$17 + G16*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <f>F16*characterization!$J$17 + G16*characterization!$J$15</f>
         <v/>
       </c>
@@ -3954,27 +3825,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="6">
         <f>L16 + I16</f>
         <v/>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="6">
         <f>L16 + J16</f>
         <v/>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="6">
         <f>L16 + K16</f>
         <v/>
       </c>
-      <c r="Q16" s="7">
+      <c r="Q16" s="6">
         <f>$B$2 - M16 - $F$2</f>
         <v/>
       </c>
-      <c r="R16" s="7">
+      <c r="R16" s="6">
         <f>$B$2 - N16 - $F$2</f>
         <v/>
       </c>
-      <c r="S16" s="7">
+      <c r="S16" s="6">
         <f>$B$2 - O16 - $F$2</f>
         <v/>
       </c>
@@ -4017,15 +3888,15 @@
           <t>r_space_free (D)</t>
         </is>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="6">
         <f>F17*characterization!$D$17 + G17*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="6">
         <f>F17*characterization!$G$17 + G17*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="6">
         <f>F17*characterization!$J$17 + G17*characterization!$J$15</f>
         <v/>
       </c>
@@ -4033,27 +3904,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="6">
         <f>L17 + I17</f>
         <v/>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="6">
         <f>L17 + J17</f>
         <v/>
       </c>
-      <c r="O17" s="7">
+      <c r="O17" s="6">
         <f>L17 + K17</f>
         <v/>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q17" s="6">
         <f>$B$2 - M17 - $F$2</f>
         <v/>
       </c>
-      <c r="R17" s="7">
+      <c r="R17" s="6">
         <f>$B$2 - N17 - $F$2</f>
         <v/>
       </c>
-      <c r="S17" s="7">
+      <c r="S17" s="6">
         <f>$B$2 - O17 - $F$2</f>
         <v/>
       </c>
@@ -4096,15 +3967,15 @@
           <t>r_space_free (D)</t>
         </is>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="6">
         <f>F18*characterization!$D$17 + G18*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="6">
         <f>F18*characterization!$G$17 + G18*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
         <f>F18*characterization!$J$17 + G18*characterization!$J$15</f>
         <v/>
       </c>
@@ -4112,27 +3983,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="6">
         <f>L18 + I18</f>
         <v/>
       </c>
-      <c r="N18" s="7">
+      <c r="N18" s="6">
         <f>L18 + J18</f>
         <v/>
       </c>
-      <c r="O18" s="7">
+      <c r="O18" s="6">
         <f>L18 + K18</f>
         <v/>
       </c>
-      <c r="Q18" s="7">
+      <c r="Q18" s="6">
         <f>$B$2 - M18 - $F$2</f>
         <v/>
       </c>
-      <c r="R18" s="7">
+      <c r="R18" s="6">
         <f>$B$2 - N18 - $F$2</f>
         <v/>
       </c>
-      <c r="S18" s="7">
+      <c r="S18" s="6">
         <f>$B$2 - O18 - $F$2</f>
         <v/>
       </c>
@@ -4175,15 +4046,15 @@
           <t>r_wr_full (D)</t>
         </is>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="6">
         <f>F19*characterization!$D$17 + G19*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <f>F19*characterization!$G$17 + G19*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <f>F19*characterization!$J$17 + G19*characterization!$J$15</f>
         <v/>
       </c>
@@ -4191,27 +4062,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="6">
         <f>L19 + I19</f>
         <v/>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <f>L19 + J19</f>
         <v/>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <f>L19 + K19</f>
         <v/>
       </c>
-      <c r="Q19" s="7">
+      <c r="Q19" s="6">
         <f>$B$2 - M19 - $F$2</f>
         <v/>
       </c>
-      <c r="R19" s="7">
+      <c r="R19" s="6">
         <f>$B$2 - N19 - $F$2</f>
         <v/>
       </c>
-      <c r="S19" s="7">
+      <c r="S19" s="6">
         <f>$B$2 - O19 - $F$2</f>
         <v/>
       </c>
@@ -4254,15 +4125,15 @@
           <t>r_space_free (Q)</t>
         </is>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="6">
         <f>F20*characterization!$D$17 + G20*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="6">
         <f>F20*characterization!$G$17 + G20*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="6">
         <f>F20*characterization!$J$17 + G20*characterization!$J$15</f>
         <v/>
       </c>
@@ -4270,27 +4141,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="6">
         <f>L20 + I20</f>
         <v/>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="6">
         <f>L20 + J20</f>
         <v/>
       </c>
-      <c r="O20" s="7">
+      <c r="O20" s="6">
         <f>L20 + K20</f>
         <v/>
       </c>
-      <c r="Q20" s="7">
+      <c r="Q20" s="6">
         <f>$B$2 - M20 - $F$2</f>
         <v/>
       </c>
-      <c r="R20" s="7">
+      <c r="R20" s="6">
         <f>$B$2 - N20 - $F$2</f>
         <v/>
       </c>
-      <c r="S20" s="7">
+      <c r="S20" s="6">
         <f>$B$2 - O20 - $F$2</f>
         <v/>
       </c>
@@ -4333,15 +4204,15 @@
           <t>r_wr_full (Q)</t>
         </is>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="6">
         <f>F21*characterization!$D$17 + G21*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="6">
         <f>F21*characterization!$G$17 + G21*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="6">
         <f>F21*characterization!$J$17 + G21*characterization!$J$15</f>
         <v/>
       </c>
@@ -4349,27 +4220,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="6">
         <f>L21 + I21</f>
         <v/>
       </c>
-      <c r="N21" s="7">
+      <c r="N21" s="6">
         <f>L21 + J21</f>
         <v/>
       </c>
-      <c r="O21" s="7">
+      <c r="O21" s="6">
         <f>L21 + K21</f>
         <v/>
       </c>
-      <c r="Q21" s="7">
+      <c r="Q21" s="6">
         <f>$B$2 - M21 - $F$2</f>
         <v/>
       </c>
-      <c r="R21" s="7">
+      <c r="R21" s="6">
         <f>$B$2 - N21 - $F$2</f>
         <v/>
       </c>
-      <c r="S21" s="7">
+      <c r="S21" s="6">
         <f>$B$2 - O21 - $F$2</f>
         <v/>
       </c>
@@ -4412,15 +4283,15 @@
           <t>r_wr_almost_full (Q)</t>
         </is>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="6">
         <f>F22*characterization!$D$17 + G22*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J22" s="7">
+      <c r="J22" s="6">
         <f>F22*characterization!$G$17 + G22*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="6">
         <f>F22*characterization!$J$17 + G22*characterization!$J$15</f>
         <v/>
       </c>
@@ -4428,27 +4299,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="6">
         <f>L22 + I22</f>
         <v/>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="6">
         <f>L22 + J22</f>
         <v/>
       </c>
-      <c r="O22" s="7">
+      <c r="O22" s="6">
         <f>L22 + K22</f>
         <v/>
       </c>
-      <c r="Q22" s="7">
+      <c r="Q22" s="6">
         <f>$B$2 - M22 - $F$2</f>
         <v/>
       </c>
-      <c r="R22" s="7">
+      <c r="R22" s="6">
         <f>$B$2 - N22 - $F$2</f>
         <v/>
       </c>
-      <c r="S22" s="7">
+      <c r="S22" s="6">
         <f>$B$2 - O22 - $F$2</f>
         <v/>
       </c>
@@ -4498,15 +4369,15 @@
           <t>r_wr_ptr (D)</t>
         </is>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="6">
         <f>F24*characterization!$D$17 + G24*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J24" s="7">
+      <c r="J24" s="6">
         <f>F24*characterization!$G$17 + G24*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K24" s="7">
+      <c r="K24" s="6">
         <f>F24*characterization!$J$17 + G24*characterization!$J$15</f>
         <v/>
       </c>
@@ -4514,27 +4385,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="6">
         <f>L24 + I24</f>
         <v/>
       </c>
-      <c r="N24" s="7">
+      <c r="N24" s="6">
         <f>L24 + J24</f>
         <v/>
       </c>
-      <c r="O24" s="7">
+      <c r="O24" s="6">
         <f>L24 + K24</f>
         <v/>
       </c>
-      <c r="Q24" s="7">
+      <c r="Q24" s="6">
         <f>$B$2 - M24 - $F$2</f>
         <v/>
       </c>
-      <c r="R24" s="7">
+      <c r="R24" s="6">
         <f>$B$2 - N24 - $F$2</f>
         <v/>
       </c>
-      <c r="S24" s="7">
+      <c r="S24" s="6">
         <f>$B$2 - O24 - $F$2</f>
         <v/>
       </c>
@@ -4577,15 +4448,15 @@
           <t>r_rd_ptr (D)</t>
         </is>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="6">
         <f>F25*characterization!$D$17 + G25*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="6">
         <f>F25*characterization!$G$17 + G25*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="6">
         <f>F25*characterization!$J$17 + G25*characterization!$J$15</f>
         <v/>
       </c>
@@ -4593,27 +4464,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="6">
         <f>L25 + I25</f>
         <v/>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="6">
         <f>L25 + J25</f>
         <v/>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="6">
         <f>L25 + K25</f>
         <v/>
       </c>
-      <c r="Q25" s="7">
+      <c r="Q25" s="6">
         <f>$B$2 - M25 - $F$2</f>
         <v/>
       </c>
-      <c r="R25" s="7">
+      <c r="R25" s="6">
         <f>$B$2 - N25 - $F$2</f>
         <v/>
       </c>
-      <c r="S25" s="7">
+      <c r="S25" s="6">
         <f>$B$2 - O25 - $F$2</f>
         <v/>
       </c>
@@ -4656,15 +4527,15 @@
           <t>r_rd_ptr adder input</t>
         </is>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="6">
         <f>F26*characterization!$D$17 + G26*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J26" s="7">
+      <c r="J26" s="6">
         <f>F26*characterization!$G$17 + G26*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K26" s="7">
+      <c r="K26" s="6">
         <f>F26*characterization!$J$17 + G26*characterization!$J$15</f>
         <v/>
       </c>
@@ -4672,27 +4543,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M26" s="7">
+      <c r="M26" s="6">
         <f>L26 + I26</f>
         <v/>
       </c>
-      <c r="N26" s="7">
+      <c r="N26" s="6">
         <f>L26 + J26</f>
         <v/>
       </c>
-      <c r="O26" s="7">
+      <c r="O26" s="6">
         <f>L26 + K26</f>
         <v/>
       </c>
-      <c r="Q26" s="7">
+      <c r="Q26" s="6">
         <f>$B$2 - M26 - $F$2</f>
         <v/>
       </c>
-      <c r="R26" s="7">
+      <c r="R26" s="6">
         <f>$B$2 - N26 - $F$2</f>
         <v/>
       </c>
-      <c r="S26" s="7">
+      <c r="S26" s="6">
         <f>$B$2 - O26 - $F$2</f>
         <v/>
       </c>
@@ -4735,15 +4606,15 @@
           <t>r_data_available (D)</t>
         </is>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <f>F27*characterization!$D$17 + G27*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <f>F27*characterization!$G$17 + G27*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <f>F27*characterization!$J$17 + G27*characterization!$J$15</f>
         <v/>
       </c>
@@ -4751,27 +4622,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <f>L27 + I27</f>
         <v/>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <f>L27 + J27</f>
         <v/>
       </c>
-      <c r="O27" s="7">
+      <c r="O27" s="6">
         <f>L27 + K27</f>
         <v/>
       </c>
-      <c r="Q27" s="7">
+      <c r="Q27" s="6">
         <f>$B$2 - M27 - $F$2</f>
         <v/>
       </c>
-      <c r="R27" s="7">
+      <c r="R27" s="6">
         <f>$B$2 - N27 - $F$2</f>
         <v/>
       </c>
-      <c r="S27" s="7">
+      <c r="S27" s="6">
         <f>$B$2 - O27 - $F$2</f>
         <v/>
       </c>
@@ -4814,15 +4685,15 @@
           <t>r_data_available (D)</t>
         </is>
       </c>
-      <c r="I28" s="7">
+      <c r="I28" s="6">
         <f>F28*characterization!$D$17 + G28*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J28" s="7">
+      <c r="J28" s="6">
         <f>F28*characterization!$G$17 + G28*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="6">
         <f>F28*characterization!$J$17 + G28*characterization!$J$15</f>
         <v/>
       </c>
@@ -4830,27 +4701,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="6">
         <f>L28 + I28</f>
         <v/>
       </c>
-      <c r="N28" s="7">
+      <c r="N28" s="6">
         <f>L28 + J28</f>
         <v/>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="6">
         <f>L28 + K28</f>
         <v/>
       </c>
-      <c r="Q28" s="7">
+      <c r="Q28" s="6">
         <f>$B$2 - M28 - $F$2</f>
         <v/>
       </c>
-      <c r="R28" s="7">
+      <c r="R28" s="6">
         <f>$B$2 - N28 - $F$2</f>
         <v/>
       </c>
-      <c r="S28" s="7">
+      <c r="S28" s="6">
         <f>$B$2 - O28 - $F$2</f>
         <v/>
       </c>
@@ -4893,15 +4764,15 @@
           <t>r_rd_empty (D)</t>
         </is>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="6">
         <f>F29*characterization!$D$17 + G29*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J29" s="7">
+      <c r="J29" s="6">
         <f>F29*characterization!$G$17 + G29*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="6">
         <f>F29*characterization!$J$17 + G29*characterization!$J$15</f>
         <v/>
       </c>
@@ -4909,27 +4780,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M29" s="7">
+      <c r="M29" s="6">
         <f>L29 + I29</f>
         <v/>
       </c>
-      <c r="N29" s="7">
+      <c r="N29" s="6">
         <f>L29 + J29</f>
         <v/>
       </c>
-      <c r="O29" s="7">
+      <c r="O29" s="6">
         <f>L29 + K29</f>
         <v/>
       </c>
-      <c r="Q29" s="7">
+      <c r="Q29" s="6">
         <f>$B$2 - M29 - $F$2</f>
         <v/>
       </c>
-      <c r="R29" s="7">
+      <c r="R29" s="6">
         <f>$B$2 - N29 - $F$2</f>
         <v/>
       </c>
-      <c r="S29" s="7">
+      <c r="S29" s="6">
         <f>$B$2 - O29 - $F$2</f>
         <v/>
       </c>
@@ -4972,15 +4843,15 @@
           <t>r_data_available (Q)</t>
         </is>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="6">
         <f>F30*characterization!$D$17 + G30*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J30" s="7">
+      <c r="J30" s="6">
         <f>F30*characterization!$G$17 + G30*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <f>F30*characterization!$J$17 + G30*characterization!$J$15</f>
         <v/>
       </c>
@@ -4988,27 +4859,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="6">
         <f>L30 + I30</f>
         <v/>
       </c>
-      <c r="N30" s="7">
+      <c r="N30" s="6">
         <f>L30 + J30</f>
         <v/>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="6">
         <f>L30 + K30</f>
         <v/>
       </c>
-      <c r="Q30" s="7">
+      <c r="Q30" s="6">
         <f>$B$2 - M30 - $F$2</f>
         <v/>
       </c>
-      <c r="R30" s="7">
+      <c r="R30" s="6">
         <f>$B$2 - N30 - $F$2</f>
         <v/>
       </c>
-      <c r="S30" s="7">
+      <c r="S30" s="6">
         <f>$B$2 - O30 - $F$2</f>
         <v/>
       </c>
@@ -5051,15 +4922,15 @@
           <t>r_rd_empty (Q)</t>
         </is>
       </c>
-      <c r="I31" s="7">
+      <c r="I31" s="6">
         <f>F31*characterization!$D$17 + G31*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J31" s="7">
+      <c r="J31" s="6">
         <f>F31*characterization!$G$17 + G31*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="6">
         <f>F31*characterization!$J$17 + G31*characterization!$J$15</f>
         <v/>
       </c>
@@ -5067,27 +4938,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="6">
         <f>L31 + I31</f>
         <v/>
       </c>
-      <c r="N31" s="7">
+      <c r="N31" s="6">
         <f>L31 + J31</f>
         <v/>
       </c>
-      <c r="O31" s="7">
+      <c r="O31" s="6">
         <f>L31 + K31</f>
         <v/>
       </c>
-      <c r="Q31" s="7">
+      <c r="Q31" s="6">
         <f>$B$2 - M31 - $F$2</f>
         <v/>
       </c>
-      <c r="R31" s="7">
+      <c r="R31" s="6">
         <f>$B$2 - N31 - $F$2</f>
         <v/>
       </c>
-      <c r="S31" s="7">
+      <c r="S31" s="6">
         <f>$B$2 - O31 - $F$2</f>
         <v/>
       </c>
@@ -5130,15 +5001,15 @@
           <t>r_wr_full (Q)</t>
         </is>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="6">
         <f>F32*characterization!$D$17 + G32*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J32" s="7">
+      <c r="J32" s="6">
         <f>F32*characterization!$G$17 + G32*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="6">
         <f>F32*characterization!$J$17 + G32*characterization!$J$15</f>
         <v/>
       </c>
@@ -5146,27 +5017,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M32" s="7">
+      <c r="M32" s="6">
         <f>L32 + I32</f>
         <v/>
       </c>
-      <c r="N32" s="7">
+      <c r="N32" s="6">
         <f>L32 + J32</f>
         <v/>
       </c>
-      <c r="O32" s="7">
+      <c r="O32" s="6">
         <f>L32 + K32</f>
         <v/>
       </c>
-      <c r="Q32" s="7">
+      <c r="Q32" s="6">
         <f>$B$2 - M32 - $F$2</f>
         <v/>
       </c>
-      <c r="R32" s="7">
+      <c r="R32" s="6">
         <f>$B$2 - N32 - $F$2</f>
         <v/>
       </c>
-      <c r="S32" s="7">
+      <c r="S32" s="6">
         <f>$B$2 - O32 - $F$2</f>
         <v/>
       </c>
@@ -5216,15 +5087,15 @@
           <t>u_alloc_ctrl.wr_valid</t>
         </is>
       </c>
-      <c r="I34" s="7">
+      <c r="I34" s="6">
         <f>F34*characterization!$D$17 + G34*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J34" s="7">
+      <c r="J34" s="6">
         <f>F34*characterization!$G$17 + G34*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K34" s="7">
+      <c r="K34" s="6">
         <f>F34*characterization!$J$17 + G34*characterization!$J$15</f>
         <v/>
       </c>
@@ -5232,27 +5103,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="6">
         <f>L34 + I34</f>
         <v/>
       </c>
-      <c r="N34" s="7">
+      <c r="N34" s="6">
         <f>L34 + J34</f>
         <v/>
       </c>
-      <c r="O34" s="7">
+      <c r="O34" s="6">
         <f>L34 + K34</f>
         <v/>
       </c>
-      <c r="Q34" s="7">
+      <c r="Q34" s="6">
         <f>$B$2 - M34 - $F$2</f>
         <v/>
       </c>
-      <c r="R34" s="7">
+      <c r="R34" s="6">
         <f>$B$2 - N34 - $F$2</f>
         <v/>
       </c>
-      <c r="S34" s="7">
+      <c r="S34" s="6">
         <f>$B$2 - O34 - $F$2</f>
         <v/>
       </c>
@@ -5295,15 +5166,15 @@
           <t>u_alloc_ctrl.wr_size</t>
         </is>
       </c>
-      <c r="I35" s="7">
+      <c r="I35" s="6">
         <f>F35*characterization!$D$17 + G35*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J35" s="7">
+      <c r="J35" s="6">
         <f>F35*characterization!$G$17 + G35*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K35" s="7">
+      <c r="K35" s="6">
         <f>F35*characterization!$J$17 + G35*characterization!$J$15</f>
         <v/>
       </c>
@@ -5311,27 +5182,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M35" s="7">
+      <c r="M35" s="6">
         <f>L35 + I35</f>
         <v/>
       </c>
-      <c r="N35" s="7">
+      <c r="N35" s="6">
         <f>L35 + J35</f>
         <v/>
       </c>
-      <c r="O35" s="7">
+      <c r="O35" s="6">
         <f>L35 + K35</f>
         <v/>
       </c>
-      <c r="Q35" s="7">
+      <c r="Q35" s="6">
         <f>$B$2 - M35 - $F$2</f>
         <v/>
       </c>
-      <c r="R35" s="7">
+      <c r="R35" s="6">
         <f>$B$2 - N35 - $F$2</f>
         <v/>
       </c>
-      <c r="S35" s="7">
+      <c r="S35" s="6">
         <f>$B$2 - O35 - $F$2</f>
         <v/>
       </c>
@@ -5374,15 +5245,15 @@
           <t>axi_wr_sram_valid (Q)</t>
         </is>
       </c>
-      <c r="I36" s="7">
+      <c r="I36" s="6">
         <f>F36*characterization!$D$17 + G36*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J36" s="7">
+      <c r="J36" s="6">
         <f>F36*characterization!$G$17 + G36*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K36" s="7">
+      <c r="K36" s="6">
         <f>F36*characterization!$J$17 + G36*characterization!$J$15</f>
         <v/>
       </c>
@@ -5390,27 +5261,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M36" s="7">
+      <c r="M36" s="6">
         <f>L36 + I36</f>
         <v/>
       </c>
-      <c r="N36" s="7">
+      <c r="N36" s="6">
         <f>L36 + J36</f>
         <v/>
       </c>
-      <c r="O36" s="7">
+      <c r="O36" s="6">
         <f>L36 + K36</f>
         <v/>
       </c>
-      <c r="Q36" s="7">
+      <c r="Q36" s="6">
         <f>$B$2 - M36 - $F$2</f>
         <v/>
       </c>
-      <c r="R36" s="7">
+      <c r="R36" s="6">
         <f>$B$2 - N36 - $F$2</f>
         <v/>
       </c>
-      <c r="S36" s="7">
+      <c r="S36" s="6">
         <f>$B$2 - O36 - $F$2</f>
         <v/>
       </c>
@@ -5453,15 +5324,15 @@
           <t>u_alloc_ctrl.space_free (Q)</t>
         </is>
       </c>
-      <c r="I37" s="7">
+      <c r="I37" s="6">
         <f>F37*characterization!$D$17 + G37*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J37" s="7">
+      <c r="J37" s="6">
         <f>F37*characterization!$G$17 + G37*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K37" s="7">
+      <c r="K37" s="6">
         <f>F37*characterization!$J$17 + G37*characterization!$J$15</f>
         <v/>
       </c>
@@ -5469,27 +5340,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M37" s="7">
+      <c r="M37" s="6">
         <f>L37 + I37</f>
         <v/>
       </c>
-      <c r="N37" s="7">
+      <c r="N37" s="6">
         <f>L37 + J37</f>
         <v/>
       </c>
-      <c r="O37" s="7">
+      <c r="O37" s="6">
         <f>L37 + K37</f>
         <v/>
       </c>
-      <c r="Q37" s="7">
+      <c r="Q37" s="6">
         <f>$B$2 - M37 - $F$2</f>
         <v/>
       </c>
-      <c r="R37" s="7">
+      <c r="R37" s="6">
         <f>$B$2 - N37 - $F$2</f>
         <v/>
       </c>
-      <c r="S37" s="7">
+      <c r="S37" s="6">
         <f>$B$2 - O37 - $F$2</f>
         <v/>
       </c>
@@ -5536,15 +5407,15 @@
           <t>u_channel_fifo.wr_valid</t>
         </is>
       </c>
-      <c r="I38" s="7">
+      <c r="I38" s="6">
         <f>F38*characterization!$D$17 + G38*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J38" s="7">
+      <c r="J38" s="6">
         <f>F38*characterization!$G$17 + G38*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K38" s="7">
+      <c r="K38" s="6">
         <f>F38*characterization!$J$17 + G38*characterization!$J$15</f>
         <v/>
       </c>
@@ -5552,27 +5423,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M38" s="7">
+      <c r="M38" s="6">
         <f>L38 + I38</f>
         <v/>
       </c>
-      <c r="N38" s="7">
+      <c r="N38" s="6">
         <f>L38 + J38</f>
         <v/>
       </c>
-      <c r="O38" s="7">
+      <c r="O38" s="6">
         <f>L38 + K38</f>
         <v/>
       </c>
-      <c r="Q38" s="7">
+      <c r="Q38" s="6">
         <f>$B$2 - M38 - $F$2</f>
         <v/>
       </c>
-      <c r="R38" s="7">
+      <c r="R38" s="6">
         <f>$B$2 - N38 - $F$2</f>
         <v/>
       </c>
-      <c r="S38" s="7">
+      <c r="S38" s="6">
         <f>$B$2 - O38 - $F$2</f>
         <v/>
       </c>
@@ -5619,15 +5490,15 @@
           <t>u_channel_fifo.wr_data</t>
         </is>
       </c>
-      <c r="I39" s="7">
+      <c r="I39" s="6">
         <f>F39*characterization!$D$17 + G39*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J39" s="7">
+      <c r="J39" s="6">
         <f>F39*characterization!$G$17 + G39*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="6">
         <f>F39*characterization!$J$17 + G39*characterization!$J$15</f>
         <v/>
       </c>
@@ -5635,27 +5506,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M39" s="7">
+      <c r="M39" s="6">
         <f>L39 + I39</f>
         <v/>
       </c>
-      <c r="N39" s="7">
+      <c r="N39" s="6">
         <f>L39 + J39</f>
         <v/>
       </c>
-      <c r="O39" s="7">
+      <c r="O39" s="6">
         <f>L39 + K39</f>
         <v/>
       </c>
-      <c r="Q39" s="7">
+      <c r="Q39" s="6">
         <f>$B$2 - M39 - $F$2</f>
         <v/>
       </c>
-      <c r="R39" s="7">
+      <c r="R39" s="6">
         <f>$B$2 - N39 - $F$2</f>
         <v/>
       </c>
-      <c r="S39" s="7">
+      <c r="S39" s="6">
         <f>$B$2 - O39 - $F$2</f>
         <v/>
       </c>
@@ -5702,15 +5573,15 @@
           <t>u_channel_fifo.wr_ready (Q)</t>
         </is>
       </c>
-      <c r="I40" s="7">
+      <c r="I40" s="6">
         <f>F40*characterization!$D$17 + G40*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J40" s="7">
+      <c r="J40" s="6">
         <f>F40*characterization!$G$17 + G40*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="6">
         <f>F40*characterization!$J$17 + G40*characterization!$J$15</f>
         <v/>
       </c>
@@ -5718,27 +5589,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M40" s="7">
+      <c r="M40" s="6">
         <f>L40 + I40</f>
         <v/>
       </c>
-      <c r="N40" s="7">
+      <c r="N40" s="6">
         <f>L40 + J40</f>
         <v/>
       </c>
-      <c r="O40" s="7">
+      <c r="O40" s="6">
         <f>L40 + K40</f>
         <v/>
       </c>
-      <c r="Q40" s="7">
+      <c r="Q40" s="6">
         <f>$B$2 - M40 - $F$2</f>
         <v/>
       </c>
-      <c r="R40" s="7">
+      <c r="R40" s="6">
         <f>$B$2 - N40 - $F$2</f>
         <v/>
       </c>
-      <c r="S40" s="7">
+      <c r="S40" s="6">
         <f>$B$2 - O40 - $F$2</f>
         <v/>
       </c>
@@ -5781,15 +5652,15 @@
           <t>r_axi_wr_sram_valid (Q)</t>
         </is>
       </c>
-      <c r="I41" s="7">
+      <c r="I41" s="6">
         <f>F41*characterization!$D$17 + G41*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J41" s="7">
+      <c r="J41" s="6">
         <f>F41*characterization!$G$17 + G41*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="6">
         <f>F41*characterization!$J$17 + G41*characterization!$J$15</f>
         <v/>
       </c>
@@ -5797,27 +5668,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M41" s="7">
+      <c r="M41" s="6">
         <f>L41 + I41</f>
         <v/>
       </c>
-      <c r="N41" s="7">
+      <c r="N41" s="6">
         <f>L41 + J41</f>
         <v/>
       </c>
-      <c r="O41" s="7">
+      <c r="O41" s="6">
         <f>L41 + K41</f>
         <v/>
       </c>
-      <c r="Q41" s="7">
+      <c r="Q41" s="6">
         <f>$B$2 - M41 - $F$2</f>
         <v/>
       </c>
-      <c r="R41" s="7">
+      <c r="R41" s="6">
         <f>$B$2 - N41 - $F$2</f>
         <v/>
       </c>
-      <c r="S41" s="7">
+      <c r="S41" s="6">
         <f>$B$2 - O41 - $F$2</f>
         <v/>
       </c>
@@ -5864,15 +5735,15 @@
           <t>u_latency_bridge.m_data (Q)</t>
         </is>
       </c>
-      <c r="I42" s="7">
+      <c r="I42" s="6">
         <f>F42*characterization!$D$17 + G42*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J42" s="7">
+      <c r="J42" s="6">
         <f>F42*characterization!$G$17 + G42*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="6">
         <f>F42*characterization!$J$17 + G42*characterization!$J$15</f>
         <v/>
       </c>
@@ -5880,27 +5751,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M42" s="7">
+      <c r="M42" s="6">
         <f>L42 + I42</f>
         <v/>
       </c>
-      <c r="N42" s="7">
+      <c r="N42" s="6">
         <f>L42 + J42</f>
         <v/>
       </c>
-      <c r="O42" s="7">
+      <c r="O42" s="6">
         <f>L42 + K42</f>
         <v/>
       </c>
-      <c r="Q42" s="7">
+      <c r="Q42" s="6">
         <f>$B$2 - M42 - $F$2</f>
         <v/>
       </c>
-      <c r="R42" s="7">
+      <c r="R42" s="6">
         <f>$B$2 - N42 - $F$2</f>
         <v/>
       </c>
-      <c r="S42" s="7">
+      <c r="S42" s="6">
         <f>$B$2 - O42 - $F$2</f>
         <v/>
       </c>
@@ -5943,15 +5814,15 @@
           <t>u_latency_bridge.m_ready</t>
         </is>
       </c>
-      <c r="I43" s="7">
+      <c r="I43" s="6">
         <f>F43*characterization!$D$17 + G43*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J43" s="7">
+      <c r="J43" s="6">
         <f>F43*characterization!$G$17 + G43*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K43" s="7">
+      <c r="K43" s="6">
         <f>F43*characterization!$J$17 + G43*characterization!$J$15</f>
         <v/>
       </c>
@@ -5959,27 +5830,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M43" s="7">
+      <c r="M43" s="6">
         <f>L43 + I43</f>
         <v/>
       </c>
-      <c r="N43" s="7">
+      <c r="N43" s="6">
         <f>L43 + J43</f>
         <v/>
       </c>
-      <c r="O43" s="7">
+      <c r="O43" s="6">
         <f>L43 + K43</f>
         <v/>
       </c>
-      <c r="Q43" s="7">
+      <c r="Q43" s="6">
         <f>$B$2 - M43 - $F$2</f>
         <v/>
       </c>
-      <c r="R43" s="7">
+      <c r="R43" s="6">
         <f>$B$2 - N43 - $F$2</f>
         <v/>
       </c>
-      <c r="S43" s="7">
+      <c r="S43" s="6">
         <f>$B$2 - O43 - $F$2</f>
         <v/>
       </c>
@@ -6022,15 +5893,15 @@
           <t>u_drain_ctrl.rd_valid</t>
         </is>
       </c>
-      <c r="I44" s="7">
+      <c r="I44" s="6">
         <f>F44*characterization!$D$17 + G44*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J44" s="7">
+      <c r="J44" s="6">
         <f>F44*characterization!$G$17 + G44*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K44" s="7">
+      <c r="K44" s="6">
         <f>F44*characterization!$J$17 + G44*characterization!$J$15</f>
         <v/>
       </c>
@@ -6038,27 +5909,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M44" s="7">
+      <c r="M44" s="6">
         <f>L44 + I44</f>
         <v/>
       </c>
-      <c r="N44" s="7">
+      <c r="N44" s="6">
         <f>L44 + J44</f>
         <v/>
       </c>
-      <c r="O44" s="7">
+      <c r="O44" s="6">
         <f>L44 + K44</f>
         <v/>
       </c>
-      <c r="Q44" s="7">
+      <c r="Q44" s="6">
         <f>$B$2 - M44 - $F$2</f>
         <v/>
       </c>
-      <c r="R44" s="7">
+      <c r="R44" s="6">
         <f>$B$2 - N44 - $F$2</f>
         <v/>
       </c>
-      <c r="S44" s="7">
+      <c r="S44" s="6">
         <f>$B$2 - O44 - $F$2</f>
         <v/>
       </c>
@@ -6108,15 +5979,15 @@
           <t>u_unit[ch].axi_rd_alloc_req (D)</t>
         </is>
       </c>
-      <c r="I46" s="7">
+      <c r="I46" s="6">
         <f>F46*characterization!$D$17 + G46*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J46" s="7">
+      <c r="J46" s="6">
         <f>F46*characterization!$G$17 + G46*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K46" s="7">
+      <c r="K46" s="6">
         <f>F46*characterization!$J$17 + G46*characterization!$J$15</f>
         <v/>
       </c>
@@ -6124,27 +5995,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M46" s="7">
+      <c r="M46" s="6">
         <f>L46 + I46</f>
         <v/>
       </c>
-      <c r="N46" s="7">
+      <c r="N46" s="6">
         <f>L46 + J46</f>
         <v/>
       </c>
-      <c r="O46" s="7">
+      <c r="O46" s="6">
         <f>L46 + K46</f>
         <v/>
       </c>
-      <c r="Q46" s="7">
+      <c r="Q46" s="6">
         <f>$B$2 - M46 - $F$2</f>
         <v/>
       </c>
-      <c r="R46" s="7">
+      <c r="R46" s="6">
         <f>$B$2 - N46 - $F$2</f>
         <v/>
       </c>
-      <c r="S46" s="7">
+      <c r="S46" s="6">
         <f>$B$2 - O46 - $F$2</f>
         <v/>
       </c>
@@ -6187,15 +6058,15 @@
           <t>u_unit[ch].axi_rd_alloc_space_free</t>
         </is>
       </c>
-      <c r="I47" s="7">
+      <c r="I47" s="6">
         <f>F47*characterization!$D$17 + G47*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J47" s="7">
+      <c r="J47" s="6">
         <f>F47*characterization!$G$17 + G47*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K47" s="7">
+      <c r="K47" s="6">
         <f>F47*characterization!$J$17 + G47*characterization!$J$15</f>
         <v/>
       </c>
@@ -6203,27 +6074,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M47" s="7">
+      <c r="M47" s="6">
         <f>L47 + I47</f>
         <v/>
       </c>
-      <c r="N47" s="7">
+      <c r="N47" s="6">
         <f>L47 + J47</f>
         <v/>
       </c>
-      <c r="O47" s="7">
+      <c r="O47" s="6">
         <f>L47 + K47</f>
         <v/>
       </c>
-      <c r="Q47" s="7">
+      <c r="Q47" s="6">
         <f>$B$2 - M47 - $F$2</f>
         <v/>
       </c>
-      <c r="R47" s="7">
+      <c r="R47" s="6">
         <f>$B$2 - N47 - $F$2</f>
         <v/>
       </c>
-      <c r="S47" s="7">
+      <c r="S47" s="6">
         <f>$B$2 - O47 - $F$2</f>
         <v/>
       </c>
@@ -6266,15 +6137,15 @@
           <t>u_unit[ch].axi_rd_sram_valid (D)</t>
         </is>
       </c>
-      <c r="I48" s="7">
+      <c r="I48" s="6">
         <f>F48*characterization!$D$17 + G48*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J48" s="7">
+      <c r="J48" s="6">
         <f>F48*characterization!$G$17 + G48*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K48" s="7">
+      <c r="K48" s="6">
         <f>F48*characterization!$J$17 + G48*characterization!$J$15</f>
         <v/>
       </c>
@@ -6282,27 +6153,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M48" s="7">
+      <c r="M48" s="6">
         <f>L48 + I48</f>
         <v/>
       </c>
-      <c r="N48" s="7">
+      <c r="N48" s="6">
         <f>L48 + J48</f>
         <v/>
       </c>
-      <c r="O48" s="7">
+      <c r="O48" s="6">
         <f>L48 + K48</f>
         <v/>
       </c>
-      <c r="Q48" s="7">
+      <c r="Q48" s="6">
         <f>$B$2 - M48 - $F$2</f>
         <v/>
       </c>
-      <c r="R48" s="7">
+      <c r="R48" s="6">
         <f>$B$2 - N48 - $F$2</f>
         <v/>
       </c>
-      <c r="S48" s="7">
+      <c r="S48" s="6">
         <f>$B$2 - O48 - $F$2</f>
         <v/>
       </c>
@@ -6345,15 +6216,15 @@
           <t>u_unit[ch].axi_wr_sram_valid (Q)</t>
         </is>
       </c>
-      <c r="I49" s="7">
+      <c r="I49" s="6">
         <f>F49*characterization!$D$17 + G49*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="6">
         <f>F49*characterization!$G$17 + G49*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K49" s="7">
+      <c r="K49" s="6">
         <f>F49*characterization!$J$17 + G49*characterization!$J$15</f>
         <v/>
       </c>
@@ -6361,27 +6232,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M49" s="7">
+      <c r="M49" s="6">
         <f>L49 + I49</f>
         <v/>
       </c>
-      <c r="N49" s="7">
+      <c r="N49" s="6">
         <f>L49 + J49</f>
         <v/>
       </c>
-      <c r="O49" s="7">
+      <c r="O49" s="6">
         <f>L49 + K49</f>
         <v/>
       </c>
-      <c r="Q49" s="7">
+      <c r="Q49" s="6">
         <f>$B$2 - M49 - $F$2</f>
         <v/>
       </c>
-      <c r="R49" s="7">
+      <c r="R49" s="6">
         <f>$B$2 - N49 - $F$2</f>
         <v/>
       </c>
-      <c r="S49" s="7">
+      <c r="S49" s="6">
         <f>$B$2 - O49 - $F$2</f>
         <v/>
       </c>
@@ -6424,15 +6295,15 @@
           <t>u_unit[ch].axi_wr_sram_data (Q)</t>
         </is>
       </c>
-      <c r="I50" s="7">
+      <c r="I50" s="6">
         <f>F50*characterization!$D$17 + G50*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J50" s="7">
+      <c r="J50" s="6">
         <f>F50*characterization!$G$17 + G50*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K50" s="7">
+      <c r="K50" s="6">
         <f>F50*characterization!$J$17 + G50*characterization!$J$15</f>
         <v/>
       </c>
@@ -6440,27 +6311,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M50" s="7">
+      <c r="M50" s="6">
         <f>L50 + I50</f>
         <v/>
       </c>
-      <c r="N50" s="7">
+      <c r="N50" s="6">
         <f>L50 + J50</f>
         <v/>
       </c>
-      <c r="O50" s="7">
+      <c r="O50" s="6">
         <f>L50 + K50</f>
         <v/>
       </c>
-      <c r="Q50" s="7">
+      <c r="Q50" s="6">
         <f>$B$2 - M50 - $F$2</f>
         <v/>
       </c>
-      <c r="R50" s="7">
+      <c r="R50" s="6">
         <f>$B$2 - N50 - $F$2</f>
         <v/>
       </c>
-      <c r="S50" s="7">
+      <c r="S50" s="6">
         <f>$B$2 - O50 - $F$2</f>
         <v/>
       </c>
@@ -6510,15 +6381,15 @@
           <t>r_channel_idle_prev (D)</t>
         </is>
       </c>
-      <c r="I52" s="7">
+      <c r="I52" s="6">
         <f>F52*characterization!$D$17 + G52*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J52" s="7">
+      <c r="J52" s="6">
         <f>F52*characterization!$G$17 + G52*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K52" s="7">
+      <c r="K52" s="6">
         <f>F52*characterization!$J$17 + G52*characterization!$J$15</f>
         <v/>
       </c>
@@ -6526,27 +6397,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M52" s="7">
+      <c r="M52" s="6">
         <f>L52 + I52</f>
         <v/>
       </c>
-      <c r="N52" s="7">
+      <c r="N52" s="6">
         <f>L52 + J52</f>
         <v/>
       </c>
-      <c r="O52" s="7">
+      <c r="O52" s="6">
         <f>L52 + K52</f>
         <v/>
       </c>
-      <c r="Q52" s="7">
+      <c r="Q52" s="6">
         <f>$B$2 - M52 - $F$2</f>
         <v/>
       </c>
-      <c r="R52" s="7">
+      <c r="R52" s="6">
         <f>$B$2 - N52 - $F$2</f>
         <v/>
       </c>
-      <c r="S52" s="7">
+      <c r="S52" s="6">
         <f>$B$2 - O52 - $F$2</f>
         <v/>
       </c>
@@ -6589,15 +6460,15 @@
           <t>r_enable (D)</t>
         </is>
       </c>
-      <c r="I53" s="7">
+      <c r="I53" s="6">
         <f>F53*characterization!$D$17 + G53*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J53" s="7">
+      <c r="J53" s="6">
         <f>F53*characterization!$G$17 + G53*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K53" s="7">
+      <c r="K53" s="6">
         <f>F53*characterization!$J$17 + G53*characterization!$J$15</f>
         <v/>
       </c>
@@ -6605,27 +6476,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M53" s="7">
+      <c r="M53" s="6">
         <f>L53 + I53</f>
         <v/>
       </c>
-      <c r="N53" s="7">
+      <c r="N53" s="6">
         <f>L53 + J53</f>
         <v/>
       </c>
-      <c r="O53" s="7">
+      <c r="O53" s="6">
         <f>L53 + K53</f>
         <v/>
       </c>
-      <c r="Q53" s="7">
+      <c r="Q53" s="6">
         <f>$B$2 - M53 - $F$2</f>
         <v/>
       </c>
-      <c r="R53" s="7">
+      <c r="R53" s="6">
         <f>$B$2 - N53 - $F$2</f>
         <v/>
       </c>
-      <c r="S53" s="7">
+      <c r="S53" s="6">
         <f>$B$2 - O53 - $F$2</f>
         <v/>
       </c>
@@ -6668,15 +6539,15 @@
           <t>FIFO async-clear path</t>
         </is>
       </c>
-      <c r="I54" s="7">
+      <c r="I54" s="6">
         <f>F54*characterization!$D$17 + G54*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J54" s="7">
+      <c r="J54" s="6">
         <f>F54*characterization!$G$17 + G54*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K54" s="7">
+      <c r="K54" s="6">
         <f>F54*characterization!$J$17 + G54*characterization!$J$15</f>
         <v/>
       </c>
@@ -6684,27 +6555,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M54" s="7">
+      <c r="M54" s="6">
         <f>L54 + I54</f>
         <v/>
       </c>
-      <c r="N54" s="7">
+      <c r="N54" s="6">
         <f>L54 + J54</f>
         <v/>
       </c>
-      <c r="O54" s="7">
+      <c r="O54" s="6">
         <f>L54 + K54</f>
         <v/>
       </c>
-      <c r="Q54" s="7">
+      <c r="Q54" s="6">
         <f>$B$2 - M54 - $F$2</f>
         <v/>
       </c>
-      <c r="R54" s="7">
+      <c r="R54" s="6">
         <f>$B$2 - N54 - $F$2</f>
         <v/>
       </c>
-      <c r="S54" s="7">
+      <c r="S54" s="6">
         <f>$B$2 - O54 - $F$2</f>
         <v/>
       </c>
@@ -6747,15 +6618,15 @@
           <t>r_event_payload (D)</t>
         </is>
       </c>
-      <c r="I55" s="7">
+      <c r="I55" s="6">
         <f>F55*characterization!$D$17 + G55*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J55" s="7">
+      <c r="J55" s="6">
         <f>F55*characterization!$G$17 + G55*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K55" s="7">
+      <c r="K55" s="6">
         <f>F55*characterization!$J$17 + G55*characterization!$J$15</f>
         <v/>
       </c>
@@ -6763,27 +6634,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M55" s="7">
+      <c r="M55" s="6">
         <f>L55 + I55</f>
         <v/>
       </c>
-      <c r="N55" s="7">
+      <c r="N55" s="6">
         <f>L55 + J55</f>
         <v/>
       </c>
-      <c r="O55" s="7">
+      <c r="O55" s="6">
         <f>L55 + K55</f>
         <v/>
       </c>
-      <c r="Q55" s="7">
+      <c r="Q55" s="6">
         <f>$B$2 - M55 - $F$2</f>
         <v/>
       </c>
-      <c r="R55" s="7">
+      <c r="R55" s="6">
         <f>$B$2 - N55 - $F$2</f>
         <v/>
       </c>
-      <c r="S55" s="7">
+      <c r="S55" s="6">
         <f>$B$2 - O55 - $F$2</f>
         <v/>
       </c>
@@ -6826,15 +6697,15 @@
           <t>r_event_pending (D)</t>
         </is>
       </c>
-      <c r="I56" s="7">
+      <c r="I56" s="6">
         <f>F56*characterization!$D$17 + G56*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J56" s="7">
+      <c r="J56" s="6">
         <f>F56*characterization!$G$17 + G56*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K56" s="7">
+      <c r="K56" s="6">
         <f>F56*characterization!$J$17 + G56*characterization!$J$15</f>
         <v/>
       </c>
@@ -6842,27 +6713,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M56" s="7">
+      <c r="M56" s="6">
         <f>L56 + I56</f>
         <v/>
       </c>
-      <c r="N56" s="7">
+      <c r="N56" s="6">
         <f>L56 + J56</f>
         <v/>
       </c>
-      <c r="O56" s="7">
+      <c r="O56" s="6">
         <f>L56 + K56</f>
         <v/>
       </c>
-      <c r="Q56" s="7">
+      <c r="Q56" s="6">
         <f>$B$2 - M56 - $F$2</f>
         <v/>
       </c>
-      <c r="R56" s="7">
+      <c r="R56" s="6">
         <f>$B$2 - N56 - $F$2</f>
         <v/>
       </c>
-      <c r="S56" s="7">
+      <c r="S56" s="6">
         <f>$B$2 - O56 - $F$2</f>
         <v/>
       </c>
@@ -6905,15 +6776,15 @@
           <t>u_perf_fifo.wr_valid (D)</t>
         </is>
       </c>
-      <c r="I57" s="7">
+      <c r="I57" s="6">
         <f>F57*characterization!$D$17 + G57*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J57" s="7">
+      <c r="J57" s="6">
         <f>F57*characterization!$G$17 + G57*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K57" s="7">
+      <c r="K57" s="6">
         <f>F57*characterization!$J$17 + G57*characterization!$J$15</f>
         <v/>
       </c>
@@ -6921,27 +6792,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M57" s="7">
+      <c r="M57" s="6">
         <f>L57 + I57</f>
         <v/>
       </c>
-      <c r="N57" s="7">
+      <c r="N57" s="6">
         <f>L57 + J57</f>
         <v/>
       </c>
-      <c r="O57" s="7">
+      <c r="O57" s="6">
         <f>L57 + K57</f>
         <v/>
       </c>
-      <c r="Q57" s="7">
+      <c r="Q57" s="6">
         <f>$B$2 - M57 - $F$2</f>
         <v/>
       </c>
-      <c r="R57" s="7">
+      <c r="R57" s="6">
         <f>$B$2 - N57 - $F$2</f>
         <v/>
       </c>
-      <c r="S57" s="7">
+      <c r="S57" s="6">
         <f>$B$2 - O57 - $F$2</f>
         <v/>
       </c>
@@ -6984,15 +6855,15 @@
           <t>u_perf_fifo.wr_data[high] (D)</t>
         </is>
       </c>
-      <c r="I58" s="7">
+      <c r="I58" s="6">
         <f>F58*characterization!$D$17 + G58*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J58" s="7">
+      <c r="J58" s="6">
         <f>F58*characterization!$G$17 + G58*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K58" s="7">
+      <c r="K58" s="6">
         <f>F58*characterization!$J$17 + G58*characterization!$J$15</f>
         <v/>
       </c>
@@ -7000,27 +6871,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M58" s="7">
+      <c r="M58" s="6">
         <f>L58 + I58</f>
         <v/>
       </c>
-      <c r="N58" s="7">
+      <c r="N58" s="6">
         <f>L58 + J58</f>
         <v/>
       </c>
-      <c r="O58" s="7">
+      <c r="O58" s="6">
         <f>L58 + K58</f>
         <v/>
       </c>
-      <c r="Q58" s="7">
+      <c r="Q58" s="6">
         <f>$B$2 - M58 - $F$2</f>
         <v/>
       </c>
-      <c r="R58" s="7">
+      <c r="R58" s="6">
         <f>$B$2 - N58 - $F$2</f>
         <v/>
       </c>
-      <c r="S58" s="7">
+      <c r="S58" s="6">
         <f>$B$2 - O58 - $F$2</f>
         <v/>
       </c>
@@ -7067,15 +6938,15 @@
           <t>u_perf_fifo.rd_valid</t>
         </is>
       </c>
-      <c r="I59" s="7">
+      <c r="I59" s="6">
         <f>F59*characterization!$D$17 + G59*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J59" s="7">
+      <c r="J59" s="6">
         <f>F59*characterization!$G$17 + G59*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K59" s="7">
+      <c r="K59" s="6">
         <f>F59*characterization!$J$17 + G59*characterization!$J$15</f>
         <v/>
       </c>
@@ -7083,27 +6954,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M59" s="7">
+      <c r="M59" s="6">
         <f>L59 + I59</f>
         <v/>
       </c>
-      <c r="N59" s="7">
+      <c r="N59" s="6">
         <f>L59 + J59</f>
         <v/>
       </c>
-      <c r="O59" s="7">
+      <c r="O59" s="6">
         <f>L59 + K59</f>
         <v/>
       </c>
-      <c r="Q59" s="7">
+      <c r="Q59" s="6">
         <f>$B$2 - M59 - $F$2</f>
         <v/>
       </c>
-      <c r="R59" s="7">
+      <c r="R59" s="6">
         <f>$B$2 - N59 - $F$2</f>
         <v/>
       </c>
-      <c r="S59" s="7">
+      <c r="S59" s="6">
         <f>$B$2 - O59 - $F$2</f>
         <v/>
       </c>
@@ -7150,15 +7021,15 @@
           <t>u_perf_fifo.rd_data[31:0] (Q)</t>
         </is>
       </c>
-      <c r="I60" s="7">
+      <c r="I60" s="6">
         <f>F60*characterization!$D$17 + G60*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J60" s="7">
+      <c r="J60" s="6">
         <f>F60*characterization!$G$17 + G60*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K60" s="7">
+      <c r="K60" s="6">
         <f>F60*characterization!$J$17 + G60*characterization!$J$15</f>
         <v/>
       </c>
@@ -7166,27 +7037,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M60" s="7">
+      <c r="M60" s="6">
         <f>L60 + I60</f>
         <v/>
       </c>
-      <c r="N60" s="7">
+      <c r="N60" s="6">
         <f>L60 + J60</f>
         <v/>
       </c>
-      <c r="O60" s="7">
+      <c r="O60" s="6">
         <f>L60 + K60</f>
         <v/>
       </c>
-      <c r="Q60" s="7">
+      <c r="Q60" s="6">
         <f>$B$2 - M60 - $F$2</f>
         <v/>
       </c>
-      <c r="R60" s="7">
+      <c r="R60" s="6">
         <f>$B$2 - N60 - $F$2</f>
         <v/>
       </c>
-      <c r="S60" s="7">
+      <c r="S60" s="6">
         <f>$B$2 - O60 - $F$2</f>
         <v/>
       </c>
@@ -7233,15 +7104,15 @@
           <t>u_perf_fifo.rd_data[63:32] (Q)</t>
         </is>
       </c>
-      <c r="I61" s="7">
+      <c r="I61" s="6">
         <f>F61*characterization!$D$17 + G61*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J61" s="7">
+      <c r="J61" s="6">
         <f>F61*characterization!$G$17 + G61*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K61" s="7">
+      <c r="K61" s="6">
         <f>F61*characterization!$J$17 + G61*characterization!$J$15</f>
         <v/>
       </c>
@@ -7249,27 +7120,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M61" s="7">
+      <c r="M61" s="6">
         <f>L61 + I61</f>
         <v/>
       </c>
-      <c r="N61" s="7">
+      <c r="N61" s="6">
         <f>L61 + J61</f>
         <v/>
       </c>
-      <c r="O61" s="7">
+      <c r="O61" s="6">
         <f>L61 + K61</f>
         <v/>
       </c>
-      <c r="Q61" s="7">
+      <c r="Q61" s="6">
         <f>$B$2 - M61 - $F$2</f>
         <v/>
       </c>
-      <c r="R61" s="7">
+      <c r="R61" s="6">
         <f>$B$2 - N61 - $F$2</f>
         <v/>
       </c>
-      <c r="S61" s="7">
+      <c r="S61" s="6">
         <f>$B$2 - O61 - $F$2</f>
         <v/>
       </c>
@@ -7316,15 +7187,15 @@
           <t>u_perf_fifo.empty (Q)</t>
         </is>
       </c>
-      <c r="I62" s="7">
+      <c r="I62" s="6">
         <f>F62*characterization!$D$17 + G62*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J62" s="7">
+      <c r="J62" s="6">
         <f>F62*characterization!$G$17 + G62*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K62" s="7">
+      <c r="K62" s="6">
         <f>F62*characterization!$J$17 + G62*characterization!$J$15</f>
         <v/>
       </c>
@@ -7332,27 +7203,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M62" s="7">
+      <c r="M62" s="6">
         <f>L62 + I62</f>
         <v/>
       </c>
-      <c r="N62" s="7">
+      <c r="N62" s="6">
         <f>L62 + J62</f>
         <v/>
       </c>
-      <c r="O62" s="7">
+      <c r="O62" s="6">
         <f>L62 + K62</f>
         <v/>
       </c>
-      <c r="Q62" s="7">
+      <c r="Q62" s="6">
         <f>$B$2 - M62 - $F$2</f>
         <v/>
       </c>
-      <c r="R62" s="7">
+      <c r="R62" s="6">
         <f>$B$2 - N62 - $F$2</f>
         <v/>
       </c>
-      <c r="S62" s="7">
+      <c r="S62" s="6">
         <f>$B$2 - O62 - $F$2</f>
         <v/>
       </c>
@@ -7399,15 +7270,15 @@
           <t>u_perf_fifo.count (Q)</t>
         </is>
       </c>
-      <c r="I63" s="7">
+      <c r="I63" s="6">
         <f>F63*characterization!$D$17 + G63*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J63" s="7">
+      <c r="J63" s="6">
         <f>F63*characterization!$G$17 + G63*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K63" s="7">
+      <c r="K63" s="6">
         <f>F63*characterization!$J$17 + G63*characterization!$J$15</f>
         <v/>
       </c>
@@ -7415,27 +7286,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M63" s="7">
+      <c r="M63" s="6">
         <f>L63 + I63</f>
         <v/>
       </c>
-      <c r="N63" s="7">
+      <c r="N63" s="6">
         <f>L63 + J63</f>
         <v/>
       </c>
-      <c r="O63" s="7">
+      <c r="O63" s="6">
         <f>L63 + K63</f>
         <v/>
       </c>
-      <c r="Q63" s="7">
+      <c r="Q63" s="6">
         <f>$B$2 - M63 - $F$2</f>
         <v/>
       </c>
-      <c r="R63" s="7">
+      <c r="R63" s="6">
         <f>$B$2 - N63 - $F$2</f>
         <v/>
       </c>
-      <c r="S63" s="7">
+      <c r="S63" s="6">
         <f>$B$2 - O63 - $F$2</f>
         <v/>
       </c>
@@ -7485,15 +7356,15 @@
           <t>r_apb_cmd_valid (D)</t>
         </is>
       </c>
-      <c r="I65" s="7">
+      <c r="I65" s="6">
         <f>F65*characterization!$D$17 + G65*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J65" s="7">
+      <c r="J65" s="6">
         <f>F65*characterization!$G$17 + G65*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="6">
         <f>F65*characterization!$J$17 + G65*characterization!$J$15</f>
         <v/>
       </c>
@@ -7501,27 +7372,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M65" s="7">
+      <c r="M65" s="6">
         <f>L65 + I65</f>
         <v/>
       </c>
-      <c r="N65" s="7">
+      <c r="N65" s="6">
         <f>L65 + J65</f>
         <v/>
       </c>
-      <c r="O65" s="7">
+      <c r="O65" s="6">
         <f>L65 + K65</f>
         <v/>
       </c>
-      <c r="Q65" s="7">
+      <c r="Q65" s="6">
         <f>$B$2 - M65 - $F$2</f>
         <v/>
       </c>
-      <c r="R65" s="7">
+      <c r="R65" s="6">
         <f>$B$2 - N65 - $F$2</f>
         <v/>
       </c>
-      <c r="S65" s="7">
+      <c r="S65" s="6">
         <f>$B$2 - O65 - $F$2</f>
         <v/>
       </c>
@@ -7564,15 +7435,15 @@
           <t>r_state addr-decode (D)</t>
         </is>
       </c>
-      <c r="I66" s="7">
+      <c r="I66" s="6">
         <f>F66*characterization!$D$17 + G66*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J66" s="7">
+      <c r="J66" s="6">
         <f>F66*characterization!$G$17 + G66*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K66" s="7">
+      <c r="K66" s="6">
         <f>F66*characterization!$J$17 + G66*characterization!$J$15</f>
         <v/>
       </c>
@@ -7580,27 +7451,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M66" s="7">
+      <c r="M66" s="6">
         <f>L66 + I66</f>
         <v/>
       </c>
-      <c r="N66" s="7">
+      <c r="N66" s="6">
         <f>L66 + J66</f>
         <v/>
       </c>
-      <c r="O66" s="7">
+      <c r="O66" s="6">
         <f>L66 + K66</f>
         <v/>
       </c>
-      <c r="Q66" s="7">
+      <c r="Q66" s="6">
         <f>$B$2 - M66 - $F$2</f>
         <v/>
       </c>
-      <c r="R66" s="7">
+      <c r="R66" s="6">
         <f>$B$2 - N66 - $F$2</f>
         <v/>
       </c>
-      <c r="S66" s="7">
+      <c r="S66" s="6">
         <f>$B$2 - O66 - $F$2</f>
         <v/>
       </c>
@@ -7643,15 +7514,15 @@
           <t>r_ch_addr[ch] (D)</t>
         </is>
       </c>
-      <c r="I67" s="7">
+      <c r="I67" s="6">
         <f>F67*characterization!$D$17 + G67*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J67" s="7">
+      <c r="J67" s="6">
         <f>F67*characterization!$G$17 + G67*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K67" s="7">
+      <c r="K67" s="6">
         <f>F67*characterization!$J$17 + G67*characterization!$J$15</f>
         <v/>
       </c>
@@ -7659,27 +7530,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M67" s="7">
+      <c r="M67" s="6">
         <f>L67 + I67</f>
         <v/>
       </c>
-      <c r="N67" s="7">
+      <c r="N67" s="6">
         <f>L67 + J67</f>
         <v/>
       </c>
-      <c r="O67" s="7">
+      <c r="O67" s="6">
         <f>L67 + K67</f>
         <v/>
       </c>
-      <c r="Q67" s="7">
+      <c r="Q67" s="6">
         <f>$B$2 - M67 - $F$2</f>
         <v/>
       </c>
-      <c r="R67" s="7">
+      <c r="R67" s="6">
         <f>$B$2 - N67 - $F$2</f>
         <v/>
       </c>
-      <c r="S67" s="7">
+      <c r="S67" s="6">
         <f>$B$2 - O67 - $F$2</f>
         <v/>
       </c>
@@ -7722,15 +7593,15 @@
           <t>r_apb_rsp_valid (D)</t>
         </is>
       </c>
-      <c r="I68" s="7">
+      <c r="I68" s="6">
         <f>F68*characterization!$D$17 + G68*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J68" s="7">
+      <c r="J68" s="6">
         <f>F68*characterization!$G$17 + G68*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K68" s="7">
+      <c r="K68" s="6">
         <f>F68*characterization!$J$17 + G68*characterization!$J$15</f>
         <v/>
       </c>
@@ -7738,27 +7609,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M68" s="7">
+      <c r="M68" s="6">
         <f>L68 + I68</f>
         <v/>
       </c>
-      <c r="N68" s="7">
+      <c r="N68" s="6">
         <f>L68 + J68</f>
         <v/>
       </c>
-      <c r="O68" s="7">
+      <c r="O68" s="6">
         <f>L68 + K68</f>
         <v/>
       </c>
-      <c r="Q68" s="7">
+      <c r="Q68" s="6">
         <f>$B$2 - M68 - $F$2</f>
         <v/>
       </c>
-      <c r="R68" s="7">
+      <c r="R68" s="6">
         <f>$B$2 - N68 - $F$2</f>
         <v/>
       </c>
-      <c r="S68" s="7">
+      <c r="S68" s="6">
         <f>$B$2 - O68 - $F$2</f>
         <v/>
       </c>
@@ -7801,15 +7672,15 @@
           <t>desc_apb_addr (Q)</t>
         </is>
       </c>
-      <c r="I69" s="7">
+      <c r="I69" s="6">
         <f>F69*characterization!$D$17 + G69*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J69" s="7">
+      <c r="J69" s="6">
         <f>F69*characterization!$G$17 + G69*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K69" s="7">
+      <c r="K69" s="6">
         <f>F69*characterization!$J$17 + G69*characterization!$J$15</f>
         <v/>
       </c>
@@ -7817,27 +7688,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M69" s="7">
+      <c r="M69" s="6">
         <f>L69 + I69</f>
         <v/>
       </c>
-      <c r="N69" s="7">
+      <c r="N69" s="6">
         <f>L69 + J69</f>
         <v/>
       </c>
-      <c r="O69" s="7">
+      <c r="O69" s="6">
         <f>L69 + K69</f>
         <v/>
       </c>
-      <c r="Q69" s="7">
+      <c r="Q69" s="6">
         <f>$B$2 - M69 - $F$2</f>
         <v/>
       </c>
-      <c r="R69" s="7">
+      <c r="R69" s="6">
         <f>$B$2 - N69 - $F$2</f>
         <v/>
       </c>
-      <c r="S69" s="7">
+      <c r="S69" s="6">
         <f>$B$2 - O69 - $F$2</f>
         <v/>
       </c>
@@ -7880,15 +7751,15 @@
           <t>desc_apb_valid (Q)</t>
         </is>
       </c>
-      <c r="I70" s="7">
+      <c r="I70" s="6">
         <f>F70*characterization!$D$17 + G70*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J70" s="7">
+      <c r="J70" s="6">
         <f>F70*characterization!$G$17 + G70*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K70" s="7">
+      <c r="K70" s="6">
         <f>F70*characterization!$J$17 + G70*characterization!$J$15</f>
         <v/>
       </c>
@@ -7896,27 +7767,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M70" s="7">
+      <c r="M70" s="6">
         <f>L70 + I70</f>
         <v/>
       </c>
-      <c r="N70" s="7">
+      <c r="N70" s="6">
         <f>L70 + J70</f>
         <v/>
       </c>
-      <c r="O70" s="7">
+      <c r="O70" s="6">
         <f>L70 + K70</f>
         <v/>
       </c>
-      <c r="Q70" s="7">
+      <c r="Q70" s="6">
         <f>$B$2 - M70 - $F$2</f>
         <v/>
       </c>
-      <c r="R70" s="7">
+      <c r="R70" s="6">
         <f>$B$2 - N70 - $F$2</f>
         <v/>
       </c>
-      <c r="S70" s="7">
+      <c r="S70" s="6">
         <f>$B$2 - O70 - $F$2</f>
         <v/>
       </c>
@@ -7959,15 +7830,15 @@
           <t>comb (FIFO ready AND)</t>
         </is>
       </c>
-      <c r="I71" s="7">
+      <c r="I71" s="6">
         <f>F71*characterization!$D$17 + G71*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J71" s="7">
+      <c r="J71" s="6">
         <f>F71*characterization!$G$17 + G71*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K71" s="7">
+      <c r="K71" s="6">
         <f>F71*characterization!$J$17 + G71*characterization!$J$15</f>
         <v/>
       </c>
@@ -7975,27 +7846,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M71" s="7">
+      <c r="M71" s="6">
         <f>L71 + I71</f>
         <v/>
       </c>
-      <c r="N71" s="7">
+      <c r="N71" s="6">
         <f>L71 + J71</f>
         <v/>
       </c>
-      <c r="O71" s="7">
+      <c r="O71" s="6">
         <f>L71 + K71</f>
         <v/>
       </c>
-      <c r="Q71" s="7">
+      <c r="Q71" s="6">
         <f>$B$2 - M71 - $F$2</f>
         <v/>
       </c>
-      <c r="R71" s="7">
+      <c r="R71" s="6">
         <f>$B$2 - N71 - $F$2</f>
         <v/>
       </c>
-      <c r="S71" s="7">
+      <c r="S71" s="6">
         <f>$B$2 - O71 - $F$2</f>
         <v/>
       </c>
@@ -8038,15 +7909,15 @@
           <t>r_apb_rsp_valid (Q)</t>
         </is>
       </c>
-      <c r="I72" s="7">
+      <c r="I72" s="6">
         <f>F72*characterization!$D$17 + G72*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J72" s="7">
+      <c r="J72" s="6">
         <f>F72*characterization!$G$17 + G72*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K72" s="7">
+      <c r="K72" s="6">
         <f>F72*characterization!$J$17 + G72*characterization!$J$15</f>
         <v/>
       </c>
@@ -8054,27 +7925,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M72" s="7">
+      <c r="M72" s="6">
         <f>L72 + I72</f>
         <v/>
       </c>
-      <c r="N72" s="7">
+      <c r="N72" s="6">
         <f>L72 + J72</f>
         <v/>
       </c>
-      <c r="O72" s="7">
+      <c r="O72" s="6">
         <f>L72 + K72</f>
         <v/>
       </c>
-      <c r="Q72" s="7">
+      <c r="Q72" s="6">
         <f>$B$2 - M72 - $F$2</f>
         <v/>
       </c>
-      <c r="R72" s="7">
+      <c r="R72" s="6">
         <f>$B$2 - N72 - $F$2</f>
         <v/>
       </c>
-      <c r="S72" s="7">
+      <c r="S72" s="6">
         <f>$B$2 - O72 - $F$2</f>
         <v/>
       </c>
@@ -8117,15 +7988,15 @@
           <t>r_ch_valid (Q)</t>
         </is>
       </c>
-      <c r="I73" s="7">
+      <c r="I73" s="6">
         <f>F73*characterization!$D$17 + G73*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J73" s="7">
+      <c r="J73" s="6">
         <f>F73*characterization!$G$17 + G73*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K73" s="7">
+      <c r="K73" s="6">
         <f>F73*characterization!$J$17 + G73*characterization!$J$15</f>
         <v/>
       </c>
@@ -8133,27 +8004,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M73" s="7">
+      <c r="M73" s="6">
         <f>L73 + I73</f>
         <v/>
       </c>
-      <c r="N73" s="7">
+      <c r="N73" s="6">
         <f>L73 + J73</f>
         <v/>
       </c>
-      <c r="O73" s="7">
+      <c r="O73" s="6">
         <f>L73 + K73</f>
         <v/>
       </c>
-      <c r="Q73" s="7">
+      <c r="Q73" s="6">
         <f>$B$2 - M73 - $F$2</f>
         <v/>
       </c>
-      <c r="R73" s="7">
+      <c r="R73" s="6">
         <f>$B$2 - N73 - $F$2</f>
         <v/>
       </c>
-      <c r="S73" s="7">
+      <c r="S73" s="6">
         <f>$B$2 - O73 - $F$2</f>
         <v/>
       </c>
@@ -8196,15 +8067,15 @@
           <t>r_ch_addr (Q)</t>
         </is>
       </c>
-      <c r="I74" s="7">
+      <c r="I74" s="6">
         <f>F74*characterization!$D$17 + G74*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J74" s="7">
+      <c r="J74" s="6">
         <f>F74*characterization!$G$17 + G74*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K74" s="7">
+      <c r="K74" s="6">
         <f>F74*characterization!$J$17 + G74*characterization!$J$15</f>
         <v/>
       </c>
@@ -8212,27 +8083,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M74" s="7">
+      <c r="M74" s="6">
         <f>L74 + I74</f>
         <v/>
       </c>
-      <c r="N74" s="7">
+      <c r="N74" s="6">
         <f>L74 + J74</f>
         <v/>
       </c>
-      <c r="O74" s="7">
+      <c r="O74" s="6">
         <f>L74 + K74</f>
         <v/>
       </c>
-      <c r="Q74" s="7">
+      <c r="Q74" s="6">
         <f>$B$2 - M74 - $F$2</f>
         <v/>
       </c>
-      <c r="R74" s="7">
+      <c r="R74" s="6">
         <f>$B$2 - N74 - $F$2</f>
         <v/>
       </c>
-      <c r="S74" s="7">
+      <c r="S74" s="6">
         <f>$B$2 - O74 - $F$2</f>
         <v/>
       </c>
@@ -8275,15 +8146,15 @@
           <t>clears r_ch_valid[ch]</t>
         </is>
       </c>
-      <c r="I75" s="7">
+      <c r="I75" s="6">
         <f>F75*characterization!$D$17 + G75*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J75" s="7">
+      <c r="J75" s="6">
         <f>F75*characterization!$G$17 + G75*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K75" s="7">
+      <c r="K75" s="6">
         <f>F75*characterization!$J$17 + G75*characterization!$J$15</f>
         <v/>
       </c>
@@ -8291,27 +8162,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M75" s="7">
+      <c r="M75" s="6">
         <f>L75 + I75</f>
         <v/>
       </c>
-      <c r="N75" s="7">
+      <c r="N75" s="6">
         <f>L75 + J75</f>
         <v/>
       </c>
-      <c r="O75" s="7">
+      <c r="O75" s="6">
         <f>L75 + K75</f>
         <v/>
       </c>
-      <c r="Q75" s="7">
+      <c r="Q75" s="6">
         <f>$B$2 - M75 - $F$2</f>
         <v/>
       </c>
-      <c r="R75" s="7">
+      <c r="R75" s="6">
         <f>$B$2 - N75 - $F$2</f>
         <v/>
       </c>
-      <c r="S75" s="7">
+      <c r="S75" s="6">
         <f>$B$2 - O75 - $F$2</f>
         <v/>
       </c>
@@ -8361,15 +8232,15 @@
           <t>r_state (D)</t>
         </is>
       </c>
-      <c r="I77" s="7">
+      <c r="I77" s="6">
         <f>F77*characterization!$D$17 + G77*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J77" s="7">
+      <c r="J77" s="6">
         <f>F77*characterization!$G$17 + G77*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K77" s="7">
+      <c r="K77" s="6">
         <f>F77*characterization!$J$17 + G77*characterization!$J$15</f>
         <v/>
       </c>
@@ -8377,27 +8248,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M77" s="7">
+      <c r="M77" s="6">
         <f>L77 + I77</f>
         <v/>
       </c>
-      <c r="N77" s="7">
+      <c r="N77" s="6">
         <f>L77 + J77</f>
         <v/>
       </c>
-      <c r="O77" s="7">
+      <c r="O77" s="6">
         <f>L77 + K77</f>
         <v/>
       </c>
-      <c r="Q77" s="7">
+      <c r="Q77" s="6">
         <f>$B$2 - M77 - $F$2</f>
         <v/>
       </c>
-      <c r="R77" s="7">
+      <c r="R77" s="6">
         <f>$B$2 - N77 - $F$2</f>
         <v/>
       </c>
-      <c r="S77" s="7">
+      <c r="S77" s="6">
         <f>$B$2 - O77 - $F$2</f>
         <v/>
       </c>
@@ -8440,15 +8311,15 @@
           <t>r_desc_addr (D)</t>
         </is>
       </c>
-      <c r="I78" s="7">
+      <c r="I78" s="6">
         <f>F78*characterization!$D$17 + G78*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J78" s="7">
+      <c r="J78" s="6">
         <f>F78*characterization!$G$17 + G78*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K78" s="7">
+      <c r="K78" s="6">
         <f>F78*characterization!$J$17 + G78*characterization!$J$15</f>
         <v/>
       </c>
@@ -8456,27 +8327,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M78" s="7">
+      <c r="M78" s="6">
         <f>L78 + I78</f>
         <v/>
       </c>
-      <c r="N78" s="7">
+      <c r="N78" s="6">
         <f>L78 + J78</f>
         <v/>
       </c>
-      <c r="O78" s="7">
+      <c r="O78" s="6">
         <f>L78 + K78</f>
         <v/>
       </c>
-      <c r="Q78" s="7">
+      <c r="Q78" s="6">
         <f>$B$2 - M78 - $F$2</f>
         <v/>
       </c>
-      <c r="R78" s="7">
+      <c r="R78" s="6">
         <f>$B$2 - N78 - $F$2</f>
         <v/>
       </c>
-      <c r="S78" s="7">
+      <c r="S78" s="6">
         <f>$B$2 - O78 - $F$2</f>
         <v/>
       </c>
@@ -8519,15 +8390,15 @@
           <t>AR skid wr_valid (D)</t>
         </is>
       </c>
-      <c r="I79" s="7">
+      <c r="I79" s="6">
         <f>F79*characterization!$D$17 + G79*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J79" s="7">
+      <c r="J79" s="6">
         <f>F79*characterization!$G$17 + G79*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K79" s="7">
+      <c r="K79" s="6">
         <f>F79*characterization!$J$17 + G79*characterization!$J$15</f>
         <v/>
       </c>
@@ -8535,27 +8406,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M79" s="7">
+      <c r="M79" s="6">
         <f>L79 + I79</f>
         <v/>
       </c>
-      <c r="N79" s="7">
+      <c r="N79" s="6">
         <f>L79 + J79</f>
         <v/>
       </c>
-      <c r="O79" s="7">
+      <c r="O79" s="6">
         <f>L79 + K79</f>
         <v/>
       </c>
-      <c r="Q79" s="7">
+      <c r="Q79" s="6">
         <f>$B$2 - M79 - $F$2</f>
         <v/>
       </c>
-      <c r="R79" s="7">
+      <c r="R79" s="6">
         <f>$B$2 - N79 - $F$2</f>
         <v/>
       </c>
-      <c r="S79" s="7">
+      <c r="S79" s="6">
         <f>$B$2 - O79 - $F$2</f>
         <v/>
       </c>
@@ -8598,15 +8469,15 @@
           <t>AR skid wr_data (D)</t>
         </is>
       </c>
-      <c r="I80" s="7">
+      <c r="I80" s="6">
         <f>F80*characterization!$D$17 + G80*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J80" s="7">
+      <c r="J80" s="6">
         <f>F80*characterization!$G$17 + G80*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K80" s="7">
+      <c r="K80" s="6">
         <f>F80*characterization!$J$17 + G80*characterization!$J$15</f>
         <v/>
       </c>
@@ -8614,27 +8485,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M80" s="7">
+      <c r="M80" s="6">
         <f>L80 + I80</f>
         <v/>
       </c>
-      <c r="N80" s="7">
+      <c r="N80" s="6">
         <f>L80 + J80</f>
         <v/>
       </c>
-      <c r="O80" s="7">
+      <c r="O80" s="6">
         <f>L80 + K80</f>
         <v/>
       </c>
-      <c r="Q80" s="7">
+      <c r="Q80" s="6">
         <f>$B$2 - M80 - $F$2</f>
         <v/>
       </c>
-      <c r="R80" s="7">
+      <c r="R80" s="6">
         <f>$B$2 - N80 - $F$2</f>
         <v/>
       </c>
-      <c r="S80" s="7">
+      <c r="S80" s="6">
         <f>$B$2 - O80 - $F$2</f>
         <v/>
       </c>
@@ -8677,15 +8548,15 @@
           <t>i_descriptor_fifo.wr_data (D)</t>
         </is>
       </c>
-      <c r="I81" s="7">
+      <c r="I81" s="6">
         <f>F81*characterization!$D$17 + G81*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J81" s="7">
+      <c r="J81" s="6">
         <f>F81*characterization!$G$17 + G81*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K81" s="7">
+      <c r="K81" s="6">
         <f>F81*characterization!$J$17 + G81*characterization!$J$15</f>
         <v/>
       </c>
@@ -8693,27 +8564,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M81" s="7">
+      <c r="M81" s="6">
         <f>L81 + I81</f>
         <v/>
       </c>
-      <c r="N81" s="7">
+      <c r="N81" s="6">
         <f>L81 + J81</f>
         <v/>
       </c>
-      <c r="O81" s="7">
+      <c r="O81" s="6">
         <f>L81 + K81</f>
         <v/>
       </c>
-      <c r="Q81" s="7">
+      <c r="Q81" s="6">
         <f>$B$2 - M81 - $F$2</f>
         <v/>
       </c>
-      <c r="R81" s="7">
+      <c r="R81" s="6">
         <f>$B$2 - N81 - $F$2</f>
         <v/>
       </c>
-      <c r="S81" s="7">
+      <c r="S81" s="6">
         <f>$B$2 - O81 - $F$2</f>
         <v/>
       </c>
@@ -8756,15 +8627,15 @@
           <t>r_desc_addr (D, next pointer)</t>
         </is>
       </c>
-      <c r="I82" s="7">
+      <c r="I82" s="6">
         <f>F82*characterization!$D$17 + G82*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J82" s="7">
+      <c r="J82" s="6">
         <f>F82*characterization!$G$17 + G82*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="6">
         <f>F82*characterization!$J$17 + G82*characterization!$J$15</f>
         <v/>
       </c>
@@ -8772,27 +8643,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M82" s="7">
+      <c r="M82" s="6">
         <f>L82 + I82</f>
         <v/>
       </c>
-      <c r="N82" s="7">
+      <c r="N82" s="6">
         <f>L82 + J82</f>
         <v/>
       </c>
-      <c r="O82" s="7">
+      <c r="O82" s="6">
         <f>L82 + K82</f>
         <v/>
       </c>
-      <c r="Q82" s="7">
+      <c r="Q82" s="6">
         <f>$B$2 - M82 - $F$2</f>
         <v/>
       </c>
-      <c r="R82" s="7">
+      <c r="R82" s="6">
         <f>$B$2 - N82 - $F$2</f>
         <v/>
       </c>
-      <c r="S82" s="7">
+      <c r="S82" s="6">
         <f>$B$2 - O82 - $F$2</f>
         <v/>
       </c>
@@ -8839,15 +8710,15 @@
           <t>AR skid head Q</t>
         </is>
       </c>
-      <c r="I83" s="7">
+      <c r="I83" s="6">
         <f>F83*characterization!$D$17 + G83*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J83" s="7">
+      <c r="J83" s="6">
         <f>F83*characterization!$G$17 + G83*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K83" s="7">
+      <c r="K83" s="6">
         <f>F83*characterization!$J$17 + G83*characterization!$J$15</f>
         <v/>
       </c>
@@ -8855,27 +8726,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M83" s="7">
+      <c r="M83" s="6">
         <f>L83 + I83</f>
         <v/>
       </c>
-      <c r="N83" s="7">
+      <c r="N83" s="6">
         <f>L83 + J83</f>
         <v/>
       </c>
-      <c r="O83" s="7">
+      <c r="O83" s="6">
         <f>L83 + K83</f>
         <v/>
       </c>
-      <c r="Q83" s="7">
+      <c r="Q83" s="6">
         <f>$B$2 - M83 - $F$2</f>
         <v/>
       </c>
-      <c r="R83" s="7">
+      <c r="R83" s="6">
         <f>$B$2 - N83 - $F$2</f>
         <v/>
       </c>
-      <c r="S83" s="7">
+      <c r="S83" s="6">
         <f>$B$2 - O83 - $F$2</f>
         <v/>
       </c>
@@ -8922,15 +8793,15 @@
           <t>R skid input</t>
         </is>
       </c>
-      <c r="I84" s="7">
+      <c r="I84" s="6">
         <f>F84*characterization!$D$17 + G84*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J84" s="7">
+      <c r="J84" s="6">
         <f>F84*characterization!$G$17 + G84*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K84" s="7">
+      <c r="K84" s="6">
         <f>F84*characterization!$J$17 + G84*characterization!$J$15</f>
         <v/>
       </c>
@@ -8938,27 +8809,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M84" s="7">
+      <c r="M84" s="6">
         <f>L84 + I84</f>
         <v/>
       </c>
-      <c r="N84" s="7">
+      <c r="N84" s="6">
         <f>L84 + J84</f>
         <v/>
       </c>
-      <c r="O84" s="7">
+      <c r="O84" s="6">
         <f>L84 + K84</f>
         <v/>
       </c>
-      <c r="Q84" s="7">
+      <c r="Q84" s="6">
         <f>$B$2 - M84 - $F$2</f>
         <v/>
       </c>
-      <c r="R84" s="7">
+      <c r="R84" s="6">
         <f>$B$2 - N84 - $F$2</f>
         <v/>
       </c>
-      <c r="S84" s="7">
+      <c r="S84" s="6">
         <f>$B$2 - O84 - $F$2</f>
         <v/>
       </c>
@@ -9005,15 +8876,15 @@
           <t>i_descriptor_fifo.rd_valid (Q)</t>
         </is>
       </c>
-      <c r="I85" s="7">
+      <c r="I85" s="6">
         <f>F85*characterization!$D$17 + G85*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J85" s="7">
+      <c r="J85" s="6">
         <f>F85*characterization!$G$17 + G85*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K85" s="7">
+      <c r="K85" s="6">
         <f>F85*characterization!$J$17 + G85*characterization!$J$15</f>
         <v/>
       </c>
@@ -9021,27 +8892,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M85" s="7">
+      <c r="M85" s="6">
         <f>L85 + I85</f>
         <v/>
       </c>
-      <c r="N85" s="7">
+      <c r="N85" s="6">
         <f>L85 + J85</f>
         <v/>
       </c>
-      <c r="O85" s="7">
+      <c r="O85" s="6">
         <f>L85 + K85</f>
         <v/>
       </c>
-      <c r="Q85" s="7">
+      <c r="Q85" s="6">
         <f>$B$2 - M85 - $F$2</f>
         <v/>
       </c>
-      <c r="R85" s="7">
+      <c r="R85" s="6">
         <f>$B$2 - N85 - $F$2</f>
         <v/>
       </c>
-      <c r="S85" s="7">
+      <c r="S85" s="6">
         <f>$B$2 - O85 - $F$2</f>
         <v/>
       </c>
@@ -9088,15 +8959,15 @@
           <t>i_descriptor_fifo.rd_data (Q)</t>
         </is>
       </c>
-      <c r="I86" s="7">
+      <c r="I86" s="6">
         <f>F86*characterization!$D$17 + G86*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J86" s="7">
+      <c r="J86" s="6">
         <f>F86*characterization!$G$17 + G86*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K86" s="7">
+      <c r="K86" s="6">
         <f>F86*characterization!$J$17 + G86*characterization!$J$15</f>
         <v/>
       </c>
@@ -9104,27 +8975,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M86" s="7">
+      <c r="M86" s="6">
         <f>L86 + I86</f>
         <v/>
       </c>
-      <c r="N86" s="7">
+      <c r="N86" s="6">
         <f>L86 + J86</f>
         <v/>
       </c>
-      <c r="O86" s="7">
+      <c r="O86" s="6">
         <f>L86 + K86</f>
         <v/>
       </c>
-      <c r="Q86" s="7">
+      <c r="Q86" s="6">
         <f>$B$2 - M86 - $F$2</f>
         <v/>
       </c>
-      <c r="R86" s="7">
+      <c r="R86" s="6">
         <f>$B$2 - N86 - $F$2</f>
         <v/>
       </c>
-      <c r="S86" s="7">
+      <c r="S86" s="6">
         <f>$B$2 - O86 - $F$2</f>
         <v/>
       </c>
@@ -9171,15 +9042,15 @@
           <t>i_descriptor_fifo.rd_ready</t>
         </is>
       </c>
-      <c r="I87" s="7">
+      <c r="I87" s="6">
         <f>F87*characterization!$D$17 + G87*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J87" s="7">
+      <c r="J87" s="6">
         <f>F87*characterization!$G$17 + G87*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K87" s="7">
+      <c r="K87" s="6">
         <f>F87*characterization!$J$17 + G87*characterization!$J$15</f>
         <v/>
       </c>
@@ -9187,27 +9058,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M87" s="7">
+      <c r="M87" s="6">
         <f>L87 + I87</f>
         <v/>
       </c>
-      <c r="N87" s="7">
+      <c r="N87" s="6">
         <f>L87 + J87</f>
         <v/>
       </c>
-      <c r="O87" s="7">
+      <c r="O87" s="6">
         <f>L87 + K87</f>
         <v/>
       </c>
-      <c r="Q87" s="7">
+      <c r="Q87" s="6">
         <f>$B$2 - M87 - $F$2</f>
         <v/>
       </c>
-      <c r="R87" s="7">
+      <c r="R87" s="6">
         <f>$B$2 - N87 - $F$2</f>
         <v/>
       </c>
-      <c r="S87" s="7">
+      <c r="S87" s="6">
         <f>$B$2 - O87 - $F$2</f>
         <v/>
       </c>
@@ -9257,15 +9128,15 @@
           <t>r_state (D)</t>
         </is>
       </c>
-      <c r="I89" s="7">
+      <c r="I89" s="6">
         <f>F89*characterization!$D$17 + G89*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J89" s="7">
+      <c r="J89" s="6">
         <f>F89*characterization!$G$17 + G89*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K89" s="7">
+      <c r="K89" s="6">
         <f>F89*characterization!$J$17 + G89*characterization!$J$15</f>
         <v/>
       </c>
@@ -9273,27 +9144,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M89" s="7">
+      <c r="M89" s="6">
         <f>L89 + I89</f>
         <v/>
       </c>
-      <c r="N89" s="7">
+      <c r="N89" s="6">
         <f>L89 + J89</f>
         <v/>
       </c>
-      <c r="O89" s="7">
+      <c r="O89" s="6">
         <f>L89 + K89</f>
         <v/>
       </c>
-      <c r="Q89" s="7">
+      <c r="Q89" s="6">
         <f>$B$2 - M89 - $F$2</f>
         <v/>
       </c>
-      <c r="R89" s="7">
+      <c r="R89" s="6">
         <f>$B$2 - N89 - $F$2</f>
         <v/>
       </c>
-      <c r="S89" s="7">
+      <c r="S89" s="6">
         <f>$B$2 - O89 - $F$2</f>
         <v/>
       </c>
@@ -9336,15 +9207,15 @@
           <t>r_descriptor (D)</t>
         </is>
       </c>
-      <c r="I90" s="7">
+      <c r="I90" s="6">
         <f>F90*characterization!$D$17 + G90*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J90" s="7">
+      <c r="J90" s="6">
         <f>F90*characterization!$G$17 + G90*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K90" s="7">
+      <c r="K90" s="6">
         <f>F90*characterization!$J$17 + G90*characterization!$J$15</f>
         <v/>
       </c>
@@ -9352,27 +9223,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M90" s="7">
+      <c r="M90" s="6">
         <f>L90 + I90</f>
         <v/>
       </c>
-      <c r="N90" s="7">
+      <c r="N90" s="6">
         <f>L90 + J90</f>
         <v/>
       </c>
-      <c r="O90" s="7">
+      <c r="O90" s="6">
         <f>L90 + K90</f>
         <v/>
       </c>
-      <c r="Q90" s="7">
+      <c r="Q90" s="6">
         <f>$B$2 - M90 - $F$2</f>
         <v/>
       </c>
-      <c r="R90" s="7">
+      <c r="R90" s="6">
         <f>$B$2 - N90 - $F$2</f>
         <v/>
       </c>
-      <c r="S90" s="7">
+      <c r="S90" s="6">
         <f>$B$2 - O90 - $F$2</f>
         <v/>
       </c>
@@ -9415,15 +9286,15 @@
           <t>r_src_addr, r_dst_addr, r_length (D)</t>
         </is>
       </c>
-      <c r="I91" s="7">
+      <c r="I91" s="6">
         <f>F91*characterization!$D$17 + G91*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J91" s="7">
+      <c r="J91" s="6">
         <f>F91*characterization!$G$17 + G91*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K91" s="7">
+      <c r="K91" s="6">
         <f>F91*characterization!$J$17 + G91*characterization!$J$15</f>
         <v/>
       </c>
@@ -9431,27 +9302,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M91" s="7">
+      <c r="M91" s="6">
         <f>L91 + I91</f>
         <v/>
       </c>
-      <c r="N91" s="7">
+      <c r="N91" s="6">
         <f>L91 + J91</f>
         <v/>
       </c>
-      <c r="O91" s="7">
+      <c r="O91" s="6">
         <f>L91 + K91</f>
         <v/>
       </c>
-      <c r="Q91" s="7">
+      <c r="Q91" s="6">
         <f>$B$2 - M91 - $F$2</f>
         <v/>
       </c>
-      <c r="R91" s="7">
+      <c r="R91" s="6">
         <f>$B$2 - N91 - $F$2</f>
         <v/>
       </c>
-      <c r="S91" s="7">
+      <c r="S91" s="6">
         <f>$B$2 - O91 - $F$2</f>
         <v/>
       </c>
@@ -9494,15 +9365,15 @@
           <t>r_axi_rd_req / r_axi_wr_req (D)</t>
         </is>
       </c>
-      <c r="I92" s="7">
+      <c r="I92" s="6">
         <f>F92*characterization!$D$17 + G92*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J92" s="7">
+      <c r="J92" s="6">
         <f>F92*characterization!$G$17 + G92*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K92" s="7">
+      <c r="K92" s="6">
         <f>F92*characterization!$J$17 + G92*characterization!$J$15</f>
         <v/>
       </c>
@@ -9510,27 +9381,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M92" s="7">
+      <c r="M92" s="6">
         <f>L92 + I92</f>
         <v/>
       </c>
-      <c r="N92" s="7">
+      <c r="N92" s="6">
         <f>L92 + J92</f>
         <v/>
       </c>
-      <c r="O92" s="7">
+      <c r="O92" s="6">
         <f>L92 + K92</f>
         <v/>
       </c>
-      <c r="Q92" s="7">
+      <c r="Q92" s="6">
         <f>$B$2 - M92 - $F$2</f>
         <v/>
       </c>
-      <c r="R92" s="7">
+      <c r="R92" s="6">
         <f>$B$2 - N92 - $F$2</f>
         <v/>
       </c>
-      <c r="S92" s="7">
+      <c r="S92" s="6">
         <f>$B$2 - O92 - $F$2</f>
         <v/>
       </c>
@@ -9573,15 +9444,15 @@
           <t>r_axi_rd_req addr-incr (D)</t>
         </is>
       </c>
-      <c r="I93" s="7">
+      <c r="I93" s="6">
         <f>F93*characterization!$D$17 + G93*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J93" s="7">
+      <c r="J93" s="6">
         <f>F93*characterization!$G$17 + G93*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K93" s="7">
+      <c r="K93" s="6">
         <f>F93*characterization!$J$17 + G93*characterization!$J$15</f>
         <v/>
       </c>
@@ -9589,27 +9460,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M93" s="7">
+      <c r="M93" s="6">
         <f>L93 + I93</f>
         <v/>
       </c>
-      <c r="N93" s="7">
+      <c r="N93" s="6">
         <f>L93 + J93</f>
         <v/>
       </c>
-      <c r="O93" s="7">
+      <c r="O93" s="6">
         <f>L93 + K93</f>
         <v/>
       </c>
-      <c r="Q93" s="7">
+      <c r="Q93" s="6">
         <f>$B$2 - M93 - $F$2</f>
         <v/>
       </c>
-      <c r="R93" s="7">
+      <c r="R93" s="6">
         <f>$B$2 - N93 - $F$2</f>
         <v/>
       </c>
-      <c r="S93" s="7">
+      <c r="S93" s="6">
         <f>$B$2 - O93 - $F$2</f>
         <v/>
       </c>
@@ -9652,15 +9523,15 @@
           <t>r_state DONE transition (D)</t>
         </is>
       </c>
-      <c r="I94" s="7">
+      <c r="I94" s="6">
         <f>F94*characterization!$D$17 + G94*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J94" s="7">
+      <c r="J94" s="6">
         <f>F94*characterization!$G$17 + G94*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K94" s="7">
+      <c r="K94" s="6">
         <f>F94*characterization!$J$17 + G94*characterization!$J$15</f>
         <v/>
       </c>
@@ -9668,27 +9539,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M94" s="7">
+      <c r="M94" s="6">
         <f>L94 + I94</f>
         <v/>
       </c>
-      <c r="N94" s="7">
+      <c r="N94" s="6">
         <f>L94 + J94</f>
         <v/>
       </c>
-      <c r="O94" s="7">
+      <c r="O94" s="6">
         <f>L94 + K94</f>
         <v/>
       </c>
-      <c r="Q94" s="7">
+      <c r="Q94" s="6">
         <f>$B$2 - M94 - $F$2</f>
         <v/>
       </c>
-      <c r="R94" s="7">
+      <c r="R94" s="6">
         <f>$B$2 - N94 - $F$2</f>
         <v/>
       </c>
-      <c r="S94" s="7">
+      <c r="S94" s="6">
         <f>$B$2 - O94 - $F$2</f>
         <v/>
       </c>
@@ -9731,15 +9602,15 @@
           <t>r_axi_rd_req throttle (D)</t>
         </is>
       </c>
-      <c r="I95" s="7">
+      <c r="I95" s="6">
         <f>F95*characterization!$D$17 + G95*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J95" s="7">
+      <c r="J95" s="6">
         <f>F95*characterization!$G$17 + G95*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K95" s="7">
+      <c r="K95" s="6">
         <f>F95*characterization!$J$17 + G95*characterization!$J$15</f>
         <v/>
       </c>
@@ -9747,27 +9618,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M95" s="7">
+      <c r="M95" s="6">
         <f>L95 + I95</f>
         <v/>
       </c>
-      <c r="N95" s="7">
+      <c r="N95" s="6">
         <f>L95 + J95</f>
         <v/>
       </c>
-      <c r="O95" s="7">
+      <c r="O95" s="6">
         <f>L95 + K95</f>
         <v/>
       </c>
-      <c r="Q95" s="7">
+      <c r="Q95" s="6">
         <f>$B$2 - M95 - $F$2</f>
         <v/>
       </c>
-      <c r="R95" s="7">
+      <c r="R95" s="6">
         <f>$B$2 - N95 - $F$2</f>
         <v/>
       </c>
-      <c r="S95" s="7">
+      <c r="S95" s="6">
         <f>$B$2 - O95 - $F$2</f>
         <v/>
       </c>
@@ -9810,15 +9681,15 @@
           <t>r_axi_rd_req (Q)</t>
         </is>
       </c>
-      <c r="I96" s="7">
+      <c r="I96" s="6">
         <f>F96*characterization!$D$17 + G96*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J96" s="7">
+      <c r="J96" s="6">
         <f>F96*characterization!$G$17 + G96*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K96" s="7">
+      <c r="K96" s="6">
         <f>F96*characterization!$J$17 + G96*characterization!$J$15</f>
         <v/>
       </c>
@@ -9826,27 +9697,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M96" s="7">
+      <c r="M96" s="6">
         <f>L96 + I96</f>
         <v/>
       </c>
-      <c r="N96" s="7">
+      <c r="N96" s="6">
         <f>L96 + J96</f>
         <v/>
       </c>
-      <c r="O96" s="7">
+      <c r="O96" s="6">
         <f>L96 + K96</f>
         <v/>
       </c>
-      <c r="Q96" s="7">
+      <c r="Q96" s="6">
         <f>$B$2 - M96 - $F$2</f>
         <v/>
       </c>
-      <c r="R96" s="7">
+      <c r="R96" s="6">
         <f>$B$2 - N96 - $F$2</f>
         <v/>
       </c>
-      <c r="S96" s="7">
+      <c r="S96" s="6">
         <f>$B$2 - O96 - $F$2</f>
         <v/>
       </c>
@@ -9889,15 +9760,15 @@
           <t>r_src_addr + offset (Q)</t>
         </is>
       </c>
-      <c r="I97" s="7">
+      <c r="I97" s="6">
         <f>F97*characterization!$D$17 + G97*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J97" s="7">
+      <c r="J97" s="6">
         <f>F97*characterization!$G$17 + G97*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K97" s="7">
+      <c r="K97" s="6">
         <f>F97*characterization!$J$17 + G97*characterization!$J$15</f>
         <v/>
       </c>
@@ -9905,27 +9776,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M97" s="7">
+      <c r="M97" s="6">
         <f>L97 + I97</f>
         <v/>
       </c>
-      <c r="N97" s="7">
+      <c r="N97" s="6">
         <f>L97 + J97</f>
         <v/>
       </c>
-      <c r="O97" s="7">
+      <c r="O97" s="6">
         <f>L97 + K97</f>
         <v/>
       </c>
-      <c r="Q97" s="7">
+      <c r="Q97" s="6">
         <f>$B$2 - M97 - $F$2</f>
         <v/>
       </c>
-      <c r="R97" s="7">
+      <c r="R97" s="6">
         <f>$B$2 - N97 - $F$2</f>
         <v/>
       </c>
-      <c r="S97" s="7">
+      <c r="S97" s="6">
         <f>$B$2 - O97 - $F$2</f>
         <v/>
       </c>
@@ -9968,15 +9839,15 @@
           <t>r_axi_wr_req (Q)</t>
         </is>
       </c>
-      <c r="I98" s="7">
+      <c r="I98" s="6">
         <f>F98*characterization!$D$17 + G98*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J98" s="7">
+      <c r="J98" s="6">
         <f>F98*characterization!$G$17 + G98*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K98" s="7">
+      <c r="K98" s="6">
         <f>F98*characterization!$J$17 + G98*characterization!$J$15</f>
         <v/>
       </c>
@@ -9984,27 +9855,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M98" s="7">
+      <c r="M98" s="6">
         <f>L98 + I98</f>
         <v/>
       </c>
-      <c r="N98" s="7">
+      <c r="N98" s="6">
         <f>L98 + J98</f>
         <v/>
       </c>
-      <c r="O98" s="7">
+      <c r="O98" s="6">
         <f>L98 + K98</f>
         <v/>
       </c>
-      <c r="Q98" s="7">
+      <c r="Q98" s="6">
         <f>$B$2 - M98 - $F$2</f>
         <v/>
       </c>
-      <c r="R98" s="7">
+      <c r="R98" s="6">
         <f>$B$2 - N98 - $F$2</f>
         <v/>
       </c>
-      <c r="S98" s="7">
+      <c r="S98" s="6">
         <f>$B$2 - O98 - $F$2</f>
         <v/>
       </c>
@@ -10047,15 +9918,15 @@
           <t>r_dst_addr + offset (Q)</t>
         </is>
       </c>
-      <c r="I99" s="7">
+      <c r="I99" s="6">
         <f>F99*characterization!$D$17 + G99*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J99" s="7">
+      <c r="J99" s="6">
         <f>F99*characterization!$G$17 + G99*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K99" s="7">
+      <c r="K99" s="6">
         <f>F99*characterization!$J$17 + G99*characterization!$J$15</f>
         <v/>
       </c>
@@ -10063,27 +9934,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M99" s="7">
+      <c r="M99" s="6">
         <f>L99 + I99</f>
         <v/>
       </c>
-      <c r="N99" s="7">
+      <c r="N99" s="6">
         <f>L99 + J99</f>
         <v/>
       </c>
-      <c r="O99" s="7">
+      <c r="O99" s="6">
         <f>L99 + K99</f>
         <v/>
       </c>
-      <c r="Q99" s="7">
+      <c r="Q99" s="6">
         <f>$B$2 - M99 - $F$2</f>
         <v/>
       </c>
-      <c r="R99" s="7">
+      <c r="R99" s="6">
         <f>$B$2 - N99 - $F$2</f>
         <v/>
       </c>
-      <c r="S99" s="7">
+      <c r="S99" s="6">
         <f>$B$2 - O99 - $F$2</f>
         <v/>
       </c>
@@ -10126,15 +9997,15 @@
           <t>comb of r_state == IDLE</t>
         </is>
       </c>
-      <c r="I100" s="7">
+      <c r="I100" s="6">
         <f>F100*characterization!$D$17 + G100*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J100" s="7">
+      <c r="J100" s="6">
         <f>F100*characterization!$G$17 + G100*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K100" s="7">
+      <c r="K100" s="6">
         <f>F100*characterization!$J$17 + G100*characterization!$J$15</f>
         <v/>
       </c>
@@ -10142,27 +10013,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M100" s="7">
+      <c r="M100" s="6">
         <f>L100 + I100</f>
         <v/>
       </c>
-      <c r="N100" s="7">
+      <c r="N100" s="6">
         <f>L100 + J100</f>
         <v/>
       </c>
-      <c r="O100" s="7">
+      <c r="O100" s="6">
         <f>L100 + K100</f>
         <v/>
       </c>
-      <c r="Q100" s="7">
+      <c r="Q100" s="6">
         <f>$B$2 - M100 - $F$2</f>
         <v/>
       </c>
-      <c r="R100" s="7">
+      <c r="R100" s="6">
         <f>$B$2 - N100 - $F$2</f>
         <v/>
       </c>
-      <c r="S100" s="7">
+      <c r="S100" s="6">
         <f>$B$2 - O100 - $F$2</f>
         <v/>
       </c>
@@ -10205,15 +10076,15 @@
           <t>r_state DONE-pulse (Q)</t>
         </is>
       </c>
-      <c r="I101" s="7">
+      <c r="I101" s="6">
         <f>F101*characterization!$D$17 + G101*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J101" s="7">
+      <c r="J101" s="6">
         <f>F101*characterization!$G$17 + G101*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K101" s="7">
+      <c r="K101" s="6">
         <f>F101*characterization!$J$17 + G101*characterization!$J$15</f>
         <v/>
       </c>
@@ -10221,27 +10092,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M101" s="7">
+      <c r="M101" s="6">
         <f>L101 + I101</f>
         <v/>
       </c>
-      <c r="N101" s="7">
+      <c r="N101" s="6">
         <f>L101 + J101</f>
         <v/>
       </c>
-      <c r="O101" s="7">
+      <c r="O101" s="6">
         <f>L101 + K101</f>
         <v/>
       </c>
-      <c r="Q101" s="7">
+      <c r="Q101" s="6">
         <f>$B$2 - M101 - $F$2</f>
         <v/>
       </c>
-      <c r="R101" s="7">
+      <c r="R101" s="6">
         <f>$B$2 - N101 - $F$2</f>
         <v/>
       </c>
-      <c r="S101" s="7">
+      <c r="S101" s="6">
         <f>$B$2 - O101 - $F$2</f>
         <v/>
       </c>
@@ -10284,15 +10155,15 @@
           <t>r_monbus_pkt event-encode (Q)</t>
         </is>
       </c>
-      <c r="I102" s="7">
+      <c r="I102" s="6">
         <f>F102*characterization!$D$17 + G102*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J102" s="7">
+      <c r="J102" s="6">
         <f>F102*characterization!$G$17 + G102*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K102" s="7">
+      <c r="K102" s="6">
         <f>F102*characterization!$J$17 + G102*characterization!$J$15</f>
         <v/>
       </c>
@@ -10300,27 +10171,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M102" s="7">
+      <c r="M102" s="6">
         <f>L102 + I102</f>
         <v/>
       </c>
-      <c r="N102" s="7">
+      <c r="N102" s="6">
         <f>L102 + J102</f>
         <v/>
       </c>
-      <c r="O102" s="7">
+      <c r="O102" s="6">
         <f>L102 + K102</f>
         <v/>
       </c>
-      <c r="Q102" s="7">
+      <c r="Q102" s="6">
         <f>$B$2 - M102 - $F$2</f>
         <v/>
       </c>
-      <c r="R102" s="7">
+      <c r="R102" s="6">
         <f>$B$2 - N102 - $F$2</f>
         <v/>
       </c>
-      <c r="S102" s="7">
+      <c r="S102" s="6">
         <f>$B$2 - O102 - $F$2</f>
         <v/>
       </c>
@@ -10370,15 +10241,15 @@
           <t>u_arbiter (CLIENTS=N)</t>
         </is>
       </c>
-      <c r="I104" s="7">
+      <c r="I104" s="6">
         <f>F104*characterization!$D$17 + G104*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J104" s="7">
+      <c r="J104" s="6">
         <f>F104*characterization!$G$17 + G104*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K104" s="7">
+      <c r="K104" s="6">
         <f>F104*characterization!$J$17 + G104*characterization!$J$15</f>
         <v/>
       </c>
@@ -10386,27 +10257,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M104" s="7">
+      <c r="M104" s="6">
         <f>L104 + I104</f>
         <v/>
       </c>
-      <c r="N104" s="7">
+      <c r="N104" s="6">
         <f>L104 + J104</f>
         <v/>
       </c>
-      <c r="O104" s="7">
+      <c r="O104" s="6">
         <f>L104 + K104</f>
         <v/>
       </c>
-      <c r="Q104" s="7">
+      <c r="Q104" s="6">
         <f>$B$2 - M104 - $F$2</f>
         <v/>
       </c>
-      <c r="R104" s="7">
+      <c r="R104" s="6">
         <f>$B$2 - N104 - $F$2</f>
         <v/>
       </c>
-      <c r="S104" s="7">
+      <c r="S104" s="6">
         <f>$B$2 - O104 - $F$2</f>
         <v/>
       </c>
@@ -10449,15 +10320,15 @@
           <t>u_arbiter granted addr mux</t>
         </is>
       </c>
-      <c r="I105" s="7">
+      <c r="I105" s="6">
         <f>F105*characterization!$D$17 + G105*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J105" s="7">
+      <c r="J105" s="6">
         <f>F105*characterization!$G$17 + G105*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K105" s="7">
+      <c r="K105" s="6">
         <f>F105*characterization!$J$17 + G105*characterization!$J$15</f>
         <v/>
       </c>
@@ -10465,27 +10336,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M105" s="7">
+      <c r="M105" s="6">
         <f>L105 + I105</f>
         <v/>
       </c>
-      <c r="N105" s="7">
+      <c r="N105" s="6">
         <f>L105 + J105</f>
         <v/>
       </c>
-      <c r="O105" s="7">
+      <c r="O105" s="6">
         <f>L105 + K105</f>
         <v/>
       </c>
-      <c r="Q105" s="7">
+      <c r="Q105" s="6">
         <f>$B$2 - M105 - $F$2</f>
         <v/>
       </c>
-      <c r="R105" s="7">
+      <c r="R105" s="6">
         <f>$B$2 - N105 - $F$2</f>
         <v/>
       </c>
-      <c r="S105" s="7">
+      <c r="S105" s="6">
         <f>$B$2 - O105 - $F$2</f>
         <v/>
       </c>
@@ -10528,15 +10399,15 @@
           <t>r_active_ch (D)</t>
         </is>
       </c>
-      <c r="I106" s="7">
+      <c r="I106" s="6">
         <f>F106*characterization!$D$17 + G106*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J106" s="7">
+      <c r="J106" s="6">
         <f>F106*characterization!$G$17 + G106*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K106" s="7">
+      <c r="K106" s="6">
         <f>F106*characterization!$J$17 + G106*characterization!$J$15</f>
         <v/>
       </c>
@@ -10544,27 +10415,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M106" s="7">
+      <c r="M106" s="6">
         <f>L106 + I106</f>
         <v/>
       </c>
-      <c r="N106" s="7">
+      <c r="N106" s="6">
         <f>L106 + J106</f>
         <v/>
       </c>
-      <c r="O106" s="7">
+      <c r="O106" s="6">
         <f>L106 + K106</f>
         <v/>
       </c>
-      <c r="Q106" s="7">
+      <c r="Q106" s="6">
         <f>$B$2 - M106 - $F$2</f>
         <v/>
       </c>
-      <c r="R106" s="7">
+      <c r="R106" s="6">
         <f>$B$2 - N106 - $F$2</f>
         <v/>
       </c>
-      <c r="S106" s="7">
+      <c r="S106" s="6">
         <f>$B$2 - O106 - $F$2</f>
         <v/>
       </c>
@@ -10607,15 +10478,15 @@
           <t>r_axi_ar_addr / r_axi_ar_len (D)</t>
         </is>
       </c>
-      <c r="I107" s="7">
+      <c r="I107" s="6">
         <f>F107*characterization!$D$17 + G107*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J107" s="7">
+      <c r="J107" s="6">
         <f>F107*characterization!$G$17 + G107*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K107" s="7">
+      <c r="K107" s="6">
         <f>F107*characterization!$J$17 + G107*characterization!$J$15</f>
         <v/>
       </c>
@@ -10623,27 +10494,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M107" s="7">
+      <c r="M107" s="6">
         <f>L107 + I107</f>
         <v/>
       </c>
-      <c r="N107" s="7">
+      <c r="N107" s="6">
         <f>L107 + J107</f>
         <v/>
       </c>
-      <c r="O107" s="7">
+      <c r="O107" s="6">
         <f>L107 + K107</f>
         <v/>
       </c>
-      <c r="Q107" s="7">
+      <c r="Q107" s="6">
         <f>$B$2 - M107 - $F$2</f>
         <v/>
       </c>
-      <c r="R107" s="7">
+      <c r="R107" s="6">
         <f>$B$2 - N107 - $F$2</f>
         <v/>
       </c>
-      <c r="S107" s="7">
+      <c r="S107" s="6">
         <f>$B$2 - O107 - $F$2</f>
         <v/>
       </c>
@@ -10686,15 +10557,15 @@
           <t>u_rd_axi_skid.wr_data (D)</t>
         </is>
       </c>
-      <c r="I108" s="7">
+      <c r="I108" s="6">
         <f>F108*characterization!$D$17 + G108*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J108" s="7">
+      <c r="J108" s="6">
         <f>F108*characterization!$G$17 + G108*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K108" s="7">
+      <c r="K108" s="6">
         <f>F108*characterization!$J$17 + G108*characterization!$J$15</f>
         <v/>
       </c>
@@ -10702,27 +10573,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M108" s="7">
+      <c r="M108" s="6">
         <f>L108 + I108</f>
         <v/>
       </c>
-      <c r="N108" s="7">
+      <c r="N108" s="6">
         <f>L108 + J108</f>
         <v/>
       </c>
-      <c r="O108" s="7">
+      <c r="O108" s="6">
         <f>L108 + K108</f>
         <v/>
       </c>
-      <c r="Q108" s="7">
+      <c r="Q108" s="6">
         <f>$B$2 - M108 - $F$2</f>
         <v/>
       </c>
-      <c r="R108" s="7">
+      <c r="R108" s="6">
         <f>$B$2 - N108 - $F$2</f>
         <v/>
       </c>
-      <c r="S108" s="7">
+      <c r="S108" s="6">
         <f>$B$2 - O108 - $F$2</f>
         <v/>
       </c>
@@ -10765,15 +10636,15 @@
           <t>u_rd_axi_skid.wr_valid (D)</t>
         </is>
       </c>
-      <c r="I109" s="7">
+      <c r="I109" s="6">
         <f>F109*characterization!$D$17 + G109*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J109" s="7">
+      <c r="J109" s="6">
         <f>F109*characterization!$G$17 + G109*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K109" s="7">
+      <c r="K109" s="6">
         <f>F109*characterization!$J$17 + G109*characterization!$J$15</f>
         <v/>
       </c>
@@ -10781,27 +10652,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M109" s="7">
+      <c r="M109" s="6">
         <f>L109 + I109</f>
         <v/>
       </c>
-      <c r="N109" s="7">
+      <c r="N109" s="6">
         <f>L109 + J109</f>
         <v/>
       </c>
-      <c r="O109" s="7">
+      <c r="O109" s="6">
         <f>L109 + K109</f>
         <v/>
       </c>
-      <c r="Q109" s="7">
+      <c r="Q109" s="6">
         <f>$B$2 - M109 - $F$2</f>
         <v/>
       </c>
-      <c r="R109" s="7">
+      <c r="R109" s="6">
         <f>$B$2 - N109 - $F$2</f>
         <v/>
       </c>
-      <c r="S109" s="7">
+      <c r="S109" s="6">
         <f>$B$2 - O109 - $F$2</f>
         <v/>
       </c>
@@ -10844,15 +10715,15 @@
           <t>r_axi_ar_valid throttle</t>
         </is>
       </c>
-      <c r="I110" s="7">
+      <c r="I110" s="6">
         <f>F110*characterization!$D$17 + G110*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J110" s="7">
+      <c r="J110" s="6">
         <f>F110*characterization!$G$17 + G110*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K110" s="7">
+      <c r="K110" s="6">
         <f>F110*characterization!$J$17 + G110*characterization!$J$15</f>
         <v/>
       </c>
@@ -10860,27 +10731,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M110" s="7">
+      <c r="M110" s="6">
         <f>L110 + I110</f>
         <v/>
       </c>
-      <c r="N110" s="7">
+      <c r="N110" s="6">
         <f>L110 + J110</f>
         <v/>
       </c>
-      <c r="O110" s="7">
+      <c r="O110" s="6">
         <f>L110 + K110</f>
         <v/>
       </c>
-      <c r="Q110" s="7">
+      <c r="Q110" s="6">
         <f>$B$2 - M110 - $F$2</f>
         <v/>
       </c>
-      <c r="R110" s="7">
+      <c r="R110" s="6">
         <f>$B$2 - N110 - $F$2</f>
         <v/>
       </c>
-      <c r="S110" s="7">
+      <c r="S110" s="6">
         <f>$B$2 - O110 - $F$2</f>
         <v/>
       </c>
@@ -10923,15 +10794,15 @@
           <t>r_axi_ar_addr id field (D)</t>
         </is>
       </c>
-      <c r="I111" s="7">
+      <c r="I111" s="6">
         <f>F111*characterization!$D$17 + G111*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J111" s="7">
+      <c r="J111" s="6">
         <f>F111*characterization!$G$17 + G111*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K111" s="7">
+      <c r="K111" s="6">
         <f>F111*characterization!$J$17 + G111*characterization!$J$15</f>
         <v/>
       </c>
@@ -10939,27 +10810,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M111" s="7">
+      <c r="M111" s="6">
         <f>L111 + I111</f>
         <v/>
       </c>
-      <c r="N111" s="7">
+      <c r="N111" s="6">
         <f>L111 + J111</f>
         <v/>
       </c>
-      <c r="O111" s="7">
+      <c r="O111" s="6">
         <f>L111 + K111</f>
         <v/>
       </c>
-      <c r="Q111" s="7">
+      <c r="Q111" s="6">
         <f>$B$2 - M111 - $F$2</f>
         <v/>
       </c>
-      <c r="R111" s="7">
+      <c r="R111" s="6">
         <f>$B$2 - N111 - $F$2</f>
         <v/>
       </c>
-      <c r="S111" s="7">
+      <c r="S111" s="6">
         <f>$B$2 - O111 - $F$2</f>
         <v/>
       </c>
@@ -11006,15 +10877,15 @@
           <t>u_rd_axi_skid AR head (Q)</t>
         </is>
       </c>
-      <c r="I112" s="7">
+      <c r="I112" s="6">
         <f>F112*characterization!$D$17 + G112*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J112" s="7">
+      <c r="J112" s="6">
         <f>F112*characterization!$G$17 + G112*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K112" s="7">
+      <c r="K112" s="6">
         <f>F112*characterization!$J$17 + G112*characterization!$J$15</f>
         <v/>
       </c>
@@ -11022,27 +10893,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M112" s="7">
+      <c r="M112" s="6">
         <f>L112 + I112</f>
         <v/>
       </c>
-      <c r="N112" s="7">
+      <c r="N112" s="6">
         <f>L112 + J112</f>
         <v/>
       </c>
-      <c r="O112" s="7">
+      <c r="O112" s="6">
         <f>L112 + K112</f>
         <v/>
       </c>
-      <c r="Q112" s="7">
+      <c r="Q112" s="6">
         <f>$B$2 - M112 - $F$2</f>
         <v/>
       </c>
-      <c r="R112" s="7">
+      <c r="R112" s="6">
         <f>$B$2 - N112 - $F$2</f>
         <v/>
       </c>
-      <c r="S112" s="7">
+      <c r="S112" s="6">
         <f>$B$2 - O112 - $F$2</f>
         <v/>
       </c>
@@ -11089,15 +10960,15 @@
           <t>u_rd_axi_skid R input</t>
         </is>
       </c>
-      <c r="I113" s="7">
+      <c r="I113" s="6">
         <f>F113*characterization!$D$17 + G113*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J113" s="7">
+      <c r="J113" s="6">
         <f>F113*characterization!$G$17 + G113*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K113" s="7">
+      <c r="K113" s="6">
         <f>F113*characterization!$J$17 + G113*characterization!$J$15</f>
         <v/>
       </c>
@@ -11105,27 +10976,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M113" s="7">
+      <c r="M113" s="6">
         <f>L113 + I113</f>
         <v/>
       </c>
-      <c r="N113" s="7">
+      <c r="N113" s="6">
         <f>L113 + J113</f>
         <v/>
       </c>
-      <c r="O113" s="7">
+      <c r="O113" s="6">
         <f>L113 + K113</f>
         <v/>
       </c>
-      <c r="Q113" s="7">
+      <c r="Q113" s="6">
         <f>$B$2 - M113 - $F$2</f>
         <v/>
       </c>
-      <c r="R113" s="7">
+      <c r="R113" s="6">
         <f>$B$2 - N113 - $F$2</f>
         <v/>
       </c>
-      <c r="S113" s="7">
+      <c r="S113" s="6">
         <f>$B$2 - O113 - $F$2</f>
         <v/>
       </c>
@@ -11168,15 +11039,15 @@
           <t>r_axi_ar_valid demux (Q)</t>
         </is>
       </c>
-      <c r="I114" s="7">
+      <c r="I114" s="6">
         <f>F114*characterization!$D$17 + G114*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J114" s="7">
+      <c r="J114" s="6">
         <f>F114*characterization!$G$17 + G114*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K114" s="7">
+      <c r="K114" s="6">
         <f>F114*characterization!$J$17 + G114*characterization!$J$15</f>
         <v/>
       </c>
@@ -11184,27 +11055,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M114" s="7">
+      <c r="M114" s="6">
         <f>L114 + I114</f>
         <v/>
       </c>
-      <c r="N114" s="7">
+      <c r="N114" s="6">
         <f>L114 + J114</f>
         <v/>
       </c>
-      <c r="O114" s="7">
+      <c r="O114" s="6">
         <f>L114 + K114</f>
         <v/>
       </c>
-      <c r="Q114" s="7">
+      <c r="Q114" s="6">
         <f>$B$2 - M114 - $F$2</f>
         <v/>
       </c>
-      <c r="R114" s="7">
+      <c r="R114" s="6">
         <f>$B$2 - N114 - $F$2</f>
         <v/>
       </c>
-      <c r="S114" s="7">
+      <c r="S114" s="6">
         <f>$B$2 - O114 - $F$2</f>
         <v/>
       </c>
@@ -11247,15 +11118,15 @@
           <t>back-pressure cmp</t>
         </is>
       </c>
-      <c r="I115" s="7">
+      <c r="I115" s="6">
         <f>F115*characterization!$D$17 + G115*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J115" s="7">
+      <c r="J115" s="6">
         <f>F115*characterization!$G$17 + G115*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K115" s="7">
+      <c r="K115" s="6">
         <f>F115*characterization!$J$17 + G115*characterization!$J$15</f>
         <v/>
       </c>
@@ -11263,27 +11134,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M115" s="7">
+      <c r="M115" s="6">
         <f>L115 + I115</f>
         <v/>
       </c>
-      <c r="N115" s="7">
+      <c r="N115" s="6">
         <f>L115 + J115</f>
         <v/>
       </c>
-      <c r="O115" s="7">
+      <c r="O115" s="6">
         <f>L115 + K115</f>
         <v/>
       </c>
-      <c r="Q115" s="7">
+      <c r="Q115" s="6">
         <f>$B$2 - M115 - $F$2</f>
         <v/>
       </c>
-      <c r="R115" s="7">
+      <c r="R115" s="6">
         <f>$B$2 - N115 - $F$2</f>
         <v/>
       </c>
-      <c r="S115" s="7">
+      <c r="S115" s="6">
         <f>$B$2 - O115 - $F$2</f>
         <v/>
       </c>
@@ -11326,15 +11197,15 @@
           <t>r_active_ch demux of R-skid valid (Q)</t>
         </is>
       </c>
-      <c r="I116" s="7">
+      <c r="I116" s="6">
         <f>F116*characterization!$D$17 + G116*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J116" s="7">
+      <c r="J116" s="6">
         <f>F116*characterization!$G$17 + G116*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K116" s="7">
+      <c r="K116" s="6">
         <f>F116*characterization!$J$17 + G116*characterization!$J$15</f>
         <v/>
       </c>
@@ -11342,27 +11213,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M116" s="7">
+      <c r="M116" s="6">
         <f>L116 + I116</f>
         <v/>
       </c>
-      <c r="N116" s="7">
+      <c r="N116" s="6">
         <f>L116 + J116</f>
         <v/>
       </c>
-      <c r="O116" s="7">
+      <c r="O116" s="6">
         <f>L116 + K116</f>
         <v/>
       </c>
-      <c r="Q116" s="7">
+      <c r="Q116" s="6">
         <f>$B$2 - M116 - $F$2</f>
         <v/>
       </c>
-      <c r="R116" s="7">
+      <c r="R116" s="6">
         <f>$B$2 - N116 - $F$2</f>
         <v/>
       </c>
-      <c r="S116" s="7">
+      <c r="S116" s="6">
         <f>$B$2 - O116 - $F$2</f>
         <v/>
       </c>
@@ -11405,15 +11276,15 @@
           <t>u_rd_axi_skid.rd_data (Q)</t>
         </is>
       </c>
-      <c r="I117" s="7">
+      <c r="I117" s="6">
         <f>F117*characterization!$D$17 + G117*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J117" s="7">
+      <c r="J117" s="6">
         <f>F117*characterization!$G$17 + G117*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K117" s="7">
+      <c r="K117" s="6">
         <f>F117*characterization!$J$17 + G117*characterization!$J$15</f>
         <v/>
       </c>
@@ -11421,27 +11292,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M117" s="7">
+      <c r="M117" s="6">
         <f>L117 + I117</f>
         <v/>
       </c>
-      <c r="N117" s="7">
+      <c r="N117" s="6">
         <f>L117 + J117</f>
         <v/>
       </c>
-      <c r="O117" s="7">
+      <c r="O117" s="6">
         <f>L117 + K117</f>
         <v/>
       </c>
-      <c r="Q117" s="7">
+      <c r="Q117" s="6">
         <f>$B$2 - M117 - $F$2</f>
         <v/>
       </c>
-      <c r="R117" s="7">
+      <c r="R117" s="6">
         <f>$B$2 - N117 - $F$2</f>
         <v/>
       </c>
-      <c r="S117" s="7">
+      <c r="S117" s="6">
         <f>$B$2 - O117 - $F$2</f>
         <v/>
       </c>
@@ -11491,15 +11362,15 @@
           <t>arbiter (D)</t>
         </is>
       </c>
-      <c r="I119" s="7">
+      <c r="I119" s="6">
         <f>F119*characterization!$D$17 + G119*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J119" s="7">
+      <c r="J119" s="6">
         <f>F119*characterization!$G$17 + G119*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K119" s="7">
+      <c r="K119" s="6">
         <f>F119*characterization!$J$17 + G119*characterization!$J$15</f>
         <v/>
       </c>
@@ -11507,27 +11378,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M119" s="7">
+      <c r="M119" s="6">
         <f>L119 + I119</f>
         <v/>
       </c>
-      <c r="N119" s="7">
+      <c r="N119" s="6">
         <f>L119 + J119</f>
         <v/>
       </c>
-      <c r="O119" s="7">
+      <c r="O119" s="6">
         <f>L119 + K119</f>
         <v/>
       </c>
-      <c r="Q119" s="7">
+      <c r="Q119" s="6">
         <f>$B$2 - M119 - $F$2</f>
         <v/>
       </c>
-      <c r="R119" s="7">
+      <c r="R119" s="6">
         <f>$B$2 - N119 - $F$2</f>
         <v/>
       </c>
-      <c r="S119" s="7">
+      <c r="S119" s="6">
         <f>$B$2 - O119 - $F$2</f>
         <v/>
       </c>
@@ -11570,15 +11441,15 @@
           <t>arbiter addr mux (D)</t>
         </is>
       </c>
-      <c r="I120" s="7">
+      <c r="I120" s="6">
         <f>F120*characterization!$D$17 + G120*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J120" s="7">
+      <c r="J120" s="6">
         <f>F120*characterization!$G$17 + G120*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K120" s="7">
+      <c r="K120" s="6">
         <f>F120*characterization!$J$17 + G120*characterization!$J$15</f>
         <v/>
       </c>
@@ -11586,27 +11457,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M120" s="7">
+      <c r="M120" s="6">
         <f>L120 + I120</f>
         <v/>
       </c>
-      <c r="N120" s="7">
+      <c r="N120" s="6">
         <f>L120 + J120</f>
         <v/>
       </c>
-      <c r="O120" s="7">
+      <c r="O120" s="6">
         <f>L120 + K120</f>
         <v/>
       </c>
-      <c r="Q120" s="7">
+      <c r="Q120" s="6">
         <f>$B$2 - M120 - $F$2</f>
         <v/>
       </c>
-      <c r="R120" s="7">
+      <c r="R120" s="6">
         <f>$B$2 - N120 - $F$2</f>
         <v/>
       </c>
-      <c r="S120" s="7">
+      <c r="S120" s="6">
         <f>$B$2 - O120 - $F$2</f>
         <v/>
       </c>
@@ -11649,15 +11520,15 @@
           <t>r_w_phase_active (D)</t>
         </is>
       </c>
-      <c r="I121" s="7">
+      <c r="I121" s="6">
         <f>F121*characterization!$D$17 + G121*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J121" s="7">
+      <c r="J121" s="6">
         <f>F121*characterization!$G$17 + G121*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K121" s="7">
+      <c r="K121" s="6">
         <f>F121*characterization!$J$17 + G121*characterization!$J$15</f>
         <v/>
       </c>
@@ -11665,27 +11536,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M121" s="7">
+      <c r="M121" s="6">
         <f>L121 + I121</f>
         <v/>
       </c>
-      <c r="N121" s="7">
+      <c r="N121" s="6">
         <f>L121 + J121</f>
         <v/>
       </c>
-      <c r="O121" s="7">
+      <c r="O121" s="6">
         <f>L121 + K121</f>
         <v/>
       </c>
-      <c r="Q121" s="7">
+      <c r="Q121" s="6">
         <f>$B$2 - M121 - $F$2</f>
         <v/>
       </c>
-      <c r="R121" s="7">
+      <c r="R121" s="6">
         <f>$B$2 - N121 - $F$2</f>
         <v/>
       </c>
-      <c r="S121" s="7">
+      <c r="S121" s="6">
         <f>$B$2 - O121 - $F$2</f>
         <v/>
       </c>
@@ -11728,15 +11599,15 @@
           <t>r_axi_w_data (D)</t>
         </is>
       </c>
-      <c r="I122" s="7">
+      <c r="I122" s="6">
         <f>F122*characterization!$D$17 + G122*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J122" s="7">
+      <c r="J122" s="6">
         <f>F122*characterization!$G$17 + G122*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K122" s="7">
+      <c r="K122" s="6">
         <f>F122*characterization!$J$17 + G122*characterization!$J$15</f>
         <v/>
       </c>
@@ -11744,27 +11615,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M122" s="7">
+      <c r="M122" s="6">
         <f>L122 + I122</f>
         <v/>
       </c>
-      <c r="N122" s="7">
+      <c r="N122" s="6">
         <f>L122 + J122</f>
         <v/>
       </c>
-      <c r="O122" s="7">
+      <c r="O122" s="6">
         <f>L122 + K122</f>
         <v/>
       </c>
-      <c r="Q122" s="7">
+      <c r="Q122" s="6">
         <f>$B$2 - M122 - $F$2</f>
         <v/>
       </c>
-      <c r="R122" s="7">
+      <c r="R122" s="6">
         <f>$B$2 - N122 - $F$2</f>
         <v/>
       </c>
-      <c r="S122" s="7">
+      <c r="S122" s="6">
         <f>$B$2 - O122 - $F$2</f>
         <v/>
       </c>
@@ -11807,15 +11678,15 @@
           <t>r_active_ch (D)</t>
         </is>
       </c>
-      <c r="I123" s="7">
+      <c r="I123" s="6">
         <f>F123*characterization!$D$17 + G123*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J123" s="7">
+      <c r="J123" s="6">
         <f>F123*characterization!$G$17 + G123*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K123" s="7">
+      <c r="K123" s="6">
         <f>F123*characterization!$J$17 + G123*characterization!$J$15</f>
         <v/>
       </c>
@@ -11823,27 +11694,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M123" s="7">
+      <c r="M123" s="6">
         <f>L123 + I123</f>
         <v/>
       </c>
-      <c r="N123" s="7">
+      <c r="N123" s="6">
         <f>L123 + J123</f>
         <v/>
       </c>
-      <c r="O123" s="7">
+      <c r="O123" s="6">
         <f>L123 + K123</f>
         <v/>
       </c>
-      <c r="Q123" s="7">
+      <c r="Q123" s="6">
         <f>$B$2 - M123 - $F$2</f>
         <v/>
       </c>
-      <c r="R123" s="7">
+      <c r="R123" s="6">
         <f>$B$2 - N123 - $F$2</f>
         <v/>
       </c>
-      <c r="S123" s="7">
+      <c r="S123" s="6">
         <f>$B$2 - O123 - $F$2</f>
         <v/>
       </c>
@@ -11886,15 +11757,15 @@
           <t>r_axi_aw_addr / r_axi_w_data (D)</t>
         </is>
       </c>
-      <c r="I124" s="7">
+      <c r="I124" s="6">
         <f>F124*characterization!$D$17 + G124*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J124" s="7">
+      <c r="J124" s="6">
         <f>F124*characterization!$G$17 + G124*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K124" s="7">
+      <c r="K124" s="6">
         <f>F124*characterization!$J$17 + G124*characterization!$J$15</f>
         <v/>
       </c>
@@ -11902,27 +11773,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M124" s="7">
+      <c r="M124" s="6">
         <f>L124 + I124</f>
         <v/>
       </c>
-      <c r="N124" s="7">
+      <c r="N124" s="6">
         <f>L124 + J124</f>
         <v/>
       </c>
-      <c r="O124" s="7">
+      <c r="O124" s="6">
         <f>L124 + K124</f>
         <v/>
       </c>
-      <c r="Q124" s="7">
+      <c r="Q124" s="6">
         <f>$B$2 - M124 - $F$2</f>
         <v/>
       </c>
-      <c r="R124" s="7">
+      <c r="R124" s="6">
         <f>$B$2 - N124 - $F$2</f>
         <v/>
       </c>
-      <c r="S124" s="7">
+      <c r="S124" s="6">
         <f>$B$2 - O124 - $F$2</f>
         <v/>
       </c>
@@ -11965,15 +11836,15 @@
           <t>u_wr_axi_skid AW.wr_data (D)</t>
         </is>
       </c>
-      <c r="I125" s="7">
+      <c r="I125" s="6">
         <f>F125*characterization!$D$17 + G125*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J125" s="7">
+      <c r="J125" s="6">
         <f>F125*characterization!$G$17 + G125*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K125" s="7">
+      <c r="K125" s="6">
         <f>F125*characterization!$J$17 + G125*characterization!$J$15</f>
         <v/>
       </c>
@@ -11981,27 +11852,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M125" s="7">
+      <c r="M125" s="6">
         <f>L125 + I125</f>
         <v/>
       </c>
-      <c r="N125" s="7">
+      <c r="N125" s="6">
         <f>L125 + J125</f>
         <v/>
       </c>
-      <c r="O125" s="7">
+      <c r="O125" s="6">
         <f>L125 + K125</f>
         <v/>
       </c>
-      <c r="Q125" s="7">
+      <c r="Q125" s="6">
         <f>$B$2 - M125 - $F$2</f>
         <v/>
       </c>
-      <c r="R125" s="7">
+      <c r="R125" s="6">
         <f>$B$2 - N125 - $F$2</f>
         <v/>
       </c>
-      <c r="S125" s="7">
+      <c r="S125" s="6">
         <f>$B$2 - O125 - $F$2</f>
         <v/>
       </c>
@@ -12044,15 +11915,15 @@
           <t>u_wr_axi_skid AW.wr_valid (D)</t>
         </is>
       </c>
-      <c r="I126" s="7">
+      <c r="I126" s="6">
         <f>F126*characterization!$D$17 + G126*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J126" s="7">
+      <c r="J126" s="6">
         <f>F126*characterization!$G$17 + G126*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K126" s="7">
+      <c r="K126" s="6">
         <f>F126*characterization!$J$17 + G126*characterization!$J$15</f>
         <v/>
       </c>
@@ -12060,27 +11931,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M126" s="7">
+      <c r="M126" s="6">
         <f>L126 + I126</f>
         <v/>
       </c>
-      <c r="N126" s="7">
+      <c r="N126" s="6">
         <f>L126 + J126</f>
         <v/>
       </c>
-      <c r="O126" s="7">
+      <c r="O126" s="6">
         <f>L126 + K126</f>
         <v/>
       </c>
-      <c r="Q126" s="7">
+      <c r="Q126" s="6">
         <f>$B$2 - M126 - $F$2</f>
         <v/>
       </c>
-      <c r="R126" s="7">
+      <c r="R126" s="6">
         <f>$B$2 - N126 - $F$2</f>
         <v/>
       </c>
-      <c r="S126" s="7">
+      <c r="S126" s="6">
         <f>$B$2 - O126 - $F$2</f>
         <v/>
       </c>
@@ -12123,15 +11994,15 @@
           <t>u_wr_axi_skid W.wr_data (D)</t>
         </is>
       </c>
-      <c r="I127" s="7">
+      <c r="I127" s="6">
         <f>F127*characterization!$D$17 + G127*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J127" s="7">
+      <c r="J127" s="6">
         <f>F127*characterization!$G$17 + G127*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K127" s="7">
+      <c r="K127" s="6">
         <f>F127*characterization!$J$17 + G127*characterization!$J$15</f>
         <v/>
       </c>
@@ -12139,27 +12010,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M127" s="7">
+      <c r="M127" s="6">
         <f>L127 + I127</f>
         <v/>
       </c>
-      <c r="N127" s="7">
+      <c r="N127" s="6">
         <f>L127 + J127</f>
         <v/>
       </c>
-      <c r="O127" s="7">
+      <c r="O127" s="6">
         <f>L127 + K127</f>
         <v/>
       </c>
-      <c r="Q127" s="7">
+      <c r="Q127" s="6">
         <f>$B$2 - M127 - $F$2</f>
         <v/>
       </c>
-      <c r="R127" s="7">
+      <c r="R127" s="6">
         <f>$B$2 - N127 - $F$2</f>
         <v/>
       </c>
-      <c r="S127" s="7">
+      <c r="S127" s="6">
         <f>$B$2 - O127 - $F$2</f>
         <v/>
       </c>
@@ -12202,15 +12073,15 @@
           <t>u_wr_axi_skid W.wr_data WLAST bit (D)</t>
         </is>
       </c>
-      <c r="I128" s="7">
+      <c r="I128" s="6">
         <f>F128*characterization!$D$17 + G128*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J128" s="7">
+      <c r="J128" s="6">
         <f>F128*characterization!$G$17 + G128*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K128" s="7">
+      <c r="K128" s="6">
         <f>F128*characterization!$J$17 + G128*characterization!$J$15</f>
         <v/>
       </c>
@@ -12218,27 +12089,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M128" s="7">
+      <c r="M128" s="6">
         <f>L128 + I128</f>
         <v/>
       </c>
-      <c r="N128" s="7">
+      <c r="N128" s="6">
         <f>L128 + J128</f>
         <v/>
       </c>
-      <c r="O128" s="7">
+      <c r="O128" s="6">
         <f>L128 + K128</f>
         <v/>
       </c>
-      <c r="Q128" s="7">
+      <c r="Q128" s="6">
         <f>$B$2 - M128 - $F$2</f>
         <v/>
       </c>
-      <c r="R128" s="7">
+      <c r="R128" s="6">
         <f>$B$2 - N128 - $F$2</f>
         <v/>
       </c>
-      <c r="S128" s="7">
+      <c r="S128" s="6">
         <f>$B$2 - O128 - $F$2</f>
         <v/>
       </c>
@@ -12281,15 +12152,15 @@
           <t>r_drain_req (D)</t>
         </is>
       </c>
-      <c r="I129" s="7">
+      <c r="I129" s="6">
         <f>F129*characterization!$D$17 + G129*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J129" s="7">
+      <c r="J129" s="6">
         <f>F129*characterization!$G$17 + G129*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K129" s="7">
+      <c r="K129" s="6">
         <f>F129*characterization!$J$17 + G129*characterization!$J$15</f>
         <v/>
       </c>
@@ -12297,27 +12168,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M129" s="7">
+      <c r="M129" s="6">
         <f>L129 + I129</f>
         <v/>
       </c>
-      <c r="N129" s="7">
+      <c r="N129" s="6">
         <f>L129 + J129</f>
         <v/>
       </c>
-      <c r="O129" s="7">
+      <c r="O129" s="6">
         <f>L129 + K129</f>
         <v/>
       </c>
-      <c r="Q129" s="7">
+      <c r="Q129" s="6">
         <f>$B$2 - M129 - $F$2</f>
         <v/>
       </c>
-      <c r="R129" s="7">
+      <c r="R129" s="6">
         <f>$B$2 - N129 - $F$2</f>
         <v/>
       </c>
-      <c r="S129" s="7">
+      <c r="S129" s="6">
         <f>$B$2 - O129 - $F$2</f>
         <v/>
       </c>
@@ -12360,15 +12231,15 @@
           <t>u_b_phase_txn_fifo wr enable (D)</t>
         </is>
       </c>
-      <c r="I130" s="7">
+      <c r="I130" s="6">
         <f>F130*characterization!$D$17 + G130*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J130" s="7">
+      <c r="J130" s="6">
         <f>F130*characterization!$G$17 + G130*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K130" s="7">
+      <c r="K130" s="6">
         <f>F130*characterization!$J$17 + G130*characterization!$J$15</f>
         <v/>
       </c>
@@ -12376,27 +12247,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M130" s="7">
+      <c r="M130" s="6">
         <f>L130 + I130</f>
         <v/>
       </c>
-      <c r="N130" s="7">
+      <c r="N130" s="6">
         <f>L130 + J130</f>
         <v/>
       </c>
-      <c r="O130" s="7">
+      <c r="O130" s="6">
         <f>L130 + K130</f>
         <v/>
       </c>
-      <c r="Q130" s="7">
+      <c r="Q130" s="6">
         <f>$B$2 - M130 - $F$2</f>
         <v/>
       </c>
-      <c r="R130" s="7">
+      <c r="R130" s="6">
         <f>$B$2 - N130 - $F$2</f>
         <v/>
       </c>
-      <c r="S130" s="7">
+      <c r="S130" s="6">
         <f>$B$2 - O130 - $F$2</f>
         <v/>
       </c>
@@ -12439,15 +12310,15 @@
           <t>sram_drain_req (Q)</t>
         </is>
       </c>
-      <c r="I131" s="7">
+      <c r="I131" s="6">
         <f>F131*characterization!$D$17 + G131*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J131" s="7">
+      <c r="J131" s="6">
         <f>F131*characterization!$G$17 + G131*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K131" s="7">
+      <c r="K131" s="6">
         <f>F131*characterization!$J$17 + G131*characterization!$J$15</f>
         <v/>
       </c>
@@ -12455,27 +12326,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M131" s="7">
+      <c r="M131" s="6">
         <f>L131 + I131</f>
         <v/>
       </c>
-      <c r="N131" s="7">
+      <c r="N131" s="6">
         <f>L131 + J131</f>
         <v/>
       </c>
-      <c r="O131" s="7">
+      <c r="O131" s="6">
         <f>L131 + K131</f>
         <v/>
       </c>
-      <c r="Q131" s="7">
+      <c r="Q131" s="6">
         <f>$B$2 - M131 - $F$2</f>
         <v/>
       </c>
-      <c r="R131" s="7">
+      <c r="R131" s="6">
         <f>$B$2 - N131 - $F$2</f>
         <v/>
       </c>
-      <c r="S131" s="7">
+      <c r="S131" s="6">
         <f>$B$2 - O131 - $F$2</f>
         <v/>
       </c>
@@ -12518,15 +12389,15 @@
           <t>r_drain_req demux (Q)</t>
         </is>
       </c>
-      <c r="I132" s="7">
+      <c r="I132" s="6">
         <f>F132*characterization!$D$17 + G132*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J132" s="7">
+      <c r="J132" s="6">
         <f>F132*characterization!$G$17 + G132*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K132" s="7">
+      <c r="K132" s="6">
         <f>F132*characterization!$J$17 + G132*characterization!$J$15</f>
         <v/>
       </c>
@@ -12534,27 +12405,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M132" s="7">
+      <c r="M132" s="6">
         <f>L132 + I132</f>
         <v/>
       </c>
-      <c r="N132" s="7">
+      <c r="N132" s="6">
         <f>L132 + J132</f>
         <v/>
       </c>
-      <c r="O132" s="7">
+      <c r="O132" s="6">
         <f>L132 + K132</f>
         <v/>
       </c>
-      <c r="Q132" s="7">
+      <c r="Q132" s="6">
         <f>$B$2 - M132 - $F$2</f>
         <v/>
       </c>
-      <c r="R132" s="7">
+      <c r="R132" s="6">
         <f>$B$2 - N132 - $F$2</f>
         <v/>
       </c>
-      <c r="S132" s="7">
+      <c r="S132" s="6">
         <f>$B$2 - O132 - $F$2</f>
         <v/>
       </c>
@@ -12601,15 +12472,15 @@
           <t>u_wr_axi_skid AW head (Q)</t>
         </is>
       </c>
-      <c r="I133" s="7">
+      <c r="I133" s="6">
         <f>F133*characterization!$D$17 + G133*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J133" s="7">
+      <c r="J133" s="6">
         <f>F133*characterization!$G$17 + G133*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K133" s="7">
+      <c r="K133" s="6">
         <f>F133*characterization!$J$17 + G133*characterization!$J$15</f>
         <v/>
       </c>
@@ -12617,27 +12488,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M133" s="7">
+      <c r="M133" s="6">
         <f>L133 + I133</f>
         <v/>
       </c>
-      <c r="N133" s="7">
+      <c r="N133" s="6">
         <f>L133 + J133</f>
         <v/>
       </c>
-      <c r="O133" s="7">
+      <c r="O133" s="6">
         <f>L133 + K133</f>
         <v/>
       </c>
-      <c r="Q133" s="7">
+      <c r="Q133" s="6">
         <f>$B$2 - M133 - $F$2</f>
         <v/>
       </c>
-      <c r="R133" s="7">
+      <c r="R133" s="6">
         <f>$B$2 - N133 - $F$2</f>
         <v/>
       </c>
-      <c r="S133" s="7">
+      <c r="S133" s="6">
         <f>$B$2 - O133 - $F$2</f>
         <v/>
       </c>
@@ -12684,15 +12555,15 @@
           <t>u_wr_axi_skid W head (Q)</t>
         </is>
       </c>
-      <c r="I134" s="7">
+      <c r="I134" s="6">
         <f>F134*characterization!$D$17 + G134*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J134" s="7">
+      <c r="J134" s="6">
         <f>F134*characterization!$G$17 + G134*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K134" s="7">
+      <c r="K134" s="6">
         <f>F134*characterization!$J$17 + G134*characterization!$J$15</f>
         <v/>
       </c>
@@ -12700,27 +12571,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M134" s="7">
+      <c r="M134" s="6">
         <f>L134 + I134</f>
         <v/>
       </c>
-      <c r="N134" s="7">
+      <c r="N134" s="6">
         <f>L134 + J134</f>
         <v/>
       </c>
-      <c r="O134" s="7">
+      <c r="O134" s="6">
         <f>L134 + K134</f>
         <v/>
       </c>
-      <c r="Q134" s="7">
+      <c r="Q134" s="6">
         <f>$B$2 - M134 - $F$2</f>
         <v/>
       </c>
-      <c r="R134" s="7">
+      <c r="R134" s="6">
         <f>$B$2 - N134 - $F$2</f>
         <v/>
       </c>
-      <c r="S134" s="7">
+      <c r="S134" s="6">
         <f>$B$2 - O134 - $F$2</f>
         <v/>
       </c>
@@ -12767,15 +12638,15 @@
           <t>u_wr_axi_skid B input</t>
         </is>
       </c>
-      <c r="I135" s="7">
+      <c r="I135" s="6">
         <f>F135*characterization!$D$17 + G135*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J135" s="7">
+      <c r="J135" s="6">
         <f>F135*characterization!$G$17 + G135*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K135" s="7">
+      <c r="K135" s="6">
         <f>F135*characterization!$J$17 + G135*characterization!$J$15</f>
         <v/>
       </c>
@@ -12783,27 +12654,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M135" s="7">
+      <c r="M135" s="6">
         <f>L135 + I135</f>
         <v/>
       </c>
-      <c r="N135" s="7">
+      <c r="N135" s="6">
         <f>L135 + J135</f>
         <v/>
       </c>
-      <c r="O135" s="7">
+      <c r="O135" s="6">
         <f>L135 + K135</f>
         <v/>
       </c>
-      <c r="Q135" s="7">
+      <c r="Q135" s="6">
         <f>$B$2 - M135 - $F$2</f>
         <v/>
       </c>
-      <c r="R135" s="7">
+      <c r="R135" s="6">
         <f>$B$2 - N135 - $F$2</f>
         <v/>
       </c>
-      <c r="S135" s="7">
+      <c r="S135" s="6">
         <f>$B$2 - O135 - $F$2</f>
         <v/>
       </c>
@@ -12850,15 +12721,15 @@
           <t>b-phase txn capture</t>
         </is>
       </c>
-      <c r="I136" s="7">
+      <c r="I136" s="6">
         <f>F136*characterization!$D$17 + G136*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J136" s="7">
+      <c r="J136" s="6">
         <f>F136*characterization!$G$17 + G136*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K136" s="7">
+      <c r="K136" s="6">
         <f>F136*characterization!$J$17 + G136*characterization!$J$15</f>
         <v/>
       </c>
@@ -12866,27 +12737,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M136" s="7">
+      <c r="M136" s="6">
         <f>L136 + I136</f>
         <v/>
       </c>
-      <c r="N136" s="7">
+      <c r="N136" s="6">
         <f>L136 + J136</f>
         <v/>
       </c>
-      <c r="O136" s="7">
+      <c r="O136" s="6">
         <f>L136 + K136</f>
         <v/>
       </c>
-      <c r="Q136" s="7">
+      <c r="Q136" s="6">
         <f>$B$2 - M136 - $F$2</f>
         <v/>
       </c>
-      <c r="R136" s="7">
+      <c r="R136" s="6">
         <f>$B$2 - N136 - $F$2</f>
         <v/>
       </c>
-      <c r="S136" s="7">
+      <c r="S136" s="6">
         <f>$B$2 - O136 - $F$2</f>
         <v/>
       </c>
@@ -12933,15 +12804,15 @@
           <t>w-phase txn capture</t>
         </is>
       </c>
-      <c r="I137" s="7">
+      <c r="I137" s="6">
         <f>F137*characterization!$D$17 + G137*characterization!$D$15</f>
         <v/>
       </c>
-      <c r="J137" s="7">
+      <c r="J137" s="6">
         <f>F137*characterization!$G$17 + G137*characterization!$G$15</f>
         <v/>
       </c>
-      <c r="K137" s="7">
+      <c r="K137" s="6">
         <f>F137*characterization!$J$17 + G137*characterization!$J$15</f>
         <v/>
       </c>
@@ -12949,27 +12820,27 @@
         <f>$D$2</f>
         <v/>
       </c>
-      <c r="M137" s="7">
+      <c r="M137" s="6">
         <f>L137 + I137</f>
         <v/>
       </c>
-      <c r="N137" s="7">
+      <c r="N137" s="6">
         <f>L137 + J137</f>
         <v/>
       </c>
-      <c r="O137" s="7">
+      <c r="O137" s="6">
         <f>L137 + K137</f>
         <v/>
       </c>
-      <c r="Q137" s="7">
+      <c r="Q137" s="6">
         <f>$B$2 - M137 - $F$2</f>
         <v/>
       </c>
-      <c r="R137" s="7">
+      <c r="R137" s="6">
         <f>$B$2 - N137 - $F$2</f>
         <v/>
       </c>
-      <c r="S137" s="7">
+      <c r="S137" s="6">
         <f>$B$2 - O137 - $F$2</f>
         <v/>
       </c>
@@ -12980,7 +12851,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>Methodology</t>
         </is>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -1668,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:AG23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1694,15 +1694,16 @@
     <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="3" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
     <col width="13" customWidth="1" min="29" max="29"/>
     <col width="13" customWidth="1" min="30" max="30"/>
-    <col width="13" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="3" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1823,41 +1824,46 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>clock</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>target period (ps)</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>target corner</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>target data-&gt;D (ps)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>target flop-&gt;out (ps)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>delay_in (ps)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>delay_out TT</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>delay_out FF</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>delay_out SS</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr"/>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>slack TT (ps)</t>
-        </is>
-      </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>slack FF (ps)</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>slack SS (ps)</t>
-        </is>
-      </c>
+          <t>delay_out (ps)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr"/>
       <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>slack (ps)</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1866,33 +1872,12 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>CONFIG -&gt; target period (ps):</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>input delay 60% (ps):</t>
-        </is>
-      </c>
-      <c r="D2" s="7">
-        <f>B2*0.6</f>
-        <v/>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>output delay 40% (ps):</t>
-        </is>
-      </c>
-      <c r="F2" s="7">
-        <f>B2*0.4</f>
-        <v/>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  delay_in defaults to 0.6*period (STA input arrival). Chain by =Y_prev. slack reserves 0.4*period for downstream output delay.</t>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Each row's 'clock' cell (col X) holds a name from characterization's Design clocks table. Period, corner, input 60%, output 40% are all VLOOKUP'd per row. Change the table entry to plan a new freq/corner and watch the slack column flip from negative (fail) to positive (pass).</t>
         </is>
       </c>
     </row>
@@ -1975,35 +1960,40 @@
         <f>ROUND(1000000/(MAX(O4,T4) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X4" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X4" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y4" s="7">
-        <f>X4 + M4 + R4</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z4" s="7">
-        <f>X4 + N4 + S4</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA4" s="7">
-        <f>X4 + O4 + T4</f>
-        <v/>
-      </c>
-      <c r="AC4" s="7">
-        <f>$B$2 - Y4 - $F$2</f>
+        <f>IF(Z4="TT",M4,IF(Z4="FF",N4,IF(Z4="SS",O4,"")))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="7">
+        <f>IF(Z4="TT",R4,IF(Z4="FF",S4,IF(Z4="SS",T4,"")))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="5">
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD4" s="7">
-        <f>$B$2 - Z4 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE4" s="7">
-        <f>$B$2 - AA4 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF4" t="inlineStr">
+        <f>AC4 + AA4 + AB4</f>
+        <v/>
+      </c>
+      <c r="AF4" s="7">
+        <f>IFERROR(Y4 - AD4 - VLOOKUP(X4, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>SRAM macro (single-port, synchronous read). Storage = W*D bits goes to the macro, not flop count. Read latency = 1 cycle (data appears next clock). Replace this row's per-bit delay with vendor SRAM datasheet for accurate timing.</t>
         </is>
@@ -2082,35 +2072,40 @@
         <f>ROUND(1000000/(MAX(O5,T5) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X5" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y5" s="7">
-        <f>X5 + M5 + R5</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z5" s="7">
-        <f>X5 + N5 + S5</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA5" s="7">
-        <f>X5 + O5 + T5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7">
-        <f>$B$2 - Y5 - $F$2</f>
+        <f>IF(Z5="TT",M5,IF(Z5="FF",N5,IF(Z5="SS",O5,"")))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="7">
+        <f>IF(Z5="TT",R5,IF(Z5="FF",S5,IF(Z5="SS",T5,"")))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="5">
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD5" s="7">
-        <f>$B$2 - Z5 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE5" s="7">
-        <f>$B$2 - AA5 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF5" t="inlineStr">
+        <f>AC5 + AA5 + AB5</f>
+        <v/>
+      </c>
+      <c r="AF5" s="7">
+        <f>IFERROR(Y5 - AD5 - VLOOKUP(X5, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>REGISTERED=1 + MEM_STYLE=BRAM: storage is in an SRAM/BRAM macro, not flops. Used only by SRAM controller units in STREAM/RAPIDS. Storage bits = W*D. fmax is limited by the SRAM macro clock-to-Q, not by std-cell timing.</t>
         </is>
@@ -2196,35 +2191,40 @@
         <f>ROUND(1000000/(MAX(O7,T7) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X7" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X7" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y7" s="7">
-        <f>X7 + M7 + R7</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z7" s="7">
-        <f>X7 + N7 + S7</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA7" s="7">
-        <f>X7 + O7 + T7</f>
-        <v/>
-      </c>
-      <c r="AC7" s="7">
-        <f>$B$2 - Y7 - $F$2</f>
+        <f>IF(Z7="TT",M7,IF(Z7="FF",N7,IF(Z7="SS",O7,"")))</f>
+        <v/>
+      </c>
+      <c r="AB7" s="7">
+        <f>IF(Z7="TT",R7,IF(Z7="FF",S7,IF(Z7="SS",T7,"")))</f>
+        <v/>
+      </c>
+      <c r="AC7" s="5">
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD7" s="7">
-        <f>$B$2 - Z7 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE7" s="7">
-        <f>$B$2 - AA7 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF7" t="inlineStr">
+        <f>AC7 + AA7 + AB7</f>
+        <v/>
+      </c>
+      <c r="AF7" s="7">
+        <f>IFERROR(Y7 - AD7 - VLOOKUP(X7, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Skid buffer outputs come straight from the head flop Q - no output muxing. Input side has the bypass MUX2. Flops = W*D storage + D valid + 2 control.</t>
         </is>
@@ -2304,35 +2304,40 @@
         <f>ROUND(1000000/(MAX(O8,T8) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X8" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X8" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y8" s="7">
-        <f>X8 + M8 + R8</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z8" s="7">
-        <f>X8 + N8 + S8</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA8" s="7">
-        <f>X8 + O8 + T8</f>
-        <v/>
-      </c>
-      <c r="AC8" s="7">
-        <f>$B$2 - Y8 - $F$2</f>
+        <f>IF(Z8="TT",M8,IF(Z8="FF",N8,IF(Z8="SS",O8,"")))</f>
+        <v/>
+      </c>
+      <c r="AB8" s="7">
+        <f>IF(Z8="TT",R8,IF(Z8="FF",S8,IF(Z8="SS",T8,"")))</f>
+        <v/>
+      </c>
+      <c r="AC8" s="5">
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD8" s="7">
-        <f>$B$2 - Z8 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE8" s="7">
-        <f>$B$2 - AA8 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF8" t="inlineStr">
+        <f>AC8 + AA8 + AB8</f>
+        <v/>
+      </c>
+      <c r="AF8" s="7">
+        <f>IFERROR(Y8 - AD8 - VLOOKUP(X8, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Output critical path is the READ mux tree, depth=log2(D). Flops = W*D storage + 3*log2(D) ptrs/count + 1 state. Default FIFO in STREAM/RAPIDS (non-SRAM-backed).</t>
         </is>
@@ -2409,35 +2414,40 @@
         <f>ROUND(1000000/(MAX(O9,T9) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X9" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X9" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y9" s="7">
-        <f>X9 + M9 + R9</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z9" s="7">
-        <f>X9 + N9 + S9</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA9" s="7">
-        <f>X9 + O9 + T9</f>
-        <v/>
-      </c>
-      <c r="AC9" s="7">
-        <f>$B$2 - Y9 - $F$2</f>
+        <f>IF(Z9="TT",M9,IF(Z9="FF",N9,IF(Z9="SS",O9,"")))</f>
+        <v/>
+      </c>
+      <c r="AB9" s="7">
+        <f>IF(Z9="TT",R9,IF(Z9="FF",S9,IF(Z9="SS",T9,"")))</f>
+        <v/>
+      </c>
+      <c r="AC9" s="5">
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD9" s="7">
-        <f>$B$2 - Z9 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE9" s="7">
-        <f>$B$2 - AA9 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF9" t="inlineStr">
+        <f>AC9 + AA9 + AB9</f>
+        <v/>
+      </c>
+      <c r="AF9" s="7">
+        <f>IFERROR(Y9 - AD9 - VLOOKUP(X9, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Priority encoder is log2(N) MUX levels on the OUTPUT side (req -&gt; encode -&gt; gnt). Flops = N (last-grant tracker) + 2.</t>
         </is>
@@ -2528,35 +2538,40 @@
         <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X10" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X10" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y10" s="7">
-        <f>X10 + M10 + R10</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z10" s="7">
-        <f>X10 + N10 + S10</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA10" s="7">
-        <f>X10 + O10 + T10</f>
-        <v/>
-      </c>
-      <c r="AC10" s="7">
-        <f>$B$2 - Y10 - $F$2</f>
+        <f>IF(Z10="TT",M10,IF(Z10="FF",N10,IF(Z10="SS",O10,"")))</f>
+        <v/>
+      </c>
+      <c r="AB10" s="7">
+        <f>IF(Z10="TT",R10,IF(Z10="FF",S10,IF(Z10="SS",T10,"")))</f>
+        <v/>
+      </c>
+      <c r="AC10" s="5">
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD10" s="7">
-        <f>$B$2 - Z10 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE10" s="7">
-        <f>$B$2 - AA10 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF10" t="inlineStr">
+        <f>AC10 + AA10 + AB10</f>
+        <v/>
+      </c>
+      <c r="AF10" s="7">
+        <f>IFERROR(Y10 - AD10 - VLOOKUP(X10, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Two skid buffers in series (AR + R). Input bypass MUX2 + output select MUX2. Flops scale with SKID_AR*ARw + SKID_R*Rw.</t>
         </is>
@@ -2647,35 +2662,40 @@
         <f>ROUND(1000000/(MAX(O11,T11) + characterization!$J$3), 0)</f>
         <v/>
       </c>
-      <c r="X11" s="5">
-        <f>$D$2</f>
-        <v/>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>clk_main</t>
+        </is>
       </c>
       <c r="Y11" s="7">
-        <f>X11 + M11 + R11</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z11" s="7">
-        <f>X11 + N11 + S11</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA11" s="7">
-        <f>X11 + O11 + T11</f>
-        <v/>
-      </c>
-      <c r="AC11" s="7">
-        <f>$B$2 - Y11 - $F$2</f>
+        <f>IF(Z11="TT",M11,IF(Z11="FF",N11,IF(Z11="SS",O11,"")))</f>
+        <v/>
+      </c>
+      <c r="AB11" s="7">
+        <f>IF(Z11="TT",R11,IF(Z11="FF",S11,IF(Z11="SS",T11,"")))</f>
+        <v/>
+      </c>
+      <c r="AC11" s="5">
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 5, FALSE), "")</f>
         <v/>
       </c>
       <c r="AD11" s="7">
-        <f>$B$2 - Z11 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AE11" s="7">
-        <f>$B$2 - AA11 - $F$2</f>
-        <v/>
-      </c>
-      <c r="AF11" t="inlineStr">
+        <f>AC11 + AA11 + AB11</f>
+        <v/>
+      </c>
+      <c r="AF11" s="7">
+        <f>IFERROR(Y11 - AD11 - VLOOKUP(X11, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Three skid buffers (AW + W + B); SKID_B fixed at 2 in this row. Input bypass + output select MUXes; both are 1 level.</t>
         </is>
@@ -2781,9 +2801,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:AF3"/>
-    <mergeCell ref="A6:AF6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A6:AG6"/>
+    <mergeCell ref="B2:AG2"/>
+    <mergeCell ref="A3:AG3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -1982,7 +1982,7 @@
         <v/>
       </c>
       <c r="AC4" s="5">
-        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD4" s="7">
@@ -2094,7 +2094,7 @@
         <v/>
       </c>
       <c r="AC5" s="5">
-        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD5" s="7">
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="AC7" s="5">
-        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD7" s="7">
@@ -2326,7 +2326,7 @@
         <v/>
       </c>
       <c r="AC8" s="5">
-        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD8" s="7">
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="AC9" s="5">
-        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD9" s="7">
@@ -2560,7 +2560,7 @@
         <v/>
       </c>
       <c r="AC10" s="5">
-        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD10" s="7">
@@ -2684,7 +2684,7 @@
         <v/>
       </c>
       <c r="AC11" s="5">
-        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD11" s="7">
@@ -3010,7 +3010,7 @@
         <v/>
       </c>
       <c r="O4" s="5">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P4" s="7">
@@ -3089,7 +3089,7 @@
         <v/>
       </c>
       <c r="O5" s="5">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P5" s="7">
@@ -3164,7 +3164,7 @@
         <v/>
       </c>
       <c r="O6" s="5">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P6" s="7">
@@ -3239,7 +3239,7 @@
         <v/>
       </c>
       <c r="O7" s="5">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P7" s="7">
@@ -3318,7 +3318,7 @@
         <v/>
       </c>
       <c r="O8" s="5">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P8" s="7">
@@ -3397,7 +3397,7 @@
         <v/>
       </c>
       <c r="O9" s="5">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P9" s="7">
@@ -3476,7 +3476,7 @@
         <v/>
       </c>
       <c r="O10" s="5">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P10" s="7">
@@ -3555,7 +3555,7 @@
         <v/>
       </c>
       <c r="O11" s="5">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P11" s="7">
@@ -3630,7 +3630,7 @@
         <v/>
       </c>
       <c r="O12" s="5">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P12" s="7">
@@ -3712,7 +3712,7 @@
         <v/>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P14" s="7">
@@ -3787,7 +3787,7 @@
         <v/>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P15" s="7">
@@ -3862,7 +3862,7 @@
         <v/>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P16" s="7">
@@ -3937,7 +3937,7 @@
         <v/>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P17" s="7">
@@ -4012,7 +4012,7 @@
         <v/>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P18" s="7">
@@ -4087,7 +4087,7 @@
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P19" s="7">
@@ -4162,7 +4162,7 @@
         <v/>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P20" s="7">
@@ -4237,7 +4237,7 @@
         <v/>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P21" s="7">
@@ -4312,7 +4312,7 @@
         <v/>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P22" s="7">
@@ -4394,7 +4394,7 @@
         <v/>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P24" s="7">
@@ -4469,7 +4469,7 @@
         <v/>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P25" s="7">
@@ -4544,7 +4544,7 @@
         <v/>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P26" s="7">
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P27" s="7">
@@ -4694,7 +4694,7 @@
         <v/>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P28" s="7">
@@ -4769,7 +4769,7 @@
         <v/>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P29" s="7">
@@ -4844,7 +4844,7 @@
         <v/>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P30" s="7">
@@ -4919,7 +4919,7 @@
         <v/>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P31" s="7">
@@ -4994,7 +4994,7 @@
         <v/>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P32" s="7">
@@ -5076,7 +5076,7 @@
         <v/>
       </c>
       <c r="O34" s="5">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P34" s="7">
@@ -5151,7 +5151,7 @@
         <v/>
       </c>
       <c r="O35" s="5">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P35" s="7">
@@ -5226,7 +5226,7 @@
         <v/>
       </c>
       <c r="O36" s="5">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P36" s="7">
@@ -5301,7 +5301,7 @@
         <v/>
       </c>
       <c r="O37" s="5">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P37" s="7">
@@ -5380,7 +5380,7 @@
         <v/>
       </c>
       <c r="O38" s="5">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P38" s="7">
@@ -5459,7 +5459,7 @@
         <v/>
       </c>
       <c r="O39" s="5">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P39" s="7">
@@ -5538,7 +5538,7 @@
         <v/>
       </c>
       <c r="O40" s="5">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P40" s="7">
@@ -5613,7 +5613,7 @@
         <v/>
       </c>
       <c r="O41" s="5">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P41" s="7">
@@ -5692,7 +5692,7 @@
         <v/>
       </c>
       <c r="O42" s="5">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P42" s="7">
@@ -5767,7 +5767,7 @@
         <v/>
       </c>
       <c r="O43" s="5">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P43" s="7">
@@ -5842,7 +5842,7 @@
         <v/>
       </c>
       <c r="O44" s="5">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P44" s="7">
@@ -5924,7 +5924,7 @@
         <v/>
       </c>
       <c r="O46" s="5">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P46" s="7">
@@ -5999,7 +5999,7 @@
         <v/>
       </c>
       <c r="O47" s="5">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P47" s="7">
@@ -6074,7 +6074,7 @@
         <v/>
       </c>
       <c r="O48" s="5">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P48" s="7">
@@ -6149,7 +6149,7 @@
         <v/>
       </c>
       <c r="O49" s="5">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P49" s="7">
@@ -6224,7 +6224,7 @@
         <v/>
       </c>
       <c r="O50" s="5">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P50" s="7">
@@ -6306,7 +6306,7 @@
         <v/>
       </c>
       <c r="O52" s="5">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P52" s="7">
@@ -6381,7 +6381,7 @@
         <v/>
       </c>
       <c r="O53" s="5">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P53" s="7">
@@ -6456,7 +6456,7 @@
         <v/>
       </c>
       <c r="O54" s="5">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P54" s="7">
@@ -6531,7 +6531,7 @@
         <v/>
       </c>
       <c r="O55" s="5">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P55" s="7">
@@ -6606,7 +6606,7 @@
         <v/>
       </c>
       <c r="O56" s="5">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P56" s="7">
@@ -6681,7 +6681,7 @@
         <v/>
       </c>
       <c r="O57" s="5">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P57" s="7">
@@ -6756,7 +6756,7 @@
         <v/>
       </c>
       <c r="O58" s="5">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P58" s="7">
@@ -6835,7 +6835,7 @@
         <v/>
       </c>
       <c r="O59" s="5">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P59" s="7">
@@ -6914,7 +6914,7 @@
         <v/>
       </c>
       <c r="O60" s="5">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P60" s="7">
@@ -6993,7 +6993,7 @@
         <v/>
       </c>
       <c r="O61" s="5">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P61" s="7">
@@ -7072,7 +7072,7 @@
         <v/>
       </c>
       <c r="O62" s="5">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P62" s="7">
@@ -7151,7 +7151,7 @@
         <v/>
       </c>
       <c r="O63" s="5">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P63" s="7">
@@ -7233,7 +7233,7 @@
         <v/>
       </c>
       <c r="O65" s="5">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P65" s="7">
@@ -7308,7 +7308,7 @@
         <v/>
       </c>
       <c r="O66" s="5">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P66" s="7">
@@ -7383,7 +7383,7 @@
         <v/>
       </c>
       <c r="O67" s="5">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P67" s="7">
@@ -7458,7 +7458,7 @@
         <v/>
       </c>
       <c r="O68" s="5">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P68" s="7">
@@ -7533,7 +7533,7 @@
         <v/>
       </c>
       <c r="O69" s="5">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P69" s="7">
@@ -7608,7 +7608,7 @@
         <v/>
       </c>
       <c r="O70" s="5">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P70" s="7">
@@ -7683,7 +7683,7 @@
         <v/>
       </c>
       <c r="O71" s="5">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P71" s="7">
@@ -7758,7 +7758,7 @@
         <v/>
       </c>
       <c r="O72" s="5">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P72" s="7">
@@ -7833,7 +7833,7 @@
         <v/>
       </c>
       <c r="O73" s="5">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P73" s="7">
@@ -7908,7 +7908,7 @@
         <v/>
       </c>
       <c r="O74" s="5">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P74" s="7">
@@ -7983,7 +7983,7 @@
         <v/>
       </c>
       <c r="O75" s="5">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P75" s="7">
@@ -8065,7 +8065,7 @@
         <v/>
       </c>
       <c r="O77" s="5">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P77" s="7">
@@ -8140,7 +8140,7 @@
         <v/>
       </c>
       <c r="O78" s="5">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P78" s="7">
@@ -8215,7 +8215,7 @@
         <v/>
       </c>
       <c r="O79" s="5">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P79" s="7">
@@ -8290,7 +8290,7 @@
         <v/>
       </c>
       <c r="O80" s="5">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P80" s="7">
@@ -8365,7 +8365,7 @@
         <v/>
       </c>
       <c r="O81" s="5">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P81" s="7">
@@ -8440,7 +8440,7 @@
         <v/>
       </c>
       <c r="O82" s="5">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P82" s="7">
@@ -8519,7 +8519,7 @@
         <v/>
       </c>
       <c r="O83" s="5">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P83" s="7">
@@ -8598,7 +8598,7 @@
         <v/>
       </c>
       <c r="O84" s="5">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P84" s="7">
@@ -8677,7 +8677,7 @@
         <v/>
       </c>
       <c r="O85" s="5">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P85" s="7">
@@ -8756,7 +8756,7 @@
         <v/>
       </c>
       <c r="O86" s="5">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P86" s="7">
@@ -8835,7 +8835,7 @@
         <v/>
       </c>
       <c r="O87" s="5">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P87" s="7">
@@ -8917,7 +8917,7 @@
         <v/>
       </c>
       <c r="O89" s="5">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P89" s="7">
@@ -8992,7 +8992,7 @@
         <v/>
       </c>
       <c r="O90" s="5">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P90" s="7">
@@ -9067,7 +9067,7 @@
         <v/>
       </c>
       <c r="O91" s="5">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P91" s="7">
@@ -9142,7 +9142,7 @@
         <v/>
       </c>
       <c r="O92" s="5">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P92" s="7">
@@ -9217,7 +9217,7 @@
         <v/>
       </c>
       <c r="O93" s="5">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P93" s="7">
@@ -9292,7 +9292,7 @@
         <v/>
       </c>
       <c r="O94" s="5">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P94" s="7">
@@ -9367,7 +9367,7 @@
         <v/>
       </c>
       <c r="O95" s="5">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P95" s="7">
@@ -9442,7 +9442,7 @@
         <v/>
       </c>
       <c r="O96" s="5">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P96" s="7">
@@ -9517,7 +9517,7 @@
         <v/>
       </c>
       <c r="O97" s="5">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P97" s="7">
@@ -9592,7 +9592,7 @@
         <v/>
       </c>
       <c r="O98" s="5">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P98" s="7">
@@ -9667,7 +9667,7 @@
         <v/>
       </c>
       <c r="O99" s="5">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P99" s="7">
@@ -9742,7 +9742,7 @@
         <v/>
       </c>
       <c r="O100" s="5">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P100" s="7">
@@ -9817,7 +9817,7 @@
         <v/>
       </c>
       <c r="O101" s="5">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P101" s="7">
@@ -9892,7 +9892,7 @@
         <v/>
       </c>
       <c r="O102" s="5">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P102" s="7">
@@ -9974,7 +9974,7 @@
         <v/>
       </c>
       <c r="O104" s="5">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P104" s="7">
@@ -10049,7 +10049,7 @@
         <v/>
       </c>
       <c r="O105" s="5">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P105" s="7">
@@ -10124,7 +10124,7 @@
         <v/>
       </c>
       <c r="O106" s="5">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P106" s="7">
@@ -10199,7 +10199,7 @@
         <v/>
       </c>
       <c r="O107" s="5">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P107" s="7">
@@ -10274,7 +10274,7 @@
         <v/>
       </c>
       <c r="O108" s="5">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P108" s="7">
@@ -10349,7 +10349,7 @@
         <v/>
       </c>
       <c r="O109" s="5">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P109" s="7">
@@ -10424,7 +10424,7 @@
         <v/>
       </c>
       <c r="O110" s="5">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P110" s="7">
@@ -10499,7 +10499,7 @@
         <v/>
       </c>
       <c r="O111" s="5">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P111" s="7">
@@ -10578,7 +10578,7 @@
         <v/>
       </c>
       <c r="O112" s="5">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P112" s="7">
@@ -10657,7 +10657,7 @@
         <v/>
       </c>
       <c r="O113" s="5">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P113" s="7">
@@ -10732,7 +10732,7 @@
         <v/>
       </c>
       <c r="O114" s="5">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P114" s="7">
@@ -10807,7 +10807,7 @@
         <v/>
       </c>
       <c r="O115" s="5">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P115" s="7">
@@ -10882,7 +10882,7 @@
         <v/>
       </c>
       <c r="O116" s="5">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P116" s="7">
@@ -10957,7 +10957,7 @@
         <v/>
       </c>
       <c r="O117" s="5">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P117" s="7">
@@ -11039,7 +11039,7 @@
         <v/>
       </c>
       <c r="O119" s="5">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P119" s="7">
@@ -11114,7 +11114,7 @@
         <v/>
       </c>
       <c r="O120" s="5">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P120" s="7">
@@ -11189,7 +11189,7 @@
         <v/>
       </c>
       <c r="O121" s="5">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P121" s="7">
@@ -11264,7 +11264,7 @@
         <v/>
       </c>
       <c r="O122" s="5">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P122" s="7">
@@ -11339,7 +11339,7 @@
         <v/>
       </c>
       <c r="O123" s="5">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P123" s="7">
@@ -11414,7 +11414,7 @@
         <v/>
       </c>
       <c r="O124" s="5">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P124" s="7">
@@ -11489,7 +11489,7 @@
         <v/>
       </c>
       <c r="O125" s="5">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P125" s="7">
@@ -11564,7 +11564,7 @@
         <v/>
       </c>
       <c r="O126" s="5">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P126" s="7">
@@ -11639,7 +11639,7 @@
         <v/>
       </c>
       <c r="O127" s="5">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P127" s="7">
@@ -11714,7 +11714,7 @@
         <v/>
       </c>
       <c r="O128" s="5">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P128" s="7">
@@ -11789,7 +11789,7 @@
         <v/>
       </c>
       <c r="O129" s="5">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P129" s="7">
@@ -11864,7 +11864,7 @@
         <v/>
       </c>
       <c r="O130" s="5">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P130" s="7">
@@ -11939,7 +11939,7 @@
         <v/>
       </c>
       <c r="O131" s="5">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P131" s="7">
@@ -12014,7 +12014,7 @@
         <v/>
       </c>
       <c r="O132" s="5">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P132" s="7">
@@ -12093,7 +12093,7 @@
         <v/>
       </c>
       <c r="O133" s="5">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P133" s="7">
@@ -12172,7 +12172,7 @@
         <v/>
       </c>
       <c r="O134" s="5">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P134" s="7">
@@ -12251,7 +12251,7 @@
         <v/>
       </c>
       <c r="O135" s="5">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P135" s="7">
@@ -12330,7 +12330,7 @@
         <v/>
       </c>
       <c r="O136" s="5">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P136" s="7">
@@ -12409,7 +12409,7 @@
         <v/>
       </c>
       <c r="O137" s="5">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$F$34, 5, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P137" s="7">

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,12 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -506,27 +512,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TT_500MHz</t>
+          <t>TT_1000MHz</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>TT_750MHz</t>
+          <t>TT_1250MHz</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TT_1000MHz</t>
+          <t>TT_1500MHz</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FF_500MHz</t>
+          <t>TT_1750MHz</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>FF_750MHz</t>
+          <t>TT_2000MHz</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -536,17 +542,47 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SS_500MHz</t>
+          <t>FF_1250MHz</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SS_750MHz</t>
+          <t>FF_1500MHz</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>FF_1750MHz</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FF_2000MHz</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>SS_1000MHz</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SS_1250MHz</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>SS_1500MHz</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SS_1750MHz</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SS_2000MHz</t>
         </is>
       </c>
     </row>
@@ -557,31 +593,49 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1333.3</v>
+        <v>800</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1000</v>
+        <v>666.7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2000</v>
+        <v>571.4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1333.3</v>
+        <v>500</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1333.3</v>
+        <v>666.7</v>
       </c>
       <c r="J2" s="2" t="n">
+        <v>571.4</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>1000</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>666.7</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>571.4</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="3">
@@ -600,21 +654,39 @@
         <v>16.59</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.53</v>
+        <v>16.59</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10.53</v>
+        <v>16.59</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>10.53</v>
       </c>
       <c r="H3" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>22.73</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>22.73</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="N3" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>22.73</v>
       </c>
     </row>
@@ -629,6 +701,12 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -645,6 +723,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -653,31 +737,49 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>273</v>
+        <v>135</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>335</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>223</v>
+        <v>66</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>166</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J6" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="L6" s="2" t="n">
         <v>85</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -687,19 +789,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>61</v>
@@ -708,10 +810,28 @@
         <v>49</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J7" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>24</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -721,31 +841,49 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>89</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>39</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -755,31 +893,49 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>47</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J9" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>21</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -789,31 +945,49 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>45</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J10" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>26</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -823,31 +997,49 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>14</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>10</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -857,31 +1049,49 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J12" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>18</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -895,6 +1105,12 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -911,6 +1127,12 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -928,21 +1150,39 @@
         <v>7.25</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>5.93</v>
+        <v>7.25</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5.93</v>
+        <v>7.25</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5.93</v>
       </c>
       <c r="H15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>11.47</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="M15" s="2" t="n">
         <v>11.47</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="N15" s="2" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="P15" s="2" t="n">
         <v>11.47</v>
       </c>
     </row>
@@ -962,21 +1202,39 @@
         <v>26.77</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16.01</v>
+        <v>26.77</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>16.01</v>
+        <v>26.77</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>16.01</v>
       </c>
       <c r="H16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="L16" s="2" t="n">
         <v>39.69</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>39.69</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="N16" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="P16" s="2" t="n">
         <v>39.69</v>
       </c>
     </row>
@@ -996,21 +1254,39 @@
         <v>16.29</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>11</v>
+        <v>16.29</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>11</v>
+        <v>16.29</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>24.97</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="M17" s="2" t="n">
         <v>24.97</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="N17" s="2" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="P17" s="2" t="n">
         <v>24.97</v>
       </c>
     </row>
@@ -1030,21 +1306,39 @@
         <v>30.77</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>20.97</v>
+        <v>30.77</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>20.97</v>
+        <v>30.77</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>20.97</v>
       </c>
       <c r="H18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>45.22</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>45.22</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="N18" s="2" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="P18" s="2" t="n">
         <v>45.22</v>
       </c>
     </row>
@@ -1064,21 +1358,39 @@
         <v>29.95</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>21.75</v>
+        <v>29.95</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>21.75</v>
+        <v>29.95</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>21.75</v>
       </c>
       <c r="H19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>37.44</v>
       </c>
-      <c r="I19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>37.44</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="N19" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="P19" s="5" t="n">
         <v>37.44</v>
       </c>
     </row>
@@ -1098,21 +1410,39 @@
         <v>58.44</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>66.65000000000001</v>
+        <v>58.44</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>66.65000000000001</v>
+        <v>58.44</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>66.65000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>66.65000000000001</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>90.34</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="M20" s="2" t="n">
         <v>90.34</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="N20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="P20" s="2" t="n">
         <v>90.34</v>
       </c>
     </row>
@@ -1132,21 +1462,39 @@
         <v>11.57</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>40.17</v>
+        <v>11.57</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>40.17</v>
+        <v>11.57</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>40.17</v>
       </c>
       <c r="H21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="L21" s="2" t="n">
         <v>54.23</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>54.23</v>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="N21" s="2" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="P21" s="2" t="n">
         <v>54.23</v>
       </c>
     </row>
@@ -1161,6 +1509,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1177,6 +1531,12 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1194,21 +1554,39 @@
         <v>14.47</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12.22</v>
+        <v>14.47</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>12.22</v>
+        <v>14.47</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>12.22</v>
       </c>
       <c r="H24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="L24" s="2" t="n">
         <v>22.33</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="M24" s="2" t="n">
         <v>22.33</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="N24" s="2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="P24" s="2" t="n">
         <v>22.33</v>
       </c>
     </row>
@@ -1228,21 +1606,39 @@
         <v>21.05</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.61</v>
+        <v>21.05</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>16.61</v>
+        <v>21.05</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>16.61</v>
       </c>
       <c r="H25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="L25" s="2" t="n">
         <v>31.29</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="M25" s="2" t="n">
         <v>31.29</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="N25" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="P25" s="2" t="n">
         <v>31.29</v>
       </c>
     </row>
@@ -1257,6 +1653,12 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1273,6 +1675,12 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1429,6 +1837,12 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1445,6 +1859,12 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1462,21 +1882,39 @@
         <v>120</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>96</v>
       </c>
       <c r="H37" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="L37" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="M37" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="N37" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="P37" s="2" t="n">
         <v>156</v>
       </c>
     </row>
@@ -1496,21 +1934,39 @@
         <v>65</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>52</v>
       </c>
       <c r="H38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L38" s="2" t="n">
         <v>84.5</v>
       </c>
-      <c r="I38" s="2" t="n">
+      <c r="M38" s="2" t="n">
         <v>84.5</v>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="N38" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="P38" s="2" t="n">
         <v>84.5</v>
       </c>
     </row>
@@ -1530,21 +1986,39 @@
         <v>40</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>32</v>
       </c>
       <c r="H39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="L39" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="M39" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="N39" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="P39" s="2" t="n">
         <v>52</v>
       </c>
     </row>
@@ -1564,21 +2038,39 @@
         <v>22</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>17.6</v>
+        <v>22</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>17.6</v>
+        <v>22</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>17.6</v>
       </c>
       <c r="H40" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="I40" s="2" t="n">
+      <c r="M40" s="2" t="n">
         <v>28.6</v>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="N40" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="P40" s="2" t="n">
         <v>28.6</v>
       </c>
     </row>
@@ -1593,6 +2085,12 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -1919,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="M4" s="7">
-        <f>K4*characterization!$D$17 + L4*characterization!$D$15</f>
+        <f>K4*characterization!$B$17 + L4*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N4" s="7">
@@ -1927,7 +2425,7 @@
         <v/>
       </c>
       <c r="O4" s="7">
-        <f>K4*characterization!$J$17 + L4*characterization!$J$15</f>
+        <f>K4*characterization!$L$17 + L4*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P4" t="n">
@@ -1937,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="R4" s="7">
-        <f>P4*characterization!$D$17 + Q4*characterization!$D$15</f>
+        <f>P4*characterization!$B$17 + Q4*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S4" s="7">
@@ -1945,11 +2443,11 @@
         <v/>
       </c>
       <c r="T4" s="7">
-        <f>P4*characterization!$J$17 + Q4*characterization!$J$15</f>
+        <f>P4*characterization!$L$17 + Q4*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U4" s="7">
-        <f>ROUND(1000000/(MAX(M4,R4) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M4,R4) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V4" s="7">
@@ -1957,7 +2455,7 @@
         <v/>
       </c>
       <c r="W4" s="7">
-        <f>ROUND(1000000/(MAX(O4,T4) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O4,T4) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X4" s="5" t="inlineStr">
@@ -2031,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="7">
-        <f>K5*characterization!$D$17 + L5*characterization!$D$15</f>
+        <f>K5*characterization!$B$17 + L5*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N5" s="7">
@@ -2039,7 +2537,7 @@
         <v/>
       </c>
       <c r="O5" s="7">
-        <f>K5*characterization!$J$17 + L5*characterization!$J$15</f>
+        <f>K5*characterization!$L$17 + L5*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P5" t="n">
@@ -2049,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="R5" s="7">
-        <f>P5*characterization!$D$17 + Q5*characterization!$D$15</f>
+        <f>P5*characterization!$B$17 + Q5*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S5" s="7">
@@ -2057,11 +2555,11 @@
         <v/>
       </c>
       <c r="T5" s="7">
-        <f>P5*characterization!$J$17 + Q5*characterization!$J$15</f>
+        <f>P5*characterization!$L$17 + Q5*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U5" s="7">
-        <f>ROUND(1000000/(MAX(M5,R5) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M5,R5) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V5" s="7">
@@ -2069,7 +2567,7 @@
         <v/>
       </c>
       <c r="W5" s="7">
-        <f>ROUND(1000000/(MAX(O5,T5) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O5,T5) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X5" s="5" t="inlineStr">
@@ -2150,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="7">
-        <f>K7*characterization!$D$17 + L7*characterization!$D$15</f>
+        <f>K7*characterization!$B$17 + L7*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N7" s="7">
@@ -2158,7 +2656,7 @@
         <v/>
       </c>
       <c r="O7" s="7">
-        <f>K7*characterization!$J$17 + L7*characterization!$J$15</f>
+        <f>K7*characterization!$L$17 + L7*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P7" t="n">
@@ -2168,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="7">
-        <f>P7*characterization!$D$17 + Q7*characterization!$D$15</f>
+        <f>P7*characterization!$B$17 + Q7*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S7" s="7">
@@ -2176,11 +2674,11 @@
         <v/>
       </c>
       <c r="T7" s="7">
-        <f>P7*characterization!$J$17 + Q7*characterization!$J$15</f>
+        <f>P7*characterization!$L$17 + Q7*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U7" s="7">
-        <f>ROUND(1000000/(MAX(M7,R7) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M7,R7) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V7" s="7">
@@ -2188,7 +2686,7 @@
         <v/>
       </c>
       <c r="W7" s="7">
-        <f>ROUND(1000000/(MAX(O7,T7) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O7,T7) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X7" s="5" t="inlineStr">
@@ -2262,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="M8" s="7">
-        <f>K8*characterization!$D$17 + L8*characterization!$D$15</f>
+        <f>K8*characterization!$B$17 + L8*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N8" s="7">
@@ -2270,7 +2768,7 @@
         <v/>
       </c>
       <c r="O8" s="7">
-        <f>K8*characterization!$J$17 + L8*characterization!$J$15</f>
+        <f>K8*characterization!$L$17 + L8*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P8">
@@ -2281,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="7">
-        <f>P8*characterization!$D$17 + Q8*characterization!$D$15</f>
+        <f>P8*characterization!$B$17 + Q8*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S8" s="7">
@@ -2289,11 +2787,11 @@
         <v/>
       </c>
       <c r="T8" s="7">
-        <f>P8*characterization!$J$17 + Q8*characterization!$J$15</f>
+        <f>P8*characterization!$L$17 + Q8*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U8" s="7">
-        <f>ROUND(1000000/(MAX(M8,R8) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M8,R8) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V8" s="7">
@@ -2301,7 +2799,7 @@
         <v/>
       </c>
       <c r="W8" s="7">
-        <f>ROUND(1000000/(MAX(O8,T8) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O8,T8) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X8" s="5" t="inlineStr">
@@ -2372,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="7">
-        <f>K9*characterization!$D$17 + L9*characterization!$D$15</f>
+        <f>K9*characterization!$B$17 + L9*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N9" s="7">
@@ -2380,7 +2878,7 @@
         <v/>
       </c>
       <c r="O9" s="7">
-        <f>K9*characterization!$J$17 + L9*characterization!$J$15</f>
+        <f>K9*characterization!$L$17 + L9*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P9">
@@ -2391,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="R9" s="7">
-        <f>P9*characterization!$D$17 + Q9*characterization!$D$15</f>
+        <f>P9*characterization!$B$17 + Q9*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S9" s="7">
@@ -2399,11 +2897,11 @@
         <v/>
       </c>
       <c r="T9" s="7">
-        <f>P9*characterization!$J$17 + Q9*characterization!$J$15</f>
+        <f>P9*characterization!$L$17 + Q9*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U9" s="7">
-        <f>ROUND(1000000/(MAX(M9,R9) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M9,R9) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V9" s="7">
@@ -2411,7 +2909,7 @@
         <v/>
       </c>
       <c r="W9" s="7">
-        <f>ROUND(1000000/(MAX(O9,T9) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O9,T9) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X9" s="5" t="inlineStr">
@@ -2497,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="7">
-        <f>K10*characterization!$D$17 + L10*characterization!$D$15</f>
+        <f>K10*characterization!$B$17 + L10*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N10" s="7">
@@ -2505,7 +3003,7 @@
         <v/>
       </c>
       <c r="O10" s="7">
-        <f>K10*characterization!$J$17 + L10*characterization!$J$15</f>
+        <f>K10*characterization!$L$17 + L10*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P10" t="n">
@@ -2515,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="7">
-        <f>P10*characterization!$D$17 + Q10*characterization!$D$15</f>
+        <f>P10*characterization!$B$17 + Q10*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S10" s="7">
@@ -2523,11 +3021,11 @@
         <v/>
       </c>
       <c r="T10" s="7">
-        <f>P10*characterization!$J$17 + Q10*characterization!$J$15</f>
+        <f>P10*characterization!$L$17 + Q10*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U10" s="7">
-        <f>ROUND(1000000/(MAX(M10,R10) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M10,R10) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V10" s="7">
@@ -2535,7 +3033,7 @@
         <v/>
       </c>
       <c r="W10" s="7">
-        <f>ROUND(1000000/(MAX(O10,T10) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O10,T10) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X10" s="5" t="inlineStr">
@@ -2621,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="7">
-        <f>K11*characterization!$D$17 + L11*characterization!$D$15</f>
+        <f>K11*characterization!$B$17 + L11*characterization!$B$15</f>
         <v/>
       </c>
       <c r="N11" s="7">
@@ -2629,7 +3127,7 @@
         <v/>
       </c>
       <c r="O11" s="7">
-        <f>K11*characterization!$J$17 + L11*characterization!$J$15</f>
+        <f>K11*characterization!$L$17 + L11*characterization!$L$15</f>
         <v/>
       </c>
       <c r="P11" t="n">
@@ -2639,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="R11" s="7">
-        <f>P11*characterization!$D$17 + Q11*characterization!$D$15</f>
+        <f>P11*characterization!$B$17 + Q11*characterization!$B$15</f>
         <v/>
       </c>
       <c r="S11" s="7">
@@ -2647,11 +3145,11 @@
         <v/>
       </c>
       <c r="T11" s="7">
-        <f>P11*characterization!$J$17 + Q11*characterization!$J$15</f>
+        <f>P11*characterization!$L$17 + Q11*characterization!$L$15</f>
         <v/>
       </c>
       <c r="U11" s="7">
-        <f>ROUND(1000000/(MAX(M11,R11) + characterization!$D$3), 0)</f>
+        <f>ROUND(1000000/(MAX(M11,R11) + characterization!$B$3), 0)</f>
         <v/>
       </c>
       <c r="V11" s="7">
@@ -2659,7 +3157,7 @@
         <v/>
       </c>
       <c r="W11" s="7">
-        <f>ROUND(1000000/(MAX(O11,T11) + characterization!$J$3), 0)</f>
+        <f>ROUND(1000000/(MAX(O11,T11) + characterization!$L$3), 0)</f>
         <v/>
       </c>
       <c r="X11" s="5" t="inlineStr">
@@ -2986,7 +3484,7 @@
         </is>
       </c>
       <c r="I4" s="7">
-        <f>F4*characterization!$D$17 + G4*characterization!$D$15</f>
+        <f>F4*characterization!$B$17 + G4*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J4" s="7">
@@ -2994,7 +3492,7 @@
         <v/>
       </c>
       <c r="K4" s="7">
-        <f>F4*characterization!$J$17 + G4*characterization!$J$15</f>
+        <f>F4*characterization!$L$17 + G4*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L4" s="7">
@@ -3065,7 +3563,7 @@
         </is>
       </c>
       <c r="I5" s="7">
-        <f>F5*characterization!$D$17 + G5*characterization!$D$15</f>
+        <f>F5*characterization!$B$17 + G5*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J5" s="7">
@@ -3073,7 +3571,7 @@
         <v/>
       </c>
       <c r="K5" s="7">
-        <f>F5*characterization!$J$17 + G5*characterization!$J$15</f>
+        <f>F5*characterization!$L$17 + G5*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L5" s="7">
@@ -3140,7 +3638,7 @@
         </is>
       </c>
       <c r="I6" s="7">
-        <f>F6*characterization!$D$17 + G6*characterization!$D$15</f>
+        <f>F6*characterization!$B$17 + G6*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J6" s="7">
@@ -3148,7 +3646,7 @@
         <v/>
       </c>
       <c r="K6" s="7">
-        <f>F6*characterization!$J$17 + G6*characterization!$J$15</f>
+        <f>F6*characterization!$L$17 + G6*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L6" s="7">
@@ -3215,7 +3713,7 @@
         </is>
       </c>
       <c r="I7" s="7">
-        <f>F7*characterization!$D$17 + G7*characterization!$D$15</f>
+        <f>F7*characterization!$B$17 + G7*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J7" s="7">
@@ -3223,7 +3721,7 @@
         <v/>
       </c>
       <c r="K7" s="7">
-        <f>F7*characterization!$J$17 + G7*characterization!$J$15</f>
+        <f>F7*characterization!$L$17 + G7*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L7" s="7">
@@ -3294,7 +3792,7 @@
         </is>
       </c>
       <c r="I8" s="7">
-        <f>F8*characterization!$D$17 + G8*characterization!$D$15</f>
+        <f>F8*characterization!$B$17 + G8*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J8" s="7">
@@ -3302,7 +3800,7 @@
         <v/>
       </c>
       <c r="K8" s="7">
-        <f>F8*characterization!$J$17 + G8*characterization!$J$15</f>
+        <f>F8*characterization!$L$17 + G8*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L8" s="7">
@@ -3373,7 +3871,7 @@
         </is>
       </c>
       <c r="I9" s="7">
-        <f>F9*characterization!$D$17 + G9*characterization!$D$15</f>
+        <f>F9*characterization!$B$17 + G9*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J9" s="7">
@@ -3381,7 +3879,7 @@
         <v/>
       </c>
       <c r="K9" s="7">
-        <f>F9*characterization!$J$17 + G9*characterization!$J$15</f>
+        <f>F9*characterization!$L$17 + G9*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L9" s="7">
@@ -3452,7 +3950,7 @@
         </is>
       </c>
       <c r="I10" s="7">
-        <f>F10*characterization!$D$17 + G10*characterization!$D$15</f>
+        <f>F10*characterization!$B$17 + G10*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J10" s="7">
@@ -3460,7 +3958,7 @@
         <v/>
       </c>
       <c r="K10" s="7">
-        <f>F10*characterization!$J$17 + G10*characterization!$J$15</f>
+        <f>F10*characterization!$L$17 + G10*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L10" s="7">
@@ -3531,7 +4029,7 @@
         </is>
       </c>
       <c r="I11" s="7">
-        <f>F11*characterization!$D$17 + G11*characterization!$D$15</f>
+        <f>F11*characterization!$B$17 + G11*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J11" s="7">
@@ -3539,7 +4037,7 @@
         <v/>
       </c>
       <c r="K11" s="7">
-        <f>F11*characterization!$J$17 + G11*characterization!$J$15</f>
+        <f>F11*characterization!$L$17 + G11*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L11" s="7">
@@ -3606,7 +4104,7 @@
         </is>
       </c>
       <c r="I12" s="7">
-        <f>F12*characterization!$D$17 + G12*characterization!$D$15</f>
+        <f>F12*characterization!$B$17 + G12*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J12" s="7">
@@ -3614,7 +4112,7 @@
         <v/>
       </c>
       <c r="K12" s="7">
-        <f>F12*characterization!$J$17 + G12*characterization!$J$15</f>
+        <f>F12*characterization!$L$17 + G12*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L12" s="7">
@@ -3688,7 +4186,7 @@
         </is>
       </c>
       <c r="I14" s="7">
-        <f>F14*characterization!$D$17 + G14*characterization!$D$15</f>
+        <f>F14*characterization!$B$17 + G14*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J14" s="7">
@@ -3696,7 +4194,7 @@
         <v/>
       </c>
       <c r="K14" s="7">
-        <f>F14*characterization!$J$17 + G14*characterization!$J$15</f>
+        <f>F14*characterization!$L$17 + G14*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L14" s="7">
@@ -3763,7 +4261,7 @@
         </is>
       </c>
       <c r="I15" s="7">
-        <f>F15*characterization!$D$17 + G15*characterization!$D$15</f>
+        <f>F15*characterization!$B$17 + G15*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J15" s="7">
@@ -3771,7 +4269,7 @@
         <v/>
       </c>
       <c r="K15" s="7">
-        <f>F15*characterization!$J$17 + G15*characterization!$J$15</f>
+        <f>F15*characterization!$L$17 + G15*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L15" s="7">
@@ -3838,7 +4336,7 @@
         </is>
       </c>
       <c r="I16" s="7">
-        <f>F16*characterization!$D$17 + G16*characterization!$D$15</f>
+        <f>F16*characterization!$B$17 + G16*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J16" s="7">
@@ -3846,7 +4344,7 @@
         <v/>
       </c>
       <c r="K16" s="7">
-        <f>F16*characterization!$J$17 + G16*characterization!$J$15</f>
+        <f>F16*characterization!$L$17 + G16*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L16" s="7">
@@ -3913,7 +4411,7 @@
         </is>
       </c>
       <c r="I17" s="7">
-        <f>F17*characterization!$D$17 + G17*characterization!$D$15</f>
+        <f>F17*characterization!$B$17 + G17*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J17" s="7">
@@ -3921,7 +4419,7 @@
         <v/>
       </c>
       <c r="K17" s="7">
-        <f>F17*characterization!$J$17 + G17*characterization!$J$15</f>
+        <f>F17*characterization!$L$17 + G17*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L17" s="7">
@@ -3988,7 +4486,7 @@
         </is>
       </c>
       <c r="I18" s="7">
-        <f>F18*characterization!$D$17 + G18*characterization!$D$15</f>
+        <f>F18*characterization!$B$17 + G18*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J18" s="7">
@@ -3996,7 +4494,7 @@
         <v/>
       </c>
       <c r="K18" s="7">
-        <f>F18*characterization!$J$17 + G18*characterization!$J$15</f>
+        <f>F18*characterization!$L$17 + G18*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L18" s="7">
@@ -4063,7 +4561,7 @@
         </is>
       </c>
       <c r="I19" s="7">
-        <f>F19*characterization!$D$17 + G19*characterization!$D$15</f>
+        <f>F19*characterization!$B$17 + G19*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J19" s="7">
@@ -4071,7 +4569,7 @@
         <v/>
       </c>
       <c r="K19" s="7">
-        <f>F19*characterization!$J$17 + G19*characterization!$J$15</f>
+        <f>F19*characterization!$L$17 + G19*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L19" s="7">
@@ -4138,7 +4636,7 @@
         </is>
       </c>
       <c r="I20" s="7">
-        <f>F20*characterization!$D$17 + G20*characterization!$D$15</f>
+        <f>F20*characterization!$B$17 + G20*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J20" s="7">
@@ -4146,7 +4644,7 @@
         <v/>
       </c>
       <c r="K20" s="7">
-        <f>F20*characterization!$J$17 + G20*characterization!$J$15</f>
+        <f>F20*characterization!$L$17 + G20*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L20" s="7">
@@ -4213,7 +4711,7 @@
         </is>
       </c>
       <c r="I21" s="7">
-        <f>F21*characterization!$D$17 + G21*characterization!$D$15</f>
+        <f>F21*characterization!$B$17 + G21*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J21" s="7">
@@ -4221,7 +4719,7 @@
         <v/>
       </c>
       <c r="K21" s="7">
-        <f>F21*characterization!$J$17 + G21*characterization!$J$15</f>
+        <f>F21*characterization!$L$17 + G21*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L21" s="7">
@@ -4288,7 +4786,7 @@
         </is>
       </c>
       <c r="I22" s="7">
-        <f>F22*characterization!$D$17 + G22*characterization!$D$15</f>
+        <f>F22*characterization!$B$17 + G22*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J22" s="7">
@@ -4296,7 +4794,7 @@
         <v/>
       </c>
       <c r="K22" s="7">
-        <f>F22*characterization!$J$17 + G22*characterization!$J$15</f>
+        <f>F22*characterization!$L$17 + G22*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L22" s="7">
@@ -4370,7 +4868,7 @@
         </is>
       </c>
       <c r="I24" s="7">
-        <f>F24*characterization!$D$17 + G24*characterization!$D$15</f>
+        <f>F24*characterization!$B$17 + G24*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J24" s="7">
@@ -4378,7 +4876,7 @@
         <v/>
       </c>
       <c r="K24" s="7">
-        <f>F24*characterization!$J$17 + G24*characterization!$J$15</f>
+        <f>F24*characterization!$L$17 + G24*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L24" s="7">
@@ -4445,7 +4943,7 @@
         </is>
       </c>
       <c r="I25" s="7">
-        <f>F25*characterization!$D$17 + G25*characterization!$D$15</f>
+        <f>F25*characterization!$B$17 + G25*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J25" s="7">
@@ -4453,7 +4951,7 @@
         <v/>
       </c>
       <c r="K25" s="7">
-        <f>F25*characterization!$J$17 + G25*characterization!$J$15</f>
+        <f>F25*characterization!$L$17 + G25*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L25" s="7">
@@ -4520,7 +5018,7 @@
         </is>
       </c>
       <c r="I26" s="7">
-        <f>F26*characterization!$D$17 + G26*characterization!$D$15</f>
+        <f>F26*characterization!$B$17 + G26*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J26" s="7">
@@ -4528,7 +5026,7 @@
         <v/>
       </c>
       <c r="K26" s="7">
-        <f>F26*characterization!$J$17 + G26*characterization!$J$15</f>
+        <f>F26*characterization!$L$17 + G26*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L26" s="7">
@@ -4595,7 +5093,7 @@
         </is>
       </c>
       <c r="I27" s="7">
-        <f>F27*characterization!$D$17 + G27*characterization!$D$15</f>
+        <f>F27*characterization!$B$17 + G27*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J27" s="7">
@@ -4603,7 +5101,7 @@
         <v/>
       </c>
       <c r="K27" s="7">
-        <f>F27*characterization!$J$17 + G27*characterization!$J$15</f>
+        <f>F27*characterization!$L$17 + G27*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L27" s="7">
@@ -4670,7 +5168,7 @@
         </is>
       </c>
       <c r="I28" s="7">
-        <f>F28*characterization!$D$17 + G28*characterization!$D$15</f>
+        <f>F28*characterization!$B$17 + G28*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J28" s="7">
@@ -4678,7 +5176,7 @@
         <v/>
       </c>
       <c r="K28" s="7">
-        <f>F28*characterization!$J$17 + G28*characterization!$J$15</f>
+        <f>F28*characterization!$L$17 + G28*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L28" s="7">
@@ -4745,7 +5243,7 @@
         </is>
       </c>
       <c r="I29" s="7">
-        <f>F29*characterization!$D$17 + G29*characterization!$D$15</f>
+        <f>F29*characterization!$B$17 + G29*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J29" s="7">
@@ -4753,7 +5251,7 @@
         <v/>
       </c>
       <c r="K29" s="7">
-        <f>F29*characterization!$J$17 + G29*characterization!$J$15</f>
+        <f>F29*characterization!$L$17 + G29*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L29" s="7">
@@ -4820,7 +5318,7 @@
         </is>
       </c>
       <c r="I30" s="7">
-        <f>F30*characterization!$D$17 + G30*characterization!$D$15</f>
+        <f>F30*characterization!$B$17 + G30*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J30" s="7">
@@ -4828,7 +5326,7 @@
         <v/>
       </c>
       <c r="K30" s="7">
-        <f>F30*characterization!$J$17 + G30*characterization!$J$15</f>
+        <f>F30*characterization!$L$17 + G30*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L30" s="7">
@@ -4895,7 +5393,7 @@
         </is>
       </c>
       <c r="I31" s="7">
-        <f>F31*characterization!$D$17 + G31*characterization!$D$15</f>
+        <f>F31*characterization!$B$17 + G31*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J31" s="7">
@@ -4903,7 +5401,7 @@
         <v/>
       </c>
       <c r="K31" s="7">
-        <f>F31*characterization!$J$17 + G31*characterization!$J$15</f>
+        <f>F31*characterization!$L$17 + G31*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L31" s="7">
@@ -4970,7 +5468,7 @@
         </is>
       </c>
       <c r="I32" s="7">
-        <f>F32*characterization!$D$17 + G32*characterization!$D$15</f>
+        <f>F32*characterization!$B$17 + G32*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J32" s="7">
@@ -4978,7 +5476,7 @@
         <v/>
       </c>
       <c r="K32" s="7">
-        <f>F32*characterization!$J$17 + G32*characterization!$J$15</f>
+        <f>F32*characterization!$L$17 + G32*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L32" s="7">
@@ -5052,7 +5550,7 @@
         </is>
       </c>
       <c r="I34" s="7">
-        <f>F34*characterization!$D$17 + G34*characterization!$D$15</f>
+        <f>F34*characterization!$B$17 + G34*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J34" s="7">
@@ -5060,7 +5558,7 @@
         <v/>
       </c>
       <c r="K34" s="7">
-        <f>F34*characterization!$J$17 + G34*characterization!$J$15</f>
+        <f>F34*characterization!$L$17 + G34*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L34" s="7">
@@ -5127,7 +5625,7 @@
         </is>
       </c>
       <c r="I35" s="7">
-        <f>F35*characterization!$D$17 + G35*characterization!$D$15</f>
+        <f>F35*characterization!$B$17 + G35*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J35" s="7">
@@ -5135,7 +5633,7 @@
         <v/>
       </c>
       <c r="K35" s="7">
-        <f>F35*characterization!$J$17 + G35*characterization!$J$15</f>
+        <f>F35*characterization!$L$17 + G35*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L35" s="7">
@@ -5202,7 +5700,7 @@
         </is>
       </c>
       <c r="I36" s="7">
-        <f>F36*characterization!$D$17 + G36*characterization!$D$15</f>
+        <f>F36*characterization!$B$17 + G36*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J36" s="7">
@@ -5210,7 +5708,7 @@
         <v/>
       </c>
       <c r="K36" s="7">
-        <f>F36*characterization!$J$17 + G36*characterization!$J$15</f>
+        <f>F36*characterization!$L$17 + G36*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L36" s="7">
@@ -5277,7 +5775,7 @@
         </is>
       </c>
       <c r="I37" s="7">
-        <f>F37*characterization!$D$17 + G37*characterization!$D$15</f>
+        <f>F37*characterization!$B$17 + G37*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J37" s="7">
@@ -5285,7 +5783,7 @@
         <v/>
       </c>
       <c r="K37" s="7">
-        <f>F37*characterization!$J$17 + G37*characterization!$J$15</f>
+        <f>F37*characterization!$L$17 + G37*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L37" s="7">
@@ -5356,7 +5854,7 @@
         </is>
       </c>
       <c r="I38" s="7">
-        <f>F38*characterization!$D$17 + G38*characterization!$D$15</f>
+        <f>F38*characterization!$B$17 + G38*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J38" s="7">
@@ -5364,7 +5862,7 @@
         <v/>
       </c>
       <c r="K38" s="7">
-        <f>F38*characterization!$J$17 + G38*characterization!$J$15</f>
+        <f>F38*characterization!$L$17 + G38*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L38" s="7">
@@ -5435,7 +5933,7 @@
         </is>
       </c>
       <c r="I39" s="7">
-        <f>F39*characterization!$D$17 + G39*characterization!$D$15</f>
+        <f>F39*characterization!$B$17 + G39*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J39" s="7">
@@ -5443,7 +5941,7 @@
         <v/>
       </c>
       <c r="K39" s="7">
-        <f>F39*characterization!$J$17 + G39*characterization!$J$15</f>
+        <f>F39*characterization!$L$17 + G39*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L39" s="7">
@@ -5514,7 +6012,7 @@
         </is>
       </c>
       <c r="I40" s="7">
-        <f>F40*characterization!$D$17 + G40*characterization!$D$15</f>
+        <f>F40*characterization!$B$17 + G40*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J40" s="7">
@@ -5522,7 +6020,7 @@
         <v/>
       </c>
       <c r="K40" s="7">
-        <f>F40*characterization!$J$17 + G40*characterization!$J$15</f>
+        <f>F40*characterization!$L$17 + G40*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L40" s="7">
@@ -5589,7 +6087,7 @@
         </is>
       </c>
       <c r="I41" s="7">
-        <f>F41*characterization!$D$17 + G41*characterization!$D$15</f>
+        <f>F41*characterization!$B$17 + G41*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J41" s="7">
@@ -5597,7 +6095,7 @@
         <v/>
       </c>
       <c r="K41" s="7">
-        <f>F41*characterization!$J$17 + G41*characterization!$J$15</f>
+        <f>F41*characterization!$L$17 + G41*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L41" s="7">
@@ -5668,7 +6166,7 @@
         </is>
       </c>
       <c r="I42" s="7">
-        <f>F42*characterization!$D$17 + G42*characterization!$D$15</f>
+        <f>F42*characterization!$B$17 + G42*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J42" s="7">
@@ -5676,7 +6174,7 @@
         <v/>
       </c>
       <c r="K42" s="7">
-        <f>F42*characterization!$J$17 + G42*characterization!$J$15</f>
+        <f>F42*characterization!$L$17 + G42*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L42" s="7">
@@ -5743,7 +6241,7 @@
         </is>
       </c>
       <c r="I43" s="7">
-        <f>F43*characterization!$D$17 + G43*characterization!$D$15</f>
+        <f>F43*characterization!$B$17 + G43*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J43" s="7">
@@ -5751,7 +6249,7 @@
         <v/>
       </c>
       <c r="K43" s="7">
-        <f>F43*characterization!$J$17 + G43*characterization!$J$15</f>
+        <f>F43*characterization!$L$17 + G43*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L43" s="7">
@@ -5818,7 +6316,7 @@
         </is>
       </c>
       <c r="I44" s="7">
-        <f>F44*characterization!$D$17 + G44*characterization!$D$15</f>
+        <f>F44*characterization!$B$17 + G44*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J44" s="7">
@@ -5826,7 +6324,7 @@
         <v/>
       </c>
       <c r="K44" s="7">
-        <f>F44*characterization!$J$17 + G44*characterization!$J$15</f>
+        <f>F44*characterization!$L$17 + G44*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L44" s="7">
@@ -5900,7 +6398,7 @@
         </is>
       </c>
       <c r="I46" s="7">
-        <f>F46*characterization!$D$17 + G46*characterization!$D$15</f>
+        <f>F46*characterization!$B$17 + G46*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J46" s="7">
@@ -5908,7 +6406,7 @@
         <v/>
       </c>
       <c r="K46" s="7">
-        <f>F46*characterization!$J$17 + G46*characterization!$J$15</f>
+        <f>F46*characterization!$L$17 + G46*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L46" s="7">
@@ -5975,7 +6473,7 @@
         </is>
       </c>
       <c r="I47" s="7">
-        <f>F47*characterization!$D$17 + G47*characterization!$D$15</f>
+        <f>F47*characterization!$B$17 + G47*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J47" s="7">
@@ -5983,7 +6481,7 @@
         <v/>
       </c>
       <c r="K47" s="7">
-        <f>F47*characterization!$J$17 + G47*characterization!$J$15</f>
+        <f>F47*characterization!$L$17 + G47*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L47" s="7">
@@ -6050,7 +6548,7 @@
         </is>
       </c>
       <c r="I48" s="7">
-        <f>F48*characterization!$D$17 + G48*characterization!$D$15</f>
+        <f>F48*characterization!$B$17 + G48*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J48" s="7">
@@ -6058,7 +6556,7 @@
         <v/>
       </c>
       <c r="K48" s="7">
-        <f>F48*characterization!$J$17 + G48*characterization!$J$15</f>
+        <f>F48*characterization!$L$17 + G48*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L48" s="7">
@@ -6125,7 +6623,7 @@
         </is>
       </c>
       <c r="I49" s="7">
-        <f>F49*characterization!$D$17 + G49*characterization!$D$15</f>
+        <f>F49*characterization!$B$17 + G49*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J49" s="7">
@@ -6133,7 +6631,7 @@
         <v/>
       </c>
       <c r="K49" s="7">
-        <f>F49*characterization!$J$17 + G49*characterization!$J$15</f>
+        <f>F49*characterization!$L$17 + G49*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L49" s="7">
@@ -6200,7 +6698,7 @@
         </is>
       </c>
       <c r="I50" s="7">
-        <f>F50*characterization!$D$17 + G50*characterization!$D$15</f>
+        <f>F50*characterization!$B$17 + G50*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J50" s="7">
@@ -6208,7 +6706,7 @@
         <v/>
       </c>
       <c r="K50" s="7">
-        <f>F50*characterization!$J$17 + G50*characterization!$J$15</f>
+        <f>F50*characterization!$L$17 + G50*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L50" s="7">
@@ -6282,7 +6780,7 @@
         </is>
       </c>
       <c r="I52" s="7">
-        <f>F52*characterization!$D$17 + G52*characterization!$D$15</f>
+        <f>F52*characterization!$B$17 + G52*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J52" s="7">
@@ -6290,7 +6788,7 @@
         <v/>
       </c>
       <c r="K52" s="7">
-        <f>F52*characterization!$J$17 + G52*characterization!$J$15</f>
+        <f>F52*characterization!$L$17 + G52*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L52" s="7">
@@ -6357,7 +6855,7 @@
         </is>
       </c>
       <c r="I53" s="7">
-        <f>F53*characterization!$D$17 + G53*characterization!$D$15</f>
+        <f>F53*characterization!$B$17 + G53*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J53" s="7">
@@ -6365,7 +6863,7 @@
         <v/>
       </c>
       <c r="K53" s="7">
-        <f>F53*characterization!$J$17 + G53*characterization!$J$15</f>
+        <f>F53*characterization!$L$17 + G53*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L53" s="7">
@@ -6432,7 +6930,7 @@
         </is>
       </c>
       <c r="I54" s="7">
-        <f>F54*characterization!$D$17 + G54*characterization!$D$15</f>
+        <f>F54*characterization!$B$17 + G54*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J54" s="7">
@@ -6440,7 +6938,7 @@
         <v/>
       </c>
       <c r="K54" s="7">
-        <f>F54*characterization!$J$17 + G54*characterization!$J$15</f>
+        <f>F54*characterization!$L$17 + G54*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L54" s="7">
@@ -6507,7 +7005,7 @@
         </is>
       </c>
       <c r="I55" s="7">
-        <f>F55*characterization!$D$17 + G55*characterization!$D$15</f>
+        <f>F55*characterization!$B$17 + G55*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J55" s="7">
@@ -6515,7 +7013,7 @@
         <v/>
       </c>
       <c r="K55" s="7">
-        <f>F55*characterization!$J$17 + G55*characterization!$J$15</f>
+        <f>F55*characterization!$L$17 + G55*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L55" s="7">
@@ -6582,7 +7080,7 @@
         </is>
       </c>
       <c r="I56" s="7">
-        <f>F56*characterization!$D$17 + G56*characterization!$D$15</f>
+        <f>F56*characterization!$B$17 + G56*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J56" s="7">
@@ -6590,7 +7088,7 @@
         <v/>
       </c>
       <c r="K56" s="7">
-        <f>F56*characterization!$J$17 + G56*characterization!$J$15</f>
+        <f>F56*characterization!$L$17 + G56*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L56" s="7">
@@ -6657,7 +7155,7 @@
         </is>
       </c>
       <c r="I57" s="7">
-        <f>F57*characterization!$D$17 + G57*characterization!$D$15</f>
+        <f>F57*characterization!$B$17 + G57*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J57" s="7">
@@ -6665,7 +7163,7 @@
         <v/>
       </c>
       <c r="K57" s="7">
-        <f>F57*characterization!$J$17 + G57*characterization!$J$15</f>
+        <f>F57*characterization!$L$17 + G57*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L57" s="7">
@@ -6732,7 +7230,7 @@
         </is>
       </c>
       <c r="I58" s="7">
-        <f>F58*characterization!$D$17 + G58*characterization!$D$15</f>
+        <f>F58*characterization!$B$17 + G58*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J58" s="7">
@@ -6740,7 +7238,7 @@
         <v/>
       </c>
       <c r="K58" s="7">
-        <f>F58*characterization!$J$17 + G58*characterization!$J$15</f>
+        <f>F58*characterization!$L$17 + G58*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L58" s="7">
@@ -6811,7 +7309,7 @@
         </is>
       </c>
       <c r="I59" s="7">
-        <f>F59*characterization!$D$17 + G59*characterization!$D$15</f>
+        <f>F59*characterization!$B$17 + G59*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J59" s="7">
@@ -6819,7 +7317,7 @@
         <v/>
       </c>
       <c r="K59" s="7">
-        <f>F59*characterization!$J$17 + G59*characterization!$J$15</f>
+        <f>F59*characterization!$L$17 + G59*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L59" s="7">
@@ -6890,7 +7388,7 @@
         </is>
       </c>
       <c r="I60" s="7">
-        <f>F60*characterization!$D$17 + G60*characterization!$D$15</f>
+        <f>F60*characterization!$B$17 + G60*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J60" s="7">
@@ -6898,7 +7396,7 @@
         <v/>
       </c>
       <c r="K60" s="7">
-        <f>F60*characterization!$J$17 + G60*characterization!$J$15</f>
+        <f>F60*characterization!$L$17 + G60*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L60" s="7">
@@ -6969,7 +7467,7 @@
         </is>
       </c>
       <c r="I61" s="7">
-        <f>F61*characterization!$D$17 + G61*characterization!$D$15</f>
+        <f>F61*characterization!$B$17 + G61*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J61" s="7">
@@ -6977,7 +7475,7 @@
         <v/>
       </c>
       <c r="K61" s="7">
-        <f>F61*characterization!$J$17 + G61*characterization!$J$15</f>
+        <f>F61*characterization!$L$17 + G61*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L61" s="7">
@@ -7048,7 +7546,7 @@
         </is>
       </c>
       <c r="I62" s="7">
-        <f>F62*characterization!$D$17 + G62*characterization!$D$15</f>
+        <f>F62*characterization!$B$17 + G62*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J62" s="7">
@@ -7056,7 +7554,7 @@
         <v/>
       </c>
       <c r="K62" s="7">
-        <f>F62*characterization!$J$17 + G62*characterization!$J$15</f>
+        <f>F62*characterization!$L$17 + G62*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L62" s="7">
@@ -7127,7 +7625,7 @@
         </is>
       </c>
       <c r="I63" s="7">
-        <f>F63*characterization!$D$17 + G63*characterization!$D$15</f>
+        <f>F63*characterization!$B$17 + G63*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J63" s="7">
@@ -7135,7 +7633,7 @@
         <v/>
       </c>
       <c r="K63" s="7">
-        <f>F63*characterization!$J$17 + G63*characterization!$J$15</f>
+        <f>F63*characterization!$L$17 + G63*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L63" s="7">
@@ -7209,7 +7707,7 @@
         </is>
       </c>
       <c r="I65" s="7">
-        <f>F65*characterization!$D$17 + G65*characterization!$D$15</f>
+        <f>F65*characterization!$B$17 + G65*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J65" s="7">
@@ -7217,7 +7715,7 @@
         <v/>
       </c>
       <c r="K65" s="7">
-        <f>F65*characterization!$J$17 + G65*characterization!$J$15</f>
+        <f>F65*characterization!$L$17 + G65*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L65" s="7">
@@ -7284,7 +7782,7 @@
         </is>
       </c>
       <c r="I66" s="7">
-        <f>F66*characterization!$D$17 + G66*characterization!$D$15</f>
+        <f>F66*characterization!$B$17 + G66*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J66" s="7">
@@ -7292,7 +7790,7 @@
         <v/>
       </c>
       <c r="K66" s="7">
-        <f>F66*characterization!$J$17 + G66*characterization!$J$15</f>
+        <f>F66*characterization!$L$17 + G66*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L66" s="7">
@@ -7359,7 +7857,7 @@
         </is>
       </c>
       <c r="I67" s="7">
-        <f>F67*characterization!$D$17 + G67*characterization!$D$15</f>
+        <f>F67*characterization!$B$17 + G67*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J67" s="7">
@@ -7367,7 +7865,7 @@
         <v/>
       </c>
       <c r="K67" s="7">
-        <f>F67*characterization!$J$17 + G67*characterization!$J$15</f>
+        <f>F67*characterization!$L$17 + G67*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L67" s="7">
@@ -7434,7 +7932,7 @@
         </is>
       </c>
       <c r="I68" s="7">
-        <f>F68*characterization!$D$17 + G68*characterization!$D$15</f>
+        <f>F68*characterization!$B$17 + G68*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J68" s="7">
@@ -7442,7 +7940,7 @@
         <v/>
       </c>
       <c r="K68" s="7">
-        <f>F68*characterization!$J$17 + G68*characterization!$J$15</f>
+        <f>F68*characterization!$L$17 + G68*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L68" s="7">
@@ -7509,7 +8007,7 @@
         </is>
       </c>
       <c r="I69" s="7">
-        <f>F69*characterization!$D$17 + G69*characterization!$D$15</f>
+        <f>F69*characterization!$B$17 + G69*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J69" s="7">
@@ -7517,7 +8015,7 @@
         <v/>
       </c>
       <c r="K69" s="7">
-        <f>F69*characterization!$J$17 + G69*characterization!$J$15</f>
+        <f>F69*characterization!$L$17 + G69*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L69" s="7">
@@ -7584,7 +8082,7 @@
         </is>
       </c>
       <c r="I70" s="7">
-        <f>F70*characterization!$D$17 + G70*characterization!$D$15</f>
+        <f>F70*characterization!$B$17 + G70*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J70" s="7">
@@ -7592,7 +8090,7 @@
         <v/>
       </c>
       <c r="K70" s="7">
-        <f>F70*characterization!$J$17 + G70*characterization!$J$15</f>
+        <f>F70*characterization!$L$17 + G70*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L70" s="7">
@@ -7659,7 +8157,7 @@
         </is>
       </c>
       <c r="I71" s="7">
-        <f>F71*characterization!$D$17 + G71*characterization!$D$15</f>
+        <f>F71*characterization!$B$17 + G71*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J71" s="7">
@@ -7667,7 +8165,7 @@
         <v/>
       </c>
       <c r="K71" s="7">
-        <f>F71*characterization!$J$17 + G71*characterization!$J$15</f>
+        <f>F71*characterization!$L$17 + G71*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L71" s="7">
@@ -7734,7 +8232,7 @@
         </is>
       </c>
       <c r="I72" s="7">
-        <f>F72*characterization!$D$17 + G72*characterization!$D$15</f>
+        <f>F72*characterization!$B$17 + G72*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J72" s="7">
@@ -7742,7 +8240,7 @@
         <v/>
       </c>
       <c r="K72" s="7">
-        <f>F72*characterization!$J$17 + G72*characterization!$J$15</f>
+        <f>F72*characterization!$L$17 + G72*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L72" s="7">
@@ -7809,7 +8307,7 @@
         </is>
       </c>
       <c r="I73" s="7">
-        <f>F73*characterization!$D$17 + G73*characterization!$D$15</f>
+        <f>F73*characterization!$B$17 + G73*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J73" s="7">
@@ -7817,7 +8315,7 @@
         <v/>
       </c>
       <c r="K73" s="7">
-        <f>F73*characterization!$J$17 + G73*characterization!$J$15</f>
+        <f>F73*characterization!$L$17 + G73*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L73" s="7">
@@ -7884,7 +8382,7 @@
         </is>
       </c>
       <c r="I74" s="7">
-        <f>F74*characterization!$D$17 + G74*characterization!$D$15</f>
+        <f>F74*characterization!$B$17 + G74*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J74" s="7">
@@ -7892,7 +8390,7 @@
         <v/>
       </c>
       <c r="K74" s="7">
-        <f>F74*characterization!$J$17 + G74*characterization!$J$15</f>
+        <f>F74*characterization!$L$17 + G74*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L74" s="7">
@@ -7959,7 +8457,7 @@
         </is>
       </c>
       <c r="I75" s="7">
-        <f>F75*characterization!$D$17 + G75*characterization!$D$15</f>
+        <f>F75*characterization!$B$17 + G75*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J75" s="7">
@@ -7967,7 +8465,7 @@
         <v/>
       </c>
       <c r="K75" s="7">
-        <f>F75*characterization!$J$17 + G75*characterization!$J$15</f>
+        <f>F75*characterization!$L$17 + G75*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L75" s="7">
@@ -8041,7 +8539,7 @@
         </is>
       </c>
       <c r="I77" s="7">
-        <f>F77*characterization!$D$17 + G77*characterization!$D$15</f>
+        <f>F77*characterization!$B$17 + G77*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J77" s="7">
@@ -8049,7 +8547,7 @@
         <v/>
       </c>
       <c r="K77" s="7">
-        <f>F77*characterization!$J$17 + G77*characterization!$J$15</f>
+        <f>F77*characterization!$L$17 + G77*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L77" s="7">
@@ -8116,7 +8614,7 @@
         </is>
       </c>
       <c r="I78" s="7">
-        <f>F78*characterization!$D$17 + G78*characterization!$D$15</f>
+        <f>F78*characterization!$B$17 + G78*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J78" s="7">
@@ -8124,7 +8622,7 @@
         <v/>
       </c>
       <c r="K78" s="7">
-        <f>F78*characterization!$J$17 + G78*characterization!$J$15</f>
+        <f>F78*characterization!$L$17 + G78*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L78" s="7">
@@ -8191,7 +8689,7 @@
         </is>
       </c>
       <c r="I79" s="7">
-        <f>F79*characterization!$D$17 + G79*characterization!$D$15</f>
+        <f>F79*characterization!$B$17 + G79*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J79" s="7">
@@ -8199,7 +8697,7 @@
         <v/>
       </c>
       <c r="K79" s="7">
-        <f>F79*characterization!$J$17 + G79*characterization!$J$15</f>
+        <f>F79*characterization!$L$17 + G79*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L79" s="7">
@@ -8266,7 +8764,7 @@
         </is>
       </c>
       <c r="I80" s="7">
-        <f>F80*characterization!$D$17 + G80*characterization!$D$15</f>
+        <f>F80*characterization!$B$17 + G80*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J80" s="7">
@@ -8274,7 +8772,7 @@
         <v/>
       </c>
       <c r="K80" s="7">
-        <f>F80*characterization!$J$17 + G80*characterization!$J$15</f>
+        <f>F80*characterization!$L$17 + G80*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L80" s="7">
@@ -8341,7 +8839,7 @@
         </is>
       </c>
       <c r="I81" s="7">
-        <f>F81*characterization!$D$17 + G81*characterization!$D$15</f>
+        <f>F81*characterization!$B$17 + G81*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J81" s="7">
@@ -8349,7 +8847,7 @@
         <v/>
       </c>
       <c r="K81" s="7">
-        <f>F81*characterization!$J$17 + G81*characterization!$J$15</f>
+        <f>F81*characterization!$L$17 + G81*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L81" s="7">
@@ -8416,7 +8914,7 @@
         </is>
       </c>
       <c r="I82" s="7">
-        <f>F82*characterization!$D$17 + G82*characterization!$D$15</f>
+        <f>F82*characterization!$B$17 + G82*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J82" s="7">
@@ -8424,7 +8922,7 @@
         <v/>
       </c>
       <c r="K82" s="7">
-        <f>F82*characterization!$J$17 + G82*characterization!$J$15</f>
+        <f>F82*characterization!$L$17 + G82*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L82" s="7">
@@ -8495,7 +8993,7 @@
         </is>
       </c>
       <c r="I83" s="7">
-        <f>F83*characterization!$D$17 + G83*characterization!$D$15</f>
+        <f>F83*characterization!$B$17 + G83*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J83" s="7">
@@ -8503,7 +9001,7 @@
         <v/>
       </c>
       <c r="K83" s="7">
-        <f>F83*characterization!$J$17 + G83*characterization!$J$15</f>
+        <f>F83*characterization!$L$17 + G83*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L83" s="7">
@@ -8574,7 +9072,7 @@
         </is>
       </c>
       <c r="I84" s="7">
-        <f>F84*characterization!$D$17 + G84*characterization!$D$15</f>
+        <f>F84*characterization!$B$17 + G84*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J84" s="7">
@@ -8582,7 +9080,7 @@
         <v/>
       </c>
       <c r="K84" s="7">
-        <f>F84*characterization!$J$17 + G84*characterization!$J$15</f>
+        <f>F84*characterization!$L$17 + G84*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L84" s="7">
@@ -8653,7 +9151,7 @@
         </is>
       </c>
       <c r="I85" s="7">
-        <f>F85*characterization!$D$17 + G85*characterization!$D$15</f>
+        <f>F85*characterization!$B$17 + G85*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J85" s="7">
@@ -8661,7 +9159,7 @@
         <v/>
       </c>
       <c r="K85" s="7">
-        <f>F85*characterization!$J$17 + G85*characterization!$J$15</f>
+        <f>F85*characterization!$L$17 + G85*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L85" s="7">
@@ -8732,7 +9230,7 @@
         </is>
       </c>
       <c r="I86" s="7">
-        <f>F86*characterization!$D$17 + G86*characterization!$D$15</f>
+        <f>F86*characterization!$B$17 + G86*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J86" s="7">
@@ -8740,7 +9238,7 @@
         <v/>
       </c>
       <c r="K86" s="7">
-        <f>F86*characterization!$J$17 + G86*characterization!$J$15</f>
+        <f>F86*characterization!$L$17 + G86*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L86" s="7">
@@ -8811,7 +9309,7 @@
         </is>
       </c>
       <c r="I87" s="7">
-        <f>F87*characterization!$D$17 + G87*characterization!$D$15</f>
+        <f>F87*characterization!$B$17 + G87*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J87" s="7">
@@ -8819,7 +9317,7 @@
         <v/>
       </c>
       <c r="K87" s="7">
-        <f>F87*characterization!$J$17 + G87*characterization!$J$15</f>
+        <f>F87*characterization!$L$17 + G87*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L87" s="7">
@@ -8893,7 +9391,7 @@
         </is>
       </c>
       <c r="I89" s="7">
-        <f>F89*characterization!$D$17 + G89*characterization!$D$15</f>
+        <f>F89*characterization!$B$17 + G89*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J89" s="7">
@@ -8901,7 +9399,7 @@
         <v/>
       </c>
       <c r="K89" s="7">
-        <f>F89*characterization!$J$17 + G89*characterization!$J$15</f>
+        <f>F89*characterization!$L$17 + G89*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L89" s="7">
@@ -8968,7 +9466,7 @@
         </is>
       </c>
       <c r="I90" s="7">
-        <f>F90*characterization!$D$17 + G90*characterization!$D$15</f>
+        <f>F90*characterization!$B$17 + G90*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J90" s="7">
@@ -8976,7 +9474,7 @@
         <v/>
       </c>
       <c r="K90" s="7">
-        <f>F90*characterization!$J$17 + G90*characterization!$J$15</f>
+        <f>F90*characterization!$L$17 + G90*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L90" s="7">
@@ -9043,7 +9541,7 @@
         </is>
       </c>
       <c r="I91" s="7">
-        <f>F91*characterization!$D$17 + G91*characterization!$D$15</f>
+        <f>F91*characterization!$B$17 + G91*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J91" s="7">
@@ -9051,7 +9549,7 @@
         <v/>
       </c>
       <c r="K91" s="7">
-        <f>F91*characterization!$J$17 + G91*characterization!$J$15</f>
+        <f>F91*characterization!$L$17 + G91*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L91" s="7">
@@ -9118,7 +9616,7 @@
         </is>
       </c>
       <c r="I92" s="7">
-        <f>F92*characterization!$D$17 + G92*characterization!$D$15</f>
+        <f>F92*characterization!$B$17 + G92*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J92" s="7">
@@ -9126,7 +9624,7 @@
         <v/>
       </c>
       <c r="K92" s="7">
-        <f>F92*characterization!$J$17 + G92*characterization!$J$15</f>
+        <f>F92*characterization!$L$17 + G92*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L92" s="7">
@@ -9193,7 +9691,7 @@
         </is>
       </c>
       <c r="I93" s="7">
-        <f>F93*characterization!$D$17 + G93*characterization!$D$15</f>
+        <f>F93*characterization!$B$17 + G93*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J93" s="7">
@@ -9201,7 +9699,7 @@
         <v/>
       </c>
       <c r="K93" s="7">
-        <f>F93*characterization!$J$17 + G93*characterization!$J$15</f>
+        <f>F93*characterization!$L$17 + G93*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L93" s="7">
@@ -9268,7 +9766,7 @@
         </is>
       </c>
       <c r="I94" s="7">
-        <f>F94*characterization!$D$17 + G94*characterization!$D$15</f>
+        <f>F94*characterization!$B$17 + G94*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J94" s="7">
@@ -9276,7 +9774,7 @@
         <v/>
       </c>
       <c r="K94" s="7">
-        <f>F94*characterization!$J$17 + G94*characterization!$J$15</f>
+        <f>F94*characterization!$L$17 + G94*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L94" s="7">
@@ -9343,7 +9841,7 @@
         </is>
       </c>
       <c r="I95" s="7">
-        <f>F95*characterization!$D$17 + G95*characterization!$D$15</f>
+        <f>F95*characterization!$B$17 + G95*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J95" s="7">
@@ -9351,7 +9849,7 @@
         <v/>
       </c>
       <c r="K95" s="7">
-        <f>F95*characterization!$J$17 + G95*characterization!$J$15</f>
+        <f>F95*characterization!$L$17 + G95*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L95" s="7">
@@ -9418,7 +9916,7 @@
         </is>
       </c>
       <c r="I96" s="7">
-        <f>F96*characterization!$D$17 + G96*characterization!$D$15</f>
+        <f>F96*characterization!$B$17 + G96*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J96" s="7">
@@ -9426,7 +9924,7 @@
         <v/>
       </c>
       <c r="K96" s="7">
-        <f>F96*characterization!$J$17 + G96*characterization!$J$15</f>
+        <f>F96*characterization!$L$17 + G96*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L96" s="7">
@@ -9493,7 +9991,7 @@
         </is>
       </c>
       <c r="I97" s="7">
-        <f>F97*characterization!$D$17 + G97*characterization!$D$15</f>
+        <f>F97*characterization!$B$17 + G97*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J97" s="7">
@@ -9501,7 +9999,7 @@
         <v/>
       </c>
       <c r="K97" s="7">
-        <f>F97*characterization!$J$17 + G97*characterization!$J$15</f>
+        <f>F97*characterization!$L$17 + G97*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L97" s="7">
@@ -9568,7 +10066,7 @@
         </is>
       </c>
       <c r="I98" s="7">
-        <f>F98*characterization!$D$17 + G98*characterization!$D$15</f>
+        <f>F98*characterization!$B$17 + G98*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J98" s="7">
@@ -9576,7 +10074,7 @@
         <v/>
       </c>
       <c r="K98" s="7">
-        <f>F98*characterization!$J$17 + G98*characterization!$J$15</f>
+        <f>F98*characterization!$L$17 + G98*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L98" s="7">
@@ -9643,7 +10141,7 @@
         </is>
       </c>
       <c r="I99" s="7">
-        <f>F99*characterization!$D$17 + G99*characterization!$D$15</f>
+        <f>F99*characterization!$B$17 + G99*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J99" s="7">
@@ -9651,7 +10149,7 @@
         <v/>
       </c>
       <c r="K99" s="7">
-        <f>F99*characterization!$J$17 + G99*characterization!$J$15</f>
+        <f>F99*characterization!$L$17 + G99*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L99" s="7">
@@ -9718,7 +10216,7 @@
         </is>
       </c>
       <c r="I100" s="7">
-        <f>F100*characterization!$D$17 + G100*characterization!$D$15</f>
+        <f>F100*characterization!$B$17 + G100*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J100" s="7">
@@ -9726,7 +10224,7 @@
         <v/>
       </c>
       <c r="K100" s="7">
-        <f>F100*characterization!$J$17 + G100*characterization!$J$15</f>
+        <f>F100*characterization!$L$17 + G100*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L100" s="7">
@@ -9793,7 +10291,7 @@
         </is>
       </c>
       <c r="I101" s="7">
-        <f>F101*characterization!$D$17 + G101*characterization!$D$15</f>
+        <f>F101*characterization!$B$17 + G101*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J101" s="7">
@@ -9801,7 +10299,7 @@
         <v/>
       </c>
       <c r="K101" s="7">
-        <f>F101*characterization!$J$17 + G101*characterization!$J$15</f>
+        <f>F101*characterization!$L$17 + G101*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L101" s="7">
@@ -9868,7 +10366,7 @@
         </is>
       </c>
       <c r="I102" s="7">
-        <f>F102*characterization!$D$17 + G102*characterization!$D$15</f>
+        <f>F102*characterization!$B$17 + G102*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J102" s="7">
@@ -9876,7 +10374,7 @@
         <v/>
       </c>
       <c r="K102" s="7">
-        <f>F102*characterization!$J$17 + G102*characterization!$J$15</f>
+        <f>F102*characterization!$L$17 + G102*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L102" s="7">
@@ -9950,7 +10448,7 @@
         </is>
       </c>
       <c r="I104" s="7">
-        <f>F104*characterization!$D$17 + G104*characterization!$D$15</f>
+        <f>F104*characterization!$B$17 + G104*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J104" s="7">
@@ -9958,7 +10456,7 @@
         <v/>
       </c>
       <c r="K104" s="7">
-        <f>F104*characterization!$J$17 + G104*characterization!$J$15</f>
+        <f>F104*characterization!$L$17 + G104*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L104" s="7">
@@ -10025,7 +10523,7 @@
         </is>
       </c>
       <c r="I105" s="7">
-        <f>F105*characterization!$D$17 + G105*characterization!$D$15</f>
+        <f>F105*characterization!$B$17 + G105*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J105" s="7">
@@ -10033,7 +10531,7 @@
         <v/>
       </c>
       <c r="K105" s="7">
-        <f>F105*characterization!$J$17 + G105*characterization!$J$15</f>
+        <f>F105*characterization!$L$17 + G105*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L105" s="7">
@@ -10100,7 +10598,7 @@
         </is>
       </c>
       <c r="I106" s="7">
-        <f>F106*characterization!$D$17 + G106*characterization!$D$15</f>
+        <f>F106*characterization!$B$17 + G106*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J106" s="7">
@@ -10108,7 +10606,7 @@
         <v/>
       </c>
       <c r="K106" s="7">
-        <f>F106*characterization!$J$17 + G106*characterization!$J$15</f>
+        <f>F106*characterization!$L$17 + G106*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L106" s="7">
@@ -10175,7 +10673,7 @@
         </is>
       </c>
       <c r="I107" s="7">
-        <f>F107*characterization!$D$17 + G107*characterization!$D$15</f>
+        <f>F107*characterization!$B$17 + G107*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J107" s="7">
@@ -10183,7 +10681,7 @@
         <v/>
       </c>
       <c r="K107" s="7">
-        <f>F107*characterization!$J$17 + G107*characterization!$J$15</f>
+        <f>F107*characterization!$L$17 + G107*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L107" s="7">
@@ -10250,7 +10748,7 @@
         </is>
       </c>
       <c r="I108" s="7">
-        <f>F108*characterization!$D$17 + G108*characterization!$D$15</f>
+        <f>F108*characterization!$B$17 + G108*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J108" s="7">
@@ -10258,7 +10756,7 @@
         <v/>
       </c>
       <c r="K108" s="7">
-        <f>F108*characterization!$J$17 + G108*characterization!$J$15</f>
+        <f>F108*characterization!$L$17 + G108*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L108" s="7">
@@ -10325,7 +10823,7 @@
         </is>
       </c>
       <c r="I109" s="7">
-        <f>F109*characterization!$D$17 + G109*characterization!$D$15</f>
+        <f>F109*characterization!$B$17 + G109*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J109" s="7">
@@ -10333,7 +10831,7 @@
         <v/>
       </c>
       <c r="K109" s="7">
-        <f>F109*characterization!$J$17 + G109*characterization!$J$15</f>
+        <f>F109*characterization!$L$17 + G109*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L109" s="7">
@@ -10400,7 +10898,7 @@
         </is>
       </c>
       <c r="I110" s="7">
-        <f>F110*characterization!$D$17 + G110*characterization!$D$15</f>
+        <f>F110*characterization!$B$17 + G110*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J110" s="7">
@@ -10408,7 +10906,7 @@
         <v/>
       </c>
       <c r="K110" s="7">
-        <f>F110*characterization!$J$17 + G110*characterization!$J$15</f>
+        <f>F110*characterization!$L$17 + G110*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L110" s="7">
@@ -10475,7 +10973,7 @@
         </is>
       </c>
       <c r="I111" s="7">
-        <f>F111*characterization!$D$17 + G111*characterization!$D$15</f>
+        <f>F111*characterization!$B$17 + G111*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J111" s="7">
@@ -10483,7 +10981,7 @@
         <v/>
       </c>
       <c r="K111" s="7">
-        <f>F111*characterization!$J$17 + G111*characterization!$J$15</f>
+        <f>F111*characterization!$L$17 + G111*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L111" s="7">
@@ -10554,7 +11052,7 @@
         </is>
       </c>
       <c r="I112" s="7">
-        <f>F112*characterization!$D$17 + G112*characterization!$D$15</f>
+        <f>F112*characterization!$B$17 + G112*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J112" s="7">
@@ -10562,7 +11060,7 @@
         <v/>
       </c>
       <c r="K112" s="7">
-        <f>F112*characterization!$J$17 + G112*characterization!$J$15</f>
+        <f>F112*characterization!$L$17 + G112*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L112" s="7">
@@ -10633,7 +11131,7 @@
         </is>
       </c>
       <c r="I113" s="7">
-        <f>F113*characterization!$D$17 + G113*characterization!$D$15</f>
+        <f>F113*characterization!$B$17 + G113*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J113" s="7">
@@ -10641,7 +11139,7 @@
         <v/>
       </c>
       <c r="K113" s="7">
-        <f>F113*characterization!$J$17 + G113*characterization!$J$15</f>
+        <f>F113*characterization!$L$17 + G113*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L113" s="7">
@@ -10708,7 +11206,7 @@
         </is>
       </c>
       <c r="I114" s="7">
-        <f>F114*characterization!$D$17 + G114*characterization!$D$15</f>
+        <f>F114*characterization!$B$17 + G114*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J114" s="7">
@@ -10716,7 +11214,7 @@
         <v/>
       </c>
       <c r="K114" s="7">
-        <f>F114*characterization!$J$17 + G114*characterization!$J$15</f>
+        <f>F114*characterization!$L$17 + G114*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L114" s="7">
@@ -10783,7 +11281,7 @@
         </is>
       </c>
       <c r="I115" s="7">
-        <f>F115*characterization!$D$17 + G115*characterization!$D$15</f>
+        <f>F115*characterization!$B$17 + G115*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J115" s="7">
@@ -10791,7 +11289,7 @@
         <v/>
       </c>
       <c r="K115" s="7">
-        <f>F115*characterization!$J$17 + G115*characterization!$J$15</f>
+        <f>F115*characterization!$L$17 + G115*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L115" s="7">
@@ -10858,7 +11356,7 @@
         </is>
       </c>
       <c r="I116" s="7">
-        <f>F116*characterization!$D$17 + G116*characterization!$D$15</f>
+        <f>F116*characterization!$B$17 + G116*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J116" s="7">
@@ -10866,7 +11364,7 @@
         <v/>
       </c>
       <c r="K116" s="7">
-        <f>F116*characterization!$J$17 + G116*characterization!$J$15</f>
+        <f>F116*characterization!$L$17 + G116*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L116" s="7">
@@ -10933,7 +11431,7 @@
         </is>
       </c>
       <c r="I117" s="7">
-        <f>F117*characterization!$D$17 + G117*characterization!$D$15</f>
+        <f>F117*characterization!$B$17 + G117*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J117" s="7">
@@ -10941,7 +11439,7 @@
         <v/>
       </c>
       <c r="K117" s="7">
-        <f>F117*characterization!$J$17 + G117*characterization!$J$15</f>
+        <f>F117*characterization!$L$17 + G117*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L117" s="7">
@@ -11015,7 +11513,7 @@
         </is>
       </c>
       <c r="I119" s="7">
-        <f>F119*characterization!$D$17 + G119*characterization!$D$15</f>
+        <f>F119*characterization!$B$17 + G119*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J119" s="7">
@@ -11023,7 +11521,7 @@
         <v/>
       </c>
       <c r="K119" s="7">
-        <f>F119*characterization!$J$17 + G119*characterization!$J$15</f>
+        <f>F119*characterization!$L$17 + G119*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L119" s="7">
@@ -11090,7 +11588,7 @@
         </is>
       </c>
       <c r="I120" s="7">
-        <f>F120*characterization!$D$17 + G120*characterization!$D$15</f>
+        <f>F120*characterization!$B$17 + G120*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J120" s="7">
@@ -11098,7 +11596,7 @@
         <v/>
       </c>
       <c r="K120" s="7">
-        <f>F120*characterization!$J$17 + G120*characterization!$J$15</f>
+        <f>F120*characterization!$L$17 + G120*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L120" s="7">
@@ -11165,7 +11663,7 @@
         </is>
       </c>
       <c r="I121" s="7">
-        <f>F121*characterization!$D$17 + G121*characterization!$D$15</f>
+        <f>F121*characterization!$B$17 + G121*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J121" s="7">
@@ -11173,7 +11671,7 @@
         <v/>
       </c>
       <c r="K121" s="7">
-        <f>F121*characterization!$J$17 + G121*characterization!$J$15</f>
+        <f>F121*characterization!$L$17 + G121*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L121" s="7">
@@ -11240,7 +11738,7 @@
         </is>
       </c>
       <c r="I122" s="7">
-        <f>F122*characterization!$D$17 + G122*characterization!$D$15</f>
+        <f>F122*characterization!$B$17 + G122*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J122" s="7">
@@ -11248,7 +11746,7 @@
         <v/>
       </c>
       <c r="K122" s="7">
-        <f>F122*characterization!$J$17 + G122*characterization!$J$15</f>
+        <f>F122*characterization!$L$17 + G122*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L122" s="7">
@@ -11315,7 +11813,7 @@
         </is>
       </c>
       <c r="I123" s="7">
-        <f>F123*characterization!$D$17 + G123*characterization!$D$15</f>
+        <f>F123*characterization!$B$17 + G123*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J123" s="7">
@@ -11323,7 +11821,7 @@
         <v/>
       </c>
       <c r="K123" s="7">
-        <f>F123*characterization!$J$17 + G123*characterization!$J$15</f>
+        <f>F123*characterization!$L$17 + G123*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L123" s="7">
@@ -11390,7 +11888,7 @@
         </is>
       </c>
       <c r="I124" s="7">
-        <f>F124*characterization!$D$17 + G124*characterization!$D$15</f>
+        <f>F124*characterization!$B$17 + G124*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J124" s="7">
@@ -11398,7 +11896,7 @@
         <v/>
       </c>
       <c r="K124" s="7">
-        <f>F124*characterization!$J$17 + G124*characterization!$J$15</f>
+        <f>F124*characterization!$L$17 + G124*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L124" s="7">
@@ -11465,7 +11963,7 @@
         </is>
       </c>
       <c r="I125" s="7">
-        <f>F125*characterization!$D$17 + G125*characterization!$D$15</f>
+        <f>F125*characterization!$B$17 + G125*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J125" s="7">
@@ -11473,7 +11971,7 @@
         <v/>
       </c>
       <c r="K125" s="7">
-        <f>F125*characterization!$J$17 + G125*characterization!$J$15</f>
+        <f>F125*characterization!$L$17 + G125*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L125" s="7">
@@ -11540,7 +12038,7 @@
         </is>
       </c>
       <c r="I126" s="7">
-        <f>F126*characterization!$D$17 + G126*characterization!$D$15</f>
+        <f>F126*characterization!$B$17 + G126*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J126" s="7">
@@ -11548,7 +12046,7 @@
         <v/>
       </c>
       <c r="K126" s="7">
-        <f>F126*characterization!$J$17 + G126*characterization!$J$15</f>
+        <f>F126*characterization!$L$17 + G126*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L126" s="7">
@@ -11615,7 +12113,7 @@
         </is>
       </c>
       <c r="I127" s="7">
-        <f>F127*characterization!$D$17 + G127*characterization!$D$15</f>
+        <f>F127*characterization!$B$17 + G127*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J127" s="7">
@@ -11623,7 +12121,7 @@
         <v/>
       </c>
       <c r="K127" s="7">
-        <f>F127*characterization!$J$17 + G127*characterization!$J$15</f>
+        <f>F127*characterization!$L$17 + G127*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L127" s="7">
@@ -11690,7 +12188,7 @@
         </is>
       </c>
       <c r="I128" s="7">
-        <f>F128*characterization!$D$17 + G128*characterization!$D$15</f>
+        <f>F128*characterization!$B$17 + G128*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J128" s="7">
@@ -11698,7 +12196,7 @@
         <v/>
       </c>
       <c r="K128" s="7">
-        <f>F128*characterization!$J$17 + G128*characterization!$J$15</f>
+        <f>F128*characterization!$L$17 + G128*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L128" s="7">
@@ -11765,7 +12263,7 @@
         </is>
       </c>
       <c r="I129" s="7">
-        <f>F129*characterization!$D$17 + G129*characterization!$D$15</f>
+        <f>F129*characterization!$B$17 + G129*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J129" s="7">
@@ -11773,7 +12271,7 @@
         <v/>
       </c>
       <c r="K129" s="7">
-        <f>F129*characterization!$J$17 + G129*characterization!$J$15</f>
+        <f>F129*characterization!$L$17 + G129*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L129" s="7">
@@ -11840,7 +12338,7 @@
         </is>
       </c>
       <c r="I130" s="7">
-        <f>F130*characterization!$D$17 + G130*characterization!$D$15</f>
+        <f>F130*characterization!$B$17 + G130*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J130" s="7">
@@ -11848,7 +12346,7 @@
         <v/>
       </c>
       <c r="K130" s="7">
-        <f>F130*characterization!$J$17 + G130*characterization!$J$15</f>
+        <f>F130*characterization!$L$17 + G130*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L130" s="7">
@@ -11915,7 +12413,7 @@
         </is>
       </c>
       <c r="I131" s="7">
-        <f>F131*characterization!$D$17 + G131*characterization!$D$15</f>
+        <f>F131*characterization!$B$17 + G131*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J131" s="7">
@@ -11923,7 +12421,7 @@
         <v/>
       </c>
       <c r="K131" s="7">
-        <f>F131*characterization!$J$17 + G131*characterization!$J$15</f>
+        <f>F131*characterization!$L$17 + G131*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L131" s="7">
@@ -11990,7 +12488,7 @@
         </is>
       </c>
       <c r="I132" s="7">
-        <f>F132*characterization!$D$17 + G132*characterization!$D$15</f>
+        <f>F132*characterization!$B$17 + G132*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J132" s="7">
@@ -11998,7 +12496,7 @@
         <v/>
       </c>
       <c r="K132" s="7">
-        <f>F132*characterization!$J$17 + G132*characterization!$J$15</f>
+        <f>F132*characterization!$L$17 + G132*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L132" s="7">
@@ -12069,7 +12567,7 @@
         </is>
       </c>
       <c r="I133" s="7">
-        <f>F133*characterization!$D$17 + G133*characterization!$D$15</f>
+        <f>F133*characterization!$B$17 + G133*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J133" s="7">
@@ -12077,7 +12575,7 @@
         <v/>
       </c>
       <c r="K133" s="7">
-        <f>F133*characterization!$J$17 + G133*characterization!$J$15</f>
+        <f>F133*characterization!$L$17 + G133*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L133" s="7">
@@ -12148,7 +12646,7 @@
         </is>
       </c>
       <c r="I134" s="7">
-        <f>F134*characterization!$D$17 + G134*characterization!$D$15</f>
+        <f>F134*characterization!$B$17 + G134*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J134" s="7">
@@ -12156,7 +12654,7 @@
         <v/>
       </c>
       <c r="K134" s="7">
-        <f>F134*characterization!$J$17 + G134*characterization!$J$15</f>
+        <f>F134*characterization!$L$17 + G134*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L134" s="7">
@@ -12227,7 +12725,7 @@
         </is>
       </c>
       <c r="I135" s="7">
-        <f>F135*characterization!$D$17 + G135*characterization!$D$15</f>
+        <f>F135*characterization!$B$17 + G135*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J135" s="7">
@@ -12235,7 +12733,7 @@
         <v/>
       </c>
       <c r="K135" s="7">
-        <f>F135*characterization!$J$17 + G135*characterization!$J$15</f>
+        <f>F135*characterization!$L$17 + G135*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L135" s="7">
@@ -12306,7 +12804,7 @@
         </is>
       </c>
       <c r="I136" s="7">
-        <f>F136*characterization!$D$17 + G136*characterization!$D$15</f>
+        <f>F136*characterization!$B$17 + G136*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J136" s="7">
@@ -12314,7 +12812,7 @@
         <v/>
       </c>
       <c r="K136" s="7">
-        <f>F136*characterization!$J$17 + G136*characterization!$J$15</f>
+        <f>F136*characterization!$L$17 + G136*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L136" s="7">
@@ -12385,7 +12883,7 @@
         </is>
       </c>
       <c r="I137" s="7">
-        <f>F137*characterization!$D$17 + G137*characterization!$D$15</f>
+        <f>F137*characterization!$B$17 + G137*characterization!$B$15</f>
         <v/>
       </c>
       <c r="J137" s="7">
@@ -12393,7 +12891,7 @@
         <v/>
       </c>
       <c r="K137" s="7">
-        <f>F137*characterization!$J$17 + G137*characterization!$J$15</f>
+        <f>F137*characterization!$L$17 + G137*characterization!$L$15</f>
         <v/>
       </c>
       <c r="L137" s="7">

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -512,77 +512,77 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>TT_1000MHz</t>
+          <t>TT_2000MHz</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>TT_1250MHz</t>
+          <t>TT_2250MHz</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TT_1500MHz</t>
+          <t>TT_2500MHz</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TT_1750MHz</t>
+          <t>TT_2750MHz</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>TT_2000MHz</t>
+          <t>TT_3000MHz</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>FF_1000MHz</t>
+          <t>FF_2000MHz</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>FF_1250MHz</t>
+          <t>FF_2250MHz</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>FF_1500MHz</t>
+          <t>FF_2500MHz</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>FF_1750MHz</t>
+          <t>FF_2750MHz</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FF_2000MHz</t>
+          <t>FF_3000MHz</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SS_1000MHz</t>
+          <t>SS_2000MHz</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SS_1250MHz</t>
+          <t>SS_2250MHz</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SS_1500MHz</t>
+          <t>SS_2500MHz</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SS_1750MHz</t>
+          <t>SS_2750MHz</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SS_2000MHz</t>
+          <t>SS_3000MHz</t>
         </is>
       </c>
     </row>
@@ -593,49 +593,49 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>800</v>
+        <v>444.4</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>666.7</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>571.4</v>
+        <v>363.6</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>1000</v>
-      </c>
       <c r="H2" s="2" t="n">
-        <v>800</v>
+        <v>444.4</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>666.7</v>
+        <v>400</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>571.4</v>
+        <v>363.6</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>1000</v>
-      </c>
       <c r="M2" s="2" t="n">
-        <v>800</v>
+        <v>444.4</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>666.7</v>
+        <v>400</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>571.4</v>
+        <v>363.6</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>500</v>
+        <v>333.3</v>
       </c>
     </row>
     <row r="3">
@@ -737,49 +737,49 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="J7" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="L7" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -841,49 +841,49 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="I8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44</v>
-      </c>
       <c r="L8" s="2" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -893,49 +893,49 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="J9" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>23</v>
-      </c>
       <c r="L9" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -945,49 +945,49 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>25</v>
-      </c>
       <c r="K10" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -997,49 +997,49 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1049,49 +1049,49 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -1713,6 +1713,11 @@
           <t>output delay 40% (ps)</t>
         </is>
       </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>wire/hop (ps)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1739,6 +1744,9 @@
       <c r="F29" s="7">
         <f>IF(ISNUMBER(B29), D29*0.4, "")</f>
         <v/>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -1757,6 +1765,7 @@
         <f>IF(ISNUMBER(B30), D30*0.4, "")</f>
         <v/>
       </c>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
@@ -1774,6 +1783,7 @@
         <f>IF(ISNUMBER(B31), D31*0.4, "")</f>
         <v/>
       </c>
+      <c r="G31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr"/>
@@ -1791,6 +1801,7 @@
         <f>IF(ISNUMBER(B32), D32*0.4, "")</f>
         <v/>
       </c>
+      <c r="G32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr"/>
@@ -1808,6 +1819,7 @@
         <f>IF(ISNUMBER(B33), D33*0.4, "")</f>
         <v/>
       </c>
+      <c r="G33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
@@ -1825,6 +1837,7 @@
         <f>IF(ISNUMBER(B34), D34*0.4, "")</f>
         <v/>
       </c>
+      <c r="G34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2464,11 +2477,11 @@
         </is>
       </c>
       <c r="Y4" s="7">
-        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z4" s="7">
-        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA4" s="7">
@@ -2480,7 +2493,7 @@
         <v/>
       </c>
       <c r="AC4" s="5">
-        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X4, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD4" s="7">
@@ -2488,7 +2501,7 @@
         <v/>
       </c>
       <c r="AF4" s="7">
-        <f>IFERROR(Y4 - AD4 - VLOOKUP(X4, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y4 - AD4 - VLOOKUP(X4, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X4, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG4" t="inlineStr">
@@ -2576,11 +2589,11 @@
         </is>
       </c>
       <c r="Y5" s="7">
-        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z5" s="7">
-        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA5" s="7">
@@ -2592,7 +2605,7 @@
         <v/>
       </c>
       <c r="AC5" s="5">
-        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X5, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD5" s="7">
@@ -2600,7 +2613,7 @@
         <v/>
       </c>
       <c r="AF5" s="7">
-        <f>IFERROR(Y5 - AD5 - VLOOKUP(X5, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y5 - AD5 - VLOOKUP(X5, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X5, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2695,11 +2708,11 @@
         </is>
       </c>
       <c r="Y7" s="7">
-        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z7" s="7">
-        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA7" s="7">
@@ -2711,7 +2724,7 @@
         <v/>
       </c>
       <c r="AC7" s="5">
-        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X7, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD7" s="7">
@@ -2719,7 +2732,7 @@
         <v/>
       </c>
       <c r="AF7" s="7">
-        <f>IFERROR(Y7 - AD7 - VLOOKUP(X7, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y7 - AD7 - VLOOKUP(X7, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X7, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG7" t="inlineStr">
@@ -2808,11 +2821,11 @@
         </is>
       </c>
       <c r="Y8" s="7">
-        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z8" s="7">
-        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA8" s="7">
@@ -2824,7 +2837,7 @@
         <v/>
       </c>
       <c r="AC8" s="5">
-        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X8, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD8" s="7">
@@ -2832,7 +2845,7 @@
         <v/>
       </c>
       <c r="AF8" s="7">
-        <f>IFERROR(Y8 - AD8 - VLOOKUP(X8, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y8 - AD8 - VLOOKUP(X8, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X8, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG8" t="inlineStr">
@@ -2918,11 +2931,11 @@
         </is>
       </c>
       <c r="Y9" s="7">
-        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z9" s="7">
-        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA9" s="7">
@@ -2934,7 +2947,7 @@
         <v/>
       </c>
       <c r="AC9" s="5">
-        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X9, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD9" s="7">
@@ -2942,7 +2955,7 @@
         <v/>
       </c>
       <c r="AF9" s="7">
-        <f>IFERROR(Y9 - AD9 - VLOOKUP(X9, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y9 - AD9 - VLOOKUP(X9, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X9, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG9" t="inlineStr">
@@ -3042,11 +3055,11 @@
         </is>
       </c>
       <c r="Y10" s="7">
-        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z10" s="7">
-        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA10" s="7">
@@ -3058,7 +3071,7 @@
         <v/>
       </c>
       <c r="AC10" s="5">
-        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X10, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD10" s="7">
@@ -3066,7 +3079,7 @@
         <v/>
       </c>
       <c r="AF10" s="7">
-        <f>IFERROR(Y10 - AD10 - VLOOKUP(X10, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y10 - AD10 - VLOOKUP(X10, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X10, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG10" t="inlineStr">
@@ -3166,11 +3179,11 @@
         </is>
       </c>
       <c r="Y11" s="7">
-        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="Z11" s="7">
-        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="AA11" s="7">
@@ -3182,7 +3195,7 @@
         <v/>
       </c>
       <c r="AC11" s="5">
-        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(X11, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="AD11" s="7">
@@ -3190,7 +3203,7 @@
         <v/>
       </c>
       <c r="AF11" s="7">
-        <f>IFERROR(Y11 - AD11 - VLOOKUP(X11, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(Y11 - AD11 - VLOOKUP(X11, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X11, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3496,11 +3509,11 @@
         <v/>
       </c>
       <c r="L4" s="7">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M4" s="7">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N4" s="7">
@@ -3508,7 +3521,7 @@
         <v/>
       </c>
       <c r="O4" s="5">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P4" s="7">
@@ -3516,7 +3529,7 @@
         <v/>
       </c>
       <c r="R4" s="7">
-        <f>IFERROR(L4 - P4 - VLOOKUP(C4, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L4 - P4 - VLOOKUP(C4, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C4, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S4" t="inlineStr">
@@ -3575,11 +3588,11 @@
         <v/>
       </c>
       <c r="L5" s="7">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M5" s="7">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N5" s="7">
@@ -3587,7 +3600,7 @@
         <v/>
       </c>
       <c r="O5" s="5">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P5" s="7">
@@ -3595,7 +3608,7 @@
         <v/>
       </c>
       <c r="R5" s="7">
-        <f>IFERROR(L5 - P5 - VLOOKUP(C5, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L5 - P5 - VLOOKUP(C5, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C5, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S5" t="inlineStr">
@@ -3650,11 +3663,11 @@
         <v/>
       </c>
       <c r="L6" s="7">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M6" s="7">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N6" s="7">
@@ -3662,7 +3675,7 @@
         <v/>
       </c>
       <c r="O6" s="5">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P6" s="7">
@@ -3670,7 +3683,7 @@
         <v/>
       </c>
       <c r="R6" s="7">
-        <f>IFERROR(L6 - P6 - VLOOKUP(C6, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L6 - P6 - VLOOKUP(C6, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C6, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S6" t="inlineStr">
@@ -3725,11 +3738,11 @@
         <v/>
       </c>
       <c r="L7" s="7">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M7" s="7">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N7" s="7">
@@ -3737,7 +3750,7 @@
         <v/>
       </c>
       <c r="O7" s="5">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P7" s="7">
@@ -3745,7 +3758,7 @@
         <v/>
       </c>
       <c r="R7" s="7">
-        <f>IFERROR(L7 - P7 - VLOOKUP(C7, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L7 - P7 - VLOOKUP(C7, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C7, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S7" t="inlineStr">
@@ -3804,11 +3817,11 @@
         <v/>
       </c>
       <c r="L8" s="7">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M8" s="7">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N8" s="7">
@@ -3816,7 +3829,7 @@
         <v/>
       </c>
       <c r="O8" s="5">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P8" s="7">
@@ -3824,7 +3837,7 @@
         <v/>
       </c>
       <c r="R8" s="7">
-        <f>IFERROR(L8 - P8 - VLOOKUP(C8, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L8 - P8 - VLOOKUP(C8, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C8, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S8" t="inlineStr">
@@ -3883,11 +3896,11 @@
         <v/>
       </c>
       <c r="L9" s="7">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M9" s="7">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N9" s="7">
@@ -3895,7 +3908,7 @@
         <v/>
       </c>
       <c r="O9" s="5">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P9" s="7">
@@ -3903,7 +3916,7 @@
         <v/>
       </c>
       <c r="R9" s="7">
-        <f>IFERROR(L9 - P9 - VLOOKUP(C9, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L9 - P9 - VLOOKUP(C9, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C9, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S9" t="inlineStr">
@@ -3962,11 +3975,11 @@
         <v/>
       </c>
       <c r="L10" s="7">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M10" s="7">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N10" s="7">
@@ -3974,7 +3987,7 @@
         <v/>
       </c>
       <c r="O10" s="5">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P10" s="7">
@@ -3982,7 +3995,7 @@
         <v/>
       </c>
       <c r="R10" s="7">
-        <f>IFERROR(L10 - P10 - VLOOKUP(C10, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L10 - P10 - VLOOKUP(C10, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C10, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S10" t="inlineStr">
@@ -4041,11 +4054,11 @@
         <v/>
       </c>
       <c r="L11" s="7">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M11" s="7">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N11" s="7">
@@ -4053,7 +4066,7 @@
         <v/>
       </c>
       <c r="O11" s="5">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P11" s="7">
@@ -4061,7 +4074,7 @@
         <v/>
       </c>
       <c r="R11" s="7">
-        <f>IFERROR(L11 - P11 - VLOOKUP(C11, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L11 - P11 - VLOOKUP(C11, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C11, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S11" t="inlineStr">
@@ -4116,11 +4129,11 @@
         <v/>
       </c>
       <c r="L12" s="7">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M12" s="7">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N12" s="7">
@@ -4128,7 +4141,7 @@
         <v/>
       </c>
       <c r="O12" s="5">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P12" s="7">
@@ -4136,7 +4149,7 @@
         <v/>
       </c>
       <c r="R12" s="7">
-        <f>IFERROR(L12 - P12 - VLOOKUP(C12, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L12 - P12 - VLOOKUP(C12, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C12, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S12" t="inlineStr">
@@ -4198,11 +4211,11 @@
         <v/>
       </c>
       <c r="L14" s="7">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M14" s="7">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N14" s="7">
@@ -4210,7 +4223,7 @@
         <v/>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P14" s="7">
@@ -4218,7 +4231,7 @@
         <v/>
       </c>
       <c r="R14" s="7">
-        <f>IFERROR(L14 - P14 - VLOOKUP(C14, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L14 - P14 - VLOOKUP(C14, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C14, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S14" t="inlineStr">
@@ -4273,11 +4286,11 @@
         <v/>
       </c>
       <c r="L15" s="7">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M15" s="7">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N15" s="7">
@@ -4285,7 +4298,7 @@
         <v/>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P15" s="7">
@@ -4293,7 +4306,7 @@
         <v/>
       </c>
       <c r="R15" s="7">
-        <f>IFERROR(L15 - P15 - VLOOKUP(C15, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L15 - P15 - VLOOKUP(C15, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C15, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S15" t="inlineStr">
@@ -4348,11 +4361,11 @@
         <v/>
       </c>
       <c r="L16" s="7">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M16" s="7">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N16" s="7">
@@ -4360,7 +4373,7 @@
         <v/>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P16" s="7">
@@ -4368,7 +4381,7 @@
         <v/>
       </c>
       <c r="R16" s="7">
-        <f>IFERROR(L16 - P16 - VLOOKUP(C16, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L16 - P16 - VLOOKUP(C16, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C16, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S16" t="inlineStr">
@@ -4423,11 +4436,11 @@
         <v/>
       </c>
       <c r="L17" s="7">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M17" s="7">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N17" s="7">
@@ -4435,7 +4448,7 @@
         <v/>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P17" s="7">
@@ -4443,7 +4456,7 @@
         <v/>
       </c>
       <c r="R17" s="7">
-        <f>IFERROR(L17 - P17 - VLOOKUP(C17, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L17 - P17 - VLOOKUP(C17, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C17, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S17" t="inlineStr">
@@ -4498,11 +4511,11 @@
         <v/>
       </c>
       <c r="L18" s="7">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M18" s="7">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N18" s="7">
@@ -4510,7 +4523,7 @@
         <v/>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P18" s="7">
@@ -4518,7 +4531,7 @@
         <v/>
       </c>
       <c r="R18" s="7">
-        <f>IFERROR(L18 - P18 - VLOOKUP(C18, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L18 - P18 - VLOOKUP(C18, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C18, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S18" t="inlineStr">
@@ -4573,11 +4586,11 @@
         <v/>
       </c>
       <c r="L19" s="7">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M19" s="7">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N19" s="7">
@@ -4585,7 +4598,7 @@
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P19" s="7">
@@ -4593,7 +4606,7 @@
         <v/>
       </c>
       <c r="R19" s="7">
-        <f>IFERROR(L19 - P19 - VLOOKUP(C19, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L19 - P19 - VLOOKUP(C19, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C19, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S19" t="inlineStr">
@@ -4648,11 +4661,11 @@
         <v/>
       </c>
       <c r="L20" s="7">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M20" s="7">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N20" s="7">
@@ -4660,7 +4673,7 @@
         <v/>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P20" s="7">
@@ -4668,7 +4681,7 @@
         <v/>
       </c>
       <c r="R20" s="7">
-        <f>IFERROR(L20 - P20 - VLOOKUP(C20, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L20 - P20 - VLOOKUP(C20, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C20, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S20" t="inlineStr">
@@ -4723,11 +4736,11 @@
         <v/>
       </c>
       <c r="L21" s="7">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M21" s="7">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N21" s="7">
@@ -4735,7 +4748,7 @@
         <v/>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P21" s="7">
@@ -4743,7 +4756,7 @@
         <v/>
       </c>
       <c r="R21" s="7">
-        <f>IFERROR(L21 - P21 - VLOOKUP(C21, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L21 - P21 - VLOOKUP(C21, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C21, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S21" t="inlineStr">
@@ -4798,11 +4811,11 @@
         <v/>
       </c>
       <c r="L22" s="7">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M22" s="7">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N22" s="7">
@@ -4810,7 +4823,7 @@
         <v/>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P22" s="7">
@@ -4818,7 +4831,7 @@
         <v/>
       </c>
       <c r="R22" s="7">
-        <f>IFERROR(L22 - P22 - VLOOKUP(C22, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L22 - P22 - VLOOKUP(C22, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C22, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S22" t="inlineStr">
@@ -4880,11 +4893,11 @@
         <v/>
       </c>
       <c r="L24" s="7">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M24" s="7">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N24" s="7">
@@ -4892,7 +4905,7 @@
         <v/>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P24" s="7">
@@ -4900,7 +4913,7 @@
         <v/>
       </c>
       <c r="R24" s="7">
-        <f>IFERROR(L24 - P24 - VLOOKUP(C24, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L24 - P24 - VLOOKUP(C24, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C24, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S24" t="inlineStr">
@@ -4955,11 +4968,11 @@
         <v/>
       </c>
       <c r="L25" s="7">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M25" s="7">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N25" s="7">
@@ -4967,7 +4980,7 @@
         <v/>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P25" s="7">
@@ -4975,7 +4988,7 @@
         <v/>
       </c>
       <c r="R25" s="7">
-        <f>IFERROR(L25 - P25 - VLOOKUP(C25, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L25 - P25 - VLOOKUP(C25, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C25, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S25" t="inlineStr">
@@ -5030,11 +5043,11 @@
         <v/>
       </c>
       <c r="L26" s="7">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M26" s="7">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N26" s="7">
@@ -5042,7 +5055,7 @@
         <v/>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P26" s="7">
@@ -5050,7 +5063,7 @@
         <v/>
       </c>
       <c r="R26" s="7">
-        <f>IFERROR(L26 - P26 - VLOOKUP(C26, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L26 - P26 - VLOOKUP(C26, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C26, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S26" t="inlineStr">
@@ -5105,11 +5118,11 @@
         <v/>
       </c>
       <c r="L27" s="7">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M27" s="7">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N27" s="7">
@@ -5117,7 +5130,7 @@
         <v/>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P27" s="7">
@@ -5125,7 +5138,7 @@
         <v/>
       </c>
       <c r="R27" s="7">
-        <f>IFERROR(L27 - P27 - VLOOKUP(C27, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L27 - P27 - VLOOKUP(C27, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C27, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S27" t="inlineStr">
@@ -5180,11 +5193,11 @@
         <v/>
       </c>
       <c r="L28" s="7">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M28" s="7">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N28" s="7">
@@ -5192,7 +5205,7 @@
         <v/>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P28" s="7">
@@ -5200,7 +5213,7 @@
         <v/>
       </c>
       <c r="R28" s="7">
-        <f>IFERROR(L28 - P28 - VLOOKUP(C28, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L28 - P28 - VLOOKUP(C28, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C28, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S28" t="inlineStr">
@@ -5255,11 +5268,11 @@
         <v/>
       </c>
       <c r="L29" s="7">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M29" s="7">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N29" s="7">
@@ -5267,7 +5280,7 @@
         <v/>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P29" s="7">
@@ -5275,7 +5288,7 @@
         <v/>
       </c>
       <c r="R29" s="7">
-        <f>IFERROR(L29 - P29 - VLOOKUP(C29, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L29 - P29 - VLOOKUP(C29, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C29, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S29" t="inlineStr">
@@ -5330,11 +5343,11 @@
         <v/>
       </c>
       <c r="L30" s="7">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M30" s="7">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N30" s="7">
@@ -5342,7 +5355,7 @@
         <v/>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P30" s="7">
@@ -5350,7 +5363,7 @@
         <v/>
       </c>
       <c r="R30" s="7">
-        <f>IFERROR(L30 - P30 - VLOOKUP(C30, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L30 - P30 - VLOOKUP(C30, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C30, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S30" t="inlineStr">
@@ -5405,11 +5418,11 @@
         <v/>
       </c>
       <c r="L31" s="7">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M31" s="7">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N31" s="7">
@@ -5417,7 +5430,7 @@
         <v/>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P31" s="7">
@@ -5425,7 +5438,7 @@
         <v/>
       </c>
       <c r="R31" s="7">
-        <f>IFERROR(L31 - P31 - VLOOKUP(C31, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L31 - P31 - VLOOKUP(C31, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C31, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S31" t="inlineStr">
@@ -5480,11 +5493,11 @@
         <v/>
       </c>
       <c r="L32" s="7">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M32" s="7">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N32" s="7">
@@ -5492,7 +5505,7 @@
         <v/>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P32" s="7">
@@ -5500,7 +5513,7 @@
         <v/>
       </c>
       <c r="R32" s="7">
-        <f>IFERROR(L32 - P32 - VLOOKUP(C32, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L32 - P32 - VLOOKUP(C32, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C32, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S32" t="inlineStr">
@@ -5562,11 +5575,11 @@
         <v/>
       </c>
       <c r="L34" s="7">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M34" s="7">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N34" s="7">
@@ -5574,7 +5587,7 @@
         <v/>
       </c>
       <c r="O34" s="5">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P34" s="7">
@@ -5582,7 +5595,7 @@
         <v/>
       </c>
       <c r="R34" s="7">
-        <f>IFERROR(L34 - P34 - VLOOKUP(C34, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L34 - P34 - VLOOKUP(C34, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C34, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S34" t="inlineStr">
@@ -5637,11 +5650,11 @@
         <v/>
       </c>
       <c r="L35" s="7">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M35" s="7">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N35" s="7">
@@ -5649,7 +5662,7 @@
         <v/>
       </c>
       <c r="O35" s="5">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P35" s="7">
@@ -5657,7 +5670,7 @@
         <v/>
       </c>
       <c r="R35" s="7">
-        <f>IFERROR(L35 - P35 - VLOOKUP(C35, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L35 - P35 - VLOOKUP(C35, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C35, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S35" t="inlineStr">
@@ -5712,11 +5725,11 @@
         <v/>
       </c>
       <c r="L36" s="7">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M36" s="7">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N36" s="7">
@@ -5724,7 +5737,7 @@
         <v/>
       </c>
       <c r="O36" s="5">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P36" s="7">
@@ -5732,7 +5745,7 @@
         <v/>
       </c>
       <c r="R36" s="7">
-        <f>IFERROR(L36 - P36 - VLOOKUP(C36, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L36 - P36 - VLOOKUP(C36, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C36, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S36" t="inlineStr">
@@ -5787,11 +5800,11 @@
         <v/>
       </c>
       <c r="L37" s="7">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M37" s="7">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N37" s="7">
@@ -5799,7 +5812,7 @@
         <v/>
       </c>
       <c r="O37" s="5">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P37" s="7">
@@ -5807,7 +5820,7 @@
         <v/>
       </c>
       <c r="R37" s="7">
-        <f>IFERROR(L37 - P37 - VLOOKUP(C37, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L37 - P37 - VLOOKUP(C37, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C37, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S37" t="inlineStr">
@@ -5866,11 +5879,11 @@
         <v/>
       </c>
       <c r="L38" s="7">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M38" s="7">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N38" s="7">
@@ -5878,7 +5891,7 @@
         <v/>
       </c>
       <c r="O38" s="5">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P38" s="7">
@@ -5886,7 +5899,7 @@
         <v/>
       </c>
       <c r="R38" s="7">
-        <f>IFERROR(L38 - P38 - VLOOKUP(C38, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L38 - P38 - VLOOKUP(C38, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C38, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S38" t="inlineStr">
@@ -5945,11 +5958,11 @@
         <v/>
       </c>
       <c r="L39" s="7">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M39" s="7">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N39" s="7">
@@ -5957,7 +5970,7 @@
         <v/>
       </c>
       <c r="O39" s="5">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P39" s="7">
@@ -5965,7 +5978,7 @@
         <v/>
       </c>
       <c r="R39" s="7">
-        <f>IFERROR(L39 - P39 - VLOOKUP(C39, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L39 - P39 - VLOOKUP(C39, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C39, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S39" t="inlineStr">
@@ -6024,11 +6037,11 @@
         <v/>
       </c>
       <c r="L40" s="7">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M40" s="7">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N40" s="7">
@@ -6036,7 +6049,7 @@
         <v/>
       </c>
       <c r="O40" s="5">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P40" s="7">
@@ -6044,7 +6057,7 @@
         <v/>
       </c>
       <c r="R40" s="7">
-        <f>IFERROR(L40 - P40 - VLOOKUP(C40, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L40 - P40 - VLOOKUP(C40, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C40, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S40" t="inlineStr">
@@ -6099,11 +6112,11 @@
         <v/>
       </c>
       <c r="L41" s="7">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M41" s="7">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N41" s="7">
@@ -6111,7 +6124,7 @@
         <v/>
       </c>
       <c r="O41" s="5">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P41" s="7">
@@ -6119,7 +6132,7 @@
         <v/>
       </c>
       <c r="R41" s="7">
-        <f>IFERROR(L41 - P41 - VLOOKUP(C41, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L41 - P41 - VLOOKUP(C41, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C41, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S41" t="inlineStr">
@@ -6178,11 +6191,11 @@
         <v/>
       </c>
       <c r="L42" s="7">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M42" s="7">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N42" s="7">
@@ -6190,7 +6203,7 @@
         <v/>
       </c>
       <c r="O42" s="5">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P42" s="7">
@@ -6198,7 +6211,7 @@
         <v/>
       </c>
       <c r="R42" s="7">
-        <f>IFERROR(L42 - P42 - VLOOKUP(C42, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L42 - P42 - VLOOKUP(C42, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C42, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S42" t="inlineStr">
@@ -6253,11 +6266,11 @@
         <v/>
       </c>
       <c r="L43" s="7">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M43" s="7">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N43" s="7">
@@ -6265,7 +6278,7 @@
         <v/>
       </c>
       <c r="O43" s="5">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P43" s="7">
@@ -6273,7 +6286,7 @@
         <v/>
       </c>
       <c r="R43" s="7">
-        <f>IFERROR(L43 - P43 - VLOOKUP(C43, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L43 - P43 - VLOOKUP(C43, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C43, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S43" t="inlineStr">
@@ -6328,11 +6341,11 @@
         <v/>
       </c>
       <c r="L44" s="7">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M44" s="7">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N44" s="7">
@@ -6340,7 +6353,7 @@
         <v/>
       </c>
       <c r="O44" s="5">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P44" s="7">
@@ -6348,7 +6361,7 @@
         <v/>
       </c>
       <c r="R44" s="7">
-        <f>IFERROR(L44 - P44 - VLOOKUP(C44, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L44 - P44 - VLOOKUP(C44, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C44, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S44" t="inlineStr">
@@ -6410,11 +6423,11 @@
         <v/>
       </c>
       <c r="L46" s="7">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M46" s="7">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N46" s="7">
@@ -6422,7 +6435,7 @@
         <v/>
       </c>
       <c r="O46" s="5">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P46" s="7">
@@ -6430,7 +6443,7 @@
         <v/>
       </c>
       <c r="R46" s="7">
-        <f>IFERROR(L46 - P46 - VLOOKUP(C46, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L46 - P46 - VLOOKUP(C46, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C46, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S46" t="inlineStr">
@@ -6485,11 +6498,11 @@
         <v/>
       </c>
       <c r="L47" s="7">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M47" s="7">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N47" s="7">
@@ -6497,7 +6510,7 @@
         <v/>
       </c>
       <c r="O47" s="5">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P47" s="7">
@@ -6505,7 +6518,7 @@
         <v/>
       </c>
       <c r="R47" s="7">
-        <f>IFERROR(L47 - P47 - VLOOKUP(C47, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L47 - P47 - VLOOKUP(C47, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C47, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S47" t="inlineStr">
@@ -6560,11 +6573,11 @@
         <v/>
       </c>
       <c r="L48" s="7">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M48" s="7">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N48" s="7">
@@ -6572,7 +6585,7 @@
         <v/>
       </c>
       <c r="O48" s="5">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P48" s="7">
@@ -6580,7 +6593,7 @@
         <v/>
       </c>
       <c r="R48" s="7">
-        <f>IFERROR(L48 - P48 - VLOOKUP(C48, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L48 - P48 - VLOOKUP(C48, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C48, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S48" t="inlineStr">
@@ -6635,11 +6648,11 @@
         <v/>
       </c>
       <c r="L49" s="7">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M49" s="7">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N49" s="7">
@@ -6647,7 +6660,7 @@
         <v/>
       </c>
       <c r="O49" s="5">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P49" s="7">
@@ -6655,7 +6668,7 @@
         <v/>
       </c>
       <c r="R49" s="7">
-        <f>IFERROR(L49 - P49 - VLOOKUP(C49, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L49 - P49 - VLOOKUP(C49, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C49, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S49" t="inlineStr">
@@ -6710,11 +6723,11 @@
         <v/>
       </c>
       <c r="L50" s="7">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M50" s="7">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N50" s="7">
@@ -6722,7 +6735,7 @@
         <v/>
       </c>
       <c r="O50" s="5">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P50" s="7">
@@ -6730,7 +6743,7 @@
         <v/>
       </c>
       <c r="R50" s="7">
-        <f>IFERROR(L50 - P50 - VLOOKUP(C50, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L50 - P50 - VLOOKUP(C50, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C50, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S50" t="inlineStr">
@@ -6792,11 +6805,11 @@
         <v/>
       </c>
       <c r="L52" s="7">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M52" s="7">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N52" s="7">
@@ -6804,7 +6817,7 @@
         <v/>
       </c>
       <c r="O52" s="5">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P52" s="7">
@@ -6812,7 +6825,7 @@
         <v/>
       </c>
       <c r="R52" s="7">
-        <f>IFERROR(L52 - P52 - VLOOKUP(C52, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L52 - P52 - VLOOKUP(C52, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C52, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S52" t="inlineStr">
@@ -6867,11 +6880,11 @@
         <v/>
       </c>
       <c r="L53" s="7">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M53" s="7">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N53" s="7">
@@ -6879,7 +6892,7 @@
         <v/>
       </c>
       <c r="O53" s="5">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P53" s="7">
@@ -6887,7 +6900,7 @@
         <v/>
       </c>
       <c r="R53" s="7">
-        <f>IFERROR(L53 - P53 - VLOOKUP(C53, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L53 - P53 - VLOOKUP(C53, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C53, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S53" t="inlineStr">
@@ -6942,11 +6955,11 @@
         <v/>
       </c>
       <c r="L54" s="7">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M54" s="7">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N54" s="7">
@@ -6954,7 +6967,7 @@
         <v/>
       </c>
       <c r="O54" s="5">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P54" s="7">
@@ -6962,7 +6975,7 @@
         <v/>
       </c>
       <c r="R54" s="7">
-        <f>IFERROR(L54 - P54 - VLOOKUP(C54, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L54 - P54 - VLOOKUP(C54, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C54, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S54" t="inlineStr">
@@ -7017,11 +7030,11 @@
         <v/>
       </c>
       <c r="L55" s="7">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M55" s="7">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N55" s="7">
@@ -7029,7 +7042,7 @@
         <v/>
       </c>
       <c r="O55" s="5">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P55" s="7">
@@ -7037,7 +7050,7 @@
         <v/>
       </c>
       <c r="R55" s="7">
-        <f>IFERROR(L55 - P55 - VLOOKUP(C55, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L55 - P55 - VLOOKUP(C55, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C55, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S55" t="inlineStr">
@@ -7092,11 +7105,11 @@
         <v/>
       </c>
       <c r="L56" s="7">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M56" s="7">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N56" s="7">
@@ -7104,7 +7117,7 @@
         <v/>
       </c>
       <c r="O56" s="5">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P56" s="7">
@@ -7112,7 +7125,7 @@
         <v/>
       </c>
       <c r="R56" s="7">
-        <f>IFERROR(L56 - P56 - VLOOKUP(C56, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L56 - P56 - VLOOKUP(C56, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C56, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S56" t="inlineStr">
@@ -7167,11 +7180,11 @@
         <v/>
       </c>
       <c r="L57" s="7">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M57" s="7">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N57" s="7">
@@ -7179,7 +7192,7 @@
         <v/>
       </c>
       <c r="O57" s="5">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P57" s="7">
@@ -7187,7 +7200,7 @@
         <v/>
       </c>
       <c r="R57" s="7">
-        <f>IFERROR(L57 - P57 - VLOOKUP(C57, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L57 - P57 - VLOOKUP(C57, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C57, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S57" t="inlineStr">
@@ -7242,11 +7255,11 @@
         <v/>
       </c>
       <c r="L58" s="7">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M58" s="7">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N58" s="7">
@@ -7254,7 +7267,7 @@
         <v/>
       </c>
       <c r="O58" s="5">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P58" s="7">
@@ -7262,7 +7275,7 @@
         <v/>
       </c>
       <c r="R58" s="7">
-        <f>IFERROR(L58 - P58 - VLOOKUP(C58, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L58 - P58 - VLOOKUP(C58, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C58, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S58" t="inlineStr">
@@ -7321,11 +7334,11 @@
         <v/>
       </c>
       <c r="L59" s="7">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M59" s="7">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N59" s="7">
@@ -7333,7 +7346,7 @@
         <v/>
       </c>
       <c r="O59" s="5">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P59" s="7">
@@ -7341,7 +7354,7 @@
         <v/>
       </c>
       <c r="R59" s="7">
-        <f>IFERROR(L59 - P59 - VLOOKUP(C59, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L59 - P59 - VLOOKUP(C59, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C59, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S59" t="inlineStr">
@@ -7400,11 +7413,11 @@
         <v/>
       </c>
       <c r="L60" s="7">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M60" s="7">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N60" s="7">
@@ -7412,7 +7425,7 @@
         <v/>
       </c>
       <c r="O60" s="5">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P60" s="7">
@@ -7420,7 +7433,7 @@
         <v/>
       </c>
       <c r="R60" s="7">
-        <f>IFERROR(L60 - P60 - VLOOKUP(C60, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L60 - P60 - VLOOKUP(C60, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C60, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S60" t="inlineStr">
@@ -7479,11 +7492,11 @@
         <v/>
       </c>
       <c r="L61" s="7">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M61" s="7">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N61" s="7">
@@ -7491,7 +7504,7 @@
         <v/>
       </c>
       <c r="O61" s="5">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P61" s="7">
@@ -7499,7 +7512,7 @@
         <v/>
       </c>
       <c r="R61" s="7">
-        <f>IFERROR(L61 - P61 - VLOOKUP(C61, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L61 - P61 - VLOOKUP(C61, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C61, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S61" t="inlineStr">
@@ -7558,11 +7571,11 @@
         <v/>
       </c>
       <c r="L62" s="7">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M62" s="7">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N62" s="7">
@@ -7570,7 +7583,7 @@
         <v/>
       </c>
       <c r="O62" s="5">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P62" s="7">
@@ -7578,7 +7591,7 @@
         <v/>
       </c>
       <c r="R62" s="7">
-        <f>IFERROR(L62 - P62 - VLOOKUP(C62, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L62 - P62 - VLOOKUP(C62, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C62, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S62" t="inlineStr">
@@ -7637,11 +7650,11 @@
         <v/>
       </c>
       <c r="L63" s="7">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M63" s="7">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N63" s="7">
@@ -7649,7 +7662,7 @@
         <v/>
       </c>
       <c r="O63" s="5">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P63" s="7">
@@ -7657,7 +7670,7 @@
         <v/>
       </c>
       <c r="R63" s="7">
-        <f>IFERROR(L63 - P63 - VLOOKUP(C63, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L63 - P63 - VLOOKUP(C63, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C63, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S63" t="inlineStr">
@@ -7719,11 +7732,11 @@
         <v/>
       </c>
       <c r="L65" s="7">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M65" s="7">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N65" s="7">
@@ -7731,7 +7744,7 @@
         <v/>
       </c>
       <c r="O65" s="5">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P65" s="7">
@@ -7739,7 +7752,7 @@
         <v/>
       </c>
       <c r="R65" s="7">
-        <f>IFERROR(L65 - P65 - VLOOKUP(C65, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L65 - P65 - VLOOKUP(C65, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C65, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S65" t="inlineStr">
@@ -7794,11 +7807,11 @@
         <v/>
       </c>
       <c r="L66" s="7">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M66" s="7">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N66" s="7">
@@ -7806,7 +7819,7 @@
         <v/>
       </c>
       <c r="O66" s="5">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P66" s="7">
@@ -7814,7 +7827,7 @@
         <v/>
       </c>
       <c r="R66" s="7">
-        <f>IFERROR(L66 - P66 - VLOOKUP(C66, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L66 - P66 - VLOOKUP(C66, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C66, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S66" t="inlineStr">
@@ -7869,11 +7882,11 @@
         <v/>
       </c>
       <c r="L67" s="7">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M67" s="7">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N67" s="7">
@@ -7881,7 +7894,7 @@
         <v/>
       </c>
       <c r="O67" s="5">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P67" s="7">
@@ -7889,7 +7902,7 @@
         <v/>
       </c>
       <c r="R67" s="7">
-        <f>IFERROR(L67 - P67 - VLOOKUP(C67, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L67 - P67 - VLOOKUP(C67, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C67, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S67" t="inlineStr">
@@ -7944,11 +7957,11 @@
         <v/>
       </c>
       <c r="L68" s="7">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M68" s="7">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N68" s="7">
@@ -7956,7 +7969,7 @@
         <v/>
       </c>
       <c r="O68" s="5">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P68" s="7">
@@ -7964,7 +7977,7 @@
         <v/>
       </c>
       <c r="R68" s="7">
-        <f>IFERROR(L68 - P68 - VLOOKUP(C68, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L68 - P68 - VLOOKUP(C68, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C68, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S68" t="inlineStr">
@@ -8019,11 +8032,11 @@
         <v/>
       </c>
       <c r="L69" s="7">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M69" s="7">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N69" s="7">
@@ -8031,7 +8044,7 @@
         <v/>
       </c>
       <c r="O69" s="5">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P69" s="7">
@@ -8039,7 +8052,7 @@
         <v/>
       </c>
       <c r="R69" s="7">
-        <f>IFERROR(L69 - P69 - VLOOKUP(C69, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L69 - P69 - VLOOKUP(C69, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C69, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S69" t="inlineStr">
@@ -8094,11 +8107,11 @@
         <v/>
       </c>
       <c r="L70" s="7">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M70" s="7">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N70" s="7">
@@ -8106,7 +8119,7 @@
         <v/>
       </c>
       <c r="O70" s="5">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P70" s="7">
@@ -8114,7 +8127,7 @@
         <v/>
       </c>
       <c r="R70" s="7">
-        <f>IFERROR(L70 - P70 - VLOOKUP(C70, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L70 - P70 - VLOOKUP(C70, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C70, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S70" t="inlineStr">
@@ -8169,11 +8182,11 @@
         <v/>
       </c>
       <c r="L71" s="7">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M71" s="7">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N71" s="7">
@@ -8181,7 +8194,7 @@
         <v/>
       </c>
       <c r="O71" s="5">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P71" s="7">
@@ -8189,7 +8202,7 @@
         <v/>
       </c>
       <c r="R71" s="7">
-        <f>IFERROR(L71 - P71 - VLOOKUP(C71, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L71 - P71 - VLOOKUP(C71, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C71, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S71" t="inlineStr">
@@ -8244,11 +8257,11 @@
         <v/>
       </c>
       <c r="L72" s="7">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M72" s="7">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N72" s="7">
@@ -8256,7 +8269,7 @@
         <v/>
       </c>
       <c r="O72" s="5">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P72" s="7">
@@ -8264,7 +8277,7 @@
         <v/>
       </c>
       <c r="R72" s="7">
-        <f>IFERROR(L72 - P72 - VLOOKUP(C72, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L72 - P72 - VLOOKUP(C72, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C72, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S72" t="inlineStr">
@@ -8319,11 +8332,11 @@
         <v/>
       </c>
       <c r="L73" s="7">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M73" s="7">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N73" s="7">
@@ -8331,7 +8344,7 @@
         <v/>
       </c>
       <c r="O73" s="5">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P73" s="7">
@@ -8339,7 +8352,7 @@
         <v/>
       </c>
       <c r="R73" s="7">
-        <f>IFERROR(L73 - P73 - VLOOKUP(C73, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L73 - P73 - VLOOKUP(C73, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C73, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S73" t="inlineStr">
@@ -8394,11 +8407,11 @@
         <v/>
       </c>
       <c r="L74" s="7">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M74" s="7">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N74" s="7">
@@ -8406,7 +8419,7 @@
         <v/>
       </c>
       <c r="O74" s="5">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P74" s="7">
@@ -8414,7 +8427,7 @@
         <v/>
       </c>
       <c r="R74" s="7">
-        <f>IFERROR(L74 - P74 - VLOOKUP(C74, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L74 - P74 - VLOOKUP(C74, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C74, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S74" t="inlineStr">
@@ -8469,11 +8482,11 @@
         <v/>
       </c>
       <c r="L75" s="7">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M75" s="7">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N75" s="7">
@@ -8481,7 +8494,7 @@
         <v/>
       </c>
       <c r="O75" s="5">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P75" s="7">
@@ -8489,7 +8502,7 @@
         <v/>
       </c>
       <c r="R75" s="7">
-        <f>IFERROR(L75 - P75 - VLOOKUP(C75, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L75 - P75 - VLOOKUP(C75, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C75, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S75" t="inlineStr">
@@ -8551,11 +8564,11 @@
         <v/>
       </c>
       <c r="L77" s="7">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M77" s="7">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N77" s="7">
@@ -8563,7 +8576,7 @@
         <v/>
       </c>
       <c r="O77" s="5">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P77" s="7">
@@ -8571,7 +8584,7 @@
         <v/>
       </c>
       <c r="R77" s="7">
-        <f>IFERROR(L77 - P77 - VLOOKUP(C77, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L77 - P77 - VLOOKUP(C77, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C77, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S77" t="inlineStr">
@@ -8626,11 +8639,11 @@
         <v/>
       </c>
       <c r="L78" s="7">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M78" s="7">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N78" s="7">
@@ -8638,7 +8651,7 @@
         <v/>
       </c>
       <c r="O78" s="5">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P78" s="7">
@@ -8646,7 +8659,7 @@
         <v/>
       </c>
       <c r="R78" s="7">
-        <f>IFERROR(L78 - P78 - VLOOKUP(C78, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L78 - P78 - VLOOKUP(C78, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C78, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S78" t="inlineStr">
@@ -8701,11 +8714,11 @@
         <v/>
       </c>
       <c r="L79" s="7">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M79" s="7">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N79" s="7">
@@ -8713,7 +8726,7 @@
         <v/>
       </c>
       <c r="O79" s="5">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P79" s="7">
@@ -8721,7 +8734,7 @@
         <v/>
       </c>
       <c r="R79" s="7">
-        <f>IFERROR(L79 - P79 - VLOOKUP(C79, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L79 - P79 - VLOOKUP(C79, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C79, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S79" t="inlineStr">
@@ -8776,11 +8789,11 @@
         <v/>
       </c>
       <c r="L80" s="7">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M80" s="7">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N80" s="7">
@@ -8788,7 +8801,7 @@
         <v/>
       </c>
       <c r="O80" s="5">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P80" s="7">
@@ -8796,7 +8809,7 @@
         <v/>
       </c>
       <c r="R80" s="7">
-        <f>IFERROR(L80 - P80 - VLOOKUP(C80, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L80 - P80 - VLOOKUP(C80, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C80, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S80" t="inlineStr">
@@ -8851,11 +8864,11 @@
         <v/>
       </c>
       <c r="L81" s="7">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M81" s="7">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N81" s="7">
@@ -8863,7 +8876,7 @@
         <v/>
       </c>
       <c r="O81" s="5">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P81" s="7">
@@ -8871,7 +8884,7 @@
         <v/>
       </c>
       <c r="R81" s="7">
-        <f>IFERROR(L81 - P81 - VLOOKUP(C81, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L81 - P81 - VLOOKUP(C81, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C81, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S81" t="inlineStr">
@@ -8926,11 +8939,11 @@
         <v/>
       </c>
       <c r="L82" s="7">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M82" s="7">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N82" s="7">
@@ -8938,7 +8951,7 @@
         <v/>
       </c>
       <c r="O82" s="5">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P82" s="7">
@@ -8946,7 +8959,7 @@
         <v/>
       </c>
       <c r="R82" s="7">
-        <f>IFERROR(L82 - P82 - VLOOKUP(C82, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L82 - P82 - VLOOKUP(C82, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C82, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S82" t="inlineStr">
@@ -9005,11 +9018,11 @@
         <v/>
       </c>
       <c r="L83" s="7">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M83" s="7">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N83" s="7">
@@ -9017,7 +9030,7 @@
         <v/>
       </c>
       <c r="O83" s="5">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P83" s="7">
@@ -9025,7 +9038,7 @@
         <v/>
       </c>
       <c r="R83" s="7">
-        <f>IFERROR(L83 - P83 - VLOOKUP(C83, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L83 - P83 - VLOOKUP(C83, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C83, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S83" t="inlineStr">
@@ -9084,11 +9097,11 @@
         <v/>
       </c>
       <c r="L84" s="7">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M84" s="7">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N84" s="7">
@@ -9096,7 +9109,7 @@
         <v/>
       </c>
       <c r="O84" s="5">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P84" s="7">
@@ -9104,7 +9117,7 @@
         <v/>
       </c>
       <c r="R84" s="7">
-        <f>IFERROR(L84 - P84 - VLOOKUP(C84, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L84 - P84 - VLOOKUP(C84, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C84, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S84" t="inlineStr">
@@ -9163,11 +9176,11 @@
         <v/>
       </c>
       <c r="L85" s="7">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M85" s="7">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N85" s="7">
@@ -9175,7 +9188,7 @@
         <v/>
       </c>
       <c r="O85" s="5">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P85" s="7">
@@ -9183,7 +9196,7 @@
         <v/>
       </c>
       <c r="R85" s="7">
-        <f>IFERROR(L85 - P85 - VLOOKUP(C85, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L85 - P85 - VLOOKUP(C85, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C85, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S85" t="inlineStr">
@@ -9242,11 +9255,11 @@
         <v/>
       </c>
       <c r="L86" s="7">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M86" s="7">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N86" s="7">
@@ -9254,7 +9267,7 @@
         <v/>
       </c>
       <c r="O86" s="5">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P86" s="7">
@@ -9262,7 +9275,7 @@
         <v/>
       </c>
       <c r="R86" s="7">
-        <f>IFERROR(L86 - P86 - VLOOKUP(C86, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L86 - P86 - VLOOKUP(C86, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C86, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S86" t="inlineStr">
@@ -9321,11 +9334,11 @@
         <v/>
       </c>
       <c r="L87" s="7">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M87" s="7">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N87" s="7">
@@ -9333,7 +9346,7 @@
         <v/>
       </c>
       <c r="O87" s="5">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P87" s="7">
@@ -9341,7 +9354,7 @@
         <v/>
       </c>
       <c r="R87" s="7">
-        <f>IFERROR(L87 - P87 - VLOOKUP(C87, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L87 - P87 - VLOOKUP(C87, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C87, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S87" t="inlineStr">
@@ -9403,11 +9416,11 @@
         <v/>
       </c>
       <c r="L89" s="7">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M89" s="7">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N89" s="7">
@@ -9415,7 +9428,7 @@
         <v/>
       </c>
       <c r="O89" s="5">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P89" s="7">
@@ -9423,7 +9436,7 @@
         <v/>
       </c>
       <c r="R89" s="7">
-        <f>IFERROR(L89 - P89 - VLOOKUP(C89, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L89 - P89 - VLOOKUP(C89, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C89, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S89" t="inlineStr">
@@ -9478,11 +9491,11 @@
         <v/>
       </c>
       <c r="L90" s="7">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M90" s="7">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N90" s="7">
@@ -9490,7 +9503,7 @@
         <v/>
       </c>
       <c r="O90" s="5">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P90" s="7">
@@ -9498,7 +9511,7 @@
         <v/>
       </c>
       <c r="R90" s="7">
-        <f>IFERROR(L90 - P90 - VLOOKUP(C90, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L90 - P90 - VLOOKUP(C90, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C90, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S90" t="inlineStr">
@@ -9553,11 +9566,11 @@
         <v/>
       </c>
       <c r="L91" s="7">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M91" s="7">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N91" s="7">
@@ -9565,7 +9578,7 @@
         <v/>
       </c>
       <c r="O91" s="5">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P91" s="7">
@@ -9573,7 +9586,7 @@
         <v/>
       </c>
       <c r="R91" s="7">
-        <f>IFERROR(L91 - P91 - VLOOKUP(C91, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L91 - P91 - VLOOKUP(C91, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C91, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S91" t="inlineStr">
@@ -9628,11 +9641,11 @@
         <v/>
       </c>
       <c r="L92" s="7">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M92" s="7">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N92" s="7">
@@ -9640,7 +9653,7 @@
         <v/>
       </c>
       <c r="O92" s="5">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P92" s="7">
@@ -9648,7 +9661,7 @@
         <v/>
       </c>
       <c r="R92" s="7">
-        <f>IFERROR(L92 - P92 - VLOOKUP(C92, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L92 - P92 - VLOOKUP(C92, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C92, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S92" t="inlineStr">
@@ -9703,11 +9716,11 @@
         <v/>
       </c>
       <c r="L93" s="7">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M93" s="7">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N93" s="7">
@@ -9715,7 +9728,7 @@
         <v/>
       </c>
       <c r="O93" s="5">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P93" s="7">
@@ -9723,7 +9736,7 @@
         <v/>
       </c>
       <c r="R93" s="7">
-        <f>IFERROR(L93 - P93 - VLOOKUP(C93, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L93 - P93 - VLOOKUP(C93, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C93, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S93" t="inlineStr">
@@ -9778,11 +9791,11 @@
         <v/>
       </c>
       <c r="L94" s="7">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M94" s="7">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N94" s="7">
@@ -9790,7 +9803,7 @@
         <v/>
       </c>
       <c r="O94" s="5">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P94" s="7">
@@ -9798,7 +9811,7 @@
         <v/>
       </c>
       <c r="R94" s="7">
-        <f>IFERROR(L94 - P94 - VLOOKUP(C94, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L94 - P94 - VLOOKUP(C94, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C94, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S94" t="inlineStr">
@@ -9853,11 +9866,11 @@
         <v/>
       </c>
       <c r="L95" s="7">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M95" s="7">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N95" s="7">
@@ -9865,7 +9878,7 @@
         <v/>
       </c>
       <c r="O95" s="5">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P95" s="7">
@@ -9873,7 +9886,7 @@
         <v/>
       </c>
       <c r="R95" s="7">
-        <f>IFERROR(L95 - P95 - VLOOKUP(C95, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L95 - P95 - VLOOKUP(C95, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C95, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S95" t="inlineStr">
@@ -9928,11 +9941,11 @@
         <v/>
       </c>
       <c r="L96" s="7">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M96" s="7">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N96" s="7">
@@ -9940,7 +9953,7 @@
         <v/>
       </c>
       <c r="O96" s="5">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P96" s="7">
@@ -9948,7 +9961,7 @@
         <v/>
       </c>
       <c r="R96" s="7">
-        <f>IFERROR(L96 - P96 - VLOOKUP(C96, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L96 - P96 - VLOOKUP(C96, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C96, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S96" t="inlineStr">
@@ -10003,11 +10016,11 @@
         <v/>
       </c>
       <c r="L97" s="7">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M97" s="7">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N97" s="7">
@@ -10015,7 +10028,7 @@
         <v/>
       </c>
       <c r="O97" s="5">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P97" s="7">
@@ -10023,7 +10036,7 @@
         <v/>
       </c>
       <c r="R97" s="7">
-        <f>IFERROR(L97 - P97 - VLOOKUP(C97, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L97 - P97 - VLOOKUP(C97, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C97, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S97" t="inlineStr">
@@ -10078,11 +10091,11 @@
         <v/>
       </c>
       <c r="L98" s="7">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M98" s="7">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N98" s="7">
@@ -10090,7 +10103,7 @@
         <v/>
       </c>
       <c r="O98" s="5">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P98" s="7">
@@ -10098,7 +10111,7 @@
         <v/>
       </c>
       <c r="R98" s="7">
-        <f>IFERROR(L98 - P98 - VLOOKUP(C98, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L98 - P98 - VLOOKUP(C98, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C98, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S98" t="inlineStr">
@@ -10153,11 +10166,11 @@
         <v/>
       </c>
       <c r="L99" s="7">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M99" s="7">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N99" s="7">
@@ -10165,7 +10178,7 @@
         <v/>
       </c>
       <c r="O99" s="5">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P99" s="7">
@@ -10173,7 +10186,7 @@
         <v/>
       </c>
       <c r="R99" s="7">
-        <f>IFERROR(L99 - P99 - VLOOKUP(C99, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L99 - P99 - VLOOKUP(C99, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C99, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S99" t="inlineStr">
@@ -10228,11 +10241,11 @@
         <v/>
       </c>
       <c r="L100" s="7">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M100" s="7">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N100" s="7">
@@ -10240,7 +10253,7 @@
         <v/>
       </c>
       <c r="O100" s="5">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P100" s="7">
@@ -10248,7 +10261,7 @@
         <v/>
       </c>
       <c r="R100" s="7">
-        <f>IFERROR(L100 - P100 - VLOOKUP(C100, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L100 - P100 - VLOOKUP(C100, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C100, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S100" t="inlineStr">
@@ -10303,11 +10316,11 @@
         <v/>
       </c>
       <c r="L101" s="7">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M101" s="7">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N101" s="7">
@@ -10315,7 +10328,7 @@
         <v/>
       </c>
       <c r="O101" s="5">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P101" s="7">
@@ -10323,7 +10336,7 @@
         <v/>
       </c>
       <c r="R101" s="7">
-        <f>IFERROR(L101 - P101 - VLOOKUP(C101, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L101 - P101 - VLOOKUP(C101, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C101, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S101" t="inlineStr">
@@ -10378,11 +10391,11 @@
         <v/>
       </c>
       <c r="L102" s="7">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M102" s="7">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N102" s="7">
@@ -10390,7 +10403,7 @@
         <v/>
       </c>
       <c r="O102" s="5">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P102" s="7">
@@ -10398,7 +10411,7 @@
         <v/>
       </c>
       <c r="R102" s="7">
-        <f>IFERROR(L102 - P102 - VLOOKUP(C102, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L102 - P102 - VLOOKUP(C102, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C102, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S102" t="inlineStr">
@@ -10460,11 +10473,11 @@
         <v/>
       </c>
       <c r="L104" s="7">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M104" s="7">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N104" s="7">
@@ -10472,7 +10485,7 @@
         <v/>
       </c>
       <c r="O104" s="5">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P104" s="7">
@@ -10480,7 +10493,7 @@
         <v/>
       </c>
       <c r="R104" s="7">
-        <f>IFERROR(L104 - P104 - VLOOKUP(C104, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L104 - P104 - VLOOKUP(C104, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C104, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S104" t="inlineStr">
@@ -10535,11 +10548,11 @@
         <v/>
       </c>
       <c r="L105" s="7">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M105" s="7">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N105" s="7">
@@ -10547,7 +10560,7 @@
         <v/>
       </c>
       <c r="O105" s="5">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P105" s="7">
@@ -10555,7 +10568,7 @@
         <v/>
       </c>
       <c r="R105" s="7">
-        <f>IFERROR(L105 - P105 - VLOOKUP(C105, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L105 - P105 - VLOOKUP(C105, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C105, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S105" t="inlineStr">
@@ -10610,11 +10623,11 @@
         <v/>
       </c>
       <c r="L106" s="7">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M106" s="7">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N106" s="7">
@@ -10622,7 +10635,7 @@
         <v/>
       </c>
       <c r="O106" s="5">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P106" s="7">
@@ -10630,7 +10643,7 @@
         <v/>
       </c>
       <c r="R106" s="7">
-        <f>IFERROR(L106 - P106 - VLOOKUP(C106, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L106 - P106 - VLOOKUP(C106, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C106, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S106" t="inlineStr">
@@ -10685,11 +10698,11 @@
         <v/>
       </c>
       <c r="L107" s="7">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M107" s="7">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N107" s="7">
@@ -10697,7 +10710,7 @@
         <v/>
       </c>
       <c r="O107" s="5">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P107" s="7">
@@ -10705,7 +10718,7 @@
         <v/>
       </c>
       <c r="R107" s="7">
-        <f>IFERROR(L107 - P107 - VLOOKUP(C107, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L107 - P107 - VLOOKUP(C107, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C107, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S107" t="inlineStr">
@@ -10760,11 +10773,11 @@
         <v/>
       </c>
       <c r="L108" s="7">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M108" s="7">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N108" s="7">
@@ -10772,7 +10785,7 @@
         <v/>
       </c>
       <c r="O108" s="5">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P108" s="7">
@@ -10780,7 +10793,7 @@
         <v/>
       </c>
       <c r="R108" s="7">
-        <f>IFERROR(L108 - P108 - VLOOKUP(C108, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L108 - P108 - VLOOKUP(C108, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C108, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S108" t="inlineStr">
@@ -10835,11 +10848,11 @@
         <v/>
       </c>
       <c r="L109" s="7">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M109" s="7">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N109" s="7">
@@ -10847,7 +10860,7 @@
         <v/>
       </c>
       <c r="O109" s="5">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P109" s="7">
@@ -10855,7 +10868,7 @@
         <v/>
       </c>
       <c r="R109" s="7">
-        <f>IFERROR(L109 - P109 - VLOOKUP(C109, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L109 - P109 - VLOOKUP(C109, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C109, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S109" t="inlineStr">
@@ -10910,11 +10923,11 @@
         <v/>
       </c>
       <c r="L110" s="7">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M110" s="7">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N110" s="7">
@@ -10922,7 +10935,7 @@
         <v/>
       </c>
       <c r="O110" s="5">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P110" s="7">
@@ -10930,7 +10943,7 @@
         <v/>
       </c>
       <c r="R110" s="7">
-        <f>IFERROR(L110 - P110 - VLOOKUP(C110, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L110 - P110 - VLOOKUP(C110, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C110, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S110" t="inlineStr">
@@ -10985,11 +10998,11 @@
         <v/>
       </c>
       <c r="L111" s="7">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M111" s="7">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N111" s="7">
@@ -10997,7 +11010,7 @@
         <v/>
       </c>
       <c r="O111" s="5">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P111" s="7">
@@ -11005,7 +11018,7 @@
         <v/>
       </c>
       <c r="R111" s="7">
-        <f>IFERROR(L111 - P111 - VLOOKUP(C111, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L111 - P111 - VLOOKUP(C111, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C111, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S111" t="inlineStr">
@@ -11064,11 +11077,11 @@
         <v/>
       </c>
       <c r="L112" s="7">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M112" s="7">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N112" s="7">
@@ -11076,7 +11089,7 @@
         <v/>
       </c>
       <c r="O112" s="5">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P112" s="7">
@@ -11084,7 +11097,7 @@
         <v/>
       </c>
       <c r="R112" s="7">
-        <f>IFERROR(L112 - P112 - VLOOKUP(C112, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L112 - P112 - VLOOKUP(C112, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C112, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S112" t="inlineStr">
@@ -11143,11 +11156,11 @@
         <v/>
       </c>
       <c r="L113" s="7">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M113" s="7">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N113" s="7">
@@ -11155,7 +11168,7 @@
         <v/>
       </c>
       <c r="O113" s="5">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P113" s="7">
@@ -11163,7 +11176,7 @@
         <v/>
       </c>
       <c r="R113" s="7">
-        <f>IFERROR(L113 - P113 - VLOOKUP(C113, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L113 - P113 - VLOOKUP(C113, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C113, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S113" t="inlineStr">
@@ -11218,11 +11231,11 @@
         <v/>
       </c>
       <c r="L114" s="7">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M114" s="7">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N114" s="7">
@@ -11230,7 +11243,7 @@
         <v/>
       </c>
       <c r="O114" s="5">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P114" s="7">
@@ -11238,7 +11251,7 @@
         <v/>
       </c>
       <c r="R114" s="7">
-        <f>IFERROR(L114 - P114 - VLOOKUP(C114, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L114 - P114 - VLOOKUP(C114, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C114, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S114" t="inlineStr">
@@ -11293,11 +11306,11 @@
         <v/>
       </c>
       <c r="L115" s="7">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M115" s="7">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N115" s="7">
@@ -11305,7 +11318,7 @@
         <v/>
       </c>
       <c r="O115" s="5">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P115" s="7">
@@ -11313,7 +11326,7 @@
         <v/>
       </c>
       <c r="R115" s="7">
-        <f>IFERROR(L115 - P115 - VLOOKUP(C115, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L115 - P115 - VLOOKUP(C115, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C115, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S115" t="inlineStr">
@@ -11368,11 +11381,11 @@
         <v/>
       </c>
       <c r="L116" s="7">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M116" s="7">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N116" s="7">
@@ -11380,7 +11393,7 @@
         <v/>
       </c>
       <c r="O116" s="5">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P116" s="7">
@@ -11388,7 +11401,7 @@
         <v/>
       </c>
       <c r="R116" s="7">
-        <f>IFERROR(L116 - P116 - VLOOKUP(C116, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L116 - P116 - VLOOKUP(C116, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C116, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S116" t="inlineStr">
@@ -11443,11 +11456,11 @@
         <v/>
       </c>
       <c r="L117" s="7">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M117" s="7">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N117" s="7">
@@ -11455,7 +11468,7 @@
         <v/>
       </c>
       <c r="O117" s="5">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P117" s="7">
@@ -11463,7 +11476,7 @@
         <v/>
       </c>
       <c r="R117" s="7">
-        <f>IFERROR(L117 - P117 - VLOOKUP(C117, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L117 - P117 - VLOOKUP(C117, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C117, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S117" t="inlineStr">
@@ -11525,11 +11538,11 @@
         <v/>
       </c>
       <c r="L119" s="7">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M119" s="7">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N119" s="7">
@@ -11537,7 +11550,7 @@
         <v/>
       </c>
       <c r="O119" s="5">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P119" s="7">
@@ -11545,7 +11558,7 @@
         <v/>
       </c>
       <c r="R119" s="7">
-        <f>IFERROR(L119 - P119 - VLOOKUP(C119, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L119 - P119 - VLOOKUP(C119, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C119, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S119" t="inlineStr">
@@ -11600,11 +11613,11 @@
         <v/>
       </c>
       <c r="L120" s="7">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M120" s="7">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N120" s="7">
@@ -11612,7 +11625,7 @@
         <v/>
       </c>
       <c r="O120" s="5">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P120" s="7">
@@ -11620,7 +11633,7 @@
         <v/>
       </c>
       <c r="R120" s="7">
-        <f>IFERROR(L120 - P120 - VLOOKUP(C120, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L120 - P120 - VLOOKUP(C120, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C120, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S120" t="inlineStr">
@@ -11675,11 +11688,11 @@
         <v/>
       </c>
       <c r="L121" s="7">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M121" s="7">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N121" s="7">
@@ -11687,7 +11700,7 @@
         <v/>
       </c>
       <c r="O121" s="5">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P121" s="7">
@@ -11695,7 +11708,7 @@
         <v/>
       </c>
       <c r="R121" s="7">
-        <f>IFERROR(L121 - P121 - VLOOKUP(C121, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L121 - P121 - VLOOKUP(C121, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C121, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S121" t="inlineStr">
@@ -11750,11 +11763,11 @@
         <v/>
       </c>
       <c r="L122" s="7">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M122" s="7">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N122" s="7">
@@ -11762,7 +11775,7 @@
         <v/>
       </c>
       <c r="O122" s="5">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P122" s="7">
@@ -11770,7 +11783,7 @@
         <v/>
       </c>
       <c r="R122" s="7">
-        <f>IFERROR(L122 - P122 - VLOOKUP(C122, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L122 - P122 - VLOOKUP(C122, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C122, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S122" t="inlineStr">
@@ -11825,11 +11838,11 @@
         <v/>
       </c>
       <c r="L123" s="7">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M123" s="7">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N123" s="7">
@@ -11837,7 +11850,7 @@
         <v/>
       </c>
       <c r="O123" s="5">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P123" s="7">
@@ -11845,7 +11858,7 @@
         <v/>
       </c>
       <c r="R123" s="7">
-        <f>IFERROR(L123 - P123 - VLOOKUP(C123, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L123 - P123 - VLOOKUP(C123, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C123, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S123" t="inlineStr">
@@ -11900,11 +11913,11 @@
         <v/>
       </c>
       <c r="L124" s="7">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M124" s="7">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N124" s="7">
@@ -11912,7 +11925,7 @@
         <v/>
       </c>
       <c r="O124" s="5">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P124" s="7">
@@ -11920,7 +11933,7 @@
         <v/>
       </c>
       <c r="R124" s="7">
-        <f>IFERROR(L124 - P124 - VLOOKUP(C124, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L124 - P124 - VLOOKUP(C124, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C124, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S124" t="inlineStr">
@@ -11975,11 +11988,11 @@
         <v/>
       </c>
       <c r="L125" s="7">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M125" s="7">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N125" s="7">
@@ -11987,7 +12000,7 @@
         <v/>
       </c>
       <c r="O125" s="5">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P125" s="7">
@@ -11995,7 +12008,7 @@
         <v/>
       </c>
       <c r="R125" s="7">
-        <f>IFERROR(L125 - P125 - VLOOKUP(C125, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L125 - P125 - VLOOKUP(C125, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C125, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S125" t="inlineStr">
@@ -12050,11 +12063,11 @@
         <v/>
       </c>
       <c r="L126" s="7">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M126" s="7">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N126" s="7">
@@ -12062,7 +12075,7 @@
         <v/>
       </c>
       <c r="O126" s="5">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P126" s="7">
@@ -12070,7 +12083,7 @@
         <v/>
       </c>
       <c r="R126" s="7">
-        <f>IFERROR(L126 - P126 - VLOOKUP(C126, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L126 - P126 - VLOOKUP(C126, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C126, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S126" t="inlineStr">
@@ -12125,11 +12138,11 @@
         <v/>
       </c>
       <c r="L127" s="7">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M127" s="7">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N127" s="7">
@@ -12137,7 +12150,7 @@
         <v/>
       </c>
       <c r="O127" s="5">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P127" s="7">
@@ -12145,7 +12158,7 @@
         <v/>
       </c>
       <c r="R127" s="7">
-        <f>IFERROR(L127 - P127 - VLOOKUP(C127, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L127 - P127 - VLOOKUP(C127, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C127, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S127" t="inlineStr">
@@ -12200,11 +12213,11 @@
         <v/>
       </c>
       <c r="L128" s="7">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M128" s="7">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N128" s="7">
@@ -12212,7 +12225,7 @@
         <v/>
       </c>
       <c r="O128" s="5">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P128" s="7">
@@ -12220,7 +12233,7 @@
         <v/>
       </c>
       <c r="R128" s="7">
-        <f>IFERROR(L128 - P128 - VLOOKUP(C128, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L128 - P128 - VLOOKUP(C128, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C128, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S128" t="inlineStr">
@@ -12275,11 +12288,11 @@
         <v/>
       </c>
       <c r="L129" s="7">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M129" s="7">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N129" s="7">
@@ -12287,7 +12300,7 @@
         <v/>
       </c>
       <c r="O129" s="5">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P129" s="7">
@@ -12295,7 +12308,7 @@
         <v/>
       </c>
       <c r="R129" s="7">
-        <f>IFERROR(L129 - P129 - VLOOKUP(C129, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L129 - P129 - VLOOKUP(C129, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C129, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S129" t="inlineStr">
@@ -12350,11 +12363,11 @@
         <v/>
       </c>
       <c r="L130" s="7">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M130" s="7">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N130" s="7">
@@ -12362,7 +12375,7 @@
         <v/>
       </c>
       <c r="O130" s="5">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P130" s="7">
@@ -12370,7 +12383,7 @@
         <v/>
       </c>
       <c r="R130" s="7">
-        <f>IFERROR(L130 - P130 - VLOOKUP(C130, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L130 - P130 - VLOOKUP(C130, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C130, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S130" t="inlineStr">
@@ -12425,11 +12438,11 @@
         <v/>
       </c>
       <c r="L131" s="7">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M131" s="7">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N131" s="7">
@@ -12437,7 +12450,7 @@
         <v/>
       </c>
       <c r="O131" s="5">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P131" s="7">
@@ -12445,7 +12458,7 @@
         <v/>
       </c>
       <c r="R131" s="7">
-        <f>IFERROR(L131 - P131 - VLOOKUP(C131, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L131 - P131 - VLOOKUP(C131, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C131, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S131" t="inlineStr">
@@ -12500,11 +12513,11 @@
         <v/>
       </c>
       <c r="L132" s="7">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M132" s="7">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N132" s="7">
@@ -12512,7 +12525,7 @@
         <v/>
       </c>
       <c r="O132" s="5">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P132" s="7">
@@ -12520,7 +12533,7 @@
         <v/>
       </c>
       <c r="R132" s="7">
-        <f>IFERROR(L132 - P132 - VLOOKUP(C132, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L132 - P132 - VLOOKUP(C132, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C132, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S132" t="inlineStr">
@@ -12579,11 +12592,11 @@
         <v/>
       </c>
       <c r="L133" s="7">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M133" s="7">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N133" s="7">
@@ -12591,7 +12604,7 @@
         <v/>
       </c>
       <c r="O133" s="5">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P133" s="7">
@@ -12599,7 +12612,7 @@
         <v/>
       </c>
       <c r="R133" s="7">
-        <f>IFERROR(L133 - P133 - VLOOKUP(C133, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L133 - P133 - VLOOKUP(C133, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C133, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S133" t="inlineStr">
@@ -12658,11 +12671,11 @@
         <v/>
       </c>
       <c r="L134" s="7">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M134" s="7">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N134" s="7">
@@ -12670,7 +12683,7 @@
         <v/>
       </c>
       <c r="O134" s="5">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P134" s="7">
@@ -12678,7 +12691,7 @@
         <v/>
       </c>
       <c r="R134" s="7">
-        <f>IFERROR(L134 - P134 - VLOOKUP(C134, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L134 - P134 - VLOOKUP(C134, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C134, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S134" t="inlineStr">
@@ -12737,11 +12750,11 @@
         <v/>
       </c>
       <c r="L135" s="7">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M135" s="7">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N135" s="7">
@@ -12749,7 +12762,7 @@
         <v/>
       </c>
       <c r="O135" s="5">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P135" s="7">
@@ -12757,7 +12770,7 @@
         <v/>
       </c>
       <c r="R135" s="7">
-        <f>IFERROR(L135 - P135 - VLOOKUP(C135, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L135 - P135 - VLOOKUP(C135, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C135, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S135" t="inlineStr">
@@ -12816,11 +12829,11 @@
         <v/>
       </c>
       <c r="L136" s="7">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M136" s="7">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N136" s="7">
@@ -12828,7 +12841,7 @@
         <v/>
       </c>
       <c r="O136" s="5">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P136" s="7">
@@ -12836,7 +12849,7 @@
         <v/>
       </c>
       <c r="R136" s="7">
-        <f>IFERROR(L136 - P136 - VLOOKUP(C136, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L136 - P136 - VLOOKUP(C136, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C136, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S136" t="inlineStr">
@@ -12895,11 +12908,11 @@
         <v/>
       </c>
       <c r="L137" s="7">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$F$34, 4, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="M137" s="7">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$F$34, 3, FALSE), "")</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="N137" s="7">
@@ -12907,7 +12920,7 @@
         <v/>
       </c>
       <c r="O137" s="5">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$F$34, 4, FALSE)*0.3, "")</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="P137" s="7">
@@ -12915,7 +12928,7 @@
         <v/>
       </c>
       <c r="R137" s="7">
-        <f>IFERROR(L137 - P137 - VLOOKUP(C137, characterization!$A$29:$F$34, 6, FALSE), "")</f>
+        <f>IFERROR(L137 - P137 - VLOOKUP(C137, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C137, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
       <c r="S137" t="inlineStr">

--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -122,6 +122,14 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00C00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -3317,6 +3325,11 @@
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="A3:AG3"/>
   </mergeCells>
+  <conditionalFormatting sqref="AF3:AF11">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12999,6 +13012,11 @@
     <mergeCell ref="A140:S140"/>
     <mergeCell ref="A64:S64"/>
   </mergeCells>
+  <conditionalFormatting sqref="R3:R137">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/components/timing_characterization/work/asap7_characterization.xlsx
+++ b/projects/components/timing_characterization/work/asap7_characterization.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -94,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -116,6 +118,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -2508,7 +2513,7 @@
         <f>AC4 + AA4 + AB4</f>
         <v/>
       </c>
-      <c r="AF4" s="7">
+      <c r="AF4" s="10">
         <f>IFERROR(Y4 - AD4 - VLOOKUP(X4, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X4, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -2620,7 +2625,7 @@
         <f>AC5 + AA5 + AB5</f>
         <v/>
       </c>
-      <c r="AF5" s="7">
+      <c r="AF5" s="10">
         <f>IFERROR(Y5 - AD5 - VLOOKUP(X5, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X5, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -2739,7 +2744,7 @@
         <f>AC7 + AA7 + AB7</f>
         <v/>
       </c>
-      <c r="AF7" s="7">
+      <c r="AF7" s="10">
         <f>IFERROR(Y7 - AD7 - VLOOKUP(X7, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X7, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -2852,7 +2857,7 @@
         <f>AC8 + AA8 + AB8</f>
         <v/>
       </c>
-      <c r="AF8" s="7">
+      <c r="AF8" s="10">
         <f>IFERROR(Y8 - AD8 - VLOOKUP(X8, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X8, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -2962,7 +2967,7 @@
         <f>AC9 + AA9 + AB9</f>
         <v/>
       </c>
-      <c r="AF9" s="7">
+      <c r="AF9" s="10">
         <f>IFERROR(Y9 - AD9 - VLOOKUP(X9, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X9, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -3086,7 +3091,7 @@
         <f>AC10 + AA10 + AB10</f>
         <v/>
       </c>
-      <c r="AF10" s="7">
+      <c r="AF10" s="10">
         <f>IFERROR(Y10 - AD10 - VLOOKUP(X10, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X10, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -3210,7 +3215,7 @@
         <f>AC11 + AA11 + AB11</f>
         <v/>
       </c>
-      <c r="AF11" s="7">
+      <c r="AF11" s="10">
         <f>IFERROR(Y11 - AD11 - VLOOKUP(X11, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(X11, characterization!$A$29:$G$34, 7, FALSE), "")</f>
         <v/>
       </c>
@@ -3292,7 +3297,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Grey = derived formula</t>
         </is>
@@ -3340,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S144"/>
+  <dimension ref="A1:P144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3351,17 +3356,14 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="3" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="50" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3407,51 +3409,36 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>local delay TT (ps)</t>
+          <t>target period (ps)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>local delay FF (ps)</t>
+          <t>target corner</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>local delay SS (ps)</t>
+          <t>local delay (ps)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>target period (ps)</t>
+          <t>delay_in (ps)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>target corner</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>target local delay (ps)</t>
-        </is>
-      </c>
+          <t>delay_out (ps)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr"/>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>delay_in (ps)</t>
+          <t>slack (ps)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>delay_out (ps)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr"/>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>slack (ps)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>places it goes (consumer / producer)</t>
         </is>
@@ -3510,42 +3497,30 @@
         </is>
       </c>
       <c r="I4" s="7">
-        <f>F4*characterization!$B$17 + G4*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J4" s="7">
-        <f>F4*characterization!$G$17 + G4*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K4" s="7">
-        <f>F4*characterization!$L$17 + G4*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L4" s="7">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F4*IF(J4="TT",characterization!$B$17,IF(J4="FF",characterization!$G$17,characterization!$L$17))+G4*IF(J4="TT",characterization!$B$15,IF(J4="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L4" s="5">
+        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M4" s="7">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N4" s="7">
-        <f>IF(M4="TT",I4,IF(M4="FF",J4,IF(M4="SS",K4,"")))</f>
-        <v/>
-      </c>
-      <c r="O4" s="5">
-        <f>IFERROR(VLOOKUP(C4, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P4" s="7">
-        <f>O4 + N4</f>
-        <v/>
-      </c>
-      <c r="R4" s="7">
-        <f>IFERROR(L4 - P4 - VLOOKUP(C4, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C4, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S4" t="inlineStr">
+        <f>L4 + K4</f>
+        <v/>
+      </c>
+      <c r="O4" s="10">
+        <f>IFERROR(I4 - M4 - VLOOKUP(C4, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C4, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>from u_channel_fifo.rd_valid in sram_controller_unit</t>
         </is>
@@ -3589,42 +3564,30 @@
         </is>
       </c>
       <c r="I5" s="7">
-        <f>F5*characterization!$B$17 + G5*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J5" s="7">
-        <f>F5*characterization!$G$17 + G5*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K5" s="7">
-        <f>F5*characterization!$L$17 + G5*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L5" s="7">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F5*IF(J5="TT",characterization!$B$17,IF(J5="FF",characterization!$G$17,characterization!$L$17))+G5*IF(J5="TT",characterization!$B$15,IF(J5="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L5" s="5">
+        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M5" s="7">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N5" s="7">
-        <f>IF(M5="TT",I5,IF(M5="FF",J5,IF(M5="SS",K5,"")))</f>
-        <v/>
-      </c>
-      <c r="O5" s="5">
-        <f>IFERROR(VLOOKUP(C5, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P5" s="7">
-        <f>O5 + N5</f>
-        <v/>
-      </c>
-      <c r="R5" s="7">
-        <f>IFERROR(L5 - P5 - VLOOKUP(C5, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C5, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S5" t="inlineStr">
+        <f>L5 + K5</f>
+        <v/>
+      </c>
+      <c r="O5" s="10">
+        <f>IFERROR(I5 - M5 - VLOOKUP(C5, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C5, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>from u_channel_fifo.rd_data</t>
         </is>
@@ -3664,42 +3627,30 @@
         </is>
       </c>
       <c r="I6" s="7">
-        <f>F6*characterization!$B$17 + G6*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J6" s="7">
-        <f>F6*characterization!$G$17 + G6*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K6" s="7">
-        <f>F6*characterization!$L$17 + G6*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L6" s="7">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F6*IF(J6="TT",characterization!$B$17,IF(J6="FF",characterization!$G$17,characterization!$L$17))+G6*IF(J6="TT",characterization!$B$15,IF(J6="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L6" s="5">
+        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M6" s="7">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N6" s="7">
-        <f>IF(M6="TT",I6,IF(M6="FF",J6,IF(M6="SS",K6,"")))</f>
-        <v/>
-      </c>
-      <c r="O6" s="5">
-        <f>IFERROR(VLOOKUP(C6, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P6" s="7">
-        <f>O6 + N6</f>
-        <v/>
-      </c>
-      <c r="R6" s="7">
-        <f>IFERROR(L6 - P6 - VLOOKUP(C6, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C6, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+        <f>L6 + K6</f>
+        <v/>
+      </c>
+      <c r="O6" s="10">
+        <f>IFERROR(I6 - M6 - VLOOKUP(C6, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C6, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>internal: only local flop; gates the skid push</t>
         </is>
@@ -3739,42 +3690,30 @@
         </is>
       </c>
       <c r="I7" s="7">
-        <f>F7*characterization!$B$17 + G7*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J7" s="7">
-        <f>F7*characterization!$G$17 + G7*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K7" s="7">
-        <f>F7*characterization!$L$17 + G7*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F7*IF(J7="TT",characterization!$B$17,IF(J7="FF",characterization!$G$17,characterization!$L$17))+G7*IF(J7="TT",characterization!$B$15,IF(J7="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L7" s="5">
+        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M7" s="7">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N7" s="7">
-        <f>IF(M7="TT",I7,IF(M7="FF",J7,IF(M7="SS",K7,"")))</f>
-        <v/>
-      </c>
-      <c r="O7" s="5">
-        <f>IFERROR(VLOOKUP(C7, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P7" s="7">
-        <f>O7 + N7</f>
-        <v/>
-      </c>
-      <c r="R7" s="7">
-        <f>IFERROR(L7 - P7 - VLOOKUP(C7, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C7, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr">
+        <f>L7 + K7</f>
+        <v/>
+      </c>
+      <c r="O7" s="10">
+        <f>IFERROR(I7 - M7 - VLOOKUP(C7, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C7, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>to u_channel_fifo.rd_ready</t>
         </is>
@@ -3818,42 +3757,30 @@
         </is>
       </c>
       <c r="I8" s="7">
-        <f>F8*characterization!$B$17 + G8*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J8" s="7">
-        <f>F8*characterization!$G$17 + G8*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K8" s="7">
-        <f>F8*characterization!$L$17 + G8*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F8*IF(J8="TT",characterization!$B$17,IF(J8="FF",characterization!$G$17,characterization!$L$17))+G8*IF(J8="TT",characterization!$B$15,IF(J8="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L8" s="5">
+        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M8" s="7">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N8" s="7">
-        <f>IF(M8="TT",I8,IF(M8="FF",J8,IF(M8="SS",K8,"")))</f>
-        <v/>
-      </c>
-      <c r="O8" s="5">
-        <f>IFERROR(VLOOKUP(C8, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P8" s="7">
-        <f>O8 + N8</f>
-        <v/>
-      </c>
-      <c r="R8" s="7">
-        <f>IFERROR(L8 - P8 - VLOOKUP(C8, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C8, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr">
+        <f>L8 + K8</f>
+        <v/>
+      </c>
+      <c r="O8" s="10">
+        <f>IFERROR(I8 - M8 - VLOOKUP(C8, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C8, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>to sram_controller_unit.axi_wr_sram_valid -&gt; axi_write_engine</t>
         </is>
@@ -3897,42 +3824,30 @@
         </is>
       </c>
       <c r="I9" s="7">
-        <f>F9*characterization!$B$17 + G9*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J9" s="7">
-        <f>F9*characterization!$G$17 + G9*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K9" s="7">
-        <f>F9*characterization!$L$17 + G9*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L9" s="7">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F9*IF(J9="TT",characterization!$B$17,IF(J9="FF",characterization!$G$17,characterization!$L$17))+G9*IF(J9="TT",characterization!$B$15,IF(J9="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L9" s="5">
+        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M9" s="7">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N9" s="7">
-        <f>IF(M9="TT",I9,IF(M9="FF",J9,IF(M9="SS",K9,"")))</f>
-        <v/>
-      </c>
-      <c r="O9" s="5">
-        <f>IFERROR(VLOOKUP(C9, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P9" s="7">
-        <f>O9 + N9</f>
-        <v/>
-      </c>
-      <c r="R9" s="7">
-        <f>IFERROR(L9 - P9 - VLOOKUP(C9, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C9, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr">
+        <f>L9 + K9</f>
+        <v/>
+      </c>
+      <c r="O9" s="10">
+        <f>IFERROR(I9 - M9 - VLOOKUP(C9, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C9, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>to sram_controller_unit.axi_wr_sram_data -&gt; axi_write_engine</t>
         </is>
@@ -3976,42 +3891,30 @@
         </is>
       </c>
       <c r="I10" s="7">
-        <f>F10*characterization!$B$17 + G10*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J10" s="7">
-        <f>F10*characterization!$G$17 + G10*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K10" s="7">
-        <f>F10*characterization!$L$17 + G10*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F10*IF(J10="TT",characterization!$B$17,IF(J10="FF",characterization!$G$17,characterization!$L$17))+G10*IF(J10="TT",characterization!$B$15,IF(J10="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L10" s="5">
+        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M10" s="7">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N10" s="7">
-        <f>IF(M10="TT",I10,IF(M10="FF",J10,IF(M10="SS",K10,"")))</f>
-        <v/>
-      </c>
-      <c r="O10" s="5">
-        <f>IFERROR(VLOOKUP(C10, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P10" s="7">
-        <f>O10 + N10</f>
-        <v/>
-      </c>
-      <c r="R10" s="7">
-        <f>IFERROR(L10 - P10 - VLOOKUP(C10, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C10, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S10" t="inlineStr">
+        <f>L10 + K10</f>
+        <v/>
+      </c>
+      <c r="O10" s="10">
+        <f>IFERROR(I10 - M10 - VLOOKUP(C10, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C10, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>from axi_write_engine via sram_controller_unit</t>
         </is>
@@ -4055,42 +3958,30 @@
         </is>
       </c>
       <c r="I11" s="7">
-        <f>F11*characterization!$B$17 + G11*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J11" s="7">
-        <f>F11*characterization!$G$17 + G11*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K11" s="7">
-        <f>F11*characterization!$L$17 + G11*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L11" s="7">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F11*IF(J11="TT",characterization!$B$17,IF(J11="FF",characterization!$G$17,characterization!$L$17))+G11*IF(J11="TT",characterization!$B$15,IF(J11="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L11" s="5">
+        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M11" s="7">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N11" s="7">
-        <f>IF(M11="TT",I11,IF(M11="FF",J11,IF(M11="SS",K11,"")))</f>
-        <v/>
-      </c>
-      <c r="O11" s="5">
-        <f>IFERROR(VLOOKUP(C11, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P11" s="7">
-        <f>O11 + N11</f>
-        <v/>
-      </c>
-      <c r="R11" s="7">
-        <f>IFERROR(L11 - P11 - VLOOKUP(C11, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C11, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S11" t="inlineStr">
+        <f>L11 + K11</f>
+        <v/>
+      </c>
+      <c r="O11" s="10">
+        <f>IFERROR(I11 - M11 - VLOOKUP(C11, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C11, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>to scheduler (drain-IP backpressure)</t>
         </is>
@@ -4130,42 +4021,30 @@
         </is>
       </c>
       <c r="I12" s="7">
-        <f>F12*characterization!$B$17 + G12*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J12" s="7">
-        <f>F12*characterization!$G$17 + G12*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K12" s="7">
-        <f>F12*characterization!$L$17 + G12*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L12" s="7">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F12*IF(J12="TT",characterization!$B$17,IF(J12="FF",characterization!$G$17,characterization!$L$17))+G12*IF(J12="TT",characterization!$B$15,IF(J12="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L12" s="5">
+        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M12" s="7">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N12" s="7">
-        <f>IF(M12="TT",I12,IF(M12="FF",J12,IF(M12="SS",K12,"")))</f>
-        <v/>
-      </c>
-      <c r="O12" s="5">
-        <f>IFERROR(VLOOKUP(C12, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P12" s="7">
-        <f>O12 + N12</f>
-        <v/>
-      </c>
-      <c r="R12" s="7">
-        <f>IFERROR(L12 - P12 - VLOOKUP(C12, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C12, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S12" t="inlineStr">
+        <f>L12 + K12</f>
+        <v/>
+      </c>
+      <c r="O12" s="10">
+        <f>IFERROR(I12 - M12 - VLOOKUP(C12, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C12, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>debug observability</t>
         </is>
@@ -4212,42 +4091,30 @@
         </is>
       </c>
       <c r="I14" s="7">
-        <f>F14*characterization!$B$17 + G14*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J14" s="7">
-        <f>F14*characterization!$G$17 + G14*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K14" s="7">
-        <f>F14*characterization!$L$17 + G14*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L14" s="7">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F14*IF(J14="TT",characterization!$B$17,IF(J14="FF",characterization!$G$17,characterization!$L$17))+G14*IF(J14="TT",characterization!$B$15,IF(J14="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L14" s="5">
+        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M14" s="7">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N14" s="7">
-        <f>IF(M14="TT",I14,IF(M14="FF",J14,IF(M14="SS",K14,"")))</f>
-        <v/>
-      </c>
-      <c r="O14" s="5">
-        <f>IFERROR(VLOOKUP(C14, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P14" s="7">
-        <f>O14 + N14</f>
-        <v/>
-      </c>
-      <c r="R14" s="7">
-        <f>IFERROR(L14 - P14 - VLOOKUP(C14, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C14, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S14" t="inlineStr">
+        <f>L14 + K14</f>
+        <v/>
+      </c>
+      <c r="O14" s="10">
+        <f>IFERROR(I14 - M14 - VLOOKUP(C14, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C14, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>from axi_read_engine (allocate request)</t>
         </is>
@@ -4287,42 +4154,30 @@
         </is>
       </c>
       <c r="I15" s="7">
-        <f>F15*characterization!$B$17 + G15*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J15" s="7">
-        <f>F15*characterization!$G$17 + G15*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K15" s="7">
-        <f>F15*characterization!$L$17 + G15*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L15" s="7">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F15*IF(J15="TT",characterization!$B$17,IF(J15="FF",characterization!$G$17,characterization!$L$17))+G15*IF(J15="TT",characterization!$B$15,IF(J15="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L15" s="5">
+        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M15" s="7">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N15" s="7">
-        <f>IF(M15="TT",I15,IF(M15="FF",J15,IF(M15="SS",K15,"")))</f>
-        <v/>
-      </c>
-      <c r="O15" s="5">
-        <f>IFERROR(VLOOKUP(C15, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P15" s="7">
-        <f>O15 + N15</f>
-        <v/>
-      </c>
-      <c r="R15" s="7">
-        <f>IFERROR(L15 - P15 - VLOOKUP(C15, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C15, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S15" t="inlineStr">
+        <f>L15 + K15</f>
+        <v/>
+      </c>
+      <c r="O15" s="10">
+        <f>IFERROR(I15 - M15 - VLOOKUP(C15, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C15, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>from axi_read_engine</t>
         </is>
@@ -4362,42 +4217,30 @@
         </is>
       </c>
       <c r="I16" s="7">
-        <f>F16*characterization!$B$17 + G16*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J16" s="7">
-        <f>F16*characterization!$G$17 + G16*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K16" s="7">
-        <f>F16*characterization!$L$17 + G16*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L16" s="7">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F16*IF(J16="TT",characterization!$B$17,IF(J16="FF",characterization!$G$17,characterization!$L$17))+G16*IF(J16="TT",characterization!$B$15,IF(J16="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L16" s="5">
+        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M16" s="7">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N16" s="7">
-        <f>IF(M16="TT",I16,IF(M16="FF",J16,IF(M16="SS",K16,"")))</f>
-        <v/>
-      </c>
-      <c r="O16" s="5">
-        <f>IFERROR(VLOOKUP(C16, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P16" s="7">
-        <f>O16 + N16</f>
-        <v/>
-      </c>
-      <c r="R16" s="7">
-        <f>IFERROR(L16 - P16 - VLOOKUP(C16, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C16, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr">
+        <f>L16 + K16</f>
+        <v/>
+      </c>
+      <c r="O16" s="10">
+        <f>IFERROR(I16 - M16 - VLOOKUP(C16, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C16, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>from sram_controller_unit (release event)</t>
         </is>
@@ -4437,42 +4280,30 @@
         </is>
       </c>
       <c r="I17" s="7">
-        <f>F17*characterization!$B$17 + G17*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J17" s="7">
-        <f>F17*characterization!$G$17 + G17*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K17" s="7">
-        <f>F17*characterization!$L$17 + G17*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L17" s="7">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F17*IF(J17="TT",characterization!$B$17,IF(J17="FF",characterization!$G$17,characterization!$L$17))+G17*IF(J17="TT",characterization!$B$15,IF(J17="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L17" s="5">
+        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M17" s="7">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N17" s="7">
-        <f>IF(M17="TT",I17,IF(M17="FF",J17,IF(M17="SS",K17,"")))</f>
-        <v/>
-      </c>
-      <c r="O17" s="5">
-        <f>IFERROR(VLOOKUP(C17, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P17" s="7">
-        <f>O17 + N17</f>
-        <v/>
-      </c>
-      <c r="R17" s="7">
-        <f>IFERROR(L17 - P17 - VLOOKUP(C17, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C17, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S17" t="inlineStr">
+        <f>L17 + K17</f>
+        <v/>
+      </c>
+      <c r="O17" s="10">
+        <f>IFERROR(I17 - M17 - VLOOKUP(C17, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C17, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>internal: wr_ptr - rd_ptr = space_free</t>
         </is>
@@ -4512,42 +4343,30 @@
         </is>
       </c>
       <c r="I18" s="7">
-        <f>F18*characterization!$B$17 + G18*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J18" s="7">
-        <f>F18*characterization!$G$17 + G18*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K18" s="7">
-        <f>F18*characterization!$L$17 + G18*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L18" s="7">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F18*IF(J18="TT",characterization!$B$17,IF(J18="FF",characterization!$G$17,characterization!$L$17))+G18*IF(J18="TT",characterization!$B$15,IF(J18="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L18" s="5">
+        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M18" s="7">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N18" s="7">
-        <f>IF(M18="TT",I18,IF(M18="FF",J18,IF(M18="SS",K18,"")))</f>
-        <v/>
-      </c>
-      <c r="O18" s="5">
-        <f>IFERROR(VLOOKUP(C18, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P18" s="7">
-        <f>O18 + N18</f>
-        <v/>
-      </c>
-      <c r="R18" s="7">
-        <f>IFERROR(L18 - P18 - VLOOKUP(C18, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C18, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S18" t="inlineStr">
+        <f>L18 + K18</f>
+        <v/>
+      </c>
+      <c r="O18" s="10">
+        <f>IFERROR(I18 - M18 - VLOOKUP(C18, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C18, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>internal: subtractor into space_free</t>
         </is>
@@ -4587,42 +4406,30 @@
         </is>
       </c>
       <c r="I19" s="7">
-        <f>F19*characterization!$B$17 + G19*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J19" s="7">
-        <f>F19*characterization!$G$17 + G19*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K19" s="7">
-        <f>F19*characterization!$L$17 + G19*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L19" s="7">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F19*IF(J19="TT",characterization!$B$17,IF(J19="FF",characterization!$G$17,characterization!$L$17))+G19*IF(J19="TT",characterization!$B$15,IF(J19="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L19" s="5">
+        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M19" s="7">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N19" s="7">
-        <f>IF(M19="TT",I19,IF(M19="FF",J19,IF(M19="SS",K19,"")))</f>
-        <v/>
-      </c>
-      <c r="O19" s="5">
-        <f>IFERROR(VLOOKUP(C19, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P19" s="7">
-        <f>O19 + N19</f>
-        <v/>
-      </c>
-      <c r="R19" s="7">
-        <f>IFERROR(L19 - P19 - VLOOKUP(C19, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C19, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S19" t="inlineStr">
+        <f>L19 + K19</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>IFERROR(I19 - M19 - VLOOKUP(C19, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C19, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>internal: cmp against DEPTH for full/almost_full flops</t>
         </is>
@@ -4662,42 +4469,30 @@
         </is>
       </c>
       <c r="I20" s="7">
-        <f>F20*characterization!$B$17 + G20*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J20" s="7">
-        <f>F20*characterization!$G$17 + G20*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K20" s="7">
-        <f>F20*characterization!$L$17 + G20*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L20" s="7">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F20*IF(J20="TT",characterization!$B$17,IF(J20="FF",characterization!$G$17,characterization!$L$17))+G20*IF(J20="TT",characterization!$B$15,IF(J20="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L20" s="5">
+        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M20" s="7">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N20" s="7">
-        <f>IF(M20="TT",I20,IF(M20="FF",J20,IF(M20="SS",K20,"")))</f>
-        <v/>
-      </c>
-      <c r="O20" s="5">
-        <f>IFERROR(VLOOKUP(C20, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P20" s="7">
-        <f>O20 + N20</f>
-        <v/>
-      </c>
-      <c r="R20" s="7">
-        <f>IFERROR(L20 - P20 - VLOOKUP(C20, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C20, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S20" t="inlineStr">
+        <f>L20 + K20</f>
+        <v/>
+      </c>
+      <c r="O20" s="10">
+        <f>IFERROR(I20 - M20 - VLOOKUP(C20, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C20, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>to axi_read_engine (sram_alloc_space_free)</t>
         </is>
@@ -4737,42 +4532,30 @@
         </is>
       </c>
       <c r="I21" s="7">
-        <f>F21*characterization!$B$17 + G21*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J21" s="7">
-        <f>F21*characterization!$G$17 + G21*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K21" s="7">
-        <f>F21*characterization!$L$17 + G21*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L21" s="7">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F21*IF(J21="TT",characterization!$B$17,IF(J21="FF",characterization!$G$17,characterization!$L$17))+G21*IF(J21="TT",characterization!$B$15,IF(J21="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L21" s="5">
+        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M21" s="7">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N21" s="7">
-        <f>IF(M21="TT",I21,IF(M21="FF",J21,IF(M21="SS",K21,"")))</f>
-        <v/>
-      </c>
-      <c r="O21" s="5">
-        <f>IFERROR(VLOOKUP(C21, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P21" s="7">
-        <f>O21 + N21</f>
-        <v/>
-      </c>
-      <c r="R21" s="7">
-        <f>IFERROR(L21 - P21 - VLOOKUP(C21, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C21, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S21" t="inlineStr">
+        <f>L21 + K21</f>
+        <v/>
+      </c>
+      <c r="O21" s="10">
+        <f>IFERROR(I21 - M21 - VLOOKUP(C21, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C21, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>to axi_read_engine (back-pressure)</t>
         </is>
@@ -4812,42 +4595,30 @@
         </is>
       </c>
       <c r="I22" s="7">
-        <f>F22*characterization!$B$17 + G22*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J22" s="7">
-        <f>F22*characterization!$G$17 + G22*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K22" s="7">
-        <f>F22*characterization!$L$17 + G22*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L22" s="7">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F22*IF(J22="TT",characterization!$B$17,IF(J22="FF",characterization!$G$17,characterization!$L$17))+G22*IF(J22="TT",characterization!$B$15,IF(J22="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L22" s="5">
+        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M22" s="7">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N22" s="7">
-        <f>IF(M22="TT",I22,IF(M22="FF",J22,IF(M22="SS",K22,"")))</f>
-        <v/>
-      </c>
-      <c r="O22" s="5">
-        <f>IFERROR(VLOOKUP(C22, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P22" s="7">
-        <f>O22 + N22</f>
-        <v/>
-      </c>
-      <c r="R22" s="7">
-        <f>IFERROR(L22 - P22 - VLOOKUP(C22, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C22, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S22" t="inlineStr">
+        <f>L22 + K22</f>
+        <v/>
+      </c>
+      <c r="O22" s="10">
+        <f>IFERROR(I22 - M22 - VLOOKUP(C22, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C22, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>to axi_read_engine (threshold)</t>
         </is>
@@ -4894,42 +4665,30 @@
         </is>
       </c>
       <c r="I24" s="7">
-        <f>F24*characterization!$B$17 + G24*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J24" s="7">
-        <f>F24*characterization!$G$17 + G24*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K24" s="7">
-        <f>F24*characterization!$L$17 + G24*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L24" s="7">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F24*IF(J24="TT",characterization!$B$17,IF(J24="FF",characterization!$G$17,characterization!$L$17))+G24*IF(J24="TT",characterization!$B$15,IF(J24="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L24" s="5">
+        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M24" s="7">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N24" s="7">
-        <f>IF(M24="TT",I24,IF(M24="FF",J24,IF(M24="SS",K24,"")))</f>
-        <v/>
-      </c>
-      <c r="O24" s="5">
-        <f>IFERROR(VLOOKUP(C24, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P24" s="7">
-        <f>O24 + N24</f>
-        <v/>
-      </c>
-      <c r="R24" s="7">
-        <f>IFERROR(L24 - P24 - VLOOKUP(C24, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C24, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S24" t="inlineStr">
+        <f>L24 + K24</f>
+        <v/>
+      </c>
+      <c r="O24" s="10">
+        <f>IFERROR(I24 - M24 - VLOOKUP(C24, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C24, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>from u_channel_fifo handshake in sram_controller_unit</t>
         </is>
@@ -4969,42 +4728,30 @@
         </is>
       </c>
       <c r="I25" s="7">
-        <f>F25*characterization!$B$17 + G25*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J25" s="7">
-        <f>F25*characterization!$G$17 + G25*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K25" s="7">
-        <f>F25*characterization!$L$17 + G25*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L25" s="7">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F25*IF(J25="TT",characterization!$B$17,IF(J25="FF",characterization!$G$17,characterization!$L$17))+G25*IF(J25="TT",characterization!$B$15,IF(J25="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L25" s="5">
+        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M25" s="7">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N25" s="7">
-        <f>IF(M25="TT",I25,IF(M25="FF",J25,IF(M25="SS",K25,"")))</f>
-        <v/>
-      </c>
-      <c r="O25" s="5">
-        <f>IFERROR(VLOOKUP(C25, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P25" s="7">
-        <f>O25 + N25</f>
-        <v/>
-      </c>
-      <c r="R25" s="7">
-        <f>IFERROR(L25 - P25 - VLOOKUP(C25, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C25, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S25" t="inlineStr">
+        <f>L25 + K25</f>
+        <v/>
+      </c>
+      <c r="O25" s="10">
+        <f>IFERROR(I25 - M25 - VLOOKUP(C25, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C25, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>from axi_write_engine (drain reservation)</t>
         </is>
@@ -5044,42 +4791,30 @@
         </is>
       </c>
       <c r="I26" s="7">
-        <f>F26*characterization!$B$17 + G26*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J26" s="7">
-        <f>F26*characterization!$G$17 + G26*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K26" s="7">
-        <f>F26*characterization!$L$17 + G26*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L26" s="7">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F26*IF(J26="TT",characterization!$B$17,IF(J26="FF",characterization!$G$17,characterization!$L$17))+G26*IF(J26="TT",characterization!$B$15,IF(J26="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L26" s="5">
+        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M26" s="7">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N26" s="7">
-        <f>IF(M26="TT",I26,IF(M26="FF",J26,IF(M26="SS",K26,"")))</f>
-        <v/>
-      </c>
-      <c r="O26" s="5">
-        <f>IFERROR(VLOOKUP(C26, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P26" s="7">
-        <f>O26 + N26</f>
-        <v/>
-      </c>
-      <c r="R26" s="7">
-        <f>IFERROR(L26 - P26 - VLOOKUP(C26, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C26, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S26" t="inlineStr">
+        <f>L26 + K26</f>
+        <v/>
+      </c>
+      <c r="O26" s="10">
+        <f>IFERROR(I26 - M26 - VLOOKUP(C26, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C26, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>from axi_write_engine</t>
         </is>
@@ -5119,42 +4854,30 @@
         </is>
       </c>
       <c r="I27" s="7">
-        <f>F27*characterization!$B$17 + G27*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J27" s="7">
-        <f>F27*characterization!$G$17 + G27*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K27" s="7">
-        <f>F27*characterization!$L$17 + G27*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L27" s="7">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F27*IF(J27="TT",characterization!$B$17,IF(J27="FF",characterization!$G$17,characterization!$L$17))+G27*IF(J27="TT",characterization!$B$15,IF(J27="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L27" s="5">
+        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M27" s="7">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N27" s="7">
-        <f>IF(M27="TT",I27,IF(M27="FF",J27,IF(M27="SS",K27,"")))</f>
-        <v/>
-      </c>
-      <c r="O27" s="5">
-        <f>IFERROR(VLOOKUP(C27, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P27" s="7">
-        <f>O27 + N27</f>
-        <v/>
-      </c>
-      <c r="R27" s="7">
-        <f>IFERROR(L27 - P27 - VLOOKUP(C27, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C27, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S27" t="inlineStr">
+        <f>L27 + K27</f>
+        <v/>
+      </c>
+      <c r="O27" s="10">
+        <f>IFERROR(I27 - M27 - VLOOKUP(C27, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C27, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>internal: wr_ptr - rd_ptr = data_available</t>
         </is>
@@ -5194,42 +4917,30 @@
         </is>
       </c>
       <c r="I28" s="7">
-        <f>F28*characterization!$B$17 + G28*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J28" s="7">
-        <f>F28*characterization!$G$17 + G28*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K28" s="7">
-        <f>F28*characterization!$L$17 + G28*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L28" s="7">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F28*IF(J28="TT",characterization!$B$17,IF(J28="FF",characterization!$G$17,characterization!$L$17))+G28*IF(J28="TT",characterization!$B$15,IF(J28="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L28" s="5">
+        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M28" s="7">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N28" s="7">
-        <f>IF(M28="TT",I28,IF(M28="FF",J28,IF(M28="SS",K28,"")))</f>
-        <v/>
-      </c>
-      <c r="O28" s="5">
-        <f>IFERROR(VLOOKUP(C28, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P28" s="7">
-        <f>O28 + N28</f>
-        <v/>
-      </c>
-      <c r="R28" s="7">
-        <f>IFERROR(L28 - P28 - VLOOKUP(C28, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C28, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S28" t="inlineStr">
+        <f>L28 + K28</f>
+        <v/>
+      </c>
+      <c r="O28" s="10">
+        <f>IFERROR(I28 - M28 - VLOOKUP(C28, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C28, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>internal: subtractor into data_available</t>
         </is>
@@ -5269,42 +4980,30 @@
         </is>
       </c>
       <c r="I29" s="7">
-        <f>F29*characterization!$B$17 + G29*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J29" s="7">
-        <f>F29*characterization!$G$17 + G29*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K29" s="7">
-        <f>F29*characterization!$L$17 + G29*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L29" s="7">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F29*IF(J29="TT",characterization!$B$17,IF(J29="FF",characterization!$G$17,characterization!$L$17))+G29*IF(J29="TT",characterization!$B$15,IF(J29="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L29" s="5">
+        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M29" s="7">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N29" s="7">
-        <f>IF(M29="TT",I29,IF(M29="FF",J29,IF(M29="SS",K29,"")))</f>
-        <v/>
-      </c>
-      <c r="O29" s="5">
-        <f>IFERROR(VLOOKUP(C29, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P29" s="7">
-        <f>O29 + N29</f>
-        <v/>
-      </c>
-      <c r="R29" s="7">
-        <f>IFERROR(L29 - P29 - VLOOKUP(C29, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C29, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S29" t="inlineStr">
+        <f>L29 + K29</f>
+        <v/>
+      </c>
+      <c r="O29" s="10">
+        <f>IFERROR(I29 - M29 - VLOOKUP(C29, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C29, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>internal: cmp 0 / cmp DEPTH for empty / full flops</t>
         </is>
@@ -5344,42 +5043,30 @@
         </is>
       </c>
       <c r="I30" s="7">
-        <f>F30*characterization!$B$17 + G30*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J30" s="7">
-        <f>F30*characterization!$G$17 + G30*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K30" s="7">
-        <f>F30*characterization!$L$17 + G30*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L30" s="7">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F30*IF(J30="TT",characterization!$B$17,IF(J30="FF",characterization!$G$17,characterization!$L$17))+G30*IF(J30="TT",characterization!$B$15,IF(J30="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L30" s="5">
+        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M30" s="7">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N30" s="7">
-        <f>IF(M30="TT",I30,IF(M30="FF",J30,IF(M30="SS",K30,"")))</f>
-        <v/>
-      </c>
-      <c r="O30" s="5">
-        <f>IFERROR(VLOOKUP(C30, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P30" s="7">
-        <f>O30 + N30</f>
-        <v/>
-      </c>
-      <c r="R30" s="7">
-        <f>IFERROR(L30 - P30 - VLOOKUP(C30, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C30, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S30" t="inlineStr">
+        <f>L30 + K30</f>
+        <v/>
+      </c>
+      <c r="O30" s="10">
+        <f>IFERROR(I30 - M30 - VLOOKUP(C30, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C30, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -5419,42 +5106,30 @@
         </is>
       </c>
       <c r="I31" s="7">
-        <f>F31*characterization!$B$17 + G31*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J31" s="7">
-        <f>F31*characterization!$G$17 + G31*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K31" s="7">
-        <f>F31*characterization!$L$17 + G31*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L31" s="7">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F31*IF(J31="TT",characterization!$B$17,IF(J31="FF",characterization!$G$17,characterization!$L$17))+G31*IF(J31="TT",characterization!$B$15,IF(J31="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L31" s="5">
+        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M31" s="7">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N31" s="7">
-        <f>IF(M31="TT",I31,IF(M31="FF",J31,IF(M31="SS",K31,"")))</f>
-        <v/>
-      </c>
-      <c r="O31" s="5">
-        <f>IFERROR(VLOOKUP(C31, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P31" s="7">
-        <f>O31 + N31</f>
-        <v/>
-      </c>
-      <c r="R31" s="7">
-        <f>IFERROR(L31 - P31 - VLOOKUP(C31, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C31, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S31" t="inlineStr">
+        <f>L31 + K31</f>
+        <v/>
+      </c>
+      <c r="O31" s="10">
+        <f>IFERROR(I31 - M31 - VLOOKUP(C31, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C31, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>to axi_write_engine (no data)</t>
         </is>
@@ -5494,42 +5169,30 @@
         </is>
       </c>
       <c r="I32" s="7">
-        <f>F32*characterization!$B$17 + G32*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J32" s="7">
-        <f>F32*characterization!$G$17 + G32*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K32" s="7">
-        <f>F32*characterization!$L$17 + G32*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L32" s="7">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F32*IF(J32="TT",characterization!$B$17,IF(J32="FF",characterization!$G$17,characterization!$L$17))+G32*IF(J32="TT",characterization!$B$15,IF(J32="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L32" s="5">
+        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M32" s="7">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N32" s="7">
-        <f>IF(M32="TT",I32,IF(M32="FF",J32,IF(M32="SS",K32,"")))</f>
-        <v/>
-      </c>
-      <c r="O32" s="5">
-        <f>IFERROR(VLOOKUP(C32, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P32" s="7">
-        <f>O32 + N32</f>
-        <v/>
-      </c>
-      <c r="R32" s="7">
-        <f>IFERROR(L32 - P32 - VLOOKUP(C32, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C32, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S32" t="inlineStr">
+        <f>L32 + K32</f>
+        <v/>
+      </c>
+      <c r="O32" s="10">
+        <f>IFERROR(I32 - M32 - VLOOKUP(C32, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C32, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>to sram_controller_unit (back-pressure)</t>
         </is>
@@ -5576,42 +5239,30 @@
         </is>
       </c>
       <c r="I34" s="7">
-        <f>F34*characterization!$B$17 + G34*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J34" s="7">
-        <f>F34*characterization!$G$17 + G34*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K34" s="7">
-        <f>F34*characterization!$L$17 + G34*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L34" s="7">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F34*IF(J34="TT",characterization!$B$17,IF(J34="FF",characterization!$G$17,characterization!$L$17))+G34*IF(J34="TT",characterization!$B$15,IF(J34="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L34" s="5">
+        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M34" s="7">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N34" s="7">
-        <f>IF(M34="TT",I34,IF(M34="FF",J34,IF(M34="SS",K34,"")))</f>
-        <v/>
-      </c>
-      <c r="O34" s="5">
-        <f>IFERROR(VLOOKUP(C34, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P34" s="7">
-        <f>O34 + N34</f>
-        <v/>
-      </c>
-      <c r="R34" s="7">
-        <f>IFERROR(L34 - P34 - VLOOKUP(C34, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C34, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S34" t="inlineStr">
+        <f>L34 + K34</f>
+        <v/>
+      </c>
+      <c r="O34" s="10">
+        <f>IFERROR(I34 - M34 - VLOOKUP(C34, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C34, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>from axi_read_engine (reserve burst space)</t>
         </is>
@@ -5651,42 +5302,30 @@
         </is>
       </c>
       <c r="I35" s="7">
-        <f>F35*characterization!$B$17 + G35*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J35" s="7">
-        <f>F35*characterization!$G$17 + G35*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K35" s="7">
-        <f>F35*characterization!$L$17 + G35*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L35" s="7">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F35*IF(J35="TT",characterization!$B$17,IF(J35="FF",characterization!$G$17,characterization!$L$17))+G35*IF(J35="TT",characterization!$B$15,IF(J35="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L35" s="5">
+        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M35" s="7">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N35" s="7">
-        <f>IF(M35="TT",I35,IF(M35="FF",J35,IF(M35="SS",K35,"")))</f>
-        <v/>
-      </c>
-      <c r="O35" s="5">
-        <f>IFERROR(VLOOKUP(C35, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P35" s="7">
-        <f>O35 + N35</f>
-        <v/>
-      </c>
-      <c r="R35" s="7">
-        <f>IFERROR(L35 - P35 - VLOOKUP(C35, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C35, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S35" t="inlineStr">
+        <f>L35 + K35</f>
+        <v/>
+      </c>
+      <c r="O35" s="10">
+        <f>IFERROR(I35 - M35 - VLOOKUP(C35, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C35, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>from axi_read_engine</t>
         </is>
@@ -5726,42 +5365,30 @@
         </is>
       </c>
       <c r="I36" s="7">
-        <f>F36*characterization!$B$17 + G36*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J36" s="7">
-        <f>F36*characterization!$G$17 + G36*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K36" s="7">
-        <f>F36*characterization!$L$17 + G36*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L36" s="7">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F36*IF(J36="TT",characterization!$B$17,IF(J36="FF",characterization!$G$17,characterization!$L$17))+G36*IF(J36="TT",characterization!$B$15,IF(J36="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L36" s="5">
+        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M36" s="7">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N36" s="7">
-        <f>IF(M36="TT",I36,IF(M36="FF",J36,IF(M36="SS",K36,"")))</f>
-        <v/>
-      </c>
-      <c r="O36" s="5">
-        <f>IFERROR(VLOOKUP(C36, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P36" s="7">
-        <f>O36 + N36</f>
-        <v/>
-      </c>
-      <c r="R36" s="7">
-        <f>IFERROR(L36 - P36 - VLOOKUP(C36, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C36, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S36" t="inlineStr">
+        <f>L36 + K36</f>
+        <v/>
+      </c>
+      <c r="O36" s="10">
+        <f>IFERROR(I36 - M36 - VLOOKUP(C36, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C36, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>registers latency_bridge.m_valid before driving the boundary</t>
         </is>
@@ -5801,42 +5428,30 @@
         </is>
       </c>
       <c r="I37" s="7">
-        <f>F37*characterization!$B$17 + G37*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J37" s="7">
-        <f>F37*characterization!$G$17 + G37*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K37" s="7">
-        <f>F37*characterization!$L$17 + G37*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L37" s="7">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F37*IF(J37="TT",characterization!$B$17,IF(J37="FF",characterization!$G$17,characterization!$L$17))+G37*IF(J37="TT",characterization!$B$15,IF(J37="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L37" s="5">
+        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M37" s="7">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N37" s="7">
-        <f>IF(M37="TT",I37,IF(M37="FF",J37,IF(M37="SS",K37,"")))</f>
-        <v/>
-      </c>
-      <c r="O37" s="5">
-        <f>IFERROR(VLOOKUP(C37, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P37" s="7">
-        <f>O37 + N37</f>
-        <v/>
-      </c>
-      <c r="R37" s="7">
-        <f>IFERROR(L37 - P37 - VLOOKUP(C37, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C37, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S37" t="inlineStr">
+        <f>L37 + K37</f>
+        <v/>
+      </c>
+      <c r="O37" s="10">
+        <f>IFERROR(I37 - M37 - VLOOKUP(C37, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C37, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>to axi_read_engine</t>
         </is>
@@ -5880,42 +5495,30 @@
         </is>
       </c>
       <c r="I38" s="7">
-        <f>F38*characterization!$B$17 + G38*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J38" s="7">
-        <f>F38*characterization!$G$17 + G38*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K38" s="7">
-        <f>F38*characterization!$L$17 + G38*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L38" s="7">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F38*IF(J38="TT",characterization!$B$17,IF(J38="FF",characterization!$G$17,characterization!$L$17))+G38*IF(J38="TT",characterization!$B$15,IF(J38="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L38" s="5">
+        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M38" s="7">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N38" s="7">
-        <f>IF(M38="TT",I38,IF(M38="FF",J38,IF(M38="SS",K38,"")))</f>
-        <v/>
-      </c>
-      <c r="O38" s="5">
-        <f>IFERROR(VLOOKUP(C38, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P38" s="7">
-        <f>O38 + N38</f>
-        <v/>
-      </c>
-      <c r="R38" s="7">
-        <f>IFERROR(L38 - P38 - VLOOKUP(C38, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C38, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S38" t="inlineStr">
+        <f>L38 + K38</f>
+        <v/>
+      </c>
+      <c r="O38" s="10">
+        <f>IFERROR(I38 - M38 - VLOOKUP(C38, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C38, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>from axi_read_engine (write data into SRAM FIFO)</t>
         </is>
@@ -5959,42 +5562,30 @@
         </is>
       </c>
       <c r="I39" s="7">
-        <f>F39*characterization!$B$17 + G39*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J39" s="7">
-        <f>F39*characterization!$G$17 + G39*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K39" s="7">
-        <f>F39*characterization!$L$17 + G39*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L39" s="7">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F39*IF(J39="TT",characterization!$B$17,IF(J39="FF",characterization!$G$17,characterization!$L$17))+G39*IF(J39="TT",characterization!$B$15,IF(J39="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L39" s="5">
+        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M39" s="7">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N39" s="7">
-        <f>IF(M39="TT",I39,IF(M39="FF",J39,IF(M39="SS",K39,"")))</f>
-        <v/>
-      </c>
-      <c r="O39" s="5">
-        <f>IFERROR(VLOOKUP(C39, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P39" s="7">
-        <f>O39 + N39</f>
-        <v/>
-      </c>
-      <c r="R39" s="7">
-        <f>IFERROR(L39 - P39 - VLOOKUP(C39, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C39, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S39" t="inlineStr">
+        <f>L39 + K39</f>
+        <v/>
+      </c>
+      <c r="O39" s="10">
+        <f>IFERROR(I39 - M39 - VLOOKUP(C39, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C39, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>from axi_read_engine</t>
         </is>
@@ -6038,42 +5629,30 @@
         </is>
       </c>
       <c r="I40" s="7">
-        <f>F40*characterization!$B$17 + G40*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J40" s="7">
-        <f>F40*characterization!$G$17 + G40*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K40" s="7">
-        <f>F40*characterization!$L$17 + G40*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L40" s="7">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F40*IF(J40="TT",characterization!$B$17,IF(J40="FF",characterization!$G$17,characterization!$L$17))+G40*IF(J40="TT",characterization!$B$15,IF(J40="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L40" s="5">
+        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M40" s="7">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N40" s="7">
-        <f>IF(M40="TT",I40,IF(M40="FF",J40,IF(M40="SS",K40,"")))</f>
-        <v/>
-      </c>
-      <c r="O40" s="5">
-        <f>IFERROR(VLOOKUP(C40, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P40" s="7">
-        <f>O40 + N40</f>
-        <v/>
-      </c>
-      <c r="R40" s="7">
-        <f>IFERROR(L40 - P40 - VLOOKUP(C40, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C40, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S40" t="inlineStr">
+        <f>L40 + K40</f>
+        <v/>
+      </c>
+      <c r="O40" s="10">
+        <f>IFERROR(I40 - M40 - VLOOKUP(C40, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C40, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>to axi_read_engine</t>
         </is>
@@ -6113,42 +5692,30 @@
         </is>
       </c>
       <c r="I41" s="7">
-        <f>F41*characterization!$B$17 + G41*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J41" s="7">
-        <f>F41*characterization!$G$17 + G41*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K41" s="7">
-        <f>F41*characterization!$L$17 + G41*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L41" s="7">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F41*IF(J41="TT",characterization!$B$17,IF(J41="FF",characterization!$G$17,characterization!$L$17))+G41*IF(J41="TT",characterization!$B$15,IF(J41="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L41" s="5">
+        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M41" s="7">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N41" s="7">
-        <f>IF(M41="TT",I41,IF(M41="FF",J41,IF(M41="SS",K41,"")))</f>
-        <v/>
-      </c>
-      <c r="O41" s="5">
-        <f>IFERROR(VLOOKUP(C41, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P41" s="7">
-        <f>O41 + N41</f>
-        <v/>
-      </c>
-      <c r="R41" s="7">
-        <f>IFERROR(L41 - P41 - VLOOKUP(C41, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C41, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S41" t="inlineStr">
+        <f>L41 + K41</f>
+        <v/>
+      </c>
+      <c r="O41" s="10">
+        <f>IFERROR(I41 - M41 - VLOOKUP(C41, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C41, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -6192,42 +5759,30 @@
         </is>
       </c>
       <c r="I42" s="7">
-        <f>F42*characterization!$B$17 + G42*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J42" s="7">
-        <f>F42*characterization!$G$17 + G42*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K42" s="7">
-        <f>F42*characterization!$L$17 + G42*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L42" s="7">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F42*IF(J42="TT",characterization!$B$17,IF(J42="FF",characterization!$G$17,characterization!$L$17))+G42*IF(J42="TT",characterization!$B$15,IF(J42="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L42" s="5">
+        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M42" s="7">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N42" s="7">
-        <f>IF(M42="TT",I42,IF(M42="FF",J42,IF(M42="SS",K42,"")))</f>
-        <v/>
-      </c>
-      <c r="O42" s="5">
-        <f>IFERROR(VLOOKUP(C42, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P42" s="7">
-        <f>O42 + N42</f>
-        <v/>
-      </c>
-      <c r="R42" s="7">
-        <f>IFERROR(L42 - P42 - VLOOKUP(C42, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C42, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S42" t="inlineStr">
+        <f>L42 + K42</f>
+        <v/>
+      </c>
+      <c r="O42" s="10">
+        <f>IFERROR(I42 - M42 - VLOOKUP(C42, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C42, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -6267,42 +5822,30 @@
         </is>
       </c>
       <c r="I43" s="7">
-        <f>F43*characterization!$B$17 + G43*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J43" s="7">
-        <f>F43*characterization!$G$17 + G43*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K43" s="7">
-        <f>F43*characterization!$L$17 + G43*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L43" s="7">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F43*IF(J43="TT",characterization!$B$17,IF(J43="FF",characterization!$G$17,characterization!$L$17))+G43*IF(J43="TT",characterization!$B$15,IF(J43="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L43" s="5">
+        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M43" s="7">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N43" s="7">
-        <f>IF(M43="TT",I43,IF(M43="FF",J43,IF(M43="SS",K43,"")))</f>
-        <v/>
-      </c>
-      <c r="O43" s="5">
-        <f>IFERROR(VLOOKUP(C43, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P43" s="7">
-        <f>O43 + N43</f>
-        <v/>
-      </c>
-      <c r="R43" s="7">
-        <f>IFERROR(L43 - P43 - VLOOKUP(C43, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C43, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S43" t="inlineStr">
+        <f>L43 + K43</f>
+        <v/>
+      </c>
+      <c r="O43" s="10">
+        <f>IFERROR(I43 - M43 - VLOOKUP(C43, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C43, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>from axi_write_engine</t>
         </is>
@@ -6342,42 +5885,30 @@
         </is>
       </c>
       <c r="I44" s="7">
-        <f>F44*characterization!$B$17 + G44*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J44" s="7">
-        <f>F44*characterization!$G$17 + G44*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K44" s="7">
-        <f>F44*characterization!$L$17 + G44*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L44" s="7">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F44*IF(J44="TT",characterization!$B$17,IF(J44="FF",characterization!$G$17,characterization!$L$17))+G44*IF(J44="TT",characterization!$B$15,IF(J44="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L44" s="5">
+        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M44" s="7">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N44" s="7">
-        <f>IF(M44="TT",I44,IF(M44="FF",J44,IF(M44="SS",K44,"")))</f>
-        <v/>
-      </c>
-      <c r="O44" s="5">
-        <f>IFERROR(VLOOKUP(C44, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P44" s="7">
-        <f>O44 + N44</f>
-        <v/>
-      </c>
-      <c r="R44" s="7">
-        <f>IFERROR(L44 - P44 - VLOOKUP(C44, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C44, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S44" t="inlineStr">
+        <f>L44 + K44</f>
+        <v/>
+      </c>
+      <c r="O44" s="10">
+        <f>IFERROR(I44 - M44 - VLOOKUP(C44, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C44, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>from axi_write_engine</t>
         </is>
@@ -6424,42 +5955,30 @@
         </is>
       </c>
       <c r="I46" s="7">
-        <f>F46*characterization!$B$17 + G46*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J46" s="7">
-        <f>F46*characterization!$G$17 + G46*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K46" s="7">
-        <f>F46*characterization!$L$17 + G46*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L46" s="7">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F46*IF(J46="TT",characterization!$B$17,IF(J46="FF",characterization!$G$17,characterization!$L$17))+G46*IF(J46="TT",characterization!$B$15,IF(J46="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L46" s="5">
+        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M46" s="7">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N46" s="7">
-        <f>IF(M46="TT",I46,IF(M46="FF",J46,IF(M46="SS",K46,"")))</f>
-        <v/>
-      </c>
-      <c r="O46" s="5">
-        <f>IFERROR(VLOOKUP(C46, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P46" s="7">
-        <f>O46 + N46</f>
-        <v/>
-      </c>
-      <c r="R46" s="7">
-        <f>IFERROR(L46 - P46 - VLOOKUP(C46, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C46, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S46" t="inlineStr">
+        <f>L46 + K46</f>
+        <v/>
+      </c>
+      <c r="O46" s="10">
+        <f>IFERROR(I46 - M46 - VLOOKUP(C46, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C46, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>from axi_read_engine (N-channel fan-out)</t>
         </is>
@@ -6499,42 +6018,30 @@
         </is>
       </c>
       <c r="I47" s="7">
-        <f>F47*characterization!$B$17 + G47*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J47" s="7">
-        <f>F47*characterization!$G$17 + G47*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K47" s="7">
-        <f>F47*characterization!$L$17 + G47*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L47" s="7">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F47*IF(J47="TT",characterization!$B$17,IF(J47="FF",characterization!$G$17,characterization!$L$17))+G47*IF(J47="TT",characterization!$B$15,IF(J47="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L47" s="5">
+        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M47" s="7">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N47" s="7">
-        <f>IF(M47="TT",I47,IF(M47="FF",J47,IF(M47="SS",K47,"")))</f>
-        <v/>
-      </c>
-      <c r="O47" s="5">
-        <f>IFERROR(VLOOKUP(C47, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P47" s="7">
-        <f>O47 + N47</f>
-        <v/>
-      </c>
-      <c r="R47" s="7">
-        <f>IFERROR(L47 - P47 - VLOOKUP(C47, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C47, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S47" t="inlineStr">
+        <f>L47 + K47</f>
+        <v/>
+      </c>
+      <c r="O47" s="10">
+        <f>IFERROR(I47 - M47 - VLOOKUP(C47, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C47, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>to axi_read_engine</t>
         </is>
@@ -6574,42 +6081,30 @@
         </is>
       </c>
       <c r="I48" s="7">
-        <f>F48*characterization!$B$17 + G48*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J48" s="7">
-        <f>F48*characterization!$G$17 + G48*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K48" s="7">
-        <f>F48*characterization!$L$17 + G48*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L48" s="7">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F48*IF(J48="TT",characterization!$B$17,IF(J48="FF",characterization!$G$17,characterization!$L$17))+G48*IF(J48="TT",characterization!$B$15,IF(J48="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L48" s="5">
+        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M48" s="7">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N48" s="7">
-        <f>IF(M48="TT",I48,IF(M48="FF",J48,IF(M48="SS",K48,"")))</f>
-        <v/>
-      </c>
-      <c r="O48" s="5">
-        <f>IFERROR(VLOOKUP(C48, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P48" s="7">
-        <f>O48 + N48</f>
-        <v/>
-      </c>
-      <c r="R48" s="7">
-        <f>IFERROR(L48 - P48 - VLOOKUP(C48, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C48, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S48" t="inlineStr">
+        <f>L48 + K48</f>
+        <v/>
+      </c>
+      <c r="O48" s="10">
+        <f>IFERROR(I48 - M48 - VLOOKUP(C48, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C48, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>from axi_read_engine</t>
         </is>
@@ -6649,42 +6144,30 @@
         </is>
       </c>
       <c r="I49" s="7">
-        <f>F49*characterization!$B$17 + G49*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J49" s="7">
-        <f>F49*characterization!$G$17 + G49*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K49" s="7">
-        <f>F49*characterization!$L$17 + G49*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L49" s="7">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F49*IF(J49="TT",characterization!$B$17,IF(J49="FF",characterization!$G$17,characterization!$L$17))+G49*IF(J49="TT",characterization!$B$15,IF(J49="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L49" s="5">
+        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M49" s="7">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N49" s="7">
-        <f>IF(M49="TT",I49,IF(M49="FF",J49,IF(M49="SS",K49,"")))</f>
-        <v/>
-      </c>
-      <c r="O49" s="5">
-        <f>IFERROR(VLOOKUP(C49, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P49" s="7">
-        <f>O49 + N49</f>
-        <v/>
-      </c>
-      <c r="R49" s="7">
-        <f>IFERROR(L49 - P49 - VLOOKUP(C49, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C49, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S49" t="inlineStr">
+        <f>L49 + K49</f>
+        <v/>
+      </c>
+      <c r="O49" s="10">
+        <f>IFERROR(I49 - M49 - VLOOKUP(C49, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C49, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -6724,42 +6207,30 @@
         </is>
       </c>
       <c r="I50" s="7">
-        <f>F50*characterization!$B$17 + G50*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J50" s="7">
-        <f>F50*characterization!$G$17 + G50*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K50" s="7">
-        <f>F50*characterization!$L$17 + G50*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L50" s="7">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F50*IF(J50="TT",characterization!$B$17,IF(J50="FF",characterization!$G$17,characterization!$L$17))+G50*IF(J50="TT",characterization!$B$15,IF(J50="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L50" s="5">
+        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M50" s="7">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N50" s="7">
-        <f>IF(M50="TT",I50,IF(M50="FF",J50,IF(M50="SS",K50,"")))</f>
-        <v/>
-      </c>
-      <c r="O50" s="5">
-        <f>IFERROR(VLOOKUP(C50, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P50" s="7">
-        <f>O50 + N50</f>
-        <v/>
-      </c>
-      <c r="R50" s="7">
-        <f>IFERROR(L50 - P50 - VLOOKUP(C50, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C50, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S50" t="inlineStr">
+        <f>L50 + K50</f>
+        <v/>
+      </c>
+      <c r="O50" s="10">
+        <f>IFERROR(I50 - M50 - VLOOKUP(C50, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C50, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -6806,42 +6277,30 @@
         </is>
       </c>
       <c r="I52" s="7">
-        <f>F52*characterization!$B$17 + G52*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J52" s="7">
-        <f>F52*characterization!$G$17 + G52*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K52" s="7">
-        <f>F52*characterization!$L$17 + G52*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L52" s="7">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F52*IF(J52="TT",characterization!$B$17,IF(J52="FF",characterization!$G$17,characterization!$L$17))+G52*IF(J52="TT",characterization!$B$15,IF(J52="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L52" s="5">
+        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M52" s="7">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N52" s="7">
-        <f>IF(M52="TT",I52,IF(M52="FF",J52,IF(M52="SS",K52,"")))</f>
-        <v/>
-      </c>
-      <c r="O52" s="5">
-        <f>IFERROR(VLOOKUP(C52, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P52" s="7">
-        <f>O52 + N52</f>
-        <v/>
-      </c>
-      <c r="R52" s="7">
-        <f>IFERROR(L52 - P52 - VLOOKUP(C52, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C52, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S52" t="inlineStr">
+        <f>L52 + K52</f>
+        <v/>
+      </c>
+      <c r="O52" s="10">
+        <f>IFERROR(I52 - M52 - VLOOKUP(C52, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C52, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>from scheduler (per-ch idle state)</t>
         </is>
@@ -6881,42 +6340,30 @@
         </is>
       </c>
       <c r="I53" s="7">
-        <f>F53*characterization!$B$17 + G53*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J53" s="7">
-        <f>F53*characterization!$G$17 + G53*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K53" s="7">
-        <f>F53*characterization!$L$17 + G53*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L53" s="7">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F53*IF(J53="TT",characterization!$B$17,IF(J53="FF",characterization!$G$17,characterization!$L$17))+G53*IF(J53="TT",characterization!$B$15,IF(J53="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L53" s="5">
+        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M53" s="7">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N53" s="7">
-        <f>IF(M53="TT",I53,IF(M53="FF",J53,IF(M53="SS",K53,"")))</f>
-        <v/>
-      </c>
-      <c r="O53" s="5">
-        <f>IFERROR(VLOOKUP(C53, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P53" s="7">
-        <f>O53 + N53</f>
-        <v/>
-      </c>
-      <c r="R53" s="7">
-        <f>IFERROR(L53 - P53 - VLOOKUP(C53, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C53, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S53" t="inlineStr">
+        <f>L53 + K53</f>
+        <v/>
+      </c>
+      <c r="O53" s="10">
+        <f>IFERROR(I53 - M53 - VLOOKUP(C53, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C53, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>from APB CSR</t>
         </is>
@@ -6956,42 +6403,30 @@
         </is>
       </c>
       <c r="I54" s="7">
-        <f>F54*characterization!$B$17 + G54*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J54" s="7">
-        <f>F54*characterization!$G$17 + G54*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K54" s="7">
-        <f>F54*characterization!$L$17 + G54*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L54" s="7">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F54*IF(J54="TT",characterization!$B$17,IF(J54="FF",characterization!$G$17,characterization!$L$17))+G54*IF(J54="TT",characterization!$B$15,IF(J54="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L54" s="5">
+        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M54" s="7">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N54" s="7">
-        <f>IF(M54="TT",I54,IF(M54="FF",J54,IF(M54="SS",K54,"")))</f>
-        <v/>
-      </c>
-      <c r="O54" s="5">
-        <f>IFERROR(VLOOKUP(C54, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P54" s="7">
-        <f>O54 + N54</f>
-        <v/>
-      </c>
-      <c r="R54" s="7">
-        <f>IFERROR(L54 - P54 - VLOOKUP(C54, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C54, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S54" t="inlineStr">
+        <f>L54 + K54</f>
+        <v/>
+      </c>
+      <c r="O54" s="10">
+        <f>IFERROR(I54 - M54 - VLOOKUP(C54, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C54, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>from APB CSR</t>
         </is>
@@ -7031,42 +6466,30 @@
         </is>
       </c>
       <c r="I55" s="7">
-        <f>F55*characterization!$B$17 + G55*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J55" s="7">
-        <f>F55*characterization!$G$17 + G55*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K55" s="7">
-        <f>F55*characterization!$L$17 + G55*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L55" s="7">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F55*IF(J55="TT",characterization!$B$17,IF(J55="FF",characterization!$G$17,characterization!$L$17))+G55*IF(J55="TT",characterization!$B$15,IF(J55="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L55" s="5">
+        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M55" s="7">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N55" s="7">
-        <f>IF(M55="TT",I55,IF(M55="FF",J55,IF(M55="SS",K55,"")))</f>
-        <v/>
-      </c>
-      <c r="O55" s="5">
-        <f>IFERROR(VLOOKUP(C55, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P55" s="7">
-        <f>O55 + N55</f>
-        <v/>
-      </c>
-      <c r="R55" s="7">
-        <f>IFERROR(L55 - P55 - VLOOKUP(C55, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C55, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S55" t="inlineStr">
+        <f>L55 + K55</f>
+        <v/>
+      </c>
+      <c r="O55" s="10">
+        <f>IFERROR(I55 - M55 - VLOOKUP(C55, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C55, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>free-running counter; +1 every cycle when enabled</t>
         </is>
@@ -7106,42 +6529,30 @@
         </is>
       </c>
       <c r="I56" s="7">
-        <f>F56*characterization!$B$17 + G56*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J56" s="7">
-        <f>F56*characterization!$G$17 + G56*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K56" s="7">
-        <f>F56*characterization!$L$17 + G56*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L56" s="7">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F56*IF(J56="TT",characterization!$B$17,IF(J56="FF",characterization!$G$17,characterization!$L$17))+G56*IF(J56="TT",characterization!$B$15,IF(J56="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L56" s="5">
+        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M56" s="7">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N56" s="7">
-        <f>IF(M56="TT",I56,IF(M56="FF",J56,IF(M56="SS",K56,"")))</f>
-        <v/>
-      </c>
-      <c r="O56" s="5">
-        <f>IFERROR(VLOOKUP(C56, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P56" s="7">
-        <f>O56 + N56</f>
-        <v/>
-      </c>
-      <c r="R56" s="7">
-        <f>IFERROR(L56 - P56 - VLOOKUP(C56, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C56, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S56" t="inlineStr">
+        <f>L56 + K56</f>
+        <v/>
+      </c>
+      <c r="O56" s="10">
+        <f>IFERROR(I56 - M56 - VLOOKUP(C56, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C56, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>XOR with channel_idle = edge detect</t>
         </is>
@@ -7181,42 +6592,30 @@
         </is>
       </c>
       <c r="I57" s="7">
-        <f>F57*characterization!$B$17 + G57*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J57" s="7">
-        <f>F57*characterization!$G$17 + G57*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K57" s="7">
-        <f>F57*characterization!$L$17 + G57*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L57" s="7">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F57*IF(J57="TT",characterization!$B$17,IF(J57="FF",characterization!$G$17,characterization!$L$17))+G57*IF(J57="TT",characterization!$B$15,IF(J57="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L57" s="5">
+        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M57" s="7">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N57" s="7">
-        <f>IF(M57="TT",I57,IF(M57="FF",J57,IF(M57="SS",K57,"")))</f>
-        <v/>
-      </c>
-      <c r="O57" s="5">
-        <f>IFERROR(VLOOKUP(C57, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P57" s="7">
-        <f>O57 + N57</f>
-        <v/>
-      </c>
-      <c r="R57" s="7">
-        <f>IFERROR(L57 - P57 - VLOOKUP(C57, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C57, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S57" t="inlineStr">
+        <f>L57 + K57</f>
+        <v/>
+      </c>
+      <c r="O57" s="10">
+        <f>IFERROR(I57 - M57 - VLOOKUP(C57, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C57, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>1 cycle pulse when edge detected</t>
         </is>
@@ -7256,42 +6655,30 @@
         </is>
       </c>
       <c r="I58" s="7">
-        <f>F58*characterization!$B$17 + G58*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J58" s="7">
-        <f>F58*characterization!$G$17 + G58*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K58" s="7">
-        <f>F58*characterization!$L$17 + G58*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L58" s="7">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F58*IF(J58="TT",characterization!$B$17,IF(J58="FF",characterization!$G$17,characterization!$L$17))+G58*IF(J58="TT",characterization!$B$15,IF(J58="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L58" s="5">
+        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M58" s="7">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N58" s="7">
-        <f>IF(M58="TT",I58,IF(M58="FF",J58,IF(M58="SS",K58,"")))</f>
-        <v/>
-      </c>
-      <c r="O58" s="5">
-        <f>IFERROR(VLOOKUP(C58, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P58" s="7">
-        <f>O58 + N58</f>
-        <v/>
-      </c>
-      <c r="R58" s="7">
-        <f>IFERROR(L58 - P58 - VLOOKUP(C58, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C58, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S58" t="inlineStr">
+        <f>L58 + K58</f>
+        <v/>
+      </c>
+      <c r="O58" s="10">
+        <f>IFERROR(I58 - M58 - VLOOKUP(C58, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C58, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>rise / fall event code</t>
         </is>
@@ -7335,42 +6722,30 @@
         </is>
       </c>
       <c r="I59" s="7">
-        <f>F59*characterization!$B$17 + G59*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J59" s="7">
-        <f>F59*characterization!$G$17 + G59*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K59" s="7">
-        <f>F59*characterization!$L$17 + G59*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L59" s="7">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F59*IF(J59="TT",characterization!$B$17,IF(J59="FF",characterization!$G$17,characterization!$L$17))+G59*IF(J59="TT",characterization!$B$15,IF(J59="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L59" s="5">
+        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M59" s="7">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N59" s="7">
-        <f>IF(M59="TT",I59,IF(M59="FF",J59,IF(M59="SS",K59,"")))</f>
-        <v/>
-      </c>
-      <c r="O59" s="5">
-        <f>IFERROR(VLOOKUP(C59, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P59" s="7">
-        <f>O59 + N59</f>
-        <v/>
-      </c>
-      <c r="R59" s="7">
-        <f>IFERROR(L59 - P59 - VLOOKUP(C59, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C59, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S59" t="inlineStr">
+        <f>L59 + K59</f>
+        <v/>
+      </c>
+      <c r="O59" s="10">
+        <f>IFERROR(I59 - M59 - VLOOKUP(C59, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C59, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>from APB CSR pop strobe</t>
         </is>
@@ -7414,42 +6789,30 @@
         </is>
       </c>
       <c r="I60" s="7">
-        <f>F60*characterization!$B$17 + G60*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J60" s="7">
-        <f>F60*characterization!$G$17 + G60*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K60" s="7">
-        <f>F60*characterization!$L$17 + G60*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L60" s="7">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F60*IF(J60="TT",characterization!$B$17,IF(J60="FF",characterization!$G$17,characterization!$L$17))+G60*IF(J60="TT",characterization!$B$15,IF(J60="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L60" s="5">
+        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M60" s="7">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N60" s="7">
-        <f>IF(M60="TT",I60,IF(M60="FF",J60,IF(M60="SS",K60,"")))</f>
-        <v/>
-      </c>
-      <c r="O60" s="5">
-        <f>IFERROR(VLOOKUP(C60, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P60" s="7">
-        <f>O60 + N60</f>
-        <v/>
-      </c>
-      <c r="R60" s="7">
-        <f>IFERROR(L60 - P60 - VLOOKUP(C60, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C60, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S60" t="inlineStr">
+        <f>L60 + K60</f>
+        <v/>
+      </c>
+      <c r="O60" s="10">
+        <f>IFERROR(I60 - M60 - VLOOKUP(C60, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C60, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>to APB CSR (host read)</t>
         </is>
@@ -7493,42 +6856,30 @@
         </is>
       </c>
       <c r="I61" s="7">
-        <f>F61*characterization!$B$17 + G61*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J61" s="7">
-        <f>F61*characterization!$G$17 + G61*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K61" s="7">
-        <f>F61*characterization!$L$17 + G61*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L61" s="7">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F61*IF(J61="TT",characterization!$B$17,IF(J61="FF",characterization!$G$17,characterization!$L$17))+G61*IF(J61="TT",characterization!$B$15,IF(J61="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L61" s="5">
+        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M61" s="7">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N61" s="7">
-        <f>IF(M61="TT",I61,IF(M61="FF",J61,IF(M61="SS",K61,"")))</f>
-        <v/>
-      </c>
-      <c r="O61" s="5">
-        <f>IFERROR(VLOOKUP(C61, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P61" s="7">
-        <f>O61 + N61</f>
-        <v/>
-      </c>
-      <c r="R61" s="7">
-        <f>IFERROR(L61 - P61 - VLOOKUP(C61, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C61, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S61" t="inlineStr">
+        <f>L61 + K61</f>
+        <v/>
+      </c>
+      <c r="O61" s="10">
+        <f>IFERROR(I61 - M61 - VLOOKUP(C61, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C61, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>to APB CSR</t>
         </is>
@@ -7572,42 +6923,30 @@
         </is>
       </c>
       <c r="I62" s="7">
-        <f>F62*characterization!$B$17 + G62*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J62" s="7">
-        <f>F62*characterization!$G$17 + G62*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K62" s="7">
-        <f>F62*characterization!$L$17 + G62*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L62" s="7">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F62*IF(J62="TT",characterization!$B$17,IF(J62="FF",characterization!$G$17,characterization!$L$17))+G62*IF(J62="TT",characterization!$B$15,IF(J62="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L62" s="5">
+        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M62" s="7">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N62" s="7">
-        <f>IF(M62="TT",I62,IF(M62="FF",J62,IF(M62="SS",K62,"")))</f>
-        <v/>
-      </c>
-      <c r="O62" s="5">
-        <f>IFERROR(VLOOKUP(C62, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P62" s="7">
-        <f>O62 + N62</f>
-        <v/>
-      </c>
-      <c r="R62" s="7">
-        <f>IFERROR(L62 - P62 - VLOOKUP(C62, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C62, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S62" t="inlineStr">
+        <f>L62 + K62</f>
+        <v/>
+      </c>
+      <c r="O62" s="10">
+        <f>IFERROR(I62 - M62 - VLOOKUP(C62, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C62, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>to APB CSR</t>
         </is>
@@ -7651,42 +6990,30 @@
         </is>
       </c>
       <c r="I63" s="7">
-        <f>F63*characterization!$B$17 + G63*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J63" s="7">
-        <f>F63*characterization!$G$17 + G63*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K63" s="7">
-        <f>F63*characterization!$L$17 + G63*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L63" s="7">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F63*IF(J63="TT",characterization!$B$17,IF(J63="FF",characterization!$G$17,characterization!$L$17))+G63*IF(J63="TT",characterization!$B$15,IF(J63="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L63" s="5">
+        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M63" s="7">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N63" s="7">
-        <f>IF(M63="TT",I63,IF(M63="FF",J63,IF(M63="SS",K63,"")))</f>
-        <v/>
-      </c>
-      <c r="O63" s="5">
-        <f>IFERROR(VLOOKUP(C63, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P63" s="7">
-        <f>O63 + N63</f>
-        <v/>
-      </c>
-      <c r="R63" s="7">
-        <f>IFERROR(L63 - P63 - VLOOKUP(C63, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C63, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S63" t="inlineStr">
+        <f>L63 + K63</f>
+        <v/>
+      </c>
+      <c r="O63" s="10">
+        <f>IFERROR(I63 - M63 - VLOOKUP(C63, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C63, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>to APB CSR</t>
         </is>
@@ -7733,42 +7060,30 @@
         </is>
       </c>
       <c r="I65" s="7">
-        <f>F65*characterization!$B$17 + G65*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J65" s="7">
-        <f>F65*characterization!$G$17 + G65*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K65" s="7">
-        <f>F65*characterization!$L$17 + G65*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L65" s="7">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F65*IF(J65="TT",characterization!$B$17,IF(J65="FF",characterization!$G$17,characterization!$L$17))+G65*IF(J65="TT",characterization!$B$15,IF(J65="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L65" s="5">
+        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M65" s="7">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N65" s="7">
-        <f>IF(M65="TT",I65,IF(M65="FF",J65,IF(M65="SS",K65,"")))</f>
-        <v/>
-      </c>
-      <c r="O65" s="5">
-        <f>IFERROR(VLOOKUP(C65, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P65" s="7">
-        <f>O65 + N65</f>
-        <v/>
-      </c>
-      <c r="R65" s="7">
-        <f>IFERROR(L65 - P65 - VLOOKUP(C65, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C65, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S65" t="inlineStr">
+        <f>L65 + K65</f>
+        <v/>
+      </c>
+      <c r="O65" s="10">
+        <f>IFERROR(I65 - M65 - VLOOKUP(C65, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C65, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>from APB master</t>
         </is>
@@ -7808,42 +7123,30 @@
         </is>
       </c>
       <c r="I66" s="7">
-        <f>F66*characterization!$B$17 + G66*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J66" s="7">
-        <f>F66*characterization!$G$17 + G66*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K66" s="7">
-        <f>F66*characterization!$L$17 + G66*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L66" s="7">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F66*IF(J66="TT",characterization!$B$17,IF(J66="FF",characterization!$G$17,characterization!$L$17))+G66*IF(J66="TT",characterization!$B$15,IF(J66="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L66" s="5">
+        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M66" s="7">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N66" s="7">
-        <f>IF(M66="TT",I66,IF(M66="FF",J66,IF(M66="SS",K66,"")))</f>
-        <v/>
-      </c>
-      <c r="O66" s="5">
-        <f>IFERROR(VLOOKUP(C66, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P66" s="7">
-        <f>O66 + N66</f>
-        <v/>
-      </c>
-      <c r="R66" s="7">
-        <f>IFERROR(L66 - P66 - VLOOKUP(C66, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C66, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S66" t="inlineStr">
+        <f>L66 + K66</f>
+        <v/>
+      </c>
+      <c r="O66" s="10">
+        <f>IFERROR(I66 - M66 - VLOOKUP(C66, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C66, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>from APB master</t>
         </is>
@@ -7883,42 +7186,30 @@
         </is>
       </c>
       <c r="I67" s="7">
-        <f>F67*characterization!$B$17 + G67*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J67" s="7">
-        <f>F67*characterization!$G$17 + G67*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K67" s="7">
-        <f>F67*characterization!$L$17 + G67*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L67" s="7">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F67*IF(J67="TT",characterization!$B$17,IF(J67="FF",characterization!$G$17,characterization!$L$17))+G67*IF(J67="TT",characterization!$B$15,IF(J67="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L67" s="5">
+        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M67" s="7">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N67" s="7">
-        <f>IF(M67="TT",I67,IF(M67="FF",J67,IF(M67="SS",K67,"")))</f>
-        <v/>
-      </c>
-      <c r="O67" s="5">
-        <f>IFERROR(VLOOKUP(C67, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P67" s="7">
-        <f>O67 + N67</f>
-        <v/>
-      </c>
-      <c r="R67" s="7">
-        <f>IFERROR(L67 - P67 - VLOOKUP(C67, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C67, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S67" t="inlineStr">
+        <f>L67 + K67</f>
+        <v/>
+      </c>
+      <c r="O67" s="10">
+        <f>IFERROR(I67 - M67 - VLOOKUP(C67, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C67, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>from APB master (descriptor pointer write)</t>
         </is>
@@ -7958,42 +7249,30 @@
         </is>
       </c>
       <c r="I68" s="7">
-        <f>F68*characterization!$B$17 + G68*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J68" s="7">
-        <f>F68*characterization!$G$17 + G68*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K68" s="7">
-        <f>F68*characterization!$L$17 + G68*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L68" s="7">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F68*IF(J68="TT",characterization!$B$17,IF(J68="FF",characterization!$G$17,characterization!$L$17))+G68*IF(J68="TT",characterization!$B$15,IF(J68="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L68" s="5">
+        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M68" s="7">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N68" s="7">
-        <f>IF(M68="TT",I68,IF(M68="FF",J68,IF(M68="SS",K68,"")))</f>
-        <v/>
-      </c>
-      <c r="O68" s="5">
-        <f>IFERROR(VLOOKUP(C68, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P68" s="7">
-        <f>O68 + N68</f>
-        <v/>
-      </c>
-      <c r="R68" s="7">
-        <f>IFERROR(L68 - P68 - VLOOKUP(C68, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C68, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S68" t="inlineStr">
+        <f>L68 + K68</f>
+        <v/>
+      </c>
+      <c r="O68" s="10">
+        <f>IFERROR(I68 - M68 - VLOOKUP(C68, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C68, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>1-state FSM: ACCEPT -&gt; RSP</t>
         </is>
@@ -8033,42 +7312,30 @@
         </is>
       </c>
       <c r="I69" s="7">
-        <f>F69*characterization!$B$17 + G69*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J69" s="7">
-        <f>F69*characterization!$G$17 + G69*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K69" s="7">
-        <f>F69*characterization!$L$17 + G69*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L69" s="7">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F69*IF(J69="TT",characterization!$B$17,IF(J69="FF",characterization!$G$17,characterization!$L$17))+G69*IF(J69="TT",characterization!$B$15,IF(J69="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L69" s="5">
+        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M69" s="7">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N69" s="7">
-        <f>IF(M69="TT",I69,IF(M69="FF",J69,IF(M69="SS",K69,"")))</f>
-        <v/>
-      </c>
-      <c r="O69" s="5">
-        <f>IFERROR(VLOOKUP(C69, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P69" s="7">
-        <f>O69 + N69</f>
-        <v/>
-      </c>
-      <c r="R69" s="7">
-        <f>IFERROR(L69 - P69 - VLOOKUP(C69, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C69, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S69" t="inlineStr">
+        <f>L69 + K69</f>
+        <v/>
+      </c>
+      <c r="O69" s="10">
+        <f>IFERROR(I69 - M69 - VLOOKUP(C69, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C69, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>per-channel registered descriptor pointer</t>
         </is>
@@ -8108,42 +7375,30 @@
         </is>
       </c>
       <c r="I70" s="7">
-        <f>F70*characterization!$B$17 + G70*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J70" s="7">
-        <f>F70*characterization!$G$17 + G70*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K70" s="7">
-        <f>F70*characterization!$L$17 + G70*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L70" s="7">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F70*IF(J70="TT",characterization!$B$17,IF(J70="FF",characterization!$G$17,characterization!$L$17))+G70*IF(J70="TT",characterization!$B$15,IF(J70="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L70" s="5">
+        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M70" s="7">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N70" s="7">
-        <f>IF(M70="TT",I70,IF(M70="FF",J70,IF(M70="SS",K70,"")))</f>
-        <v/>
-      </c>
-      <c r="O70" s="5">
-        <f>IFERROR(VLOOKUP(C70, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P70" s="7">
-        <f>O70 + N70</f>
-        <v/>
-      </c>
-      <c r="R70" s="7">
-        <f>IFERROR(L70 - P70 - VLOOKUP(C70, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C70, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S70" t="inlineStr">
+        <f>L70 + K70</f>
+        <v/>
+      </c>
+      <c r="O70" s="10">
+        <f>IFERROR(I70 - M70 - VLOOKUP(C70, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C70, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>per-channel kickoff valid; clears on desc_engine ack</t>
         </is>
@@ -8183,42 +7438,30 @@
         </is>
       </c>
       <c r="I71" s="7">
-        <f>F71*characterization!$B$17 + G71*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J71" s="7">
-        <f>F71*characterization!$G$17 + G71*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K71" s="7">
-        <f>F71*characterization!$L$17 + G71*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L71" s="7">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F71*IF(J71="TT",characterization!$B$17,IF(J71="FF",characterization!$G$17,characterization!$L$17))+G71*IF(J71="TT",characterization!$B$15,IF(J71="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L71" s="5">
+        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M71" s="7">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N71" s="7">
-        <f>IF(M71="TT",I71,IF(M71="FF",J71,IF(M71="SS",K71,"")))</f>
-        <v/>
-      </c>
-      <c r="O71" s="5">
-        <f>IFERROR(VLOOKUP(C71, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P71" s="7">
-        <f>O71 + N71</f>
-        <v/>
-      </c>
-      <c r="R71" s="7">
-        <f>IFERROR(L71 - P71 - VLOOKUP(C71, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C71, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S71" t="inlineStr">
+        <f>L71 + K71</f>
+        <v/>
+      </c>
+      <c r="O71" s="10">
+        <f>IFERROR(I71 - M71 - VLOOKUP(C71, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C71, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>to APB master</t>
         </is>
@@ -8258,42 +7501,30 @@
         </is>
       </c>
       <c r="I72" s="7">
-        <f>F72*characterization!$B$17 + G72*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J72" s="7">
-        <f>F72*characterization!$G$17 + G72*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K72" s="7">
-        <f>F72*characterization!$L$17 + G72*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L72" s="7">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F72*IF(J72="TT",characterization!$B$17,IF(J72="FF",characterization!$G$17,characterization!$L$17))+G72*IF(J72="TT",characterization!$B$15,IF(J72="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L72" s="5">
+        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M72" s="7">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N72" s="7">
-        <f>IF(M72="TT",I72,IF(M72="FF",J72,IF(M72="SS",K72,"")))</f>
-        <v/>
-      </c>
-      <c r="O72" s="5">
-        <f>IFERROR(VLOOKUP(C72, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P72" s="7">
-        <f>O72 + N72</f>
-        <v/>
-      </c>
-      <c r="R72" s="7">
-        <f>IFERROR(L72 - P72 - VLOOKUP(C72, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C72, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S72" t="inlineStr">
+        <f>L72 + K72</f>
+        <v/>
+      </c>
+      <c r="O72" s="10">
+        <f>IFERROR(I72 - M72 - VLOOKUP(C72, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C72, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>to APB master</t>
         </is>
@@ -8333,42 +7564,30 @@
         </is>
       </c>
       <c r="I73" s="7">
-        <f>F73*characterization!$B$17 + G73*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J73" s="7">
-        <f>F73*characterization!$G$17 + G73*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K73" s="7">
-        <f>F73*characterization!$L$17 + G73*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L73" s="7">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F73*IF(J73="TT",characterization!$B$17,IF(J73="FF",characterization!$G$17,characterization!$L$17))+G73*IF(J73="TT",characterization!$B$15,IF(J73="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L73" s="5">
+        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M73" s="7">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N73" s="7">
-        <f>IF(M73="TT",I73,IF(M73="FF",J73,IF(M73="SS",K73,"")))</f>
-        <v/>
-      </c>
-      <c r="O73" s="5">
-        <f>IFERROR(VLOOKUP(C73, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P73" s="7">
-        <f>O73 + N73</f>
-        <v/>
-      </c>
-      <c r="R73" s="7">
-        <f>IFERROR(L73 - P73 - VLOOKUP(C73, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C73, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S73" t="inlineStr">
+        <f>L73 + K73</f>
+        <v/>
+      </c>
+      <c r="O73" s="10">
+        <f>IFERROR(I73 - M73 - VLOOKUP(C73, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C73, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>to descriptor_engine[N] (kick-off)</t>
         </is>
@@ -8408,42 +7627,30 @@
         </is>
       </c>
       <c r="I74" s="7">
-        <f>F74*characterization!$B$17 + G74*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J74" s="7">
-        <f>F74*characterization!$G$17 + G74*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K74" s="7">
-        <f>F74*characterization!$L$17 + G74*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L74" s="7">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F74*IF(J74="TT",characterization!$B$17,IF(J74="FF",characterization!$G$17,characterization!$L$17))+G74*IF(J74="TT",characterization!$B$15,IF(J74="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L74" s="5">
+        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M74" s="7">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N74" s="7">
-        <f>IF(M74="TT",I74,IF(M74="FF",J74,IF(M74="SS",K74,"")))</f>
-        <v/>
-      </c>
-      <c r="O74" s="5">
-        <f>IFERROR(VLOOKUP(C74, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P74" s="7">
-        <f>O74 + N74</f>
-        <v/>
-      </c>
-      <c r="R74" s="7">
-        <f>IFERROR(L74 - P74 - VLOOKUP(C74, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C74, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S74" t="inlineStr">
+        <f>L74 + K74</f>
+        <v/>
+      </c>
+      <c r="O74" s="10">
+        <f>IFERROR(I74 - M74 - VLOOKUP(C74, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C74, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>to descriptor_engine[N] (initial descriptor pointer)</t>
         </is>
@@ -8483,42 +7690,30 @@
         </is>
       </c>
       <c r="I75" s="7">
-        <f>F75*characterization!$B$17 + G75*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J75" s="7">
-        <f>F75*characterization!$G$17 + G75*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K75" s="7">
-        <f>F75*characterization!$L$17 + G75*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L75" s="7">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F75*IF(J75="TT",characterization!$B$17,IF(J75="FF",characterization!$G$17,characterization!$L$17))+G75*IF(J75="TT",characterization!$B$15,IF(J75="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L75" s="5">
+        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M75" s="7">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N75" s="7">
-        <f>IF(M75="TT",I75,IF(M75="FF",J75,IF(M75="SS",K75,"")))</f>
-        <v/>
-      </c>
-      <c r="O75" s="5">
-        <f>IFERROR(VLOOKUP(C75, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P75" s="7">
-        <f>O75 + N75</f>
-        <v/>
-      </c>
-      <c r="R75" s="7">
-        <f>IFERROR(L75 - P75 - VLOOKUP(C75, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C75, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S75" t="inlineStr">
+        <f>L75 + K75</f>
+        <v/>
+      </c>
+      <c r="O75" s="10">
+        <f>IFERROR(I75 - M75 - VLOOKUP(C75, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C75, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>from descriptor_engine[N]</t>
         </is>
@@ -8565,42 +7760,30 @@
         </is>
       </c>
       <c r="I77" s="7">
-        <f>F77*characterization!$B$17 + G77*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J77" s="7">
-        <f>F77*characterization!$G$17 + G77*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K77" s="7">
-        <f>F77*characterization!$L$17 + G77*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L77" s="7">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F77*IF(J77="TT",characterization!$B$17,IF(J77="FF",characterization!$G$17,characterization!$L$17))+G77*IF(J77="TT",characterization!$B$15,IF(J77="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L77" s="5">
+        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M77" s="7">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N77" s="7">
-        <f>IF(M77="TT",I77,IF(M77="FF",J77,IF(M77="SS",K77,"")))</f>
-        <v/>
-      </c>
-      <c r="O77" s="5">
-        <f>IFERROR(VLOOKUP(C77, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P77" s="7">
-        <f>O77 + N77</f>
-        <v/>
-      </c>
-      <c r="R77" s="7">
-        <f>IFERROR(L77 - P77 - VLOOKUP(C77, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C77, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S77" t="inlineStr">
+        <f>L77 + K77</f>
+        <v/>
+      </c>
+      <c r="O77" s="10">
+        <f>IFERROR(I77 - M77 - VLOOKUP(C77, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C77, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>from apbtodescr (kick-off)</t>
         </is>
@@ -8640,42 +7823,30 @@
         </is>
       </c>
       <c r="I78" s="7">
-        <f>F78*characterization!$B$17 + G78*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J78" s="7">
-        <f>F78*characterization!$G$17 + G78*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K78" s="7">
-        <f>F78*characterization!$L$17 + G78*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L78" s="7">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F78*IF(J78="TT",characterization!$B$17,IF(J78="FF",characterization!$G$17,characterization!$L$17))+G78*IF(J78="TT",characterization!$B$15,IF(J78="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L78" s="5">
+        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M78" s="7">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N78" s="7">
-        <f>IF(M78="TT",I78,IF(M78="FF",J78,IF(M78="SS",K78,"")))</f>
-        <v/>
-      </c>
-      <c r="O78" s="5">
-        <f>IFERROR(VLOOKUP(C78, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P78" s="7">
-        <f>O78 + N78</f>
-        <v/>
-      </c>
-      <c r="R78" s="7">
-        <f>IFERROR(L78 - P78 - VLOOKUP(C78, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C78, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S78" t="inlineStr">
+        <f>L78 + K78</f>
+        <v/>
+      </c>
+      <c r="O78" s="10">
+        <f>IFERROR(I78 - M78 - VLOOKUP(C78, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C78, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t>from apbtodescr</t>
         </is>
@@ -8715,42 +7886,30 @@
         </is>
       </c>
       <c r="I79" s="7">
-        <f>F79*characterization!$B$17 + G79*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J79" s="7">
-        <f>F79*characterization!$G$17 + G79*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K79" s="7">
-        <f>F79*characterization!$L$17 + G79*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L79" s="7">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F79*IF(J79="TT",characterization!$B$17,IF(J79="FF",characterization!$G$17,characterization!$L$17))+G79*IF(J79="TT",characterization!$B$15,IF(J79="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L79" s="5">
+        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M79" s="7">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N79" s="7">
-        <f>IF(M79="TT",I79,IF(M79="FF",J79,IF(M79="SS",K79,"")))</f>
-        <v/>
-      </c>
-      <c r="O79" s="5">
-        <f>IFERROR(VLOOKUP(C79, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P79" s="7">
-        <f>O79 + N79</f>
-        <v/>
-      </c>
-      <c r="R79" s="7">
-        <f>IFERROR(L79 - P79 - VLOOKUP(C79, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C79, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S79" t="inlineStr">
+        <f>L79 + K79</f>
+        <v/>
+      </c>
+      <c r="O79" s="10">
+        <f>IFERROR(I79 - M79 - VLOOKUP(C79, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C79, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>FSM IDLE -&gt; FETCH -&gt; WAIT_RDATA</t>
         </is>
@@ -8790,42 +7949,30 @@
         </is>
       </c>
       <c r="I80" s="7">
-        <f>F80*characterization!$B$17 + G80*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J80" s="7">
-        <f>F80*characterization!$G$17 + G80*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K80" s="7">
-        <f>F80*characterization!$L$17 + G80*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L80" s="7">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F80*IF(J80="TT",characterization!$B$17,IF(J80="FF",characterization!$G$17,characterization!$L$17))+G80*IF(J80="TT",characterization!$B$15,IF(J80="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L80" s="5">
+        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M80" s="7">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N80" s="7">
-        <f>IF(M80="TT",I80,IF(M80="FF",J80,IF(M80="SS",K80,"")))</f>
-        <v/>
-      </c>
-      <c r="O80" s="5">
-        <f>IFERROR(VLOOKUP(C80, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P80" s="7">
-        <f>O80 + N80</f>
-        <v/>
-      </c>
-      <c r="R80" s="7">
-        <f>IFERROR(L80 - P80 - VLOOKUP(C80, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C80, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S80" t="inlineStr">
+        <f>L80 + K80</f>
+        <v/>
+      </c>
+      <c r="O80" s="10">
+        <f>IFERROR(I80 - M80 - VLOOKUP(C80, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C80, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>drives ARADDR into the AR skid buffer</t>
         </is>
@@ -8865,42 +8012,30 @@
         </is>
       </c>
       <c r="I81" s="7">
-        <f>F81*characterization!$B$17 + G81*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J81" s="7">
-        <f>F81*characterization!$G$17 + G81*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K81" s="7">
-        <f>F81*characterization!$L$17 + G81*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L81" s="7">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F81*IF(J81="TT",characterization!$B$17,IF(J81="FF",characterization!$G$17,characterization!$L$17))+G81*IF(J81="TT",characterization!$B$15,IF(J81="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L81" s="5">
+        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M81" s="7">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N81" s="7">
-        <f>IF(M81="TT",I81,IF(M81="FF",J81,IF(M81="SS",K81,"")))</f>
-        <v/>
-      </c>
-      <c r="O81" s="5">
-        <f>IFERROR(VLOOKUP(C81, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P81" s="7">
-        <f>O81 + N81</f>
-        <v/>
-      </c>
-      <c r="R81" s="7">
-        <f>IFERROR(L81 - P81 - VLOOKUP(C81, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C81, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S81" t="inlineStr">
+        <f>L81 + K81</f>
+        <v/>
+      </c>
+      <c r="O81" s="10">
+        <f>IFERROR(I81 - M81 - VLOOKUP(C81, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C81, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>captured descriptor data from R-channel</t>
         </is>
@@ -8940,42 +8075,30 @@
         </is>
       </c>
       <c r="I82" s="7">
-        <f>F82*characterization!$B$17 + G82*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J82" s="7">
-        <f>F82*characterization!$G$17 + G82*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K82" s="7">
-        <f>F82*characterization!$L$17 + G82*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L82" s="7">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F82*IF(J82="TT",characterization!$B$17,IF(J82="FF",characterization!$G$17,characterization!$L$17))+G82*IF(J82="TT",characterization!$B$15,IF(J82="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L82" s="5">
+        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M82" s="7">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N82" s="7">
-        <f>IF(M82="TT",I82,IF(M82="FF",J82,IF(M82="SS",K82,"")))</f>
-        <v/>
-      </c>
-      <c r="O82" s="5">
-        <f>IFERROR(VLOOKUP(C82, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P82" s="7">
-        <f>O82 + N82</f>
-        <v/>
-      </c>
-      <c r="R82" s="7">
-        <f>IFERROR(L82 - P82 - VLOOKUP(C82, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C82, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S82" t="inlineStr">
+        <f>L82 + K82</f>
+        <v/>
+      </c>
+      <c r="O82" s="10">
+        <f>IFERROR(I82 - M82 - VLOOKUP(C82, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C82, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>decodes next_descriptor_ptr -&gt; re-arm FSM</t>
         </is>
@@ -9019,42 +8142,30 @@
         </is>
       </c>
       <c r="I83" s="7">
-        <f>F83*characterization!$B$17 + G83*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J83" s="7">
-        <f>F83*characterization!$G$17 + G83*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K83" s="7">
-        <f>F83*characterization!$L$17 + G83*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L83" s="7">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F83*IF(J83="TT",characterization!$B$17,IF(J83="FF",characterization!$G$17,characterization!$L$17))+G83*IF(J83="TT",characterization!$B$15,IF(J83="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L83" s="5">
+        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M83" s="7">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N83" s="7">
-        <f>IF(M83="TT",I83,IF(M83="FF",J83,IF(M83="SS",K83,"")))</f>
-        <v/>
-      </c>
-      <c r="O83" s="5">
-        <f>IFERROR(VLOOKUP(C83, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P83" s="7">
-        <f>O83 + N83</f>
-        <v/>
-      </c>
-      <c r="R83" s="7">
-        <f>IFERROR(L83 - P83 - VLOOKUP(C83, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C83, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S83" t="inlineStr">
+        <f>L83 + K83</f>
+        <v/>
+      </c>
+      <c r="O83" s="10">
+        <f>IFERROR(I83 - M83 - VLOOKUP(C83, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C83, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>to scheduler_group desc_axi master</t>
         </is>
@@ -9098,42 +8209,30 @@
         </is>
       </c>
       <c r="I84" s="7">
-        <f>F84*characterization!$B$17 + G84*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J84" s="7">
-        <f>F84*characterization!$G$17 + G84*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K84" s="7">
-        <f>F84*characterization!$L$17 + G84*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L84" s="7">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F84*IF(J84="TT",characterization!$B$17,IF(J84="FF",characterization!$G$17,characterization!$L$17))+G84*IF(J84="TT",characterization!$B$15,IF(J84="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L84" s="5">
+        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M84" s="7">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N84" s="7">
-        <f>IF(M84="TT",I84,IF(M84="FF",J84,IF(M84="SS",K84,"")))</f>
-        <v/>
-      </c>
-      <c r="O84" s="5">
-        <f>IFERROR(VLOOKUP(C84, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P84" s="7">
-        <f>O84 + N84</f>
-        <v/>
-      </c>
-      <c r="R84" s="7">
-        <f>IFERROR(L84 - P84 - VLOOKUP(C84, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C84, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S84" t="inlineStr">
+        <f>L84 + K84</f>
+        <v/>
+      </c>
+      <c r="O84" s="10">
+        <f>IFERROR(I84 - M84 - VLOOKUP(C84, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C84, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>from scheduler_group desc_axi master</t>
         </is>
@@ -9177,42 +8276,30 @@
         </is>
       </c>
       <c r="I85" s="7">
-        <f>F85*characterization!$B$17 + G85*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J85" s="7">
-        <f>F85*characterization!$G$17 + G85*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K85" s="7">
-        <f>F85*characterization!$L$17 + G85*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L85" s="7">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F85*IF(J85="TT",characterization!$B$17,IF(J85="FF",characterization!$G$17,characterization!$L$17))+G85*IF(J85="TT",characterization!$B$15,IF(J85="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L85" s="5">
+        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M85" s="7">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N85" s="7">
-        <f>IF(M85="TT",I85,IF(M85="FF",J85,IF(M85="SS",K85,"")))</f>
-        <v/>
-      </c>
-      <c r="O85" s="5">
-        <f>IFERROR(VLOOKUP(C85, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P85" s="7">
-        <f>O85 + N85</f>
-        <v/>
-      </c>
-      <c r="R85" s="7">
-        <f>IFERROR(L85 - P85 - VLOOKUP(C85, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C85, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S85" t="inlineStr">
+        <f>L85 + K85</f>
+        <v/>
+      </c>
+      <c r="O85" s="10">
+        <f>IFERROR(I85 - M85 - VLOOKUP(C85, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C85, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>to scheduler (descriptor dispatch)</t>
         </is>
@@ -9256,42 +8343,30 @@
         </is>
       </c>
       <c r="I86" s="7">
-        <f>F86*characterization!$B$17 + G86*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J86" s="7">
-        <f>F86*characterization!$G$17 + G86*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K86" s="7">
-        <f>F86*characterization!$L$17 + G86*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L86" s="7">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F86*IF(J86="TT",characterization!$B$17,IF(J86="FF",characterization!$G$17,characterization!$L$17))+G86*IF(J86="TT",characterization!$B$15,IF(J86="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L86" s="5">
+        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M86" s="7">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N86" s="7">
-        <f>IF(M86="TT",I86,IF(M86="FF",J86,IF(M86="SS",K86,"")))</f>
-        <v/>
-      </c>
-      <c r="O86" s="5">
-        <f>IFERROR(VLOOKUP(C86, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P86" s="7">
-        <f>O86 + N86</f>
-        <v/>
-      </c>
-      <c r="R86" s="7">
-        <f>IFERROR(L86 - P86 - VLOOKUP(C86, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C86, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S86" t="inlineStr">
+        <f>L86 + K86</f>
+        <v/>
+      </c>
+      <c r="O86" s="10">
+        <f>IFERROR(I86 - M86 - VLOOKUP(C86, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C86, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>to scheduler</t>
         </is>
@@ -9335,42 +8410,30 @@
         </is>
       </c>
       <c r="I87" s="7">
-        <f>F87*characterization!$B$17 + G87*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J87" s="7">
-        <f>F87*characterization!$G$17 + G87*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K87" s="7">
-        <f>F87*characterization!$L$17 + G87*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L87" s="7">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F87*IF(J87="TT",characterization!$B$17,IF(J87="FF",characterization!$G$17,characterization!$L$17))+G87*IF(J87="TT",characterization!$B$15,IF(J87="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L87" s="5">
+        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M87" s="7">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N87" s="7">
-        <f>IF(M87="TT",I87,IF(M87="FF",J87,IF(M87="SS",K87,"")))</f>
-        <v/>
-      </c>
-      <c r="O87" s="5">
-        <f>IFERROR(VLOOKUP(C87, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P87" s="7">
-        <f>O87 + N87</f>
-        <v/>
-      </c>
-      <c r="R87" s="7">
-        <f>IFERROR(L87 - P87 - VLOOKUP(C87, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C87, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S87" t="inlineStr">
+        <f>L87 + K87</f>
+        <v/>
+      </c>
+      <c r="O87" s="10">
+        <f>IFERROR(I87 - M87 - VLOOKUP(C87, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C87, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>from scheduler</t>
         </is>
@@ -9417,42 +8480,30 @@
         </is>
       </c>
       <c r="I89" s="7">
-        <f>F89*characterization!$B$17 + G89*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J89" s="7">
-        <f>F89*characterization!$G$17 + G89*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K89" s="7">
-        <f>F89*characterization!$L$17 + G89*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L89" s="7">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F89*IF(J89="TT",characterization!$B$17,IF(J89="FF",characterization!$G$17,characterization!$L$17))+G89*IF(J89="TT",characterization!$B$15,IF(J89="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L89" s="5">
+        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M89" s="7">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N89" s="7">
-        <f>IF(M89="TT",I89,IF(M89="FF",J89,IF(M89="SS",K89,"")))</f>
-        <v/>
-      </c>
-      <c r="O89" s="5">
-        <f>IFERROR(VLOOKUP(C89, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P89" s="7">
-        <f>O89 + N89</f>
-        <v/>
-      </c>
-      <c r="R89" s="7">
-        <f>IFERROR(L89 - P89 - VLOOKUP(C89, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C89, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S89" t="inlineStr">
+        <f>L89 + K89</f>
+        <v/>
+      </c>
+      <c r="O89" s="10">
+        <f>IFERROR(I89 - M89 - VLOOKUP(C89, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C89, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t>from descriptor_engine</t>
         </is>
@@ -9492,42 +8543,30 @@
         </is>
       </c>
       <c r="I90" s="7">
-        <f>F90*characterization!$B$17 + G90*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J90" s="7">
-        <f>F90*characterization!$G$17 + G90*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K90" s="7">
-        <f>F90*characterization!$L$17 + G90*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L90" s="7">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F90*IF(J90="TT",characterization!$B$17,IF(J90="FF",characterization!$G$17,characterization!$L$17))+G90*IF(J90="TT",characterization!$B$15,IF(J90="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L90" s="5">
+        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M90" s="7">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N90" s="7">
-        <f>IF(M90="TT",I90,IF(M90="FF",J90,IF(M90="SS",K90,"")))</f>
-        <v/>
-      </c>
-      <c r="O90" s="5">
-        <f>IFERROR(VLOOKUP(C90, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P90" s="7">
-        <f>O90 + N90</f>
-        <v/>
-      </c>
-      <c r="R90" s="7">
-        <f>IFERROR(L90 - P90 - VLOOKUP(C90, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C90, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S90" t="inlineStr">
+        <f>L90 + K90</f>
+        <v/>
+      </c>
+      <c r="O90" s="10">
+        <f>IFERROR(I90 - M90 - VLOOKUP(C90, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C90, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>from descriptor_engine: latch on accept</t>
         </is>
@@ -9567,42 +8606,30 @@
         </is>
       </c>
       <c r="I91" s="7">
-        <f>F91*characterization!$B$17 + G91*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J91" s="7">
-        <f>F91*characterization!$G$17 + G91*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K91" s="7">
-        <f>F91*characterization!$L$17 + G91*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L91" s="7">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F91*IF(J91="TT",characterization!$B$17,IF(J91="FF",characterization!$G$17,characterization!$L$17))+G91*IF(J91="TT",characterization!$B$15,IF(J91="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L91" s="5">
+        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M91" s="7">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N91" s="7">
-        <f>IF(M91="TT",I91,IF(M91="FF",J91,IF(M91="SS",K91,"")))</f>
-        <v/>
-      </c>
-      <c r="O91" s="5">
-        <f>IFERROR(VLOOKUP(C91, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P91" s="7">
-        <f>O91 + N91</f>
-        <v/>
-      </c>
-      <c r="R91" s="7">
-        <f>IFERROR(L91 - P91 - VLOOKUP(C91, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C91, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S91" t="inlineStr">
+        <f>L91 + K91</f>
+        <v/>
+      </c>
+      <c r="O91" s="10">
+        <f>IFERROR(I91 - M91 - VLOOKUP(C91, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C91, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>field unpack: SRC[63:0], DST[127:64], LEN[159:128]</t>
         </is>
@@ -9642,42 +8669,30 @@
         </is>
       </c>
       <c r="I92" s="7">
-        <f>F92*characterization!$B$17 + G92*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J92" s="7">
-        <f>F92*characterization!$G$17 + G92*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K92" s="7">
-        <f>F92*characterization!$L$17 + G92*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L92" s="7">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F92*IF(J92="TT",characterization!$B$17,IF(J92="FF",characterization!$G$17,characterization!$L$17))+G92*IF(J92="TT",characterization!$B$15,IF(J92="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L92" s="5">
+        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M92" s="7">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N92" s="7">
-        <f>IF(M92="TT",I92,IF(M92="FF",J92,IF(M92="SS",K92,"")))</f>
-        <v/>
-      </c>
-      <c r="O92" s="5">
-        <f>IFERROR(VLOOKUP(C92, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P92" s="7">
-        <f>O92 + N92</f>
-        <v/>
-      </c>
-      <c r="R92" s="7">
-        <f>IFERROR(L92 - P92 - VLOOKUP(C92, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C92, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S92" t="inlineStr">
+        <f>L92 + K92</f>
+        <v/>
+      </c>
+      <c r="O92" s="10">
+        <f>IFERROR(I92 - M92 - VLOOKUP(C92, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C92, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P92" t="inlineStr">
         <is>
           <t>FSM IDLE -&gt; ISSUE_RD -&gt; ISSUE_WR -&gt; WAIT</t>
         </is>
@@ -9717,42 +8732,30 @@
         </is>
       </c>
       <c r="I93" s="7">
-        <f>F93*characterization!$B$17 + G93*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J93" s="7">
-        <f>F93*characterization!$G$17 + G93*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K93" s="7">
-        <f>F93*characterization!$L$17 + G93*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L93" s="7">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F93*IF(J93="TT",characterization!$B$17,IF(J93="FF",characterization!$G$17,characterization!$L$17))+G93*IF(J93="TT",characterization!$B$15,IF(J93="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L93" s="5">
+        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M93" s="7">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N93" s="7">
-        <f>IF(M93="TT",I93,IF(M93="FF",J93,IF(M93="SS",K93,"")))</f>
-        <v/>
-      </c>
-      <c r="O93" s="5">
-        <f>IFERROR(VLOOKUP(C93, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P93" s="7">
-        <f>O93 + N93</f>
-        <v/>
-      </c>
-      <c r="R93" s="7">
-        <f>IFERROR(L93 - P93 - VLOOKUP(C93, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C93, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S93" t="inlineStr">
+        <f>L93 + K93</f>
+        <v/>
+      </c>
+      <c r="O93" s="10">
+        <f>IFERROR(I93 - M93 - VLOOKUP(C93, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C93, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>src_addr + (beats_issued * DW/8)</t>
         </is>
@@ -9792,42 +8795,30 @@
         </is>
       </c>
       <c r="I94" s="7">
-        <f>F94*characterization!$B$17 + G94*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J94" s="7">
-        <f>F94*characterization!$G$17 + G94*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K94" s="7">
-        <f>F94*characterization!$L$17 + G94*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L94" s="7">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F94*IF(J94="TT",characterization!$B$17,IF(J94="FF",characterization!$G$17,characterization!$L$17))+G94*IF(J94="TT",characterization!$B$15,IF(J94="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L94" s="5">
+        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M94" s="7">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N94" s="7">
-        <f>IF(M94="TT",I94,IF(M94="FF",J94,IF(M94="SS",K94,"")))</f>
-        <v/>
-      </c>
-      <c r="O94" s="5">
-        <f>IFERROR(VLOOKUP(C94, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P94" s="7">
-        <f>O94 + N94</f>
-        <v/>
-      </c>
-      <c r="R94" s="7">
-        <f>IFERROR(L94 - P94 - VLOOKUP(C94, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C94, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S94" t="inlineStr">
+        <f>L94 + K94</f>
+        <v/>
+      </c>
+      <c r="O94" s="10">
+        <f>IFERROR(I94 - M94 - VLOOKUP(C94, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C94, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P94" t="inlineStr">
         <is>
           <t>decrement on each request; 0 -&gt; COMPLETE</t>
         </is>
@@ -9867,42 +8858,30 @@
         </is>
       </c>
       <c r="I95" s="7">
-        <f>F95*characterization!$B$17 + G95*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J95" s="7">
-        <f>F95*characterization!$G$17 + G95*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K95" s="7">
-        <f>F95*characterization!$L$17 + G95*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L95" s="7">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F95*IF(J95="TT",characterization!$B$17,IF(J95="FF",characterization!$G$17,characterization!$L$17))+G95*IF(J95="TT",characterization!$B$15,IF(J95="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L95" s="5">
+        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M95" s="7">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N95" s="7">
-        <f>IF(M95="TT",I95,IF(M95="FF",J95,IF(M95="SS",K95,"")))</f>
-        <v/>
-      </c>
-      <c r="O95" s="5">
-        <f>IFERROR(VLOOKUP(C95, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P95" s="7">
-        <f>O95 + N95</f>
-        <v/>
-      </c>
-      <c r="R95" s="7">
-        <f>IFERROR(L95 - P95 - VLOOKUP(C95, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C95, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S95" t="inlineStr">
+        <f>L95 + K95</f>
+        <v/>
+      </c>
+      <c r="O95" s="10">
+        <f>IFERROR(I95 - M95 - VLOOKUP(C95, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C95, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>request flow-control counter</t>
         </is>
@@ -9942,42 +8921,30 @@
         </is>
       </c>
       <c r="I96" s="7">
-        <f>F96*characterization!$B$17 + G96*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J96" s="7">
-        <f>F96*characterization!$G$17 + G96*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K96" s="7">
-        <f>F96*characterization!$L$17 + G96*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L96" s="7">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F96*IF(J96="TT",characterization!$B$17,IF(J96="FF",characterization!$G$17,characterization!$L$17))+G96*IF(J96="TT",characterization!$B$15,IF(J96="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L96" s="5">
+        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M96" s="7">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N96" s="7">
-        <f>IF(M96="TT",I96,IF(M96="FF",J96,IF(M96="SS",K96,"")))</f>
-        <v/>
-      </c>
-      <c r="O96" s="5">
-        <f>IFERROR(VLOOKUP(C96, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P96" s="7">
-        <f>O96 + N96</f>
-        <v/>
-      </c>
-      <c r="R96" s="7">
-        <f>IFERROR(L96 - P96 - VLOOKUP(C96, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C96, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S96" t="inlineStr">
+        <f>L96 + K96</f>
+        <v/>
+      </c>
+      <c r="O96" s="10">
+        <f>IFERROR(I96 - M96 - VLOOKUP(C96, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C96, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P96" t="inlineStr">
         <is>
           <t>to axi_read_engine (per-channel request)</t>
         </is>
@@ -10017,42 +8984,30 @@
         </is>
       </c>
       <c r="I97" s="7">
-        <f>F97*characterization!$B$17 + G97*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J97" s="7">
-        <f>F97*characterization!$G$17 + G97*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K97" s="7">
-        <f>F97*characterization!$L$17 + G97*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L97" s="7">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F97*IF(J97="TT",characterization!$B$17,IF(J97="FF",characterization!$G$17,characterization!$L$17))+G97*IF(J97="TT",characterization!$B$15,IF(J97="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L97" s="5">
+        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M97" s="7">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N97" s="7">
-        <f>IF(M97="TT",I97,IF(M97="FF",J97,IF(M97="SS",K97,"")))</f>
-        <v/>
-      </c>
-      <c r="O97" s="5">
-        <f>IFERROR(VLOOKUP(C97, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P97" s="7">
-        <f>O97 + N97</f>
-        <v/>
-      </c>
-      <c r="R97" s="7">
-        <f>IFERROR(L97 - P97 - VLOOKUP(C97, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C97, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S97" t="inlineStr">
+        <f>L97 + K97</f>
+        <v/>
+      </c>
+      <c r="O97" s="10">
+        <f>IFERROR(I97 - M97 - VLOOKUP(C97, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C97, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P97" t="inlineStr">
         <is>
           <t>to axi_read_engine</t>
         </is>
@@ -10092,42 +9047,30 @@
         </is>
       </c>
       <c r="I98" s="7">
-        <f>F98*characterization!$B$17 + G98*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J98" s="7">
-        <f>F98*characterization!$G$17 + G98*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K98" s="7">
-        <f>F98*characterization!$L$17 + G98*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L98" s="7">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F98*IF(J98="TT",characterization!$B$17,IF(J98="FF",characterization!$G$17,characterization!$L$17))+G98*IF(J98="TT",characterization!$B$15,IF(J98="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L98" s="5">
+        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M98" s="7">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N98" s="7">
-        <f>IF(M98="TT",I98,IF(M98="FF",J98,IF(M98="SS",K98,"")))</f>
-        <v/>
-      </c>
-      <c r="O98" s="5">
-        <f>IFERROR(VLOOKUP(C98, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P98" s="7">
-        <f>O98 + N98</f>
-        <v/>
-      </c>
-      <c r="R98" s="7">
-        <f>IFERROR(L98 - P98 - VLOOKUP(C98, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C98, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S98" t="inlineStr">
+        <f>L98 + K98</f>
+        <v/>
+      </c>
+      <c r="O98" s="10">
+        <f>IFERROR(I98 - M98 - VLOOKUP(C98, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C98, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -10167,42 +9110,30 @@
         </is>
       </c>
       <c r="I99" s="7">
-        <f>F99*characterization!$B$17 + G99*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J99" s="7">
-        <f>F99*characterization!$G$17 + G99*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K99" s="7">
-        <f>F99*characterization!$L$17 + G99*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L99" s="7">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F99*IF(J99="TT",characterization!$B$17,IF(J99="FF",characterization!$G$17,characterization!$L$17))+G99*IF(J99="TT",characterization!$B$15,IF(J99="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L99" s="5">
+        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M99" s="7">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N99" s="7">
-        <f>IF(M99="TT",I99,IF(M99="FF",J99,IF(M99="SS",K99,"")))</f>
-        <v/>
-      </c>
-      <c r="O99" s="5">
-        <f>IFERROR(VLOOKUP(C99, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P99" s="7">
-        <f>O99 + N99</f>
-        <v/>
-      </c>
-      <c r="R99" s="7">
-        <f>IFERROR(L99 - P99 - VLOOKUP(C99, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C99, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S99" t="inlineStr">
+        <f>L99 + K99</f>
+        <v/>
+      </c>
+      <c r="O99" s="10">
+        <f>IFERROR(I99 - M99 - VLOOKUP(C99, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C99, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P99" t="inlineStr">
         <is>
           <t>to axi_write_engine</t>
         </is>
@@ -10242,42 +9173,30 @@
         </is>
       </c>
       <c r="I100" s="7">
-        <f>F100*characterization!$B$17 + G100*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J100" s="7">
-        <f>F100*characterization!$G$17 + G100*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K100" s="7">
-        <f>F100*characterization!$L$17 + G100*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L100" s="7">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F100*IF(J100="TT",characterization!$B$17,IF(J100="FF",characterization!$G$17,characterization!$L$17))+G100*IF(J100="TT",characterization!$B$15,IF(J100="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L100" s="5">
+        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M100" s="7">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N100" s="7">
-        <f>IF(M100="TT",I100,IF(M100="FF",J100,IF(M100="SS",K100,"")))</f>
-        <v/>
-      </c>
-      <c r="O100" s="5">
-        <f>IFERROR(VLOOKUP(C100, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P100" s="7">
-        <f>O100 + N100</f>
-        <v/>
-      </c>
-      <c r="R100" s="7">
-        <f>IFERROR(L100 - P100 - VLOOKUP(C100, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C100, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S100" t="inlineStr">
+        <f>L100 + K100</f>
+        <v/>
+      </c>
+      <c r="O100" s="10">
+        <f>IFERROR(I100 - M100 - VLOOKUP(C100, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C100, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>to perf_profiler</t>
         </is>
@@ -10317,42 +9236,30 @@
         </is>
       </c>
       <c r="I101" s="7">
-        <f>F101*characterization!$B$17 + G101*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J101" s="7">
-        <f>F101*characterization!$G$17 + G101*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K101" s="7">
-        <f>F101*characterization!$L$17 + G101*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L101" s="7">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F101*IF(J101="TT",characterization!$B$17,IF(J101="FF",characterization!$G$17,characterization!$L$17))+G101*IF(J101="TT",characterization!$B$15,IF(J101="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L101" s="5">
+        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M101" s="7">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N101" s="7">
-        <f>IF(M101="TT",I101,IF(M101="FF",J101,IF(M101="SS",K101,"")))</f>
-        <v/>
-      </c>
-      <c r="O101" s="5">
-        <f>IFERROR(VLOOKUP(C101, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P101" s="7">
-        <f>O101 + N101</f>
-        <v/>
-      </c>
-      <c r="R101" s="7">
-        <f>IFERROR(L101 - P101 - VLOOKUP(C101, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C101, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S101" t="inlineStr">
+        <f>L101 + K101</f>
+        <v/>
+      </c>
+      <c r="O101" s="10">
+        <f>IFERROR(I101 - M101 - VLOOKUP(C101, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C101, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>to monbus_reporter</t>
         </is>
@@ -10392,42 +9299,30 @@
         </is>
       </c>
       <c r="I102" s="7">
-        <f>F102*characterization!$B$17 + G102*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J102" s="7">
-        <f>F102*characterization!$G$17 + G102*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K102" s="7">
-        <f>F102*characterization!$L$17 + G102*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L102" s="7">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F102*IF(J102="TT",characterization!$B$17,IF(J102="FF",characterization!$G$17,characterization!$L$17))+G102*IF(J102="TT",characterization!$B$15,IF(J102="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L102" s="5">
+        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M102" s="7">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N102" s="7">
-        <f>IF(M102="TT",I102,IF(M102="FF",J102,IF(M102="SS",K102,"")))</f>
-        <v/>
-      </c>
-      <c r="O102" s="5">
-        <f>IFERROR(VLOOKUP(C102, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P102" s="7">
-        <f>O102 + N102</f>
-        <v/>
-      </c>
-      <c r="R102" s="7">
-        <f>IFERROR(L102 - P102 - VLOOKUP(C102, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C102, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S102" t="inlineStr">
+        <f>L102 + K102</f>
+        <v/>
+      </c>
+      <c r="O102" s="10">
+        <f>IFERROR(I102 - M102 - VLOOKUP(C102, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C102, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P102" t="inlineStr">
         <is>
           <t>to monbus group / reporter</t>
         </is>
@@ -10474,42 +9369,30 @@
         </is>
       </c>
       <c r="I104" s="7">
-        <f>F104*characterization!$B$17 + G104*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J104" s="7">
-        <f>F104*characterization!$G$17 + G104*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K104" s="7">
-        <f>F104*characterization!$L$17 + G104*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L104" s="7">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F104*IF(J104="TT",characterization!$B$17,IF(J104="FF",characterization!$G$17,characterization!$L$17))+G104*IF(J104="TT",characterization!$B$15,IF(J104="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L104" s="5">
+        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M104" s="7">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N104" s="7">
-        <f>IF(M104="TT",I104,IF(M104="FF",J104,IF(M104="SS",K104,"")))</f>
-        <v/>
-      </c>
-      <c r="O104" s="5">
-        <f>IFERROR(VLOOKUP(C104, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P104" s="7">
-        <f>O104 + N104</f>
-        <v/>
-      </c>
-      <c r="R104" s="7">
-        <f>IFERROR(L104 - P104 - VLOOKUP(C104, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C104, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S104" t="inlineStr">
+        <f>L104 + K104</f>
+        <v/>
+      </c>
+      <c r="O104" s="10">
+        <f>IFERROR(I104 - M104 - VLOOKUP(C104, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C104, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P104" t="inlineStr">
         <is>
           <t>from scheduler[N] (per-channel)</t>
         </is>
@@ -10549,42 +9432,30 @@
         </is>
       </c>
       <c r="I105" s="7">
-        <f>F105*characterization!$B$17 + G105*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J105" s="7">
-        <f>F105*characterization!$G$17 + G105*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K105" s="7">
-        <f>F105*characterization!$L$17 + G105*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L105" s="7">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F105*IF(J105="TT",characterization!$B$17,IF(J105="FF",characterization!$G$17,characterization!$L$17))+G105*IF(J105="TT",characterization!$B$15,IF(J105="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L105" s="5">
+        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M105" s="7">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N105" s="7">
-        <f>IF(M105="TT",I105,IF(M105="FF",J105,IF(M105="SS",K105,"")))</f>
-        <v/>
-      </c>
-      <c r="O105" s="5">
-        <f>IFERROR(VLOOKUP(C105, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P105" s="7">
-        <f>O105 + N105</f>
-        <v/>
-      </c>
-      <c r="R105" s="7">
-        <f>IFERROR(L105 - P105 - VLOOKUP(C105, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C105, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S105" t="inlineStr">
+        <f>L105 + K105</f>
+        <v/>
+      </c>
+      <c r="O105" s="10">
+        <f>IFERROR(I105 - M105 - VLOOKUP(C105, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C105, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P105" t="inlineStr">
         <is>
           <t>from scheduler[N]</t>
         </is>
@@ -10624,42 +9495,30 @@
         </is>
       </c>
       <c r="I106" s="7">
-        <f>F106*characterization!$B$17 + G106*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J106" s="7">
-        <f>F106*characterization!$G$17 + G106*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K106" s="7">
-        <f>F106*characterization!$L$17 + G106*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L106" s="7">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F106*IF(J106="TT",characterization!$B$17,IF(J106="FF",characterization!$G$17,characterization!$L$17))+G106*IF(J106="TT",characterization!$B$15,IF(J106="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L106" s="5">
+        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M106" s="7">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N106" s="7">
-        <f>IF(M106="TT",I106,IF(M106="FF",J106,IF(M106="SS",K106,"")))</f>
-        <v/>
-      </c>
-      <c r="O106" s="5">
-        <f>IFERROR(VLOOKUP(C106, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P106" s="7">
-        <f>O106 + N106</f>
-        <v/>
-      </c>
-      <c r="R106" s="7">
-        <f>IFERROR(L106 - P106 - VLOOKUP(C106, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C106, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S106" t="inlineStr">
+        <f>L106 + K106</f>
+        <v/>
+      </c>
+      <c r="O106" s="10">
+        <f>IFERROR(I106 - M106 - VLOOKUP(C106, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C106, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P106" t="inlineStr">
         <is>
           <t>round-robin output latch</t>
         </is>
@@ -10699,42 +9558,30 @@
         </is>
       </c>
       <c r="I107" s="7">
-        <f>F107*characterization!$B$17 + G107*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J107" s="7">
-        <f>F107*characterization!$G$17 + G107*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K107" s="7">
-        <f>F107*characterization!$L$17 + G107*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L107" s="7">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F107*IF(J107="TT",characterization!$B$17,IF(J107="FF",characterization!$G$17,characterization!$L$17))+G107*IF(J107="TT",characterization!$B$15,IF(J107="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L107" s="5">
+        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M107" s="7">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N107" s="7">
-        <f>IF(M107="TT",I107,IF(M107="FF",J107,IF(M107="SS",K107,"")))</f>
-        <v/>
-      </c>
-      <c r="O107" s="5">
-        <f>IFERROR(VLOOKUP(C107, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P107" s="7">
-        <f>O107 + N107</f>
-        <v/>
-      </c>
-      <c r="R107" s="7">
-        <f>IFERROR(L107 - P107 - VLOOKUP(C107, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C107, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S107" t="inlineStr">
+        <f>L107 + K107</f>
+        <v/>
+      </c>
+      <c r="O107" s="10">
+        <f>IFERROR(I107 - M107 - VLOOKUP(C107, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C107, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P107" t="inlineStr">
         <is>
           <t>channel context for AR launch + R capture</t>
         </is>
@@ -10774,42 +9621,30 @@
         </is>
       </c>
       <c r="I108" s="7">
-        <f>F108*characterization!$B$17 + G108*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J108" s="7">
-        <f>F108*characterization!$G$17 + G108*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K108" s="7">
-        <f>F108*characterization!$L$17 + G108*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L108" s="7">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F108*IF(J108="TT",characterization!$B$17,IF(J108="FF",characterization!$G$17,characterization!$L$17))+G108*IF(J108="TT",characterization!$B$15,IF(J108="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L108" s="5">
+        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M108" s="7">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N108" s="7">
-        <f>IF(M108="TT",I108,IF(M108="FF",J108,IF(M108="SS",K108,"")))</f>
-        <v/>
-      </c>
-      <c r="O108" s="5">
-        <f>IFERROR(VLOOKUP(C108, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P108" s="7">
-        <f>O108 + N108</f>
-        <v/>
-      </c>
-      <c r="R108" s="7">
-        <f>IFERROR(L108 - P108 - VLOOKUP(C108, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C108, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S108" t="inlineStr">
+        <f>L108 + K108</f>
+        <v/>
+      </c>
+      <c r="O108" s="10">
+        <f>IFERROR(I108 - M108 - VLOOKUP(C108, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C108, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P108" t="inlineStr">
         <is>
           <t>pipelined ARADDR before skid</t>
         </is>
@@ -10849,42 +9684,30 @@
         </is>
       </c>
       <c r="I109" s="7">
-        <f>F109*characterization!$B$17 + G109*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J109" s="7">
-        <f>F109*characterization!$G$17 + G109*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K109" s="7">
-        <f>F109*characterization!$L$17 + G109*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L109" s="7">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F109*IF(J109="TT",characterization!$B$17,IF(J109="FF",characterization!$G$17,characterization!$L$17))+G109*IF(J109="TT",characterization!$B$15,IF(J109="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L109" s="5">
+        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M109" s="7">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N109" s="7">
-        <f>IF(M109="TT",I109,IF(M109="FF",J109,IF(M109="SS",K109,"")))</f>
-        <v/>
-      </c>
-      <c r="O109" s="5">
-        <f>IFERROR(VLOOKUP(C109, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P109" s="7">
-        <f>O109 + N109</f>
-        <v/>
-      </c>
-      <c r="R109" s="7">
-        <f>IFERROR(L109 - P109 - VLOOKUP(C109, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C109, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S109" t="inlineStr">
+        <f>L109 + K109</f>
+        <v/>
+      </c>
+      <c r="O109" s="10">
+        <f>IFERROR(I109 - M109 - VLOOKUP(C109, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C109, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>registered request to skid</t>
         </is>
@@ -10924,42 +9747,30 @@
         </is>
       </c>
       <c r="I110" s="7">
-        <f>F110*characterization!$B$17 + G110*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J110" s="7">
-        <f>F110*characterization!$G$17 + G110*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K110" s="7">
-        <f>F110*characterization!$L$17 + G110*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L110" s="7">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F110*IF(J110="TT",characterization!$B$17,IF(J110="FF",characterization!$G$17,characterization!$L$17))+G110*IF(J110="TT",characterization!$B$15,IF(J110="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L110" s="5">
+        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M110" s="7">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N110" s="7">
-        <f>IF(M110="TT",I110,IF(M110="FF",J110,IF(M110="SS",K110,"")))</f>
-        <v/>
-      </c>
-      <c r="O110" s="5">
-        <f>IFERROR(VLOOKUP(C110, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P110" s="7">
-        <f>O110 + N110</f>
-        <v/>
-      </c>
-      <c r="R110" s="7">
-        <f>IFERROR(L110 - P110 - VLOOKUP(C110, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C110, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S110" t="inlineStr">
+        <f>L110 + K110</f>
+        <v/>
+      </c>
+      <c r="O110" s="10">
+        <f>IFERROR(I110 - M110 - VLOOKUP(C110, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C110, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P110" t="inlineStr">
         <is>
           <t>per-channel in-flight counter</t>
         </is>
@@ -10999,42 +9810,30 @@
         </is>
       </c>
       <c r="I111" s="7">
-        <f>F111*characterization!$B$17 + G111*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J111" s="7">
-        <f>F111*characterization!$G$17 + G111*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K111" s="7">
-        <f>F111*characterization!$L$17 + G111*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L111" s="7">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F111*IF(J111="TT",characterization!$B$17,IF(J111="FF",characterization!$G$17,characterization!$L$17))+G111*IF(J111="TT",characterization!$B$15,IF(J111="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L111" s="5">
+        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M111" s="7">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N111" s="7">
-        <f>IF(M111="TT",I111,IF(M111="FF",J111,IF(M111="SS",K111,"")))</f>
-        <v/>
-      </c>
-      <c r="O111" s="5">
-        <f>IFERROR(VLOOKUP(C111, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P111" s="7">
-        <f>O111 + N111</f>
-        <v/>
-      </c>
-      <c r="R111" s="7">
-        <f>IFERROR(L111 - P111 - VLOOKUP(C111, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C111, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S111" t="inlineStr">
+        <f>L111 + K111</f>
+        <v/>
+      </c>
+      <c r="O111" s="10">
+        <f>IFERROR(I111 - M111 - VLOOKUP(C111, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C111, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P111" t="inlineStr">
         <is>
           <t>monotonic AXI ID generator</t>
         </is>
@@ -11078,42 +9877,30 @@
         </is>
       </c>
       <c r="I112" s="7">
-        <f>F112*characterization!$B$17 + G112*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J112" s="7">
-        <f>F112*characterization!$G$17 + G112*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K112" s="7">
-        <f>F112*characterization!$L$17 + G112*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L112" s="7">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F112*IF(J112="TT",characterization!$B$17,IF(J112="FF",characterization!$G$17,characterization!$L$17))+G112*IF(J112="TT",characterization!$B$15,IF(J112="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L112" s="5">
+        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M112" s="7">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N112" s="7">
-        <f>IF(M112="TT",I112,IF(M112="FF",J112,IF(M112="SS",K112,"")))</f>
-        <v/>
-      </c>
-      <c r="O112" s="5">
-        <f>IFERROR(VLOOKUP(C112, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P112" s="7">
-        <f>O112 + N112</f>
-        <v/>
-      </c>
-      <c r="R112" s="7">
-        <f>IFERROR(L112 - P112 - VLOOKUP(C112, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C112, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S112" t="inlineStr">
+        <f>L112 + K112</f>
+        <v/>
+      </c>
+      <c r="O112" s="10">
+        <f>IFERROR(I112 - M112 - VLOOKUP(C112, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C112, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P112" t="inlineStr">
         <is>
           <t>to AXI4 master read system bus</t>
         </is>
@@ -11157,42 +9944,30 @@
         </is>
       </c>
       <c r="I113" s="7">
-        <f>F113*characterization!$B$17 + G113*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J113" s="7">
-        <f>F113*characterization!$G$17 + G113*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K113" s="7">
-        <f>F113*characterization!$L$17 + G113*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L113" s="7">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F113*IF(J113="TT",characterization!$B$17,IF(J113="FF",characterization!$G$17,characterization!$L$17))+G113*IF(J113="TT",characterization!$B$15,IF(J113="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L113" s="5">
+        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M113" s="7">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N113" s="7">
-        <f>IF(M113="TT",I113,IF(M113="FF",J113,IF(M113="SS",K113,"")))</f>
-        <v/>
-      </c>
-      <c r="O113" s="5">
-        <f>IFERROR(VLOOKUP(C113, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P113" s="7">
-        <f>O113 + N113</f>
-        <v/>
-      </c>
-      <c r="R113" s="7">
-        <f>IFERROR(L113 - P113 - VLOOKUP(C113, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C113, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S113" t="inlineStr">
+        <f>L113 + K113</f>
+        <v/>
+      </c>
+      <c r="O113" s="10">
+        <f>IFERROR(I113 - M113 - VLOOKUP(C113, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C113, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P113" t="inlineStr">
         <is>
           <t>from AXI4 master read system bus</t>
         </is>
@@ -11232,42 +10007,30 @@
         </is>
       </c>
       <c r="I114" s="7">
-        <f>F114*characterization!$B$17 + G114*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J114" s="7">
-        <f>F114*characterization!$G$17 + G114*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K114" s="7">
-        <f>F114*characterization!$L$17 + G114*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L114" s="7">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F114*IF(J114="TT",characterization!$B$17,IF(J114="FF",characterization!$G$17,characterization!$L$17))+G114*IF(J114="TT",characterization!$B$15,IF(J114="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L114" s="5">
+        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M114" s="7">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N114" s="7">
-        <f>IF(M114="TT",I114,IF(M114="FF",J114,IF(M114="SS",K114,"")))</f>
-        <v/>
-      </c>
-      <c r="O114" s="5">
-        <f>IFERROR(VLOOKUP(C114, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P114" s="7">
-        <f>O114 + N114</f>
-        <v/>
-      </c>
-      <c r="R114" s="7">
-        <f>IFERROR(L114 - P114 - VLOOKUP(C114, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C114, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S114" t="inlineStr">
+        <f>L114 + K114</f>
+        <v/>
+      </c>
+      <c r="O114" s="10">
+        <f>IFERROR(I114 - M114 - VLOOKUP(C114, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C114, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P114" t="inlineStr">
         <is>
           <t>to sram_controller_unit[N] (reserve burst space)</t>
         </is>
@@ -11307,42 +10070,30 @@
         </is>
       </c>
       <c r="I115" s="7">
-        <f>F115*characterization!$B$17 + G115*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J115" s="7">
-        <f>F115*characterization!$G$17 + G115*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K115" s="7">
-        <f>F115*characterization!$L$17 + G115*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L115" s="7">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F115*IF(J115="TT",characterization!$B$17,IF(J115="FF",characterization!$G$17,characterization!$L$17))+G115*IF(J115="TT",characterization!$B$15,IF(J115="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L115" s="5">
+        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M115" s="7">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N115" s="7">
-        <f>IF(M115="TT",I115,IF(M115="FF",J115,IF(M115="SS",K115,"")))</f>
-        <v/>
-      </c>
-      <c r="O115" s="5">
-        <f>IFERROR(VLOOKUP(C115, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P115" s="7">
-        <f>O115 + N115</f>
-        <v/>
-      </c>
-      <c r="R115" s="7">
-        <f>IFERROR(L115 - P115 - VLOOKUP(C115, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C115, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S115" t="inlineStr">
+        <f>L115 + K115</f>
+        <v/>
+      </c>
+      <c r="O115" s="10">
+        <f>IFERROR(I115 - M115 - VLOOKUP(C115, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C115, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P115" t="inlineStr">
         <is>
           <t>from sram_controller_unit[N]</t>
         </is>
@@ -11382,42 +10133,30 @@
         </is>
       </c>
       <c r="I116" s="7">
-        <f>F116*characterization!$B$17 + G116*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J116" s="7">
-        <f>F116*characterization!$G$17 + G116*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K116" s="7">
-        <f>F116*characterization!$L$17 + G116*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L116" s="7">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F116*IF(J116="TT",characterization!$B$17,IF(J116="FF",characterization!$G$17,characterization!$L$17))+G116*IF(J116="TT",characterization!$B$15,IF(J116="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L116" s="5">
+        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M116" s="7">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N116" s="7">
-        <f>IF(M116="TT",I116,IF(M116="FF",J116,IF(M116="SS",K116,"")))</f>
-        <v/>
-      </c>
-      <c r="O116" s="5">
-        <f>IFERROR(VLOOKUP(C116, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P116" s="7">
-        <f>O116 + N116</f>
-        <v/>
-      </c>
-      <c r="R116" s="7">
-        <f>IFERROR(L116 - P116 - VLOOKUP(C116, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C116, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S116" t="inlineStr">
+        <f>L116 + K116</f>
+        <v/>
+      </c>
+      <c r="O116" s="10">
+        <f>IFERROR(I116 - M116 - VLOOKUP(C116, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C116, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P116" t="inlineStr">
         <is>
           <t>to sram_controller_unit[N].wr</t>
         </is>
@@ -11457,42 +10196,30 @@
         </is>
       </c>
       <c r="I117" s="7">
-        <f>F117*characterization!$B$17 + G117*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J117" s="7">
-        <f>F117*characterization!$G$17 + G117*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K117" s="7">
-        <f>F117*characterization!$L$17 + G117*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L117" s="7">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F117*IF(J117="TT",characterization!$B$17,IF(J117="FF",characterization!$G$17,characterization!$L$17))+G117*IF(J117="TT",characterization!$B$15,IF(J117="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L117" s="5">
+        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M117" s="7">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N117" s="7">
-        <f>IF(M117="TT",I117,IF(M117="FF",J117,IF(M117="SS",K117,"")))</f>
-        <v/>
-      </c>
-      <c r="O117" s="5">
-        <f>IFERROR(VLOOKUP(C117, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P117" s="7">
-        <f>O117 + N117</f>
-        <v/>
-      </c>
-      <c r="R117" s="7">
-        <f>IFERROR(L117 - P117 - VLOOKUP(C117, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C117, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S117" t="inlineStr">
+        <f>L117 + K117</f>
+        <v/>
+      </c>
+      <c r="O117" s="10">
+        <f>IFERROR(I117 - M117 - VLOOKUP(C117, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C117, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P117" t="inlineStr">
         <is>
           <t>to sram_controller_unit[N].wr (channel-id muxed)</t>
         </is>
@@ -11539,42 +10266,30 @@
         </is>
       </c>
       <c r="I119" s="7">
-        <f>F119*characterization!$B$17 + G119*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J119" s="7">
-        <f>F119*characterization!$G$17 + G119*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K119" s="7">
-        <f>F119*characterization!$L$17 + G119*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L119" s="7">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F119*IF(J119="TT",characterization!$B$17,IF(J119="FF",characterization!$G$17,characterization!$L$17))+G119*IF(J119="TT",characterization!$B$15,IF(J119="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L119" s="5">
+        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M119" s="7">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N119" s="7">
-        <f>IF(M119="TT",I119,IF(M119="FF",J119,IF(M119="SS",K119,"")))</f>
-        <v/>
-      </c>
-      <c r="O119" s="5">
-        <f>IFERROR(VLOOKUP(C119, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P119" s="7">
-        <f>O119 + N119</f>
-        <v/>
-      </c>
-      <c r="R119" s="7">
-        <f>IFERROR(L119 - P119 - VLOOKUP(C119, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C119, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S119" t="inlineStr">
+        <f>L119 + K119</f>
+        <v/>
+      </c>
+      <c r="O119" s="10">
+        <f>IFERROR(I119 - M119 - VLOOKUP(C119, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C119, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P119" t="inlineStr">
         <is>
           <t>from scheduler[N]</t>
         </is>
@@ -11614,42 +10329,30 @@
         </is>
       </c>
       <c r="I120" s="7">
-        <f>F120*characterization!$B$17 + G120*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J120" s="7">
-        <f>F120*characterization!$G$17 + G120*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K120" s="7">
-        <f>F120*characterization!$L$17 + G120*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L120" s="7">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F120*IF(J120="TT",characterization!$B$17,IF(J120="FF",characterization!$G$17,characterization!$L$17))+G120*IF(J120="TT",characterization!$B$15,IF(J120="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L120" s="5">
+        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M120" s="7">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N120" s="7">
-        <f>IF(M120="TT",I120,IF(M120="FF",J120,IF(M120="SS",K120,"")))</f>
-        <v/>
-      </c>
-      <c r="O120" s="5">
-        <f>IFERROR(VLOOKUP(C120, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P120" s="7">
-        <f>O120 + N120</f>
-        <v/>
-      </c>
-      <c r="R120" s="7">
-        <f>IFERROR(L120 - P120 - VLOOKUP(C120, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C120, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S120" t="inlineStr">
+        <f>L120 + K120</f>
+        <v/>
+      </c>
+      <c r="O120" s="10">
+        <f>IFERROR(I120 - M120 - VLOOKUP(C120, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C120, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P120" t="inlineStr">
         <is>
           <t>from scheduler[N]</t>
         </is>
@@ -11689,42 +10392,30 @@
         </is>
       </c>
       <c r="I121" s="7">
-        <f>F121*characterization!$B$17 + G121*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J121" s="7">
-        <f>F121*characterization!$G$17 + G121*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K121" s="7">
-        <f>F121*characterization!$L$17 + G121*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L121" s="7">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F121*IF(J121="TT",characterization!$B$17,IF(J121="FF",characterization!$G$17,characterization!$L$17))+G121*IF(J121="TT",characterization!$B$15,IF(J121="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L121" s="5">
+        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M121" s="7">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N121" s="7">
-        <f>IF(M121="TT",I121,IF(M121="FF",J121,IF(M121="SS",K121,"")))</f>
-        <v/>
-      </c>
-      <c r="O121" s="5">
-        <f>IFERROR(VLOOKUP(C121, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P121" s="7">
-        <f>O121 + N121</f>
-        <v/>
-      </c>
-      <c r="R121" s="7">
-        <f>IFERROR(L121 - P121 - VLOOKUP(C121, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C121, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S121" t="inlineStr">
+        <f>L121 + K121</f>
+        <v/>
+      </c>
+      <c r="O121" s="10">
+        <f>IFERROR(I121 - M121 - VLOOKUP(C121, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C121, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P121" t="inlineStr">
         <is>
           <t>from sram_controller_unit[N] (data ready)</t>
         </is>
@@ -11764,42 +10455,30 @@
         </is>
       </c>
       <c r="I122" s="7">
-        <f>F122*characterization!$B$17 + G122*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J122" s="7">
-        <f>F122*characterization!$G$17 + G122*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K122" s="7">
-        <f>F122*characterization!$L$17 + G122*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L122" s="7">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F122*IF(J122="TT",characterization!$B$17,IF(J122="FF",characterization!$G$17,characterization!$L$17))+G122*IF(J122="TT",characterization!$B$15,IF(J122="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L122" s="5">
+        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M122" s="7">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N122" s="7">
-        <f>IF(M122="TT",I122,IF(M122="FF",J122,IF(M122="SS",K122,"")))</f>
-        <v/>
-      </c>
-      <c r="O122" s="5">
-        <f>IFERROR(VLOOKUP(C122, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P122" s="7">
-        <f>O122 + N122</f>
-        <v/>
-      </c>
-      <c r="R122" s="7">
-        <f>IFERROR(L122 - P122 - VLOOKUP(C122, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C122, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S122" t="inlineStr">
+        <f>L122 + K122</f>
+        <v/>
+      </c>
+      <c r="O122" s="10">
+        <f>IFERROR(I122 - M122 - VLOOKUP(C122, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C122, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P122" t="inlineStr">
         <is>
           <t>from sram_controller_unit[N]</t>
         </is>
@@ -11839,42 +10518,30 @@
         </is>
       </c>
       <c r="I123" s="7">
-        <f>F123*characterization!$B$17 + G123*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J123" s="7">
-        <f>F123*characterization!$G$17 + G123*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K123" s="7">
-        <f>F123*characterization!$L$17 + G123*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L123" s="7">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F123*IF(J123="TT",characterization!$B$17,IF(J123="FF",characterization!$G$17,characterization!$L$17))+G123*IF(J123="TT",characterization!$B$15,IF(J123="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L123" s="5">
+        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M123" s="7">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N123" s="7">
-        <f>IF(M123="TT",I123,IF(M123="FF",J123,IF(M123="SS",K123,"")))</f>
-        <v/>
-      </c>
-      <c r="O123" s="5">
-        <f>IFERROR(VLOOKUP(C123, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P123" s="7">
-        <f>O123 + N123</f>
-        <v/>
-      </c>
-      <c r="R123" s="7">
-        <f>IFERROR(L123 - P123 - VLOOKUP(C123, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C123, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S123" t="inlineStr">
+        <f>L123 + K123</f>
+        <v/>
+      </c>
+      <c r="O123" s="10">
+        <f>IFERROR(I123 - M123 - VLOOKUP(C123, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C123, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P123" t="inlineStr">
         <is>
           <t>round-robin output latch</t>
         </is>
@@ -11914,42 +10581,30 @@
         </is>
       </c>
       <c r="I124" s="7">
-        <f>F124*characterization!$B$17 + G124*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J124" s="7">
-        <f>F124*characterization!$G$17 + G124*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K124" s="7">
-        <f>F124*characterization!$L$17 + G124*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L124" s="7">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F124*IF(J124="TT",characterization!$B$17,IF(J124="FF",characterization!$G$17,characterization!$L$17))+G124*IF(J124="TT",characterization!$B$15,IF(J124="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L124" s="5">
+        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M124" s="7">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N124" s="7">
-        <f>IF(M124="TT",I124,IF(M124="FF",J124,IF(M124="SS",K124,"")))</f>
-        <v/>
-      </c>
-      <c r="O124" s="5">
-        <f>IFERROR(VLOOKUP(C124, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P124" s="7">
-        <f>O124 + N124</f>
-        <v/>
-      </c>
-      <c r="R124" s="7">
-        <f>IFERROR(L124 - P124 - VLOOKUP(C124, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C124, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S124" t="inlineStr">
+        <f>L124 + K124</f>
+        <v/>
+      </c>
+      <c r="O124" s="10">
+        <f>IFERROR(I124 - M124 - VLOOKUP(C124, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C124, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P124" t="inlineStr">
         <is>
           <t>channel context for AW launch + W stream</t>
         </is>
@@ -11989,42 +10644,30 @@
         </is>
       </c>
       <c r="I125" s="7">
-        <f>F125*characterization!$B$17 + G125*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J125" s="7">
-        <f>F125*characterization!$G$17 + G125*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K125" s="7">
-        <f>F125*characterization!$L$17 + G125*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L125" s="7">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F125*IF(J125="TT",characterization!$B$17,IF(J125="FF",characterization!$G$17,characterization!$L$17))+G125*IF(J125="TT",characterization!$B$15,IF(J125="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L125" s="5">
+        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M125" s="7">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N125" s="7">
-        <f>IF(M125="TT",I125,IF(M125="FF",J125,IF(M125="SS",K125,"")))</f>
-        <v/>
-      </c>
-      <c r="O125" s="5">
-        <f>IFERROR(VLOOKUP(C125, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P125" s="7">
-        <f>O125 + N125</f>
-        <v/>
-      </c>
-      <c r="R125" s="7">
-        <f>IFERROR(L125 - P125 - VLOOKUP(C125, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C125, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S125" t="inlineStr">
+        <f>L125 + K125</f>
+        <v/>
+      </c>
+      <c r="O125" s="10">
+        <f>IFERROR(I125 - M125 - VLOOKUP(C125, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C125, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P125" t="inlineStr">
         <is>
           <t>pipelined AWADDR</t>
         </is>
@@ -12064,42 +10707,30 @@
         </is>
       </c>
       <c r="I126" s="7">
-        <f>F126*characterization!$B$17 + G126*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J126" s="7">
-        <f>F126*characterization!$G$17 + G126*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K126" s="7">
-        <f>F126*characterization!$L$17 + G126*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L126" s="7">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F126*IF(J126="TT",characterization!$B$17,IF(J126="FF",characterization!$G$17,characterization!$L$17))+G126*IF(J126="TT",characterization!$B$15,IF(J126="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L126" s="5">
+        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M126" s="7">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N126" s="7">
-        <f>IF(M126="TT",I126,IF(M126="FF",J126,IF(M126="SS",K126,"")))</f>
-        <v/>
-      </c>
-      <c r="O126" s="5">
-        <f>IFERROR(VLOOKUP(C126, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P126" s="7">
-        <f>O126 + N126</f>
-        <v/>
-      </c>
-      <c r="R126" s="7">
-        <f>IFERROR(L126 - P126 - VLOOKUP(C126, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C126, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S126" t="inlineStr">
+        <f>L126 + K126</f>
+        <v/>
+      </c>
+      <c r="O126" s="10">
+        <f>IFERROR(I126 - M126 - VLOOKUP(C126, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C126, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P126" t="inlineStr">
         <is>
           <t>registered AW request</t>
         </is>
@@ -12139,42 +10770,30 @@
         </is>
       </c>
       <c r="I127" s="7">
-        <f>F127*characterization!$B$17 + G127*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J127" s="7">
-        <f>F127*characterization!$G$17 + G127*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K127" s="7">
-        <f>F127*characterization!$L$17 + G127*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L127" s="7">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F127*IF(J127="TT",characterization!$B$17,IF(J127="FF",characterization!$G$17,characterization!$L$17))+G127*IF(J127="TT",characterization!$B$15,IF(J127="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L127" s="5">
+        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M127" s="7">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N127" s="7">
-        <f>IF(M127="TT",I127,IF(M127="FF",J127,IF(M127="SS",K127,"")))</f>
-        <v/>
-      </c>
-      <c r="O127" s="5">
-        <f>IFERROR(VLOOKUP(C127, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P127" s="7">
-        <f>O127 + N127</f>
-        <v/>
-      </c>
-      <c r="R127" s="7">
-        <f>IFERROR(L127 - P127 - VLOOKUP(C127, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C127, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S127" t="inlineStr">
+        <f>L127 + K127</f>
+        <v/>
+      </c>
+      <c r="O127" s="10">
+        <f>IFERROR(I127 - M127 - VLOOKUP(C127, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C127, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P127" t="inlineStr">
         <is>
           <t>W-beat data pipeline reg</t>
         </is>
@@ -12214,42 +10833,30 @@
         </is>
       </c>
       <c r="I128" s="7">
-        <f>F128*characterization!$B$17 + G128*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J128" s="7">
-        <f>F128*characterization!$G$17 + G128*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K128" s="7">
-        <f>F128*characterization!$L$17 + G128*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L128" s="7">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F128*IF(J128="TT",characterization!$B$17,IF(J128="FF",characterization!$G$17,characterization!$L$17))+G128*IF(J128="TT",characterization!$B$15,IF(J128="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L128" s="5">
+        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M128" s="7">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N128" s="7">
-        <f>IF(M128="TT",I128,IF(M128="FF",J128,IF(M128="SS",K128,"")))</f>
-        <v/>
-      </c>
-      <c r="O128" s="5">
-        <f>IFERROR(VLOOKUP(C128, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P128" s="7">
-        <f>O128 + N128</f>
-        <v/>
-      </c>
-      <c r="R128" s="7">
-        <f>IFERROR(L128 - P128 - VLOOKUP(C128, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C128, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S128" t="inlineStr">
+        <f>L128 + K128</f>
+        <v/>
+      </c>
+      <c r="O128" s="10">
+        <f>IFERROR(I128 - M128 - VLOOKUP(C128, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C128, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P128" t="inlineStr">
         <is>
           <t>burst termination flag</t>
         </is>
@@ -12289,42 +10896,30 @@
         </is>
       </c>
       <c r="I129" s="7">
-        <f>F129*characterization!$B$17 + G129*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J129" s="7">
-        <f>F129*characterization!$G$17 + G129*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K129" s="7">
-        <f>F129*characterization!$L$17 + G129*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L129" s="7">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F129*IF(J129="TT",characterization!$B$17,IF(J129="FF",characterization!$G$17,characterization!$L$17))+G129*IF(J129="TT",characterization!$B$15,IF(J129="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L129" s="5">
+        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M129" s="7">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N129" s="7">
-        <f>IF(M129="TT",I129,IF(M129="FF",J129,IF(M129="SS",K129,"")))</f>
-        <v/>
-      </c>
-      <c r="O129" s="5">
-        <f>IFERROR(VLOOKUP(C129, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P129" s="7">
-        <f>O129 + N129</f>
-        <v/>
-      </c>
-      <c r="R129" s="7">
-        <f>IFERROR(L129 - P129 - VLOOKUP(C129, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C129, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S129" t="inlineStr">
+        <f>L129 + K129</f>
+        <v/>
+      </c>
+      <c r="O129" s="10">
+        <f>IFERROR(I129 - M129 - VLOOKUP(C129, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C129, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P129" t="inlineStr">
         <is>
           <t>tracks burst in-flight; gates drain request</t>
         </is>
@@ -12364,42 +10959,30 @@
         </is>
       </c>
       <c r="I130" s="7">
-        <f>F130*characterization!$B$17 + G130*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J130" s="7">
-        <f>F130*characterization!$G$17 + G130*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K130" s="7">
-        <f>F130*characterization!$L$17 + G130*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L130" s="7">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F130*IF(J130="TT",characterization!$B$17,IF(J130="FF",characterization!$G$17,characterization!$L$17))+G130*IF(J130="TT",characterization!$B$15,IF(J130="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L130" s="5">
+        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M130" s="7">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N130" s="7">
-        <f>IF(M130="TT",I130,IF(M130="FF",J130,IF(M130="SS",K130,"")))</f>
-        <v/>
-      </c>
-      <c r="O130" s="5">
-        <f>IFERROR(VLOOKUP(C130, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P130" s="7">
-        <f>O130 + N130</f>
-        <v/>
-      </c>
-      <c r="R130" s="7">
-        <f>IFERROR(L130 - P130 - VLOOKUP(C130, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C130, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S130" t="inlineStr">
+        <f>L130 + K130</f>
+        <v/>
+      </c>
+      <c r="O130" s="10">
+        <f>IFERROR(I130 - M130 - VLOOKUP(C130, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C130, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P130" t="inlineStr">
         <is>
           <t>BRESP-await counter</t>
         </is>
@@ -12439,42 +11022,30 @@
         </is>
       </c>
       <c r="I131" s="7">
-        <f>F131*characterization!$B$17 + G131*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J131" s="7">
-        <f>F131*characterization!$G$17 + G131*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K131" s="7">
-        <f>F131*characterization!$L$17 + G131*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L131" s="7">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F131*IF(J131="TT",characterization!$B$17,IF(J131="FF",characterization!$G$17,characterization!$L$17))+G131*IF(J131="TT",characterization!$B$15,IF(J131="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L131" s="5">
+        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M131" s="7">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N131" s="7">
-        <f>IF(M131="TT",I131,IF(M131="FF",J131,IF(M131="SS",K131,"")))</f>
-        <v/>
-      </c>
-      <c r="O131" s="5">
-        <f>IFERROR(VLOOKUP(C131, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P131" s="7">
-        <f>O131 + N131</f>
-        <v/>
-      </c>
-      <c r="R131" s="7">
-        <f>IFERROR(L131 - P131 - VLOOKUP(C131, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C131, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S131" t="inlineStr">
+        <f>L131 + K131</f>
+        <v/>
+      </c>
+      <c r="O131" s="10">
+        <f>IFERROR(I131 - M131 - VLOOKUP(C131, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C131, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P131" t="inlineStr">
         <is>
           <t>to sram_controller_unit</t>
         </is>
@@ -12514,42 +11085,30 @@
         </is>
       </c>
       <c r="I132" s="7">
-        <f>F132*characterization!$B$17 + G132*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J132" s="7">
-        <f>F132*characterization!$G$17 + G132*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K132" s="7">
-        <f>F132*characterization!$L$17 + G132*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L132" s="7">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F132*IF(J132="TT",characterization!$B$17,IF(J132="FF",characterization!$G$17,characterization!$L$17))+G132*IF(J132="TT",characterization!$B$15,IF(J132="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L132" s="5">
+        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M132" s="7">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N132" s="7">
-        <f>IF(M132="TT",I132,IF(M132="FF",J132,IF(M132="SS",K132,"")))</f>
-        <v/>
-      </c>
-      <c r="O132" s="5">
-        <f>IFERROR(VLOOKUP(C132, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P132" s="7">
-        <f>O132 + N132</f>
-        <v/>
-      </c>
-      <c r="R132" s="7">
-        <f>IFERROR(L132 - P132 - VLOOKUP(C132, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C132, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S132" t="inlineStr">
+        <f>L132 + K132</f>
+        <v/>
+      </c>
+      <c r="O132" s="10">
+        <f>IFERROR(I132 - M132 - VLOOKUP(C132, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C132, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P132" t="inlineStr">
         <is>
           <t>to sram_controller_unit[N]</t>
         </is>
@@ -12593,42 +11152,30 @@
         </is>
       </c>
       <c r="I133" s="7">
-        <f>F133*characterization!$B$17 + G133*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J133" s="7">
-        <f>F133*characterization!$G$17 + G133*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K133" s="7">
-        <f>F133*characterization!$L$17 + G133*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L133" s="7">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F133*IF(J133="TT",characterization!$B$17,IF(J133="FF",characterization!$G$17,characterization!$L$17))+G133*IF(J133="TT",characterization!$B$15,IF(J133="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L133" s="5">
+        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M133" s="7">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N133" s="7">
-        <f>IF(M133="TT",I133,IF(M133="FF",J133,IF(M133="SS",K133,"")))</f>
-        <v/>
-      </c>
-      <c r="O133" s="5">
-        <f>IFERROR(VLOOKUP(C133, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P133" s="7">
-        <f>O133 + N133</f>
-        <v/>
-      </c>
-      <c r="R133" s="7">
-        <f>IFERROR(L133 - P133 - VLOOKUP(C133, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C133, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S133" t="inlineStr">
+        <f>L133 + K133</f>
+        <v/>
+      </c>
+      <c r="O133" s="10">
+        <f>IFERROR(I133 - M133 - VLOOKUP(C133, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C133, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P133" t="inlineStr">
         <is>
           <t>to AXI4 master write system bus</t>
         </is>
@@ -12672,42 +11219,30 @@
         </is>
       </c>
       <c r="I134" s="7">
-        <f>F134*characterization!$B$17 + G134*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J134" s="7">
-        <f>F134*characterization!$G$17 + G134*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K134" s="7">
-        <f>F134*characterization!$L$17 + G134*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L134" s="7">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F134*IF(J134="TT",characterization!$B$17,IF(J134="FF",characterization!$G$17,characterization!$L$17))+G134*IF(J134="TT",characterization!$B$15,IF(J134="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L134" s="5">
+        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M134" s="7">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N134" s="7">
-        <f>IF(M134="TT",I134,IF(M134="FF",J134,IF(M134="SS",K134,"")))</f>
-        <v/>
-      </c>
-      <c r="O134" s="5">
-        <f>IFERROR(VLOOKUP(C134, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P134" s="7">
-        <f>O134 + N134</f>
-        <v/>
-      </c>
-      <c r="R134" s="7">
-        <f>IFERROR(L134 - P134 - VLOOKUP(C134, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C134, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S134" t="inlineStr">
+        <f>L134 + K134</f>
+        <v/>
+      </c>
+      <c r="O134" s="10">
+        <f>IFERROR(I134 - M134 - VLOOKUP(C134, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C134, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P134" t="inlineStr">
         <is>
           <t>to AXI4 master write system bus</t>
         </is>
@@ -12751,42 +11286,30 @@
         </is>
       </c>
       <c r="I135" s="7">
-        <f>F135*characterization!$B$17 + G135*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J135" s="7">
-        <f>F135*characterization!$G$17 + G135*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K135" s="7">
-        <f>F135*characterization!$L$17 + G135*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L135" s="7">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F135*IF(J135="TT",characterization!$B$17,IF(J135="FF",characterization!$G$17,characterization!$L$17))+G135*IF(J135="TT",characterization!$B$15,IF(J135="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L135" s="5">
+        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M135" s="7">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N135" s="7">
-        <f>IF(M135="TT",I135,IF(M135="FF",J135,IF(M135="SS",K135,"")))</f>
-        <v/>
-      </c>
-      <c r="O135" s="5">
-        <f>IFERROR(VLOOKUP(C135, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P135" s="7">
-        <f>O135 + N135</f>
-        <v/>
-      </c>
-      <c r="R135" s="7">
-        <f>IFERROR(L135 - P135 - VLOOKUP(C135, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C135, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S135" t="inlineStr">
+        <f>L135 + K135</f>
+        <v/>
+      </c>
+      <c r="O135" s="10">
+        <f>IFERROR(I135 - M135 - VLOOKUP(C135, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C135, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P135" t="inlineStr">
         <is>
           <t>from AXI4 master write system bus</t>
         </is>
@@ -12830,42 +11353,30 @@
         </is>
       </c>
       <c r="I136" s="7">
-        <f>F136*characterization!$B$17 + G136*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J136" s="7">
-        <f>F136*characterization!$G$17 + G136*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K136" s="7">
-        <f>F136*characterization!$L$17 + G136*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L136" s="7">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F136*IF(J136="TT",characterization!$B$17,IF(J136="FF",characterization!$G$17,characterization!$L$17))+G136*IF(J136="TT",characterization!$B$15,IF(J136="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L136" s="5">
+        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M136" s="7">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N136" s="7">
-        <f>IF(M136="TT",I136,IF(M136="FF",J136,IF(M136="SS",K136,"")))</f>
-        <v/>
-      </c>
-      <c r="O136" s="5">
-        <f>IFERROR(VLOOKUP(C136, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P136" s="7">
-        <f>O136 + N136</f>
-        <v/>
-      </c>
-      <c r="R136" s="7">
-        <f>IFERROR(L136 - P136 - VLOOKUP(C136, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C136, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S136" t="inlineStr">
+        <f>L136 + K136</f>
+        <v/>
+      </c>
+      <c r="O136" s="10">
+        <f>IFERROR(I136 - M136 - VLOOKUP(C136, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C136, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P136" t="inlineStr">
         <is>
           <t>B-phase awaiting response</t>
         </is>
@@ -12909,42 +11420,30 @@
         </is>
       </c>
       <c r="I137" s="7">
-        <f>F137*characterization!$B$17 + G137*characterization!$B$15</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE), "")</f>
         <v/>
       </c>
       <c r="J137" s="7">
-        <f>F137*characterization!$G$17 + G137*characterization!$G$15</f>
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 3, FALSE), "")</f>
         <v/>
       </c>
       <c r="K137" s="7">
-        <f>F137*characterization!$L$17 + G137*characterization!$L$15</f>
-        <v/>
-      </c>
-      <c r="L137" s="7">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE), "")</f>
+        <f>F137*IF(J137="TT",characterization!$B$17,IF(J137="FF",characterization!$G$17,characterization!$L$17))+G137*IF(J137="TT",characterization!$B$15,IF(J137="FF",characterization!$G$15,characterization!$L$15))</f>
+        <v/>
+      </c>
+      <c r="L137" s="5">
+        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
         <v/>
       </c>
       <c r="M137" s="7">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 3, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="N137" s="7">
-        <f>IF(M137="TT",I137,IF(M137="FF",J137,IF(M137="SS",K137,"")))</f>
-        <v/>
-      </c>
-      <c r="O137" s="5">
-        <f>IFERROR(VLOOKUP(C137, characterization!$A$29:$G$34, 4, FALSE)*0.3, "")</f>
-        <v/>
-      </c>
-      <c r="P137" s="7">
-        <f>O137 + N137</f>
-        <v/>
-      </c>
-      <c r="R137" s="7">
-        <f>IFERROR(L137 - P137 - VLOOKUP(C137, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C137, characterization!$A$29:$G$34, 7, FALSE), "")</f>
-        <v/>
-      </c>
-      <c r="S137" t="inlineStr">
+        <f>L137 + K137</f>
+        <v/>
+      </c>
+      <c r="O137" s="10">
+        <f>IFERROR(I137 - M137 - VLOOKUP(C137, characterization!$A$29:$G$34, 6, FALSE) - VLOOKUP(C137, characterization!$A$29:$G$34, 7, FALSE), "")</f>
+        <v/>
+      </c>
+      <c r="P137" t="inlineStr">
         <is>
           <t>W-phase awaiting last-beat</t>
         </is>
@@ -12994,25 +11493,25 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A76:S76"/>
-    <mergeCell ref="A33:S33"/>
-    <mergeCell ref="A51:S51"/>
-    <mergeCell ref="A142:S142"/>
-    <mergeCell ref="A45:S45"/>
-    <mergeCell ref="A23:S23"/>
-    <mergeCell ref="A103:S103"/>
-    <mergeCell ref="B2:S2"/>
-    <mergeCell ref="A13:S13"/>
-    <mergeCell ref="A141:S141"/>
-    <mergeCell ref="A88:S88"/>
-    <mergeCell ref="A118:S118"/>
-    <mergeCell ref="A143:S143"/>
-    <mergeCell ref="A144:S144"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A140:S140"/>
-    <mergeCell ref="A64:S64"/>
+    <mergeCell ref="A51:P51"/>
+    <mergeCell ref="A103:P103"/>
+    <mergeCell ref="A76:P76"/>
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="A141:P141"/>
+    <mergeCell ref="A45:P45"/>
+    <mergeCell ref="A23:P23"/>
+    <mergeCell ref="A88:P88"/>
+    <mergeCell ref="A118:P118"/>
+    <mergeCell ref="A144:P144"/>
+    <mergeCell ref="A143:P143"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A140:P140"/>
+    <mergeCell ref="A64:P64"/>
+    <mergeCell ref="A142:P142"/>
+    <mergeCell ref="A33:P33"/>
   </mergeCells>
-  <conditionalFormatting sqref="R3:R137">
+  <conditionalFormatting sqref="O3:O137">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
